--- a/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
@@ -264,7 +264,7 @@
     </row>
     <row r="3">
       <c r="A3" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B3">
         <is>
@@ -277,7 +277,7 @@
         </is>
       </c>
       <c t="n" r="D3">
-        <v>44.034377</v>
+        <v>49.377520</v>
       </c>
       <c r="E3" s="66">
         <v>58000000.00</v>
@@ -286,15 +286,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="66">
-        <v>2553993870.93</v>
+        <v>2863896168.21</v>
       </c>
       <c r="H3" s="66">
-        <v>44.06</v>
+        <v>49.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B4">
         <is>
@@ -307,7 +307,7 @@
         </is>
       </c>
       <c t="n" r="D4">
-        <v>34.196104</v>
+        <v>37.383347</v>
       </c>
       <c r="E4" s="66">
         <v>14400000.00</v>
@@ -316,15 +316,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="66">
-        <v>492423890.75</v>
+        <v>538320197.93</v>
       </c>
       <c r="H4" s="66">
-        <v>34.01</v>
+        <v>37.35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B5">
         <is>
@@ -337,7 +337,7 @@
         </is>
       </c>
       <c t="n" r="D5">
-        <v>36.008647</v>
+        <v>39.556011</v>
       </c>
       <c r="E5" s="66">
         <v>33700000.00</v>
@@ -346,15 +346,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="66">
-        <v>1213491398.10</v>
+        <v>1333037577.70</v>
       </c>
       <c r="H5" s="66">
-        <v>36.02</v>
+        <v>39.50</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B6">
         <is>
@@ -367,7 +367,7 @@
         </is>
       </c>
       <c t="n" r="D6">
-        <v>54.843201</v>
+        <v>55.134854</v>
       </c>
       <c r="E6" s="66">
         <v>2550000.00</v>
@@ -376,15 +376,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="66">
-        <v>139850162.19</v>
+        <v>140593878.75</v>
       </c>
       <c r="H6" s="66">
-        <v>54.92</v>
+        <v>55.22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B7">
         <is>
@@ -397,7 +397,7 @@
         </is>
       </c>
       <c t="n" r="D7">
-        <v>334.051577</v>
+        <v>354.221890</v>
       </c>
       <c r="E7" s="66">
         <v>150000.00</v>
@@ -406,15 +406,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="66">
-        <v>50107736.52</v>
+        <v>53133283.46</v>
       </c>
       <c r="H7" s="66">
-        <v>333.80</v>
+        <v>353.50</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B8">
         <is>
@@ -427,7 +427,7 @@
         </is>
       </c>
       <c t="n" r="D8">
-        <v>556.691335</v>
+        <v>575.727900</v>
       </c>
       <c r="E8" s="66">
         <v>47850000.00</v>
@@ -436,15 +436,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="66">
-        <v>26637680392.64</v>
+        <v>27548580038.29</v>
       </c>
       <c r="H8" s="66">
-        <v>570.50</v>
+        <v>584.25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B9">
         <is>
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c t="n" r="D9">
-        <v>625.310660</v>
+        <v>677.941684</v>
       </c>
       <c r="E9" s="66">
         <v>75550000.00</v>
@@ -466,15 +466,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="66">
-        <v>47242220337.20</v>
+        <v>51218494224.62</v>
       </c>
       <c r="H9" s="66">
-        <v>630.50</v>
+        <v>678.00</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B10">
         <is>
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c t="n" r="D10">
-        <v>4158.028198</v>
+        <v>4164.867779</v>
       </c>
       <c r="E10" s="66">
         <v>244000.00</v>
@@ -496,15 +496,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="66">
-        <v>1014558880.21</v>
+        <v>1016227738.04</v>
       </c>
       <c r="H10" s="66">
-        <v>4176.00</v>
+        <v>4180.00</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B11">
         <is>
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c t="n" r="D11">
-        <v>672.393939</v>
+        <v>687.060116</v>
       </c>
       <c r="E11" s="66">
         <v>113800000.00</v>
@@ -526,15 +526,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="66">
-        <v>76518430229.42</v>
+        <v>78187441198.54</v>
       </c>
       <c r="H11" s="66">
-        <v>718.00</v>
+        <v>734.00</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B12">
         <is>
@@ -547,24 +547,24 @@
         </is>
       </c>
       <c t="n" r="D12">
-        <v>559.369088</v>
+        <v>567.457021</v>
       </c>
       <c r="E12" s="66">
-        <v>33300000.00</v>
+        <v>33450000.00</v>
       </c>
       <c r="F12" s="65">
         <v>0</v>
       </c>
       <c r="G12" s="66">
-        <v>18626990626.83</v>
+        <v>18981437354.44</v>
       </c>
       <c r="H12" s="66">
-        <v>556.00</v>
+        <v>572.25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B13">
         <is>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c t="n" r="D13">
-        <v>24.023708</v>
+        <v>26.087874</v>
       </c>
       <c r="E13" s="66">
         <v>12300000.00</v>
@@ -586,15 +586,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="66">
-        <v>295491614.24</v>
+        <v>320880847.19</v>
       </c>
       <c r="H13" s="66">
-        <v>24.05</v>
+        <v>26.12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B14">
         <is>
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c t="n" r="D14">
-        <v>44.419065</v>
+        <v>44.644998</v>
       </c>
       <c r="E14" s="66">
         <v>1525000.00</v>
@@ -616,15 +616,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="66">
-        <v>67739074.54</v>
+        <v>68083622.38</v>
       </c>
       <c r="H14" s="66">
-        <v>44.48</v>
+        <v>44.70</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B15">
         <is>
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c t="n" r="D15">
-        <v>64.050896</v>
+        <v>67.981250</v>
       </c>
       <c r="E15" s="66">
         <v>1530000.00</v>
@@ -646,15 +646,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="66">
-        <v>97997871.54</v>
+        <v>104011312.93</v>
       </c>
       <c r="H15" s="66">
-        <v>64.10</v>
+        <v>67.96</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B16">
         <is>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c t="n" r="D16">
-        <v>77.229764</v>
+        <v>84.972088</v>
       </c>
       <c r="E16" s="66">
         <v>1155000.00</v>
@@ -676,15 +676,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="66">
-        <v>89200377.18</v>
+        <v>98142761.74</v>
       </c>
       <c r="H16" s="66">
-        <v>77.16</v>
+        <v>84.56</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B17">
         <is>
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c t="n" r="D17">
-        <v>48.379191</v>
+        <v>52.142224</v>
       </c>
       <c r="E17" s="66">
         <v>2985000.00</v>
@@ -706,15 +706,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="66">
-        <v>144411884.78</v>
+        <v>155644539.43</v>
       </c>
       <c r="H17" s="66">
-        <v>49.08</v>
+        <v>52.12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B18">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c t="n" r="D18">
-        <v>159.581646</v>
+        <v>167.135026</v>
       </c>
       <c r="E18" s="66">
         <v>600000.00</v>
@@ -736,15 +736,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="66">
-        <v>95748987.56</v>
+        <v>100281015.82</v>
       </c>
       <c r="H18" s="66">
-        <v>159.90</v>
+        <v>167.45</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B19">
         <is>
@@ -757,24 +757,24 @@
         </is>
       </c>
       <c t="n" r="D19">
-        <v>194.308139</v>
+        <v>213.500378</v>
       </c>
       <c r="E19" s="66">
-        <v>128280000.00</v>
+        <v>133400000.00</v>
       </c>
       <c r="F19" s="65">
         <v>0</v>
       </c>
       <c r="G19" s="66">
-        <v>24925848065.00</v>
+        <v>28480950418.25</v>
       </c>
       <c r="H19" s="66">
-        <v>194.20</v>
+        <v>213.35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B20">
         <is>
@@ -787,24 +787,24 @@
         </is>
       </c>
       <c t="n" r="D20">
-        <v>186.742486</v>
+        <v>209.742148</v>
       </c>
       <c r="E20" s="66">
-        <v>194280000.00</v>
+        <v>195280000.00</v>
       </c>
       <c r="F20" s="65">
         <v>0</v>
       </c>
       <c r="G20" s="66">
-        <v>36280330204.31</v>
+        <v>40958446577.28</v>
       </c>
       <c r="H20" s="66">
-        <v>186.85</v>
+        <v>210.00</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B21">
         <is>
@@ -817,24 +817,24 @@
         </is>
       </c>
       <c t="n" r="D21">
-        <v>179.811567</v>
+        <v>196.207203</v>
       </c>
       <c r="E21" s="66">
-        <v>400000.00</v>
+        <v>320000.00</v>
       </c>
       <c r="F21" s="65">
         <v>0</v>
       </c>
       <c r="G21" s="66">
-        <v>71924626.85</v>
+        <v>62786304.98</v>
       </c>
       <c r="H21" s="66">
-        <v>180.05</v>
+        <v>196.20</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B22">
         <is>
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c t="n" r="D22">
-        <v>115.292076</v>
+        <v>123.979163</v>
       </c>
       <c r="E22" s="66">
         <v>600000.00</v>
@@ -856,15 +856,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="66">
-        <v>69175245.32</v>
+        <v>74387497.94</v>
       </c>
       <c r="H22" s="66">
-        <v>115.40</v>
+        <v>124.00</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B23">
         <is>
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c t="n" r="D23">
-        <v>676.234351</v>
+        <v>699.318959</v>
       </c>
       <c r="E23" s="66">
         <v>152040000.00</v>
@@ -886,15 +886,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="66">
-        <v>102814670741.20</v>
+        <v>106324454479.70</v>
       </c>
       <c r="H23" s="66">
-        <v>721.00</v>
+        <v>735.00</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B24">
         <is>
@@ -907,24 +907,24 @@
         </is>
       </c>
       <c t="n" r="D24">
-        <v>153.441099</v>
+        <v>161.034512</v>
       </c>
       <c r="E24" s="66">
-        <v>9840000.00</v>
+        <v>9960000.00</v>
       </c>
       <c r="F24" s="65">
         <v>0</v>
       </c>
       <c r="G24" s="66">
-        <v>1509860413.79</v>
+        <v>1603903738.25</v>
       </c>
       <c r="H24" s="66">
-        <v>152.90</v>
+        <v>174.00</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B25">
         <is>
@@ -937,24 +937,24 @@
         </is>
       </c>
       <c t="n" r="D25">
-        <v>225.877717</v>
+        <v>240.212022</v>
       </c>
       <c r="E25" s="66">
-        <v>31640000.00</v>
+        <v>32000000.00</v>
       </c>
       <c r="F25" s="65">
         <v>0</v>
       </c>
       <c r="G25" s="66">
-        <v>7146770959.95</v>
+        <v>7686784694.62</v>
       </c>
       <c r="H25" s="66">
-        <v>226.50</v>
+        <v>253.90</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B26">
         <is>
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c t="n" r="D26">
-        <v>229.626991</v>
+        <v>250.774730</v>
       </c>
       <c r="E26" s="66">
         <v>7200000.00</v>
@@ -976,15 +976,15 @@
         <v>0</v>
       </c>
       <c r="G26" s="66">
-        <v>1653314334.17</v>
+        <v>1805578056.15</v>
       </c>
       <c r="H26" s="66">
-        <v>229.50</v>
+        <v>250.70</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B27">
         <is>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c t="n" r="D27">
-        <v>104.760395</v>
+        <v>112.607595</v>
       </c>
       <c r="E27" s="66">
         <v>360000.00</v>
@@ -1006,15 +1006,15 @@
         <v>0</v>
       </c>
       <c r="G27" s="66">
-        <v>37713742.16</v>
+        <v>40538734.10</v>
       </c>
       <c r="H27" s="66">
-        <v>104.65</v>
+        <v>112.50</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B28">
         <is>
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c t="n" r="D28">
-        <v>163.787923</v>
+        <v>178.661955</v>
       </c>
       <c r="E28" s="66">
         <v>400000.00</v>
@@ -1036,15 +1036,15 @@
         <v>0</v>
       </c>
       <c r="G28" s="66">
-        <v>65515169.12</v>
+        <v>71464782.04</v>
       </c>
       <c r="H28" s="66">
-        <v>163.85</v>
+        <v>178.30</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B29">
         <is>
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c t="n" r="D29">
-        <v>45.625992</v>
+        <v>50.108979</v>
       </c>
       <c r="E29" s="66">
         <v>1200000.00</v>
@@ -1066,15 +1066,15 @@
         <v>0</v>
       </c>
       <c r="G29" s="66">
-        <v>54751190.30</v>
+        <v>60130774.96</v>
       </c>
       <c r="H29" s="66">
-        <v>45.65</v>
+        <v>50.10</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B30">
         <is>
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c t="n" r="D30">
-        <v>1180.539725</v>
+        <v>1186.870862</v>
       </c>
       <c r="E30" s="66">
         <v>520000.00</v>
@@ -1096,15 +1096,15 @@
         <v>0</v>
       </c>
       <c r="G30" s="66">
-        <v>613880657.09</v>
+        <v>617172848.43</v>
       </c>
       <c r="H30" s="66">
-        <v>1181.50</v>
+        <v>1188.50</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B31">
         <is>
@@ -1117,7 +1117,7 @@
         </is>
       </c>
       <c t="n" r="D31">
-        <v>171.708805</v>
+        <v>185.439161</v>
       </c>
       <c r="E31" s="66">
         <v>680000.00</v>
@@ -1126,15 +1126,15 @@
         <v>0</v>
       </c>
       <c r="G31" s="66">
-        <v>116761987.22</v>
+        <v>126098629.61</v>
       </c>
       <c r="H31" s="66">
-        <v>171.90</v>
+        <v>185.45</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B32">
         <is>
@@ -1147,19 +1147,19 @@
         </is>
       </c>
       <c t="n" r="D32">
-        <v>1181.361183</v>
+        <v>1187.735721</v>
       </c>
       <c r="E32" s="66">
-        <v>2800000.00</v>
+        <v>2840000.00</v>
       </c>
       <c r="F32" s="65">
         <v>0</v>
       </c>
       <c r="G32" s="66">
-        <v>3307811312.87</v>
+        <v>3373169448.06</v>
       </c>
       <c r="H32" s="66">
-        <v>1183.00</v>
+        <v>1189.50</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
@@ -264,7 +264,7 @@
     </row>
     <row r="3">
       <c r="A3" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B3">
         <is>
@@ -277,7 +277,7 @@
         </is>
       </c>
       <c t="n" r="D3">
-        <v>49.377520</v>
+        <v>48.799645</v>
       </c>
       <c r="E3" s="66">
         <v>58000000.00</v>
@@ -286,15 +286,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="66">
-        <v>2863896168.21</v>
+        <v>2830379405.17</v>
       </c>
       <c r="H3" s="66">
-        <v>49.25</v>
+        <v>48.11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B4">
         <is>
@@ -307,7 +307,7 @@
         </is>
       </c>
       <c t="n" r="D4">
-        <v>37.383347</v>
+        <v>37.855601</v>
       </c>
       <c r="E4" s="66">
         <v>14400000.00</v>
@@ -316,15 +316,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="66">
-        <v>538320197.93</v>
+        <v>545120648.99</v>
       </c>
       <c r="H4" s="66">
-        <v>37.35</v>
+        <v>37.90</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B5">
         <is>
@@ -337,7 +337,7 @@
         </is>
       </c>
       <c t="n" r="D5">
-        <v>39.556011</v>
+        <v>39.542046</v>
       </c>
       <c r="E5" s="66">
         <v>33700000.00</v>
@@ -346,15 +346,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="66">
-        <v>1333037577.70</v>
+        <v>1332566955.04</v>
       </c>
       <c r="H5" s="66">
-        <v>39.50</v>
+        <v>39.53</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B6">
         <is>
@@ -367,7 +367,7 @@
         </is>
       </c>
       <c t="n" r="D6">
-        <v>55.134854</v>
+        <v>55.193143</v>
       </c>
       <c r="E6" s="66">
         <v>2550000.00</v>
@@ -376,15 +376,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="66">
-        <v>140593878.75</v>
+        <v>140742514.09</v>
       </c>
       <c r="H6" s="66">
-        <v>55.22</v>
+        <v>55.26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B7">
         <is>
@@ -397,7 +397,7 @@
         </is>
       </c>
       <c t="n" r="D7">
-        <v>354.221890</v>
+        <v>353.615106</v>
       </c>
       <c r="E7" s="66">
         <v>150000.00</v>
@@ -406,15 +406,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="66">
-        <v>53133283.46</v>
+        <v>53042265.88</v>
       </c>
       <c r="H7" s="66">
-        <v>353.50</v>
+        <v>352.60</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B8">
         <is>
@@ -427,7 +427,7 @@
         </is>
       </c>
       <c t="n" r="D8">
-        <v>575.727900</v>
+        <v>567.047104</v>
       </c>
       <c r="E8" s="66">
         <v>47850000.00</v>
@@ -436,15 +436,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="66">
-        <v>27548580038.29</v>
+        <v>27133203930.01</v>
       </c>
       <c r="H8" s="66">
-        <v>584.25</v>
+        <v>575.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B9">
         <is>
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c t="n" r="D9">
-        <v>677.941684</v>
+        <v>656.253340</v>
       </c>
       <c r="E9" s="66">
         <v>75550000.00</v>
@@ -466,15 +466,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="66">
-        <v>51218494224.62</v>
+        <v>49579939850.45</v>
       </c>
       <c r="H9" s="66">
-        <v>678.00</v>
+        <v>661.25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B10">
         <is>
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c t="n" r="D10">
-        <v>4164.867779</v>
+        <v>4166.721920</v>
       </c>
       <c r="E10" s="66">
         <v>244000.00</v>
@@ -496,15 +496,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="66">
-        <v>1016227738.04</v>
+        <v>1016680148.51</v>
       </c>
       <c r="H10" s="66">
-        <v>4180.00</v>
+        <v>4183.00</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B11">
         <is>
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c t="n" r="D11">
-        <v>687.060116</v>
+        <v>684.002191</v>
       </c>
       <c r="E11" s="66">
         <v>113800000.00</v>
@@ -526,15 +526,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="66">
-        <v>78187441198.54</v>
+        <v>77839449391.40</v>
       </c>
       <c r="H11" s="66">
-        <v>734.00</v>
+        <v>723.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B12">
         <is>
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c t="n" r="D12">
-        <v>567.457021</v>
+        <v>566.711705</v>
       </c>
       <c r="E12" s="66">
         <v>33450000.00</v>
@@ -556,15 +556,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="66">
-        <v>18981437354.44</v>
+        <v>18956506535.31</v>
       </c>
       <c r="H12" s="66">
-        <v>572.25</v>
+        <v>566.50</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B13">
         <is>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c t="n" r="D13">
-        <v>26.087874</v>
+        <v>25.935704</v>
       </c>
       <c r="E13" s="66">
         <v>12300000.00</v>
@@ -586,15 +586,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="66">
-        <v>320880847.19</v>
+        <v>319009162.72</v>
       </c>
       <c r="H13" s="66">
-        <v>26.12</v>
+        <v>25.90</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B14">
         <is>
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c t="n" r="D14">
-        <v>44.644998</v>
+        <v>44.690358</v>
       </c>
       <c r="E14" s="66">
         <v>1525000.00</v>
@@ -616,15 +616,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="66">
-        <v>68083622.38</v>
+        <v>68152795.53</v>
       </c>
       <c r="H14" s="66">
-        <v>44.70</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B15">
         <is>
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c t="n" r="D15">
-        <v>67.981250</v>
+        <v>68.771261</v>
       </c>
       <c r="E15" s="66">
         <v>1530000.00</v>
@@ -646,15 +646,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="66">
-        <v>104011312.93</v>
+        <v>105220028.63</v>
       </c>
       <c r="H15" s="66">
-        <v>67.96</v>
+        <v>68.54</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B16">
         <is>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c t="n" r="D16">
-        <v>84.972088</v>
+        <v>85.014747</v>
       </c>
       <c r="E16" s="66">
         <v>1155000.00</v>
@@ -676,15 +676,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="66">
-        <v>98142761.74</v>
+        <v>98192032.78</v>
       </c>
       <c r="H16" s="66">
-        <v>84.56</v>
+        <v>85.08</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B17">
         <is>
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c t="n" r="D17">
-        <v>52.142224</v>
+        <v>52.010518</v>
       </c>
       <c r="E17" s="66">
         <v>2985000.00</v>
@@ -706,15 +706,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="66">
-        <v>155644539.43</v>
+        <v>155251396.60</v>
       </c>
       <c r="H17" s="66">
-        <v>52.12</v>
+        <v>52.02</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B18">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c t="n" r="D18">
-        <v>167.135026</v>
+        <v>165.856880</v>
       </c>
       <c r="E18" s="66">
         <v>600000.00</v>
@@ -736,15 +736,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="66">
-        <v>100281015.82</v>
+        <v>99514128.21</v>
       </c>
       <c r="H18" s="66">
-        <v>167.45</v>
+        <v>164.55</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B19">
         <is>
@@ -757,24 +757,24 @@
         </is>
       </c>
       <c t="n" r="D19">
-        <v>213.500378</v>
+        <v>213.451420</v>
       </c>
       <c r="E19" s="66">
-        <v>133400000.00</v>
+        <v>134680000.00</v>
       </c>
       <c r="F19" s="65">
         <v>0</v>
       </c>
       <c r="G19" s="66">
-        <v>28480950418.25</v>
+        <v>28747637209.36</v>
       </c>
       <c r="H19" s="66">
-        <v>213.35</v>
+        <v>214.90</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B20">
         <is>
@@ -787,24 +787,24 @@
         </is>
       </c>
       <c t="n" r="D20">
-        <v>209.742148</v>
+        <v>207.274975</v>
       </c>
       <c r="E20" s="66">
-        <v>195280000.00</v>
+        <v>195800000.00</v>
       </c>
       <c r="F20" s="65">
         <v>0</v>
       </c>
       <c r="G20" s="66">
-        <v>40958446577.28</v>
+        <v>40584440193.39</v>
       </c>
       <c r="H20" s="66">
-        <v>210.00</v>
+        <v>207.55</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B21">
         <is>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c t="n" r="D21">
-        <v>196.207203</v>
+        <v>194.322074</v>
       </c>
       <c r="E21" s="66">
         <v>320000.00</v>
@@ -826,15 +826,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="66">
-        <v>62786304.98</v>
+        <v>62183063.77</v>
       </c>
       <c r="H21" s="66">
-        <v>196.20</v>
+        <v>194.15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B22">
         <is>
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c t="n" r="D22">
-        <v>123.979163</v>
+        <v>123.614815</v>
       </c>
       <c r="E22" s="66">
         <v>600000.00</v>
@@ -856,15 +856,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="66">
-        <v>74387497.94</v>
+        <v>74168888.97</v>
       </c>
       <c r="H22" s="66">
-        <v>124.00</v>
+        <v>123.60</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B23">
         <is>
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c t="n" r="D23">
-        <v>699.318959</v>
+        <v>690.612948</v>
       </c>
       <c r="E23" s="66">
         <v>152040000.00</v>
@@ -886,15 +886,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="66">
-        <v>106324454479.70</v>
+        <v>105000792562.10</v>
       </c>
       <c r="H23" s="66">
-        <v>735.00</v>
+        <v>727.75</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B24">
         <is>
@@ -907,24 +907,24 @@
         </is>
       </c>
       <c t="n" r="D24">
-        <v>161.034512</v>
+        <v>162.081692</v>
       </c>
       <c r="E24" s="66">
-        <v>9960000.00</v>
+        <v>10000000.00</v>
       </c>
       <c r="F24" s="65">
         <v>0</v>
       </c>
       <c r="G24" s="66">
-        <v>1603903738.25</v>
+        <v>1620816916.94</v>
       </c>
       <c r="H24" s="66">
-        <v>174.00</v>
+        <v>161.50</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B25">
         <is>
@@ -937,24 +937,24 @@
         </is>
       </c>
       <c t="n" r="D25">
-        <v>240.212022</v>
+        <v>242.999593</v>
       </c>
       <c r="E25" s="66">
-        <v>32000000.00</v>
+        <v>32040000.00</v>
       </c>
       <c r="F25" s="65">
         <v>0</v>
       </c>
       <c r="G25" s="66">
-        <v>7686784694.62</v>
+        <v>7785706948.73</v>
       </c>
       <c r="H25" s="66">
-        <v>253.90</v>
+        <v>248.00</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B26">
         <is>
@@ -967,24 +967,24 @@
         </is>
       </c>
       <c t="n" r="D26">
-        <v>250.774730</v>
+        <v>253.816919</v>
       </c>
       <c r="E26" s="66">
-        <v>7200000.00</v>
+        <v>6200000.00</v>
       </c>
       <c r="F26" s="65">
         <v>0</v>
       </c>
       <c r="G26" s="66">
-        <v>1805578056.15</v>
+        <v>1573664900.74</v>
       </c>
       <c r="H26" s="66">
-        <v>250.70</v>
+        <v>253.80</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B27">
         <is>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c t="n" r="D27">
-        <v>112.607595</v>
+        <v>112.974170</v>
       </c>
       <c r="E27" s="66">
         <v>360000.00</v>
@@ -1006,15 +1006,15 @@
         <v>0</v>
       </c>
       <c r="G27" s="66">
-        <v>40538734.10</v>
+        <v>40670701.31</v>
       </c>
       <c r="H27" s="66">
-        <v>112.50</v>
+        <v>112.95</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B28">
         <is>
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c t="n" r="D28">
-        <v>178.661955</v>
+        <v>176.977064</v>
       </c>
       <c r="E28" s="66">
         <v>400000.00</v>
@@ -1036,15 +1036,15 @@
         <v>0</v>
       </c>
       <c r="G28" s="66">
-        <v>71464782.04</v>
+        <v>70790825.52</v>
       </c>
       <c r="H28" s="66">
-        <v>178.30</v>
+        <v>177.00</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B29">
         <is>
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c t="n" r="D29">
-        <v>50.108979</v>
+        <v>49.961150</v>
       </c>
       <c r="E29" s="66">
         <v>1200000.00</v>
@@ -1066,15 +1066,15 @@
         <v>0</v>
       </c>
       <c r="G29" s="66">
-        <v>60130774.96</v>
+        <v>59953379.53</v>
       </c>
       <c r="H29" s="66">
-        <v>50.10</v>
+        <v>49.93</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B30">
         <is>
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c t="n" r="D30">
-        <v>1186.870862</v>
+        <v>1188.149569</v>
       </c>
       <c r="E30" s="66">
         <v>520000.00</v>
@@ -1096,15 +1096,15 @@
         <v>0</v>
       </c>
       <c r="G30" s="66">
-        <v>617172848.43</v>
+        <v>617837775.79</v>
       </c>
       <c r="H30" s="66">
-        <v>1188.50</v>
+        <v>1189.50</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B31">
         <is>
@@ -1117,7 +1117,7 @@
         </is>
       </c>
       <c t="n" r="D31">
-        <v>185.439161</v>
+        <v>184.706383</v>
       </c>
       <c r="E31" s="66">
         <v>680000.00</v>
@@ -1126,15 +1126,15 @@
         <v>0</v>
       </c>
       <c r="G31" s="66">
-        <v>126098629.61</v>
+        <v>125600340.55</v>
       </c>
       <c r="H31" s="66">
-        <v>185.45</v>
+        <v>184.70</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B32">
         <is>
@@ -1147,19 +1147,19 @@
         </is>
       </c>
       <c t="n" r="D32">
-        <v>1187.735721</v>
+        <v>1189.014859</v>
       </c>
       <c r="E32" s="66">
-        <v>2840000.00</v>
+        <v>3720000.00</v>
       </c>
       <c r="F32" s="65">
         <v>0</v>
       </c>
       <c r="G32" s="66">
-        <v>3373169448.06</v>
+        <v>4423135276.59</v>
       </c>
       <c r="H32" s="66">
-        <v>1189.50</v>
+        <v>1190.50</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
@@ -264,7 +264,7 @@
     </row>
     <row r="3">
       <c r="A3" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B3">
         <is>
@@ -277,7 +277,7 @@
         </is>
       </c>
       <c t="n" r="D3">
-        <v>48.799645</v>
+        <v>48.881066</v>
       </c>
       <c r="E3" s="66">
         <v>58000000.00</v>
@@ -286,15 +286,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="66">
-        <v>2830379405.17</v>
+        <v>2835101807.52</v>
       </c>
       <c r="H3" s="66">
-        <v>48.11</v>
+        <v>48.94</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B4">
         <is>
@@ -307,7 +307,7 @@
         </is>
       </c>
       <c t="n" r="D4">
-        <v>37.855601</v>
+        <v>38.116276</v>
       </c>
       <c r="E4" s="66">
         <v>14400000.00</v>
@@ -316,15 +316,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="66">
-        <v>545120648.99</v>
+        <v>548874374.63</v>
       </c>
       <c r="H4" s="66">
-        <v>37.90</v>
+        <v>38.17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B5">
         <is>
@@ -337,7 +337,7 @@
         </is>
       </c>
       <c t="n" r="D5">
-        <v>39.542046</v>
+        <v>39.873773</v>
       </c>
       <c r="E5" s="66">
         <v>33700000.00</v>
@@ -346,15 +346,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="66">
-        <v>1332566955.04</v>
+        <v>1343746138.23</v>
       </c>
       <c r="H5" s="66">
-        <v>39.53</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B6">
         <is>
@@ -367,7 +367,7 @@
         </is>
       </c>
       <c t="n" r="D6">
-        <v>55.193143</v>
+        <v>55.252121</v>
       </c>
       <c r="E6" s="66">
         <v>2550000.00</v>
@@ -376,15 +376,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="66">
-        <v>140742514.09</v>
+        <v>140892908.68</v>
       </c>
       <c r="H6" s="66">
-        <v>55.26</v>
+        <v>55.32</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B7">
         <is>
@@ -397,7 +397,7 @@
         </is>
       </c>
       <c t="n" r="D7">
-        <v>353.615106</v>
+        <v>355.174067</v>
       </c>
       <c r="E7" s="66">
         <v>150000.00</v>
@@ -406,15 +406,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="66">
-        <v>53042265.88</v>
+        <v>53276110.11</v>
       </c>
       <c r="H7" s="66">
-        <v>352.60</v>
+        <v>354.70</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B8">
         <is>
@@ -427,7 +427,7 @@
         </is>
       </c>
       <c t="n" r="D8">
-        <v>567.047104</v>
+        <v>577.428869</v>
       </c>
       <c r="E8" s="66">
         <v>47850000.00</v>
@@ -436,15 +436,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="66">
-        <v>27133203930.01</v>
+        <v>27629971368.57</v>
       </c>
       <c r="H8" s="66">
-        <v>575.75</v>
+        <v>584.00</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B9">
         <is>
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c t="n" r="D9">
-        <v>656.253340</v>
+        <v>697.698542</v>
       </c>
       <c r="E9" s="66">
         <v>75550000.00</v>
@@ -466,15 +466,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="66">
-        <v>49579939850.45</v>
+        <v>52711124878.65</v>
       </c>
       <c r="H9" s="66">
-        <v>661.25</v>
+        <v>700.00</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B10">
         <is>
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c t="n" r="D10">
-        <v>4166.721920</v>
+        <v>4165.920475</v>
       </c>
       <c r="E10" s="66">
         <v>244000.00</v>
@@ -496,15 +496,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="66">
-        <v>1016680148.51</v>
+        <v>1016484595.90</v>
       </c>
       <c r="H10" s="66">
-        <v>4183.00</v>
+        <v>4173.00</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B11">
         <is>
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c t="n" r="D11">
-        <v>684.002191</v>
+        <v>689.946224</v>
       </c>
       <c r="E11" s="66">
         <v>113800000.00</v>
@@ -526,15 +526,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="66">
-        <v>77839449391.40</v>
+        <v>78515880297.71</v>
       </c>
       <c r="H11" s="66">
-        <v>723.25</v>
+        <v>732.00</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B12">
         <is>
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c t="n" r="D12">
-        <v>566.711705</v>
+        <v>571.072379</v>
       </c>
       <c r="E12" s="66">
         <v>33450000.00</v>
@@ -556,15 +556,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="66">
-        <v>18956506535.31</v>
+        <v>19102371067.67</v>
       </c>
       <c r="H12" s="66">
-        <v>566.50</v>
+        <v>572.00</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B13">
         <is>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c t="n" r="D13">
-        <v>25.935704</v>
+        <v>26.321995</v>
       </c>
       <c r="E13" s="66">
         <v>12300000.00</v>
@@ -586,15 +586,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="66">
-        <v>319009162.72</v>
+        <v>323760533.04</v>
       </c>
       <c r="H13" s="66">
-        <v>25.90</v>
+        <v>26.28</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B14">
         <is>
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c t="n" r="D14">
-        <v>44.690358</v>
+        <v>44.735751</v>
       </c>
       <c r="E14" s="66">
         <v>1525000.00</v>
@@ -616,15 +616,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="66">
-        <v>68152795.53</v>
+        <v>68222020.36</v>
       </c>
       <c r="H14" s="66">
-        <v>44.73</v>
+        <v>44.78</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B15">
         <is>
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c t="n" r="D15">
-        <v>68.771261</v>
+        <v>69.091250</v>
       </c>
       <c r="E15" s="66">
         <v>1530000.00</v>
@@ -646,15 +646,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="66">
-        <v>105220028.63</v>
+        <v>105709612.51</v>
       </c>
       <c r="H15" s="66">
-        <v>68.54</v>
+        <v>69.18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B16">
         <is>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c t="n" r="D16">
-        <v>85.014747</v>
+        <v>85.659833</v>
       </c>
       <c r="E16" s="66">
         <v>1155000.00</v>
@@ -676,15 +676,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="66">
-        <v>98192032.78</v>
+        <v>98937107.22</v>
       </c>
       <c r="H16" s="66">
-        <v>85.08</v>
+        <v>86.04</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B17">
         <is>
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c t="n" r="D17">
-        <v>52.010518</v>
+        <v>52.642644</v>
       </c>
       <c r="E17" s="66">
         <v>2985000.00</v>
@@ -706,15 +706,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="66">
-        <v>155251396.60</v>
+        <v>157138290.94</v>
       </c>
       <c r="H17" s="66">
-        <v>52.02</v>
+        <v>52.70</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B18">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c t="n" r="D18">
-        <v>165.856880</v>
+        <v>168.492261</v>
       </c>
       <c r="E18" s="66">
         <v>600000.00</v>
@@ -736,15 +736,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="66">
-        <v>99514128.21</v>
+        <v>101095356.59</v>
       </c>
       <c r="H18" s="66">
-        <v>164.55</v>
+        <v>168.20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B19">
         <is>
@@ -757,24 +757,24 @@
         </is>
       </c>
       <c t="n" r="D19">
-        <v>213.451420</v>
+        <v>215.284119</v>
       </c>
       <c r="E19" s="66">
-        <v>134680000.00</v>
+        <v>141520000.00</v>
       </c>
       <c r="F19" s="65">
         <v>0</v>
       </c>
       <c r="G19" s="66">
-        <v>28747637209.36</v>
+        <v>30467008504.91</v>
       </c>
       <c r="H19" s="66">
-        <v>214.90</v>
+        <v>217.90</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B20">
         <is>
@@ -787,24 +787,24 @@
         </is>
       </c>
       <c t="n" r="D20">
-        <v>207.274975</v>
+        <v>207.572921</v>
       </c>
       <c r="E20" s="66">
-        <v>195800000.00</v>
+        <v>193680000.00</v>
       </c>
       <c r="F20" s="65">
         <v>0</v>
       </c>
       <c r="G20" s="66">
-        <v>40584440193.39</v>
+        <v>40202723266.65</v>
       </c>
       <c r="H20" s="66">
-        <v>207.55</v>
+        <v>209.30</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B21">
         <is>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c t="n" r="D21">
-        <v>194.322074</v>
+        <v>196.642265</v>
       </c>
       <c r="E21" s="66">
         <v>320000.00</v>
@@ -826,15 +826,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="66">
-        <v>62183063.77</v>
+        <v>62925524.81</v>
       </c>
       <c r="H21" s="66">
-        <v>194.15</v>
+        <v>196.50</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B22">
         <is>
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c t="n" r="D22">
-        <v>123.614815</v>
+        <v>124.768606</v>
       </c>
       <c r="E22" s="66">
         <v>600000.00</v>
@@ -856,15 +856,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="66">
-        <v>74168888.97</v>
+        <v>74861163.75</v>
       </c>
       <c r="H22" s="66">
-        <v>123.60</v>
+        <v>125.00</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B23">
         <is>
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c t="n" r="D23">
-        <v>690.612948</v>
+        <v>703.428930</v>
       </c>
       <c r="E23" s="66">
         <v>152040000.00</v>
@@ -886,15 +886,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="66">
-        <v>105000792562.10</v>
+        <v>106949334501.83</v>
       </c>
       <c r="H23" s="66">
-        <v>727.75</v>
+        <v>736.75</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B24">
         <is>
@@ -907,24 +907,24 @@
         </is>
       </c>
       <c t="n" r="D24">
-        <v>162.081692</v>
+        <v>163.235720</v>
       </c>
       <c r="E24" s="66">
-        <v>10000000.00</v>
+        <v>10200000.00</v>
       </c>
       <c r="F24" s="65">
         <v>0</v>
       </c>
       <c r="G24" s="66">
-        <v>1620816916.94</v>
+        <v>1665004345.25</v>
       </c>
       <c r="H24" s="66">
-        <v>161.50</v>
+        <v>163.90</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B25">
         <is>
@@ -937,24 +937,24 @@
         </is>
       </c>
       <c t="n" r="D25">
-        <v>242.999593</v>
+        <v>244.031052</v>
       </c>
       <c r="E25" s="66">
-        <v>32040000.00</v>
+        <v>32120000.00</v>
       </c>
       <c r="F25" s="65">
         <v>0</v>
       </c>
       <c r="G25" s="66">
-        <v>7785706948.73</v>
+        <v>7838277385.21</v>
       </c>
       <c r="H25" s="66">
-        <v>248.00</v>
+        <v>243.90</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B26">
         <is>
@@ -967,24 +967,24 @@
         </is>
       </c>
       <c t="n" r="D26">
-        <v>253.816919</v>
+        <v>255.731829</v>
       </c>
       <c r="E26" s="66">
-        <v>6200000.00</v>
+        <v>5200000.00</v>
       </c>
       <c r="F26" s="65">
         <v>0</v>
       </c>
       <c r="G26" s="66">
-        <v>1573664900.74</v>
+        <v>1329805511.24</v>
       </c>
       <c r="H26" s="66">
-        <v>253.80</v>
+        <v>255.90</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B27">
         <is>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c t="n" r="D27">
-        <v>112.974170</v>
+        <v>112.442089</v>
       </c>
       <c r="E27" s="66">
         <v>360000.00</v>
@@ -1006,15 +1006,15 @@
         <v>0</v>
       </c>
       <c r="G27" s="66">
-        <v>40670701.31</v>
+        <v>40479152.03</v>
       </c>
       <c r="H27" s="66">
-        <v>112.95</v>
+        <v>113.10</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B28">
         <is>
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c t="n" r="D28">
-        <v>176.977064</v>
+        <v>179.573003</v>
       </c>
       <c r="E28" s="66">
         <v>400000.00</v>
@@ -1036,15 +1036,15 @@
         <v>0</v>
       </c>
       <c r="G28" s="66">
-        <v>70790825.52</v>
+        <v>71829201.14</v>
       </c>
       <c r="H28" s="66">
-        <v>177.00</v>
+        <v>180.75</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B29">
         <is>
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c t="n" r="D29">
-        <v>49.961150</v>
+        <v>50.397301</v>
       </c>
       <c r="E29" s="66">
         <v>1200000.00</v>
@@ -1066,15 +1066,15 @@
         <v>0</v>
       </c>
       <c r="G29" s="66">
-        <v>59953379.53</v>
+        <v>60476760.81</v>
       </c>
       <c r="H29" s="66">
-        <v>49.93</v>
+        <v>50.38</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B30">
         <is>
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c t="n" r="D30">
-        <v>1188.149569</v>
+        <v>1189.434581</v>
       </c>
       <c r="E30" s="66">
         <v>520000.00</v>
@@ -1096,15 +1096,15 @@
         <v>0</v>
       </c>
       <c r="G30" s="66">
-        <v>617837775.79</v>
+        <v>618505981.87</v>
       </c>
       <c r="H30" s="66">
-        <v>1189.50</v>
+        <v>1191.00</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B31">
         <is>
@@ -1117,7 +1117,7 @@
         </is>
       </c>
       <c t="n" r="D31">
-        <v>184.706383</v>
+        <v>187.137072</v>
       </c>
       <c r="E31" s="66">
         <v>680000.00</v>
@@ -1126,15 +1126,15 @@
         <v>0</v>
       </c>
       <c r="G31" s="66">
-        <v>125600340.55</v>
+        <v>127253209.23</v>
       </c>
       <c r="H31" s="66">
-        <v>184.70</v>
+        <v>187.35</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B32">
         <is>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c t="n" r="D32">
-        <v>1189.014859</v>
+        <v>1190.298292</v>
       </c>
       <c r="E32" s="66">
         <v>3720000.00</v>
@@ -1156,10 +1156,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="66">
-        <v>4423135276.59</v>
+        <v>4427909648.07</v>
       </c>
       <c r="H32" s="66">
-        <v>1190.50</v>
+        <v>1192.00</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
@@ -264,7 +264,7 @@
     </row>
     <row r="3">
       <c r="A3" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B3">
         <is>
@@ -277,7 +277,7 @@
         </is>
       </c>
       <c t="n" r="D3">
-        <v>48.462095</v>
+        <v>51.173068</v>
       </c>
       <c r="E3" s="66">
         <v>58000000.00</v>
@@ -286,15 +286,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="66">
-        <v>2810801534.54</v>
+        <v>2968037919.85</v>
       </c>
       <c r="H3" s="66">
-        <v>48.47</v>
+        <v>51.10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B4">
         <is>
@@ -307,7 +307,7 @@
         </is>
       </c>
       <c t="n" r="D4">
-        <v>37.970936</v>
+        <v>38.485705</v>
       </c>
       <c r="E4" s="66">
         <v>14400000.00</v>
@@ -316,15 +316,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="66">
-        <v>546781477.93</v>
+        <v>554194147.76</v>
       </c>
       <c r="H4" s="66">
-        <v>37.85</v>
+        <v>38.42</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B5">
         <is>
@@ -337,7 +337,7 @@
         </is>
       </c>
       <c t="n" r="D5">
-        <v>39.639518</v>
+        <v>40.696289</v>
       </c>
       <c r="E5" s="66">
         <v>33700000.00</v>
@@ -346,15 +346,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="66">
-        <v>1335851742.63</v>
+        <v>1371464934.23</v>
       </c>
       <c r="H5" s="66">
-        <v>39.57</v>
+        <v>41.81</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B6">
         <is>
@@ -367,7 +367,7 @@
         </is>
       </c>
       <c t="n" r="D6">
-        <v>55.369314</v>
+        <v>55.544499</v>
       </c>
       <c r="E6" s="66">
         <v>2550000.00</v>
@@ -376,15 +376,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="66">
-        <v>141191751.20</v>
+        <v>141638472.50</v>
       </c>
       <c r="H6" s="66">
-        <v>55.56</v>
+        <v>55.62</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B7">
         <is>
@@ -397,7 +397,7 @@
         </is>
       </c>
       <c t="n" r="D7">
-        <v>359.290846</v>
+        <v>360.709223</v>
       </c>
       <c r="E7" s="66">
         <v>150000.00</v>
@@ -406,15 +406,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="66">
-        <v>53893626.84</v>
+        <v>54106383.47</v>
       </c>
       <c r="H7" s="66">
-        <v>359.90</v>
+        <v>362.00</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B8">
         <is>
@@ -427,7 +427,7 @@
         </is>
       </c>
       <c t="n" r="D8">
-        <v>580.139690</v>
+        <v>589.043659</v>
       </c>
       <c r="E8" s="66">
         <v>47850000.00</v>
@@ -436,15 +436,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="66">
-        <v>27759684173.66</v>
+        <v>28185739064.91</v>
       </c>
       <c r="H8" s="66">
-        <v>585.00</v>
+        <v>601.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B9">
         <is>
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c t="n" r="D9">
-        <v>701.700726</v>
+        <v>735.926770</v>
       </c>
       <c r="E9" s="66">
         <v>75050000.00</v>
@@ -466,15 +466,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="66">
-        <v>52662639500.85</v>
+        <v>55231304069.17</v>
       </c>
       <c r="H9" s="66">
-        <v>699.50</v>
+        <v>734.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B10">
         <is>
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c t="n" r="D10">
-        <v>4171.866281</v>
+        <v>4180.685871</v>
       </c>
       <c r="E10" s="66">
         <v>246000.00</v>
@@ -496,15 +496,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="66">
-        <v>1026279105.07</v>
+        <v>1028448724.22</v>
       </c>
       <c r="H10" s="66">
-        <v>4185.00</v>
+        <v>4189.00</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B11">
         <is>
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c t="n" r="D11">
-        <v>695.327140</v>
+        <v>697.570077</v>
       </c>
       <c r="E11" s="66">
         <v>113800000.00</v>
@@ -526,15 +526,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="66">
-        <v>79128228542.77</v>
+        <v>79383474751.12</v>
       </c>
       <c r="H11" s="66">
-        <v>727.00</v>
+        <v>744.50</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B12">
         <is>
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c t="n" r="D12">
-        <v>574.941640</v>
+        <v>572.255518</v>
       </c>
       <c r="E12" s="66">
         <v>33450000.00</v>
@@ -556,15 +556,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="66">
-        <v>19231797865.16</v>
+        <v>19141947069.97</v>
       </c>
       <c r="H12" s="66">
-        <v>575.50</v>
+        <v>585.00</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B13">
         <is>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c t="n" r="D13">
-        <v>26.248082</v>
+        <v>27.141517</v>
       </c>
       <c r="E13" s="66">
         <v>12300000.00</v>
@@ -586,15 +586,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="66">
-        <v>322851407.46</v>
+        <v>333840657.83</v>
       </c>
       <c r="H13" s="66">
-        <v>26.19</v>
+        <v>27.07</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B14">
         <is>
@@ -607,24 +607,24 @@
         </is>
       </c>
       <c t="n" r="D14">
-        <v>44.826054</v>
+        <v>44.962846</v>
       </c>
       <c r="E14" s="66">
-        <v>1525000.00</v>
+        <v>1625000.00</v>
       </c>
       <c r="F14" s="65">
         <v>0</v>
       </c>
       <c r="G14" s="66">
-        <v>68359731.89</v>
+        <v>73064624.60</v>
       </c>
       <c r="H14" s="66">
-        <v>44.98</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B15">
         <is>
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c t="n" r="D15">
-        <v>69.500824</v>
+        <v>70.409899</v>
       </c>
       <c r="E15" s="66">
         <v>1530000.00</v>
@@ -646,15 +646,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="66">
-        <v>106336261.08</v>
+        <v>107727145.31</v>
       </c>
       <c r="H15" s="66">
-        <v>69.12</v>
+        <v>70.60</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B16">
         <is>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c t="n" r="D16">
-        <v>85.195353</v>
+        <v>87.485857</v>
       </c>
       <c r="E16" s="66">
         <v>1155000.00</v>
@@ -676,15 +676,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="66">
-        <v>98400632.55</v>
+        <v>101046164.66</v>
       </c>
       <c r="H16" s="66">
-        <v>86.06</v>
+        <v>87.46</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B17">
         <is>
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c t="n" r="D17">
-        <v>52.401965</v>
+        <v>53.678255</v>
       </c>
       <c r="E17" s="66">
         <v>2985000.00</v>
@@ -706,15 +706,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="66">
-        <v>156419865.93</v>
+        <v>160229592.16</v>
       </c>
       <c r="H17" s="66">
-        <v>52.16</v>
+        <v>53.64</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B18">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c t="n" r="D18">
-        <v>166.505488</v>
+        <v>171.360244</v>
       </c>
       <c r="E18" s="66">
         <v>600000.00</v>
@@ -736,15 +736,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="66">
-        <v>99903292.76</v>
+        <v>102816146.60</v>
       </c>
       <c r="H18" s="66">
-        <v>166.55</v>
+        <v>176.10</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B19">
         <is>
@@ -757,24 +757,24 @@
         </is>
       </c>
       <c t="n" r="D19">
-        <v>214.156259</v>
+        <v>219.871055</v>
       </c>
       <c r="E19" s="66">
-        <v>136160000.00</v>
+        <v>136720000.00</v>
       </c>
       <c r="F19" s="65">
         <v>0</v>
       </c>
       <c r="G19" s="66">
-        <v>29159516218.00</v>
+        <v>30060770683.17</v>
       </c>
       <c r="H19" s="66">
-        <v>214.20</v>
+        <v>220.25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B20">
         <is>
@@ -787,24 +787,24 @@
         </is>
       </c>
       <c t="n" r="D20">
-        <v>205.746826</v>
+        <v>217.375671</v>
       </c>
       <c r="E20" s="66">
-        <v>196760000.00</v>
+        <v>195640000.00</v>
       </c>
       <c r="F20" s="65">
         <v>0</v>
       </c>
       <c r="G20" s="66">
-        <v>40482745496.05</v>
+        <v>42527376334.22</v>
       </c>
       <c r="H20" s="66">
-        <v>207.00</v>
+        <v>218.30</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B21">
         <is>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c t="n" r="D21">
-        <v>196.451195</v>
+        <v>203.189873</v>
       </c>
       <c r="E21" s="66">
         <v>320000.00</v>
@@ -826,15 +826,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="66">
-        <v>62864382.36</v>
+        <v>65020759.27</v>
       </c>
       <c r="H21" s="66">
-        <v>196.60</v>
+        <v>203.20</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B22">
         <is>
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c t="n" r="D22">
-        <v>125.898748</v>
+        <v>129.200658</v>
       </c>
       <c r="E22" s="66">
         <v>600000.00</v>
@@ -856,15 +856,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="66">
-        <v>75539248.90</v>
+        <v>77520394.53</v>
       </c>
       <c r="H22" s="66">
-        <v>125.50</v>
+        <v>129.20</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B23">
         <is>
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c t="n" r="D23">
-        <v>703.678116</v>
+        <v>714.976477</v>
       </c>
       <c r="E23" s="66">
         <v>152040000.00</v>
@@ -886,15 +886,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="66">
-        <v>106987220739.89</v>
+        <v>108705023494.49</v>
       </c>
       <c r="H23" s="66">
-        <v>736.75</v>
+        <v>755.00</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B24">
         <is>
@@ -907,24 +907,24 @@
         </is>
       </c>
       <c t="n" r="D24">
-        <v>164.242661</v>
+        <v>166.544428</v>
       </c>
       <c r="E24" s="66">
-        <v>10200000.00</v>
+        <v>10680000.00</v>
       </c>
       <c r="F24" s="65">
         <v>0</v>
       </c>
       <c r="G24" s="66">
-        <v>1675275138.78</v>
+        <v>1778694495.30</v>
       </c>
       <c r="H24" s="66">
-        <v>163.90</v>
+        <v>167.60</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B25">
         <is>
@@ -937,24 +937,24 @@
         </is>
       </c>
       <c t="n" r="D25">
-        <v>245.474470</v>
+        <v>248.645437</v>
       </c>
       <c r="E25" s="66">
-        <v>32080000.00</v>
+        <v>32400000.00</v>
       </c>
       <c r="F25" s="65">
         <v>0</v>
       </c>
       <c r="G25" s="66">
-        <v>7874820991.26</v>
+        <v>8056112170.14</v>
       </c>
       <c r="H25" s="66">
-        <v>245.00</v>
+        <v>250.00</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B26">
         <is>
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c t="n" r="D26">
-        <v>255.155181</v>
+        <v>258.679431</v>
       </c>
       <c r="E26" s="66">
         <v>5200000.00</v>
@@ -976,15 +976,15 @@
         <v>0</v>
       </c>
       <c r="G26" s="66">
-        <v>1326806939.23</v>
+        <v>1345133043.44</v>
       </c>
       <c r="H26" s="66">
-        <v>254.70</v>
+        <v>259.50</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B27">
         <is>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c t="n" r="D27">
-        <v>113.895445</v>
+        <v>116.441478</v>
       </c>
       <c r="E27" s="66">
         <v>360000.00</v>
@@ -1006,15 +1006,15 @@
         <v>0</v>
       </c>
       <c r="G27" s="66">
-        <v>41002360.26</v>
+        <v>41918932.00</v>
       </c>
       <c r="H27" s="66">
-        <v>113.35</v>
+        <v>116.45</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B28">
         <is>
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c t="n" r="D28">
-        <v>179.091687</v>
+        <v>184.484028</v>
       </c>
       <c r="E28" s="66">
         <v>400000.00</v>
@@ -1036,15 +1036,15 @@
         <v>0</v>
       </c>
       <c r="G28" s="66">
-        <v>71636674.62</v>
+        <v>73793611.00</v>
       </c>
       <c r="H28" s="66">
-        <v>178.60</v>
+        <v>184.50</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B29">
         <is>
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c t="n" r="D29">
-        <v>50.014745</v>
+        <v>51.360836</v>
       </c>
       <c r="E29" s="66">
         <v>1200000.00</v>
@@ -1066,15 +1066,15 @@
         <v>0</v>
       </c>
       <c r="G29" s="66">
-        <v>60017693.50</v>
+        <v>61633003.55</v>
       </c>
       <c r="H29" s="66">
-        <v>49.92</v>
+        <v>51.34</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B30">
         <is>
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c t="n" r="D30">
-        <v>1192.001963</v>
+        <v>1195.860316</v>
       </c>
       <c r="E30" s="66">
         <v>560000.00</v>
@@ -1096,15 +1096,15 @@
         <v>0</v>
       </c>
       <c r="G30" s="66">
-        <v>667521099.19</v>
+        <v>669681777.18</v>
       </c>
       <c r="H30" s="66">
-        <v>1196.00</v>
+        <v>1197.50</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B31">
         <is>
@@ -1117,7 +1117,7 @@
         </is>
       </c>
       <c t="n" r="D31">
-        <v>186.013001</v>
+        <v>190.811513</v>
       </c>
       <c r="E31" s="66">
         <v>680000.00</v>
@@ -1126,15 +1126,15 @@
         <v>0</v>
       </c>
       <c r="G31" s="66">
-        <v>126488840.81</v>
+        <v>129751828.89</v>
       </c>
       <c r="H31" s="66">
-        <v>185.15</v>
+        <v>190.80</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B32">
         <is>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c t="n" r="D32">
-        <v>1192.863734</v>
+        <v>1196.709276</v>
       </c>
       <c r="E32" s="66">
         <v>5400000.00</v>
@@ -1156,10 +1156,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="66">
-        <v>6441464163.38</v>
+        <v>6462230090.96</v>
       </c>
       <c r="H32" s="66">
-        <v>1197.00</v>
+        <v>1198.50</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
@@ -264,7 +264,7 @@
     </row>
     <row r="3">
       <c r="A3" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B3">
         <is>
@@ -277,7 +277,7 @@
         </is>
       </c>
       <c t="n" r="D3">
-        <v>51.173068</v>
+        <v>50.403978</v>
       </c>
       <c r="E3" s="66">
         <v>58000000.00</v>
@@ -286,15 +286,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="66">
-        <v>2968037919.85</v>
+        <v>2923430746.23</v>
       </c>
       <c r="H3" s="66">
-        <v>51.10</v>
+        <v>50.50</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B4">
         <is>
@@ -307,7 +307,7 @@
         </is>
       </c>
       <c t="n" r="D4">
-        <v>38.485705</v>
+        <v>38.237647</v>
       </c>
       <c r="E4" s="66">
         <v>14400000.00</v>
@@ -316,15 +316,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="66">
-        <v>554194147.76</v>
+        <v>550622114.87</v>
       </c>
       <c r="H4" s="66">
-        <v>38.42</v>
+        <v>38.28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B5">
         <is>
@@ -337,7 +337,7 @@
         </is>
       </c>
       <c t="n" r="D5">
-        <v>40.696289</v>
+        <v>40.337730</v>
       </c>
       <c r="E5" s="66">
         <v>33700000.00</v>
@@ -346,15 +346,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="66">
-        <v>1371464934.23</v>
+        <v>1359381506.96</v>
       </c>
       <c r="H5" s="66">
-        <v>41.81</v>
+        <v>40.36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B6">
         <is>
@@ -367,7 +367,7 @@
         </is>
       </c>
       <c t="n" r="D6">
-        <v>55.544499</v>
+        <v>55.603234</v>
       </c>
       <c r="E6" s="66">
         <v>2550000.00</v>
@@ -376,15 +376,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="66">
-        <v>141638472.50</v>
+        <v>141788246.91</v>
       </c>
       <c r="H6" s="66">
-        <v>55.62</v>
+        <v>55.68</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B7">
         <is>
@@ -397,7 +397,7 @@
         </is>
       </c>
       <c t="n" r="D7">
-        <v>360.709223</v>
+        <v>361.597340</v>
       </c>
       <c r="E7" s="66">
         <v>150000.00</v>
@@ -406,15 +406,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="66">
-        <v>54106383.47</v>
+        <v>54239600.93</v>
       </c>
       <c r="H7" s="66">
-        <v>362.00</v>
+        <v>361.70</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B8">
         <is>
@@ -427,7 +427,7 @@
         </is>
       </c>
       <c t="n" r="D8">
-        <v>589.043659</v>
+        <v>580.036005</v>
       </c>
       <c r="E8" s="66">
         <v>47850000.00</v>
@@ -436,15 +436,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="66">
-        <v>28185739064.91</v>
+        <v>27754722856.45</v>
       </c>
       <c r="H8" s="66">
-        <v>601.75</v>
+        <v>590.50</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B9">
         <is>
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c t="n" r="D9">
-        <v>735.926770</v>
+        <v>708.262276</v>
       </c>
       <c r="E9" s="66">
         <v>75050000.00</v>
@@ -466,15 +466,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="66">
-        <v>55231304069.17</v>
+        <v>53155083830.68</v>
       </c>
       <c r="H9" s="66">
-        <v>734.75</v>
+        <v>709.25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B10">
         <is>
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c t="n" r="D10">
-        <v>4180.685871</v>
+        <v>4180.816266</v>
       </c>
       <c r="E10" s="66">
         <v>246000.00</v>
@@ -496,15 +496,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="66">
-        <v>1028448724.22</v>
+        <v>1028480801.52</v>
       </c>
       <c r="H10" s="66">
-        <v>4189.00</v>
+        <v>4195.00</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B11">
         <is>
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c t="n" r="D11">
-        <v>697.570077</v>
+        <v>696.190567</v>
       </c>
       <c r="E11" s="66">
         <v>113800000.00</v>
@@ -526,15 +526,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="66">
-        <v>79383474751.12</v>
+        <v>79226486532.28</v>
       </c>
       <c r="H11" s="66">
-        <v>744.50</v>
+        <v>732.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B12">
         <is>
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c t="n" r="D12">
-        <v>572.255518</v>
+        <v>574.547151</v>
       </c>
       <c r="E12" s="66">
         <v>33450000.00</v>
@@ -556,15 +556,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="66">
-        <v>19141947069.97</v>
+        <v>19218602216.16</v>
       </c>
       <c r="H12" s="66">
-        <v>585.00</v>
+        <v>577.25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B13">
         <is>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c t="n" r="D13">
-        <v>27.141517</v>
+        <v>26.747525</v>
       </c>
       <c r="E13" s="66">
         <v>12300000.00</v>
@@ -586,15 +586,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="66">
-        <v>333840657.83</v>
+        <v>328994556.87</v>
       </c>
       <c r="H13" s="66">
-        <v>27.07</v>
+        <v>26.61</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B14">
         <is>
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c t="n" r="D14">
-        <v>44.962846</v>
+        <v>45.008526</v>
       </c>
       <c r="E14" s="66">
         <v>1625000.00</v>
@@ -616,15 +616,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="66">
-        <v>73064624.60</v>
+        <v>73138855.44</v>
       </c>
       <c r="H14" s="66">
-        <v>45.03</v>
+        <v>45.07</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B15">
         <is>
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c t="n" r="D15">
-        <v>70.409899</v>
+        <v>70.682757</v>
       </c>
       <c r="E15" s="66">
         <v>1530000.00</v>
@@ -646,15 +646,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="66">
-        <v>107727145.31</v>
+        <v>108144617.73</v>
       </c>
       <c r="H15" s="66">
-        <v>70.60</v>
+        <v>71.18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B16">
         <is>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c t="n" r="D16">
-        <v>87.485857</v>
+        <v>86.774072</v>
       </c>
       <c r="E16" s="66">
         <v>1155000.00</v>
@@ -676,15 +676,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="66">
-        <v>101046164.66</v>
+        <v>100224053.18</v>
       </c>
       <c r="H16" s="66">
-        <v>87.46</v>
+        <v>86.80</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B17">
         <is>
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c t="n" r="D17">
-        <v>53.678255</v>
+        <v>53.222899</v>
       </c>
       <c r="E17" s="66">
         <v>2985000.00</v>
@@ -706,15 +706,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="66">
-        <v>160229592.16</v>
+        <v>158870352.65</v>
       </c>
       <c r="H17" s="66">
-        <v>53.64</v>
+        <v>53.28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B18">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c t="n" r="D18">
-        <v>171.360244</v>
+        <v>169.352147</v>
       </c>
       <c r="E18" s="66">
         <v>600000.00</v>
@@ -736,15 +736,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="66">
-        <v>102816146.60</v>
+        <v>101611288.17</v>
       </c>
       <c r="H18" s="66">
-        <v>176.10</v>
+        <v>169.75</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B19">
         <is>
@@ -757,24 +757,24 @@
         </is>
       </c>
       <c t="n" r="D19">
-        <v>219.871055</v>
+        <v>217.897812</v>
       </c>
       <c r="E19" s="66">
-        <v>136720000.00</v>
+        <v>135520000.00</v>
       </c>
       <c r="F19" s="65">
         <v>0</v>
       </c>
       <c r="G19" s="66">
-        <v>30060770683.17</v>
+        <v>29529511527.00</v>
       </c>
       <c r="H19" s="66">
-        <v>220.25</v>
+        <v>217.85</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B20">
         <is>
@@ -787,24 +787,24 @@
         </is>
       </c>
       <c t="n" r="D20">
-        <v>217.375671</v>
+        <v>214.086917</v>
       </c>
       <c r="E20" s="66">
-        <v>195640000.00</v>
+        <v>196320000.00</v>
       </c>
       <c r="F20" s="65">
         <v>0</v>
       </c>
       <c r="G20" s="66">
-        <v>42527376334.22</v>
+        <v>42029543526.04</v>
       </c>
       <c r="H20" s="66">
-        <v>218.30</v>
+        <v>214.00</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B21">
         <is>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c t="n" r="D21">
-        <v>203.189873</v>
+        <v>201.489906</v>
       </c>
       <c r="E21" s="66">
         <v>320000.00</v>
@@ -826,15 +826,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="66">
-        <v>65020759.27</v>
+        <v>64476770.04</v>
       </c>
       <c r="H21" s="66">
-        <v>203.20</v>
+        <v>201.50</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B22">
         <is>
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c t="n" r="D22">
-        <v>129.200658</v>
+        <v>129.089701</v>
       </c>
       <c r="E22" s="66">
         <v>600000.00</v>
@@ -856,15 +856,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="66">
-        <v>77520394.53</v>
+        <v>77453820.66</v>
       </c>
       <c r="H22" s="66">
-        <v>129.20</v>
+        <v>129.05</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B23">
         <is>
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c t="n" r="D23">
-        <v>714.976477</v>
+        <v>705.413174</v>
       </c>
       <c r="E23" s="66">
         <v>152040000.00</v>
@@ -886,15 +886,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="66">
-        <v>108705023494.49</v>
+        <v>107251018917.04</v>
       </c>
       <c r="H23" s="66">
-        <v>755.00</v>
+        <v>745.75</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B24">
         <is>
@@ -907,24 +907,24 @@
         </is>
       </c>
       <c t="n" r="D24">
-        <v>166.544428</v>
+        <v>168.169033</v>
       </c>
       <c r="E24" s="66">
-        <v>10680000.00</v>
+        <v>10560000.00</v>
       </c>
       <c r="F24" s="65">
         <v>0</v>
       </c>
       <c r="G24" s="66">
-        <v>1778694495.30</v>
+        <v>1775864990.17</v>
       </c>
       <c r="H24" s="66">
-        <v>167.60</v>
+        <v>168.95</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B25">
         <is>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c t="n" r="D25">
-        <v>248.645437</v>
+        <v>248.882762</v>
       </c>
       <c r="E25" s="66">
         <v>32400000.00</v>
@@ -946,15 +946,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="66">
-        <v>8056112170.14</v>
+        <v>8063801501.98</v>
       </c>
       <c r="H25" s="66">
-        <v>250.00</v>
+        <v>249.90</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B26">
         <is>
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c t="n" r="D26">
-        <v>258.679431</v>
+        <v>256.993007</v>
       </c>
       <c r="E26" s="66">
         <v>5200000.00</v>
@@ -976,15 +976,15 @@
         <v>0</v>
       </c>
       <c r="G26" s="66">
-        <v>1345133043.44</v>
+        <v>1336363637.40</v>
       </c>
       <c r="H26" s="66">
-        <v>259.50</v>
+        <v>257.00</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B27">
         <is>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c t="n" r="D27">
-        <v>116.441478</v>
+        <v>116.122311</v>
       </c>
       <c r="E27" s="66">
         <v>360000.00</v>
@@ -1006,15 +1006,15 @@
         <v>0</v>
       </c>
       <c r="G27" s="66">
-        <v>41918932.00</v>
+        <v>41804031.99</v>
       </c>
       <c r="H27" s="66">
-        <v>116.45</v>
+        <v>117.20</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B28">
         <is>
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c t="n" r="D28">
-        <v>184.484028</v>
+        <v>182.952735</v>
       </c>
       <c r="E28" s="66">
         <v>400000.00</v>
@@ -1036,15 +1036,15 @@
         <v>0</v>
       </c>
       <c r="G28" s="66">
-        <v>73793611.00</v>
+        <v>73181093.96</v>
       </c>
       <c r="H28" s="66">
-        <v>184.50</v>
+        <v>183.90</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B29">
         <is>
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c t="n" r="D29">
-        <v>51.360836</v>
+        <v>50.760858</v>
       </c>
       <c r="E29" s="66">
         <v>1200000.00</v>
@@ -1066,15 +1066,15 @@
         <v>0</v>
       </c>
       <c r="G29" s="66">
-        <v>61633003.55</v>
+        <v>60913029.67</v>
       </c>
       <c r="H29" s="66">
-        <v>51.34</v>
+        <v>50.76</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B30">
         <is>
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c t="n" r="D30">
-        <v>1195.860316</v>
+        <v>1197.109252</v>
       </c>
       <c r="E30" s="66">
         <v>560000.00</v>
@@ -1096,15 +1096,15 @@
         <v>0</v>
       </c>
       <c r="G30" s="66">
-        <v>669681777.18</v>
+        <v>670381180.96</v>
       </c>
       <c r="H30" s="66">
-        <v>1197.50</v>
+        <v>1198.50</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B31">
         <is>
@@ -1117,7 +1117,7 @@
         </is>
       </c>
       <c t="n" r="D31">
-        <v>190.811513</v>
+        <v>189.127693</v>
       </c>
       <c r="E31" s="66">
         <v>680000.00</v>
@@ -1126,15 +1126,15 @@
         <v>0</v>
       </c>
       <c r="G31" s="66">
-        <v>129751828.89</v>
+        <v>128606831.36</v>
       </c>
       <c r="H31" s="66">
-        <v>190.80</v>
+        <v>189.10</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B32">
         <is>
@@ -1147,19 +1147,19 @@
         </is>
       </c>
       <c t="n" r="D32">
-        <v>1196.709276</v>
+        <v>1197.995042</v>
       </c>
       <c r="E32" s="66">
-        <v>5400000.00</v>
+        <v>5840000.00</v>
       </c>
       <c r="F32" s="65">
         <v>0</v>
       </c>
       <c r="G32" s="66">
-        <v>6462230090.96</v>
+        <v>6996291044.23</v>
       </c>
       <c r="H32" s="66">
-        <v>1198.50</v>
+        <v>1199.50</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
@@ -264,7 +264,7 @@
     </row>
     <row r="3">
       <c r="A3" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B3">
         <is>
@@ -277,7 +277,7 @@
         </is>
       </c>
       <c t="n" r="D3">
-        <v>50.403978</v>
+        <v>49.852357</v>
       </c>
       <c r="E3" s="66">
         <v>58000000.00</v>
@@ -286,15 +286,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="66">
-        <v>2923430746.23</v>
+        <v>2891436680.54</v>
       </c>
       <c r="H3" s="66">
-        <v>50.50</v>
+        <v>50.02</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B4">
         <is>
@@ -307,7 +307,7 @@
         </is>
       </c>
       <c t="n" r="D4">
-        <v>38.237647</v>
+        <v>37.787507</v>
       </c>
       <c r="E4" s="66">
         <v>14400000.00</v>
@@ -316,15 +316,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="66">
-        <v>550622114.87</v>
+        <v>544140102.37</v>
       </c>
       <c r="H4" s="66">
-        <v>38.28</v>
+        <v>38.02</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B5">
         <is>
@@ -337,7 +337,7 @@
         </is>
       </c>
       <c t="n" r="D5">
-        <v>40.337730</v>
+        <v>39.911774</v>
       </c>
       <c r="E5" s="66">
         <v>33700000.00</v>
@@ -346,15 +346,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="66">
-        <v>1359381506.96</v>
+        <v>1345026791.25</v>
       </c>
       <c r="H5" s="66">
-        <v>40.36</v>
+        <v>39.93</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B6">
         <is>
@@ -367,7 +367,7 @@
         </is>
       </c>
       <c t="n" r="D6">
-        <v>55.603234</v>
+        <v>55.662236</v>
       </c>
       <c r="E6" s="66">
         <v>2550000.00</v>
@@ -376,15 +376,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="66">
-        <v>141788246.91</v>
+        <v>141938702.74</v>
       </c>
       <c r="H6" s="66">
-        <v>55.68</v>
+        <v>55.80</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B7">
         <is>
@@ -397,7 +397,7 @@
         </is>
       </c>
       <c t="n" r="D7">
-        <v>361.597340</v>
+        <v>358.222475</v>
       </c>
       <c r="E7" s="66">
         <v>150000.00</v>
@@ -406,15 +406,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="66">
-        <v>54239600.93</v>
+        <v>53733371.28</v>
       </c>
       <c r="H7" s="66">
-        <v>361.70</v>
+        <v>359.10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B8">
         <is>
@@ -427,7 +427,7 @@
         </is>
       </c>
       <c t="n" r="D8">
-        <v>580.036005</v>
+        <v>573.231108</v>
       </c>
       <c r="E8" s="66">
         <v>47850000.00</v>
@@ -436,15 +436,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="66">
-        <v>27754722856.45</v>
+        <v>27429108516.01</v>
       </c>
       <c r="H8" s="66">
-        <v>590.50</v>
+        <v>584.00</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B9">
         <is>
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c t="n" r="D9">
-        <v>708.262276</v>
+        <v>685.919117</v>
       </c>
       <c r="E9" s="66">
         <v>75050000.00</v>
@@ -466,15 +466,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="66">
-        <v>53155083830.68</v>
+        <v>51478229747.74</v>
       </c>
       <c r="H9" s="66">
-        <v>709.25</v>
+        <v>687.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B10">
         <is>
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c t="n" r="D10">
-        <v>4180.816266</v>
+        <v>4181.133058</v>
       </c>
       <c r="E10" s="66">
         <v>246000.00</v>
@@ -496,15 +496,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="66">
-        <v>1028480801.52</v>
+        <v>1028558732.36</v>
       </c>
       <c r="H10" s="66">
-        <v>4195.00</v>
+        <v>4199.00</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B11">
         <is>
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c t="n" r="D11">
-        <v>696.190567</v>
+        <v>691.861384</v>
       </c>
       <c r="E11" s="66">
         <v>113800000.00</v>
@@ -526,15 +526,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="66">
-        <v>79226486532.28</v>
+        <v>78733825520.84</v>
       </c>
       <c r="H11" s="66">
-        <v>732.25</v>
+        <v>721.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B12">
         <is>
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c t="n" r="D12">
-        <v>574.547151</v>
+        <v>573.376297</v>
       </c>
       <c r="E12" s="66">
         <v>33450000.00</v>
@@ -556,15 +556,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="66">
-        <v>19218602216.16</v>
+        <v>19179437139.54</v>
       </c>
       <c r="H12" s="66">
-        <v>577.25</v>
+        <v>567.00</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B13">
         <is>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c t="n" r="D13">
-        <v>26.747525</v>
+        <v>26.582781</v>
       </c>
       <c r="E13" s="66">
         <v>12300000.00</v>
@@ -586,7 +586,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="66">
-        <v>328994556.87</v>
+        <v>326968205.09</v>
       </c>
       <c r="H13" s="66">
         <v>26.61</v>
@@ -594,7 +594,7 @@
     </row>
     <row r="14">
       <c r="A14" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B14">
         <is>
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c t="n" r="D14">
-        <v>45.008526</v>
+        <v>45.054394</v>
       </c>
       <c r="E14" s="66">
         <v>1625000.00</v>
@@ -616,15 +616,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="66">
-        <v>73138855.44</v>
+        <v>73213390.46</v>
       </c>
       <c r="H14" s="66">
-        <v>45.07</v>
+        <v>45.14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B15">
         <is>
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c t="n" r="D15">
-        <v>70.682757</v>
+        <v>70.419011</v>
       </c>
       <c r="E15" s="66">
         <v>1530000.00</v>
@@ -646,15 +646,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="66">
-        <v>108144617.73</v>
+        <v>107741087.48</v>
       </c>
       <c r="H15" s="66">
-        <v>71.18</v>
+        <v>70.44</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B16">
         <is>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c t="n" r="D16">
-        <v>86.774072</v>
+        <v>85.845965</v>
       </c>
       <c r="E16" s="66">
         <v>1155000.00</v>
@@ -676,15 +676,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="66">
-        <v>100224053.18</v>
+        <v>99152089.12</v>
       </c>
       <c r="H16" s="66">
-        <v>86.80</v>
+        <v>86.44</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B17">
         <is>
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c t="n" r="D17">
-        <v>53.222899</v>
+        <v>52.791396</v>
       </c>
       <c r="E17" s="66">
         <v>2985000.00</v>
@@ -706,7 +706,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="66">
-        <v>158870352.65</v>
+        <v>157582317.00</v>
       </c>
       <c r="H17" s="66">
         <v>53.28</v>
@@ -714,7 +714,7 @@
     </row>
     <row r="18">
       <c r="A18" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B18">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c t="n" r="D18">
-        <v>169.352147</v>
+        <v>168.883446</v>
       </c>
       <c r="E18" s="66">
         <v>600000.00</v>
@@ -736,15 +736,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="66">
-        <v>101611288.17</v>
+        <v>101330067.71</v>
       </c>
       <c r="H18" s="66">
-        <v>169.75</v>
+        <v>169.05</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B19">
         <is>
@@ -757,24 +757,24 @@
         </is>
       </c>
       <c t="n" r="D19">
-        <v>217.897812</v>
+        <v>215.533804</v>
       </c>
       <c r="E19" s="66">
-        <v>135520000.00</v>
+        <v>135760000.00</v>
       </c>
       <c r="F19" s="65">
         <v>0</v>
       </c>
       <c r="G19" s="66">
-        <v>29529511527.00</v>
+        <v>29260869179.96</v>
       </c>
       <c r="H19" s="66">
-        <v>217.85</v>
+        <v>216.00</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B20">
         <is>
@@ -787,24 +787,24 @@
         </is>
       </c>
       <c t="n" r="D20">
-        <v>214.086917</v>
+        <v>211.720157</v>
       </c>
       <c r="E20" s="66">
-        <v>196320000.00</v>
+        <v>194360000.00</v>
       </c>
       <c r="F20" s="65">
         <v>0</v>
       </c>
       <c r="G20" s="66">
-        <v>42029543526.04</v>
+        <v>41149929736.01</v>
       </c>
       <c r="H20" s="66">
-        <v>214.00</v>
+        <v>212.20</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B21">
         <is>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c t="n" r="D21">
-        <v>201.489906</v>
+        <v>200.012897</v>
       </c>
       <c r="E21" s="66">
         <v>320000.00</v>
@@ -826,15 +826,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="66">
-        <v>64476770.04</v>
+        <v>64004127.08</v>
       </c>
       <c r="H21" s="66">
-        <v>201.50</v>
+        <v>200.00</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B22">
         <is>
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c t="n" r="D22">
-        <v>129.089701</v>
+        <v>127.914896</v>
       </c>
       <c r="E22" s="66">
         <v>600000.00</v>
@@ -856,15 +856,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="66">
-        <v>77453820.66</v>
+        <v>76748937.69</v>
       </c>
       <c r="H22" s="66">
-        <v>129.05</v>
+        <v>127.90</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B23">
         <is>
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c t="n" r="D23">
-        <v>705.413174</v>
+        <v>696.366743</v>
       </c>
       <c r="E23" s="66">
         <v>152040000.00</v>
@@ -886,15 +886,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="66">
-        <v>107251018917.04</v>
+        <v>105875599677.18</v>
       </c>
       <c r="H23" s="66">
-        <v>745.75</v>
+        <v>733.50</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B24">
         <is>
@@ -907,24 +907,24 @@
         </is>
       </c>
       <c t="n" r="D24">
-        <v>168.169033</v>
+        <v>168.875089</v>
       </c>
       <c r="E24" s="66">
-        <v>10560000.00</v>
+        <v>10600000.00</v>
       </c>
       <c r="F24" s="65">
         <v>0</v>
       </c>
       <c r="G24" s="66">
-        <v>1775864990.17</v>
+        <v>1790075938.34</v>
       </c>
       <c r="H24" s="66">
-        <v>168.95</v>
+        <v>169.35</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B25">
         <is>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c t="n" r="D25">
-        <v>248.882762</v>
+        <v>247.491448</v>
       </c>
       <c r="E25" s="66">
         <v>32400000.00</v>
@@ -946,15 +946,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="66">
-        <v>8063801501.98</v>
+        <v>8018722902.21</v>
       </c>
       <c r="H25" s="66">
-        <v>249.90</v>
+        <v>250.00</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B26">
         <is>
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c t="n" r="D26">
-        <v>256.993007</v>
+        <v>254.004874</v>
       </c>
       <c r="E26" s="66">
         <v>5200000.00</v>
@@ -976,15 +976,15 @@
         <v>0</v>
       </c>
       <c r="G26" s="66">
-        <v>1336363637.40</v>
+        <v>1320825345.09</v>
       </c>
       <c r="H26" s="66">
-        <v>257.00</v>
+        <v>254.00</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B27">
         <is>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c t="n" r="D27">
-        <v>116.122311</v>
+        <v>115.392863</v>
       </c>
       <c r="E27" s="66">
         <v>360000.00</v>
@@ -1006,15 +1006,15 @@
         <v>0</v>
       </c>
       <c r="G27" s="66">
-        <v>41804031.99</v>
+        <v>41541430.65</v>
       </c>
       <c r="H27" s="66">
-        <v>117.20</v>
+        <v>115.40</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B28">
         <is>
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c t="n" r="D28">
-        <v>182.952735</v>
+        <v>181.918466</v>
       </c>
       <c r="E28" s="66">
         <v>400000.00</v>
@@ -1036,15 +1036,15 @@
         <v>0</v>
       </c>
       <c r="G28" s="66">
-        <v>73181093.96</v>
+        <v>72767386.32</v>
       </c>
       <c r="H28" s="66">
-        <v>183.90</v>
+        <v>181.95</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B29">
         <is>
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c t="n" r="D29">
-        <v>50.760858</v>
+        <v>50.223365</v>
       </c>
       <c r="E29" s="66">
         <v>1200000.00</v>
@@ -1066,15 +1066,15 @@
         <v>0</v>
       </c>
       <c r="G29" s="66">
-        <v>60913029.67</v>
+        <v>60268038.35</v>
       </c>
       <c r="H29" s="66">
-        <v>50.76</v>
+        <v>50.22</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B30">
         <is>
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c t="n" r="D30">
-        <v>1197.109252</v>
+        <v>1198.372881</v>
       </c>
       <c r="E30" s="66">
         <v>560000.00</v>
@@ -1096,15 +1096,15 @@
         <v>0</v>
       </c>
       <c r="G30" s="66">
-        <v>670381180.96</v>
+        <v>671088813.22</v>
       </c>
       <c r="H30" s="66">
-        <v>1198.50</v>
+        <v>1201.00</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B31">
         <is>
@@ -1117,7 +1117,7 @@
         </is>
       </c>
       <c t="n" r="D31">
-        <v>189.127693</v>
+        <v>187.556964</v>
       </c>
       <c r="E31" s="66">
         <v>680000.00</v>
@@ -1126,15 +1126,15 @@
         <v>0</v>
       </c>
       <c r="G31" s="66">
-        <v>128606831.36</v>
+        <v>127538735.41</v>
       </c>
       <c r="H31" s="66">
-        <v>189.10</v>
+        <v>187.55</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B32">
         <is>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c t="n" r="D32">
-        <v>1197.995042</v>
+        <v>1199.287056</v>
       </c>
       <c r="E32" s="66">
         <v>5840000.00</v>
@@ -1156,10 +1156,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="66">
-        <v>6996291044.23</v>
+        <v>7003836409.02</v>
       </c>
       <c r="H32" s="66">
-        <v>1199.50</v>
+        <v>1201.50</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
@@ -264,7 +264,7 @@
     </row>
     <row r="3">
       <c r="A3" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B3">
         <is>
@@ -277,7 +277,7 @@
         </is>
       </c>
       <c t="n" r="D3">
-        <v>49.852357</v>
+        <v>49.222014</v>
       </c>
       <c r="E3" s="66">
         <v>58000000.00</v>
@@ -286,15 +286,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="66">
-        <v>2891436680.54</v>
+        <v>2854876820.76</v>
       </c>
       <c r="H3" s="66">
-        <v>50.02</v>
+        <v>49.24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B4">
         <is>
@@ -307,7 +307,7 @@
         </is>
       </c>
       <c t="n" r="D4">
-        <v>37.787507</v>
+        <v>37.883110</v>
       </c>
       <c r="E4" s="66">
         <v>14400000.00</v>
@@ -316,15 +316,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="66">
-        <v>544140102.37</v>
+        <v>545516788.12</v>
       </c>
       <c r="H4" s="66">
-        <v>38.02</v>
+        <v>37.72</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B5">
         <is>
@@ -337,7 +337,7 @@
         </is>
       </c>
       <c t="n" r="D5">
-        <v>39.911774</v>
+        <v>39.784261</v>
       </c>
       <c r="E5" s="66">
         <v>33700000.00</v>
@@ -346,15 +346,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="66">
-        <v>1345026791.25</v>
+        <v>1340729607.71</v>
       </c>
       <c r="H5" s="66">
-        <v>39.93</v>
+        <v>39.63</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B6">
         <is>
@@ -367,7 +367,7 @@
         </is>
       </c>
       <c t="n" r="D6">
-        <v>55.662236</v>
+        <v>55.780103</v>
       </c>
       <c r="E6" s="66">
         <v>2550000.00</v>
@@ -376,15 +376,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="66">
-        <v>141938702.74</v>
+        <v>142239263.75</v>
       </c>
       <c r="H6" s="66">
-        <v>55.80</v>
+        <v>55.98</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B7">
         <is>
@@ -397,7 +397,7 @@
         </is>
       </c>
       <c t="n" r="D7">
-        <v>358.222475</v>
+        <v>356.022602</v>
       </c>
       <c r="E7" s="66">
         <v>150000.00</v>
@@ -406,15 +406,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="66">
-        <v>53733371.28</v>
+        <v>53403390.27</v>
       </c>
       <c r="H7" s="66">
-        <v>359.10</v>
+        <v>355.80</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B8">
         <is>
@@ -427,7 +427,7 @@
         </is>
       </c>
       <c t="n" r="D8">
-        <v>573.231108</v>
+        <v>573.339192</v>
       </c>
       <c r="E8" s="66">
         <v>47850000.00</v>
@@ -436,15 +436,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="66">
-        <v>27429108516.01</v>
+        <v>27434280356.49</v>
       </c>
       <c r="H8" s="66">
-        <v>584.00</v>
+        <v>579.50</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B9">
         <is>
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c t="n" r="D9">
-        <v>685.919117</v>
+        <v>694.632460</v>
       </c>
       <c r="E9" s="66">
         <v>75050000.00</v>
@@ -466,15 +466,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="66">
-        <v>51478229747.74</v>
+        <v>52132166116.75</v>
       </c>
       <c r="H9" s="66">
-        <v>687.75</v>
+        <v>696.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B10">
         <is>
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c t="n" r="D10">
-        <v>4181.133058</v>
+        <v>4186.007143</v>
       </c>
       <c r="E10" s="66">
         <v>246000.00</v>
@@ -496,15 +496,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="66">
-        <v>1028558732.36</v>
+        <v>1029757757.24</v>
       </c>
       <c r="H10" s="66">
-        <v>4199.00</v>
+        <v>4206.00</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B11">
         <is>
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c t="n" r="D11">
-        <v>691.861384</v>
+        <v>688.289379</v>
       </c>
       <c r="E11" s="66">
         <v>113800000.00</v>
@@ -526,15 +526,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="66">
-        <v>78733825520.84</v>
+        <v>78327331338.90</v>
       </c>
       <c r="H11" s="66">
-        <v>721.75</v>
+        <v>730.00</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B12">
         <is>
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c t="n" r="D12">
-        <v>573.376297</v>
+        <v>569.698906</v>
       </c>
       <c r="E12" s="66">
         <v>33450000.00</v>
@@ -556,15 +556,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="66">
-        <v>19179437139.54</v>
+        <v>19056428405.05</v>
       </c>
       <c r="H12" s="66">
-        <v>567.00</v>
+        <v>569.50</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B13">
         <is>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c t="n" r="D13">
-        <v>26.582781</v>
+        <v>26.430906</v>
       </c>
       <c r="E13" s="66">
         <v>12300000.00</v>
@@ -586,15 +586,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="66">
-        <v>326968205.09</v>
+        <v>325100144.08</v>
       </c>
       <c r="H13" s="66">
-        <v>26.61</v>
+        <v>26.55</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B14">
         <is>
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c t="n" r="D14">
-        <v>45.054394</v>
+        <v>45.146332</v>
       </c>
       <c r="E14" s="66">
         <v>1625000.00</v>
@@ -616,15 +616,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="66">
-        <v>73213390.46</v>
+        <v>73362790.22</v>
       </c>
       <c r="H14" s="66">
-        <v>45.14</v>
+        <v>45.30</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B15">
         <is>
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c t="n" r="D15">
-        <v>70.419011</v>
+        <v>70.650395</v>
       </c>
       <c r="E15" s="66">
         <v>1530000.00</v>
@@ -646,15 +646,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="66">
-        <v>107741087.48</v>
+        <v>108095103.74</v>
       </c>
       <c r="H15" s="66">
-        <v>70.44</v>
+        <v>70.56</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B16">
         <is>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c t="n" r="D16">
-        <v>85.845965</v>
+        <v>85.529828</v>
       </c>
       <c r="E16" s="66">
         <v>1155000.00</v>
@@ -676,15 +676,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="66">
-        <v>99152089.12</v>
+        <v>98786950.77</v>
       </c>
       <c r="H16" s="66">
-        <v>86.44</v>
+        <v>85.26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B17">
         <is>
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c t="n" r="D17">
-        <v>52.791396</v>
+        <v>52.722368</v>
       </c>
       <c r="E17" s="66">
         <v>2985000.00</v>
@@ -706,15 +706,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="66">
-        <v>157582317.00</v>
+        <v>157376267.14</v>
       </c>
       <c r="H17" s="66">
-        <v>53.28</v>
+        <v>52.90</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B18">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c t="n" r="D18">
-        <v>168.883446</v>
+        <v>169.352370</v>
       </c>
       <c r="E18" s="66">
         <v>600000.00</v>
@@ -736,15 +736,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="66">
-        <v>101330067.71</v>
+        <v>101611422.21</v>
       </c>
       <c r="H18" s="66">
-        <v>169.05</v>
+        <v>169.85</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B19">
         <is>
@@ -757,24 +757,24 @@
         </is>
       </c>
       <c t="n" r="D19">
-        <v>215.533804</v>
+        <v>214.790085</v>
       </c>
       <c r="E19" s="66">
-        <v>135760000.00</v>
+        <v>133800000.00</v>
       </c>
       <c r="F19" s="65">
         <v>0</v>
       </c>
       <c r="G19" s="66">
-        <v>29260869179.96</v>
+        <v>28738913372.16</v>
       </c>
       <c r="H19" s="66">
-        <v>216.00</v>
+        <v>214.70</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B20">
         <is>
@@ -787,24 +787,24 @@
         </is>
       </c>
       <c t="n" r="D20">
-        <v>211.720157</v>
+        <v>209.031693</v>
       </c>
       <c r="E20" s="66">
-        <v>194360000.00</v>
+        <v>194320000.00</v>
       </c>
       <c r="F20" s="65">
         <v>0</v>
       </c>
       <c r="G20" s="66">
-        <v>41149929736.01</v>
+        <v>40619038655.29</v>
       </c>
       <c r="H20" s="66">
-        <v>212.20</v>
+        <v>211.90</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B21">
         <is>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c t="n" r="D21">
-        <v>200.012897</v>
+        <v>198.930646</v>
       </c>
       <c r="E21" s="66">
         <v>320000.00</v>
@@ -826,15 +826,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="66">
-        <v>64004127.08</v>
+        <v>63657806.69</v>
       </c>
       <c r="H21" s="66">
-        <v>200.00</v>
+        <v>199.15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B22">
         <is>
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c t="n" r="D22">
-        <v>127.914896</v>
+        <v>126.713154</v>
       </c>
       <c r="E22" s="66">
         <v>600000.00</v>
@@ -856,15 +856,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="66">
-        <v>76748937.69</v>
+        <v>76027892.57</v>
       </c>
       <c r="H22" s="66">
-        <v>127.90</v>
+        <v>126.70</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B23">
         <is>
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c t="n" r="D23">
-        <v>696.366743</v>
+        <v>696.808049</v>
       </c>
       <c r="E23" s="66">
         <v>152040000.00</v>
@@ -886,15 +886,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="66">
-        <v>105875599677.18</v>
+        <v>105942695803.68</v>
       </c>
       <c r="H23" s="66">
-        <v>733.50</v>
+        <v>732.50</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B24">
         <is>
@@ -907,24 +907,24 @@
         </is>
       </c>
       <c t="n" r="D24">
-        <v>168.875089</v>
+        <v>169.178501</v>
       </c>
       <c r="E24" s="66">
-        <v>10600000.00</v>
+        <v>9800000.00</v>
       </c>
       <c r="F24" s="65">
         <v>0</v>
       </c>
       <c r="G24" s="66">
-        <v>1790075938.34</v>
+        <v>1657949307.34</v>
       </c>
       <c r="H24" s="66">
-        <v>169.35</v>
+        <v>169.50</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B25">
         <is>
@@ -937,24 +937,24 @@
         </is>
       </c>
       <c t="n" r="D25">
-        <v>247.491448</v>
+        <v>248.035439</v>
       </c>
       <c r="E25" s="66">
-        <v>32400000.00</v>
+        <v>32680000.00</v>
       </c>
       <c r="F25" s="65">
         <v>0</v>
       </c>
       <c r="G25" s="66">
-        <v>8018722902.21</v>
+        <v>8105798137.06</v>
       </c>
       <c r="H25" s="66">
-        <v>250.00</v>
+        <v>248.70</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B26">
         <is>
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c t="n" r="D26">
-        <v>254.004874</v>
+        <v>254.578304</v>
       </c>
       <c r="E26" s="66">
         <v>5200000.00</v>
@@ -976,15 +976,15 @@
         <v>0</v>
       </c>
       <c r="G26" s="66">
-        <v>1320825345.09</v>
+        <v>1323807180.12</v>
       </c>
       <c r="H26" s="66">
-        <v>254.00</v>
+        <v>253.00</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B27">
         <is>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c t="n" r="D27">
-        <v>115.392863</v>
+        <v>114.928712</v>
       </c>
       <c r="E27" s="66">
         <v>360000.00</v>
@@ -1006,15 +1006,15 @@
         <v>0</v>
       </c>
       <c r="G27" s="66">
-        <v>41541430.65</v>
+        <v>41374336.44</v>
       </c>
       <c r="H27" s="66">
-        <v>115.40</v>
+        <v>113.95</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B28">
         <is>
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c t="n" r="D28">
-        <v>181.918466</v>
+        <v>181.075208</v>
       </c>
       <c r="E28" s="66">
         <v>400000.00</v>
@@ -1036,15 +1036,15 @@
         <v>0</v>
       </c>
       <c r="G28" s="66">
-        <v>72767386.32</v>
+        <v>72430083.19</v>
       </c>
       <c r="H28" s="66">
-        <v>181.95</v>
+        <v>180.20</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B29">
         <is>
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c t="n" r="D29">
-        <v>50.223365</v>
+        <v>50.124665</v>
       </c>
       <c r="E29" s="66">
         <v>1200000.00</v>
@@ -1066,15 +1066,15 @@
         <v>0</v>
       </c>
       <c r="G29" s="66">
-        <v>60268038.35</v>
+        <v>60149598.30</v>
       </c>
       <c r="H29" s="66">
-        <v>50.22</v>
+        <v>50.10</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B30">
         <is>
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c t="n" r="D30">
-        <v>1198.372881</v>
+        <v>1200.893316</v>
       </c>
       <c r="E30" s="66">
         <v>560000.00</v>
@@ -1096,15 +1096,15 @@
         <v>0</v>
       </c>
       <c r="G30" s="66">
-        <v>671088813.22</v>
+        <v>672500256.78</v>
       </c>
       <c r="H30" s="66">
-        <v>1201.00</v>
+        <v>1205.00</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B31">
         <is>
@@ -1117,7 +1117,7 @@
         </is>
       </c>
       <c t="n" r="D31">
-        <v>187.556964</v>
+        <v>187.223450</v>
       </c>
       <c r="E31" s="66">
         <v>680000.00</v>
@@ -1126,15 +1126,15 @@
         <v>0</v>
       </c>
       <c r="G31" s="66">
-        <v>127538735.41</v>
+        <v>127311946.13</v>
       </c>
       <c r="H31" s="66">
-        <v>187.55</v>
+        <v>187.20</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B32">
         <is>
@@ -1147,19 +1147,19 @@
         </is>
       </c>
       <c t="n" r="D32">
-        <v>1199.287056</v>
+        <v>1201.873772</v>
       </c>
       <c r="E32" s="66">
-        <v>5840000.00</v>
+        <v>6720000.00</v>
       </c>
       <c r="F32" s="65">
         <v>0</v>
       </c>
       <c r="G32" s="66">
-        <v>7003836409.02</v>
+        <v>8076591749.87</v>
       </c>
       <c r="H32" s="66">
-        <v>1201.50</v>
+        <v>1206.00</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>27.04.2026 18:53:13</t>
+    <t>28.04.2026 18:41:52</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -235,10 +235,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="165" formatCode="###0.000000;-###0.000000;0"/>
+    <numFmt numFmtId="165" formatCode="###0.00000;-###0.00000;0"/>
     <numFmt numFmtId="166" formatCode="###0.00;-###0.00;0"/>
     <numFmt numFmtId="167" formatCode="###0;-###0;0"/>
-    <numFmt numFmtId="168" formatCode="###0.00000;-###0.00000;0"/>
+    <numFmt numFmtId="168" formatCode="###0.000000;-###0.000000;0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -743,10 +743,10 @@
         <v>13</v>
       </c>
       <c r="C6" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D6" s="7">
-        <v>48.604589</v>
+        <v>48.29092</v>
       </c>
       <c r="E6" s="8">
         <v>58000000</v>
@@ -755,10 +755,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="8">
-        <v>2819066140.09</v>
+        <v>2800873388.67</v>
       </c>
       <c r="H6" s="8">
-        <v>48.62</v>
+        <v>48.24</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -769,10 +769,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D7" s="7">
-        <v>37.989619</v>
+        <v>46140</v>
+      </c>
+      <c r="D7" s="10">
+        <v>38.612957</v>
       </c>
       <c r="E7" s="8">
         <v>14400000</v>
@@ -781,10 +781,10 @@
         <v>0</v>
       </c>
       <c r="G7" s="8">
-        <v>547050518.83</v>
+        <v>556026575.8</v>
       </c>
       <c r="H7" s="8">
-        <v>37.83</v>
+        <v>38.74</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -795,10 +795,10 @@
         <v>17</v>
       </c>
       <c r="C8" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D8" s="7">
-        <v>39.847939</v>
+        <v>46140</v>
+      </c>
+      <c r="D8" s="10">
+        <v>40.283156</v>
       </c>
       <c r="E8" s="8">
         <v>33700000</v>
@@ -807,10 +807,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="8">
-        <v>1342875544.33</v>
+        <v>1357542363.99</v>
       </c>
       <c r="H8" s="8">
-        <v>39.8</v>
+        <v>40.25</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -821,10 +821,10 @@
         <v>19</v>
       </c>
       <c r="C9" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D9" s="7">
-        <v>55.957673</v>
+        <v>46140</v>
+      </c>
+      <c r="D9" s="10">
+        <v>56.017317</v>
       </c>
       <c r="E9" s="8">
         <v>2550000</v>
@@ -833,10 +833,10 @@
         <v>0</v>
       </c>
       <c r="G9" s="8">
-        <v>142692065.54</v>
+        <v>142844157.54</v>
       </c>
       <c r="H9" s="8">
-        <v>56.04</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -847,10 +847,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D10" s="7">
-        <v>360.184134</v>
+        <v>46140</v>
+      </c>
+      <c r="D10" s="10">
+        <v>363.226129</v>
       </c>
       <c r="E10" s="8">
         <v>150000</v>
@@ -859,10 +859,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="8">
-        <v>54027620.16</v>
+        <v>54483919.29</v>
       </c>
       <c r="H10" s="8">
-        <v>361</v>
+        <v>364.4</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -873,10 +873,10 @@
         <v>23</v>
       </c>
       <c r="C11" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D11" s="7">
-        <v>572.300483</v>
+        <v>46140</v>
+      </c>
+      <c r="D11" s="10">
+        <v>566.282671</v>
       </c>
       <c r="E11" s="8">
         <v>47850000</v>
@@ -885,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="G11" s="8">
-        <v>27384578108.39</v>
+        <v>27096625783.73</v>
       </c>
       <c r="H11" s="8">
-        <v>574</v>
+        <v>567.5</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -899,10 +899,10 @@
         <v>25</v>
       </c>
       <c r="C12" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D12" s="7">
-        <v>676.105614</v>
+        <v>46140</v>
+      </c>
+      <c r="D12" s="10">
+        <v>668.716577</v>
       </c>
       <c r="E12" s="8">
         <v>75050000</v>
@@ -911,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="G12" s="8">
-        <v>50741726299.23</v>
+        <v>50187179098.58</v>
       </c>
       <c r="H12" s="8">
-        <v>689.75</v>
+        <v>678</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -925,22 +925,22 @@
         <v>27</v>
       </c>
       <c r="C13" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D13" s="7">
-        <v>4188.914444</v>
+        <v>46140</v>
+      </c>
+      <c r="D13" s="10">
+        <v>4192.389156</v>
       </c>
       <c r="E13" s="8">
-        <v>246000</v>
+        <v>248000</v>
       </c>
       <c r="F13" s="9">
         <v>0</v>
       </c>
       <c r="G13" s="8">
-        <v>1030472953.14</v>
+        <v>1039712510.73</v>
       </c>
       <c r="H13" s="8">
-        <v>4217</v>
+        <v>4218</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -951,10 +951,10 @@
         <v>29</v>
       </c>
       <c r="C14" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D14" s="7">
-        <v>683.060723</v>
+        <v>46140</v>
+      </c>
+      <c r="D14" s="10">
+        <v>683.561962</v>
       </c>
       <c r="E14" s="8">
         <v>113800000</v>
@@ -963,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="8">
-        <v>77732310307.24</v>
+        <v>77789351305.75</v>
       </c>
       <c r="H14" s="8">
-        <v>724</v>
+        <v>712.75</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -977,10 +977,10 @@
         <v>31</v>
       </c>
       <c r="C15" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D15" s="7">
-        <v>563.414542</v>
+        <v>46140</v>
+      </c>
+      <c r="D15" s="10">
+        <v>564.926184</v>
       </c>
       <c r="E15" s="8">
         <v>33450000</v>
@@ -989,10 +989,10 @@
         <v>0</v>
       </c>
       <c r="G15" s="8">
-        <v>18846216439.73</v>
+        <v>18896780865.21</v>
       </c>
       <c r="H15" s="8">
-        <v>572</v>
+        <v>564.5</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1003,10 +1003,10 @@
         <v>33</v>
       </c>
       <c r="C16" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D16" s="7">
-        <v>26.186858</v>
+        <v>46140</v>
+      </c>
+      <c r="D16" s="10">
+        <v>26.019944</v>
       </c>
       <c r="E16" s="8">
         <v>12300000</v>
@@ -1015,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="8">
-        <v>322098354.78</v>
+        <v>320045309</v>
       </c>
       <c r="H16" s="8">
-        <v>26.12</v>
+        <v>26.04</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1029,10 +1029,10 @@
         <v>35</v>
       </c>
       <c r="C17" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D17" s="7">
-        <v>45.284525</v>
+        <v>46140</v>
+      </c>
+      <c r="D17" s="10">
+        <v>45.330158</v>
       </c>
       <c r="E17" s="8">
         <v>1625000</v>
@@ -1041,10 +1041,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="8">
-        <v>73587353.48</v>
+        <v>73661506.67</v>
       </c>
       <c r="H17" s="8">
-        <v>45.34</v>
+        <v>45.37</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1055,10 +1055,10 @@
         <v>37</v>
       </c>
       <c r="C18" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D18" s="7">
-        <v>71.103337</v>
+        <v>46140</v>
+      </c>
+      <c r="D18" s="10">
+        <v>72.324613</v>
       </c>
       <c r="E18" s="8">
         <v>1140000</v>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="G18" s="8">
-        <v>81057804.71</v>
+        <v>82450058.86</v>
       </c>
       <c r="H18" s="8">
-        <v>70.62</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1081,10 +1081,10 @@
         <v>39</v>
       </c>
       <c r="C19" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D19" s="7">
-        <v>85.684885</v>
+        <v>86.62692</v>
       </c>
       <c r="E19" s="8">
         <v>1155000</v>
@@ -1093,10 +1093,10 @@
         <v>0</v>
       </c>
       <c r="G19" s="8">
-        <v>98966042.63</v>
+        <v>100054092.28</v>
       </c>
       <c r="H19" s="8">
-        <v>85.64</v>
+        <v>86.52</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1107,10 +1107,10 @@
         <v>41</v>
       </c>
       <c r="C20" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D20" s="7">
-        <v>52.868803</v>
+        <v>46140</v>
+      </c>
+      <c r="D20" s="10">
+        <v>53.062364</v>
       </c>
       <c r="E20" s="8">
         <v>2985000</v>
@@ -1119,10 +1119,10 @@
         <v>0</v>
       </c>
       <c r="G20" s="8">
-        <v>157813375.94</v>
+        <v>158391156.4</v>
       </c>
       <c r="H20" s="8">
-        <v>52.84</v>
+        <v>53.22</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1133,10 +1133,10 @@
         <v>43</v>
       </c>
       <c r="C21" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D21" s="7">
-        <v>171.349902</v>
+        <v>46140</v>
+      </c>
+      <c r="D21" s="10">
+        <v>173.064305</v>
       </c>
       <c r="E21" s="8">
         <v>600000</v>
@@ -1145,10 +1145,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="8">
-        <v>102809941.03</v>
+        <v>103838583.12</v>
       </c>
       <c r="H21" s="8">
-        <v>171.35</v>
+        <v>172.95</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1159,22 +1159,22 @@
         <v>45</v>
       </c>
       <c r="C22" s="6">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D22" s="7">
-        <v>215.169649</v>
+        <v>217.58252</v>
       </c>
       <c r="E22" s="8">
-        <v>133760000</v>
+        <v>133920000</v>
       </c>
       <c r="F22" s="9">
         <v>0</v>
       </c>
       <c r="G22" s="8">
-        <v>28781092190.55</v>
+        <v>29138651040.71</v>
       </c>
       <c r="H22" s="8">
-        <v>214.95</v>
+        <v>217.6</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1185,22 +1185,22 @@
         <v>47</v>
       </c>
       <c r="C23" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D23" s="10">
-        <v>206.39039</v>
+        <v>46140</v>
+      </c>
+      <c r="D23" s="7">
+        <v>205.01901</v>
       </c>
       <c r="E23" s="8">
-        <v>195400000</v>
+        <v>194680000</v>
       </c>
       <c r="F23" s="9">
         <v>0</v>
       </c>
       <c r="G23" s="8">
-        <v>40328682215.63</v>
+        <v>39913100904.05</v>
       </c>
       <c r="H23" s="8">
-        <v>207.5</v>
+        <v>208.75</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1211,10 +1211,10 @@
         <v>49</v>
       </c>
       <c r="C24" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D24" s="7">
-        <v>200.369912</v>
+        <v>46140</v>
+      </c>
+      <c r="D24" s="10">
+        <v>202.013825</v>
       </c>
       <c r="E24" s="8">
         <v>320000</v>
@@ -1223,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="G24" s="8">
-        <v>64118371.82</v>
+        <v>64644423.97</v>
       </c>
       <c r="H24" s="8">
-        <v>199.55</v>
+        <v>202.25</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1237,10 +1237,10 @@
         <v>51</v>
       </c>
       <c r="C25" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D25" s="7">
-        <v>126.541292</v>
+        <v>46140</v>
+      </c>
+      <c r="D25" s="10">
+        <v>126.749529</v>
       </c>
       <c r="E25" s="8">
         <v>600000</v>
@@ -1249,10 +1249,10 @@
         <v>0</v>
       </c>
       <c r="G25" s="8">
-        <v>75924775.09</v>
+        <v>76049717.61</v>
       </c>
       <c r="H25" s="8">
-        <v>125.35</v>
+        <v>127.6</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1263,10 +1263,10 @@
         <v>53</v>
       </c>
       <c r="C26" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D26" s="7">
-        <v>698.390577</v>
+        <v>46140</v>
+      </c>
+      <c r="D26" s="10">
+        <v>689.331976</v>
       </c>
       <c r="E26" s="8">
         <v>152040000</v>
@@ -1275,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="G26" s="8">
-        <v>106183303311.92</v>
+        <v>104806033667.41</v>
       </c>
       <c r="H26" s="8">
-        <v>727.5</v>
+        <v>719</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1289,22 +1289,22 @@
         <v>55</v>
       </c>
       <c r="C27" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D27" s="7">
-        <v>170.366192</v>
+        <v>46140</v>
+      </c>
+      <c r="D27" s="10">
+        <v>173.366407</v>
       </c>
       <c r="E27" s="8">
-        <v>9800000</v>
+        <v>9840000</v>
       </c>
       <c r="F27" s="9">
         <v>0</v>
       </c>
       <c r="G27" s="8">
-        <v>1669588682.18</v>
+        <v>1705925440.96</v>
       </c>
       <c r="H27" s="8">
-        <v>170.4</v>
+        <v>174.75</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1315,10 +1315,10 @@
         <v>57</v>
       </c>
       <c r="C28" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D28" s="7">
-        <v>249.515181</v>
+        <v>46140</v>
+      </c>
+      <c r="D28" s="10">
+        <v>253.800608</v>
       </c>
       <c r="E28" s="8">
         <v>32880000</v>
@@ -1327,10 +1327,10 @@
         <v>0</v>
       </c>
       <c r="G28" s="8">
-        <v>8204059141.48</v>
+        <v>8344963995.83</v>
       </c>
       <c r="H28" s="8">
-        <v>246.65</v>
+        <v>256</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1341,22 +1341,22 @@
         <v>59</v>
       </c>
       <c r="C29" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D29" s="7">
-        <v>255.547867</v>
+        <v>46140</v>
+      </c>
+      <c r="D29" s="10">
+        <v>259.752124</v>
       </c>
       <c r="E29" s="8">
-        <v>5200000</v>
+        <v>3200000</v>
       </c>
       <c r="F29" s="9">
         <v>0</v>
       </c>
       <c r="G29" s="8">
-        <v>1328848905.9</v>
+        <v>831206797.95</v>
       </c>
       <c r="H29" s="8">
-        <v>255.5</v>
+        <v>260.1</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1367,10 +1367,10 @@
         <v>61</v>
       </c>
       <c r="C30" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D30" s="7">
-        <v>114.848611</v>
+        <v>46140</v>
+      </c>
+      <c r="D30" s="10">
+        <v>117.316869</v>
       </c>
       <c r="E30" s="8">
         <v>360000</v>
@@ -1379,10 +1379,10 @@
         <v>0</v>
       </c>
       <c r="G30" s="8">
-        <v>41345499.84</v>
+        <v>42234072.89</v>
       </c>
       <c r="H30" s="8">
-        <v>115</v>
+        <v>116.75</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1393,10 +1393,10 @@
         <v>63</v>
       </c>
       <c r="C31" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D31" s="7">
-        <v>182.644318</v>
+        <v>46140</v>
+      </c>
+      <c r="D31" s="10">
+        <v>184.702813</v>
       </c>
       <c r="E31" s="8">
         <v>400000</v>
@@ -1405,10 +1405,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="8">
-        <v>73057727.36</v>
+        <v>73881125.24</v>
       </c>
       <c r="H31" s="8">
-        <v>182.25</v>
+        <v>185.25</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1419,10 +1419,10 @@
         <v>65</v>
       </c>
       <c r="C32" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D32" s="7">
-        <v>50.004728</v>
+        <v>46140</v>
+      </c>
+      <c r="D32" s="10">
+        <v>50.194666</v>
       </c>
       <c r="E32" s="8">
         <v>1200000</v>
@@ -1431,10 +1431,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="8">
-        <v>60005673.36</v>
+        <v>60233599.42</v>
       </c>
       <c r="H32" s="8">
-        <v>49.81</v>
+        <v>50.18</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1445,10 +1445,10 @@
         <v>67</v>
       </c>
       <c r="C33" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D33" s="7">
-        <v>1204.679622</v>
+        <v>46140</v>
+      </c>
+      <c r="D33" s="10">
+        <v>1205.945985</v>
       </c>
       <c r="E33" s="8">
         <v>560000</v>
@@ -1457,10 +1457,10 @@
         <v>0</v>
       </c>
       <c r="G33" s="8">
-        <v>674620588.4</v>
+        <v>675329751.32</v>
       </c>
       <c r="H33" s="8">
-        <v>1206.5</v>
+        <v>1207.5</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -1471,10 +1471,10 @@
         <v>69</v>
       </c>
       <c r="C34" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D34" s="7">
-        <v>187.711679</v>
+        <v>46140</v>
+      </c>
+      <c r="D34" s="10">
+        <v>188.299006</v>
       </c>
       <c r="E34" s="8">
         <v>680000</v>
@@ -1483,10 +1483,10 @@
         <v>0</v>
       </c>
       <c r="G34" s="8">
-        <v>127643941.49</v>
+        <v>128043324.4</v>
       </c>
       <c r="H34" s="8">
-        <v>187.8</v>
+        <v>192.85</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -1497,10 +1497,10 @@
         <v>71</v>
       </c>
       <c r="C35" s="6">
-        <v>46139</v>
-      </c>
-      <c r="D35" s="7">
-        <v>1205.762856</v>
+        <v>46140</v>
+      </c>
+      <c r="D35" s="10">
+        <v>1207.064467</v>
       </c>
       <c r="E35" s="8">
         <v>6720000</v>
@@ -1509,10 +1509,10 @@
         <v>0</v>
       </c>
       <c r="G35" s="8">
-        <v>8102726390.9</v>
+        <v>8111473217.79</v>
       </c>
       <c r="H35" s="8">
-        <v>1207</v>
+        <v>1208</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>28.04.2026 18:41:52</t>
+    <t>29.04.2026 18:50:47</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -235,10 +235,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="165" formatCode="###0.00000;-###0.00000;0"/>
+    <numFmt numFmtId="165" formatCode="###0.000000;-###0.000000;0"/>
     <numFmt numFmtId="166" formatCode="###0.00;-###0.00;0"/>
     <numFmt numFmtId="167" formatCode="###0;-###0;0"/>
-    <numFmt numFmtId="168" formatCode="###0.000000;-###0.000000;0"/>
+    <numFmt numFmtId="168" formatCode="###0.00000;-###0.00000;0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -743,10 +743,10 @@
         <v>13</v>
       </c>
       <c r="C6" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D6" s="7">
-        <v>48.29092</v>
+        <v>47.328405</v>
       </c>
       <c r="E6" s="8">
         <v>58000000</v>
@@ -755,10 +755,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="8">
-        <v>2800873388.67</v>
+        <v>2745047493.4</v>
       </c>
       <c r="H6" s="8">
-        <v>48.24</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -769,10 +769,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D7" s="10">
-        <v>38.612957</v>
+        <v>46141</v>
+      </c>
+      <c r="D7" s="7">
+        <v>37.991432</v>
       </c>
       <c r="E7" s="8">
         <v>14400000</v>
@@ -781,10 +781,10 @@
         <v>0</v>
       </c>
       <c r="G7" s="8">
-        <v>556026575.8</v>
+        <v>547076622.23</v>
       </c>
       <c r="H7" s="8">
-        <v>38.74</v>
+        <v>38.11</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -795,10 +795,10 @@
         <v>17</v>
       </c>
       <c r="C8" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D8" s="10">
-        <v>40.283156</v>
+        <v>46141</v>
+      </c>
+      <c r="D8" s="7">
+        <v>39.614064</v>
       </c>
       <c r="E8" s="8">
         <v>33700000</v>
@@ -807,10 +807,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="8">
-        <v>1357542363.99</v>
+        <v>1334993969.78</v>
       </c>
       <c r="H8" s="8">
-        <v>40.25</v>
+        <v>39.69</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -821,10 +821,10 @@
         <v>19</v>
       </c>
       <c r="C9" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D9" s="10">
-        <v>56.017317</v>
+        <v>46141</v>
+      </c>
+      <c r="D9" s="7">
+        <v>56.076353</v>
       </c>
       <c r="E9" s="8">
         <v>2550000</v>
@@ -833,10 +833,10 @@
         <v>0</v>
       </c>
       <c r="G9" s="8">
-        <v>142844157.54</v>
+        <v>142994701.42</v>
       </c>
       <c r="H9" s="8">
-        <v>56.1</v>
+        <v>56.16</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -847,10 +847,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D10" s="10">
-        <v>363.226129</v>
+        <v>46141</v>
+      </c>
+      <c r="D10" s="7">
+        <v>356.455176</v>
       </c>
       <c r="E10" s="8">
         <v>150000</v>
@@ -859,10 +859,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="8">
-        <v>54483919.29</v>
+        <v>53468276.33</v>
       </c>
       <c r="H10" s="8">
-        <v>364.4</v>
+        <v>356.6</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -873,10 +873,10 @@
         <v>23</v>
       </c>
       <c r="C11" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D11" s="10">
-        <v>566.282671</v>
+        <v>46141</v>
+      </c>
+      <c r="D11" s="7">
+        <v>555.393707</v>
       </c>
       <c r="E11" s="8">
         <v>47850000</v>
@@ -885,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="G11" s="8">
-        <v>27096625783.73</v>
+        <v>26575588877.54</v>
       </c>
       <c r="H11" s="8">
-        <v>567.5</v>
+        <v>555</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -899,22 +899,22 @@
         <v>25</v>
       </c>
       <c r="C12" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D12" s="10">
-        <v>668.716577</v>
+        <v>46141</v>
+      </c>
+      <c r="D12" s="7">
+        <v>650.541224</v>
       </c>
       <c r="E12" s="8">
-        <v>75050000</v>
+        <v>75300000</v>
       </c>
       <c r="F12" s="9">
         <v>0</v>
       </c>
       <c r="G12" s="8">
-        <v>50187179098.58</v>
+        <v>48985754171.34</v>
       </c>
       <c r="H12" s="8">
-        <v>678</v>
+        <v>655.25</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -925,10 +925,10 @@
         <v>27</v>
       </c>
       <c r="C13" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D13" s="10">
-        <v>4192.389156</v>
+        <v>46141</v>
+      </c>
+      <c r="D13" s="7">
+        <v>4199.416157</v>
       </c>
       <c r="E13" s="8">
         <v>248000</v>
@@ -937,10 +937,10 @@
         <v>0</v>
       </c>
       <c r="G13" s="8">
-        <v>1039712510.73</v>
+        <v>1041455206.94</v>
       </c>
       <c r="H13" s="8">
-        <v>4218</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -951,10 +951,10 @@
         <v>29</v>
       </c>
       <c r="C14" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D14" s="10">
-        <v>683.561962</v>
+        <v>46141</v>
+      </c>
+      <c r="D14" s="7">
+        <v>665.970164</v>
       </c>
       <c r="E14" s="8">
         <v>113800000</v>
@@ -963,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="8">
-        <v>77789351305.75</v>
+        <v>75787404712.09</v>
       </c>
       <c r="H14" s="8">
-        <v>712.75</v>
+        <v>698.5</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -977,10 +977,10 @@
         <v>31</v>
       </c>
       <c r="C15" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D15" s="10">
-        <v>564.926184</v>
+        <v>46141</v>
+      </c>
+      <c r="D15" s="7">
+        <v>549.429833</v>
       </c>
       <c r="E15" s="8">
         <v>33450000</v>
@@ -989,10 +989,10 @@
         <v>0</v>
       </c>
       <c r="G15" s="8">
-        <v>18896780865.21</v>
+        <v>18378427920.15</v>
       </c>
       <c r="H15" s="8">
-        <v>564.5</v>
+        <v>555.75</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1003,10 +1003,10 @@
         <v>33</v>
       </c>
       <c r="C16" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D16" s="10">
-        <v>26.019944</v>
+        <v>46141</v>
+      </c>
+      <c r="D16" s="7">
+        <v>25.628626</v>
       </c>
       <c r="E16" s="8">
         <v>12300000</v>
@@ -1015,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="8">
-        <v>320045309</v>
+        <v>315232099.88</v>
       </c>
       <c r="H16" s="8">
-        <v>26.04</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1029,10 +1029,10 @@
         <v>35</v>
       </c>
       <c r="C17" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D17" s="10">
-        <v>45.330158</v>
+        <v>46141</v>
+      </c>
+      <c r="D17" s="7">
+        <v>45.376424</v>
       </c>
       <c r="E17" s="8">
         <v>1625000</v>
@@ -1041,10 +1041,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="8">
-        <v>73661506.67</v>
+        <v>73736689.26</v>
       </c>
       <c r="H17" s="8">
-        <v>45.37</v>
+        <v>45.42</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1055,10 +1055,10 @@
         <v>37</v>
       </c>
       <c r="C18" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D18" s="10">
-        <v>72.324613</v>
+        <v>46141</v>
+      </c>
+      <c r="D18" s="7">
+        <v>71.006574</v>
       </c>
       <c r="E18" s="8">
         <v>1140000</v>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="G18" s="8">
-        <v>82450058.86</v>
+        <v>80947494.22</v>
       </c>
       <c r="H18" s="8">
-        <v>72.2</v>
+        <v>71.3</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1081,10 +1081,10 @@
         <v>39</v>
       </c>
       <c r="C19" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D19" s="7">
-        <v>86.62692</v>
+        <v>85.222674</v>
       </c>
       <c r="E19" s="8">
         <v>1155000</v>
@@ -1093,10 +1093,10 @@
         <v>0</v>
       </c>
       <c r="G19" s="8">
-        <v>100054092.28</v>
+        <v>98432187.99</v>
       </c>
       <c r="H19" s="8">
-        <v>86.52</v>
+        <v>85.44</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1107,10 +1107,10 @@
         <v>41</v>
       </c>
       <c r="C20" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D20" s="10">
-        <v>53.062364</v>
+        <v>46141</v>
+      </c>
+      <c r="D20" s="7">
+        <v>52.219961</v>
       </c>
       <c r="E20" s="8">
         <v>2985000</v>
@@ -1119,10 +1119,10 @@
         <v>0</v>
       </c>
       <c r="G20" s="8">
-        <v>158391156.4</v>
+        <v>155876583.25</v>
       </c>
       <c r="H20" s="8">
-        <v>53.22</v>
+        <v>52.28</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1133,10 +1133,10 @@
         <v>43</v>
       </c>
       <c r="C21" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D21" s="10">
-        <v>173.064305</v>
+        <v>46141</v>
+      </c>
+      <c r="D21" s="7">
+        <v>170.246267</v>
       </c>
       <c r="E21" s="8">
         <v>600000</v>
@@ -1145,10 +1145,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="8">
-        <v>103838583.12</v>
+        <v>102147760.18</v>
       </c>
       <c r="H21" s="8">
-        <v>172.95</v>
+        <v>170.8</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1159,22 +1159,22 @@
         <v>45</v>
       </c>
       <c r="C22" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D22" s="7">
-        <v>217.58252</v>
+        <v>213.972078</v>
       </c>
       <c r="E22" s="8">
-        <v>133920000</v>
+        <v>133960000</v>
       </c>
       <c r="F22" s="9">
         <v>0</v>
       </c>
       <c r="G22" s="8">
-        <v>29138651040.71</v>
+        <v>28663699559.72</v>
       </c>
       <c r="H22" s="8">
-        <v>217.6</v>
+        <v>214.15</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1185,22 +1185,22 @@
         <v>47</v>
       </c>
       <c r="C23" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D23" s="7">
-        <v>205.01901</v>
+        <v>200.879889</v>
       </c>
       <c r="E23" s="8">
-        <v>194680000</v>
+        <v>194000000</v>
       </c>
       <c r="F23" s="9">
         <v>0</v>
       </c>
       <c r="G23" s="8">
-        <v>39913100904.05</v>
+        <v>38970698432.82</v>
       </c>
       <c r="H23" s="8">
-        <v>208.75</v>
+        <v>202.1</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1211,10 +1211,10 @@
         <v>49</v>
       </c>
       <c r="C24" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D24" s="10">
-        <v>202.013825</v>
+        <v>46141</v>
+      </c>
+      <c r="D24" s="7">
+        <v>197.988157</v>
       </c>
       <c r="E24" s="8">
         <v>320000</v>
@@ -1223,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="G24" s="8">
-        <v>64644423.97</v>
+        <v>63356210.16</v>
       </c>
       <c r="H24" s="8">
-        <v>202.25</v>
+        <v>198</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1237,10 +1237,10 @@
         <v>51</v>
       </c>
       <c r="C25" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D25" s="10">
-        <v>126.749529</v>
+        <v>46141</v>
+      </c>
+      <c r="D25" s="7">
+        <v>123.398487</v>
       </c>
       <c r="E25" s="8">
         <v>600000</v>
@@ -1249,10 +1249,10 @@
         <v>0</v>
       </c>
       <c r="G25" s="8">
-        <v>76049717.61</v>
+        <v>74039092.05</v>
       </c>
       <c r="H25" s="8">
-        <v>127.6</v>
+        <v>124.15</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1263,10 +1263,10 @@
         <v>53</v>
       </c>
       <c r="C26" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D26" s="10">
-        <v>689.331976</v>
+        <v>46141</v>
+      </c>
+      <c r="D26" s="7">
+        <v>672.917971</v>
       </c>
       <c r="E26" s="8">
         <v>152040000</v>
@@ -1275,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="G26" s="8">
-        <v>104806033667.41</v>
+        <v>102310448319.41</v>
       </c>
       <c r="H26" s="8">
-        <v>719</v>
+        <v>709.5</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1289,22 +1289,22 @@
         <v>55</v>
       </c>
       <c r="C27" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D27" s="10">
-        <v>173.366407</v>
+        <v>170.56434</v>
       </c>
       <c r="E27" s="8">
-        <v>9840000</v>
+        <v>9400000</v>
       </c>
       <c r="F27" s="9">
         <v>0</v>
       </c>
       <c r="G27" s="8">
-        <v>1705925440.96</v>
+        <v>1603304799</v>
       </c>
       <c r="H27" s="8">
-        <v>174.75</v>
+        <v>172.5</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1315,22 +1315,22 @@
         <v>57</v>
       </c>
       <c r="C28" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D28" s="10">
-        <v>253.800608</v>
+        <v>46141</v>
+      </c>
+      <c r="D28" s="7">
+        <v>248.760346</v>
       </c>
       <c r="E28" s="8">
-        <v>32880000</v>
+        <v>32720000</v>
       </c>
       <c r="F28" s="9">
         <v>0</v>
       </c>
       <c r="G28" s="8">
-        <v>8344963995.83</v>
+        <v>8139438505.33</v>
       </c>
       <c r="H28" s="8">
-        <v>256</v>
+        <v>251</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1341,10 +1341,10 @@
         <v>59</v>
       </c>
       <c r="C29" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D29" s="10">
-        <v>259.752124</v>
+        <v>46141</v>
+      </c>
+      <c r="D29" s="7">
+        <v>255.392023</v>
       </c>
       <c r="E29" s="8">
         <v>3200000</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="G29" s="8">
-        <v>831206797.95</v>
+        <v>817254474.07</v>
       </c>
       <c r="H29" s="8">
-        <v>260.1</v>
+        <v>255.4</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1367,10 +1367,10 @@
         <v>61</v>
       </c>
       <c r="C30" s="6">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D30" s="10">
-        <v>117.316869</v>
+        <v>116.70603</v>
       </c>
       <c r="E30" s="8">
         <v>360000</v>
@@ -1379,10 +1379,10 @@
         <v>0</v>
       </c>
       <c r="G30" s="8">
-        <v>42234072.89</v>
+        <v>42014170.96</v>
       </c>
       <c r="H30" s="8">
-        <v>116.75</v>
+        <v>114</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1393,10 +1393,10 @@
         <v>63</v>
       </c>
       <c r="C31" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D31" s="10">
-        <v>184.702813</v>
+        <v>46141</v>
+      </c>
+      <c r="D31" s="7">
+        <v>180.461257</v>
       </c>
       <c r="E31" s="8">
         <v>400000</v>
@@ -1405,10 +1405,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="8">
-        <v>73881125.24</v>
+        <v>72184502.69</v>
       </c>
       <c r="H31" s="8">
-        <v>185.25</v>
+        <v>180.5</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1419,10 +1419,10 @@
         <v>65</v>
       </c>
       <c r="C32" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D32" s="10">
-        <v>50.194666</v>
+        <v>46141</v>
+      </c>
+      <c r="D32" s="7">
+        <v>49.296262</v>
       </c>
       <c r="E32" s="8">
         <v>1200000</v>
@@ -1431,10 +1431,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="8">
-        <v>60233599.42</v>
+        <v>59155513.92</v>
       </c>
       <c r="H32" s="8">
-        <v>50.18</v>
+        <v>49.29</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1445,10 +1445,10 @@
         <v>67</v>
       </c>
       <c r="C33" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D33" s="10">
-        <v>1205.945985</v>
+        <v>46141</v>
+      </c>
+      <c r="D33" s="7">
+        <v>1207.221567</v>
       </c>
       <c r="E33" s="8">
         <v>560000</v>
@@ -1457,10 +1457,10 @@
         <v>0</v>
       </c>
       <c r="G33" s="8">
-        <v>675329751.32</v>
+        <v>676044077.24</v>
       </c>
       <c r="H33" s="8">
-        <v>1207.5</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -1471,10 +1471,10 @@
         <v>69</v>
       </c>
       <c r="C34" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D34" s="10">
-        <v>188.299006</v>
+        <v>46141</v>
+      </c>
+      <c r="D34" s="7">
+        <v>185.348155</v>
       </c>
       <c r="E34" s="8">
         <v>680000</v>
@@ -1483,10 +1483,10 @@
         <v>0</v>
       </c>
       <c r="G34" s="8">
-        <v>128043324.4</v>
+        <v>126036745.29</v>
       </c>
       <c r="H34" s="8">
-        <v>192.85</v>
+        <v>185.35</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -1497,22 +1497,22 @@
         <v>71</v>
       </c>
       <c r="C35" s="6">
-        <v>46140</v>
-      </c>
-      <c r="D35" s="10">
-        <v>1207.064467</v>
+        <v>46141</v>
+      </c>
+      <c r="D35" s="7">
+        <v>1208.365362</v>
       </c>
       <c r="E35" s="8">
-        <v>6720000</v>
+        <v>6640000</v>
       </c>
       <c r="F35" s="9">
         <v>0</v>
       </c>
       <c r="G35" s="8">
-        <v>8111473217.79</v>
+        <v>8023546003.64</v>
       </c>
       <c r="H35" s="8">
-        <v>1208</v>
+        <v>1210</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>29.04.2026 18:50:47</t>
+    <t>30.04.2026 18:47:30</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -233,12 +233,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="###0.000000;-###0.000000;0"/>
     <numFmt numFmtId="166" formatCode="###0.00;-###0.00;0"/>
     <numFmt numFmtId="167" formatCode="###0;-###0;0"/>
     <numFmt numFmtId="168" formatCode="###0.00000;-###0.00000;0"/>
+    <numFmt numFmtId="169" formatCode="###0.0000;-###0.0000;0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -308,7 +309,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -334,6 +335,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -743,10 +747,10 @@
         <v>13</v>
       </c>
       <c r="C6" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D6" s="7">
-        <v>47.328405</v>
+        <v>46.611869</v>
       </c>
       <c r="E6" s="8">
         <v>58000000</v>
@@ -755,10 +759,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="8">
-        <v>2745047493.4</v>
+        <v>2703488409.57</v>
       </c>
       <c r="H6" s="8">
-        <v>47.4</v>
+        <v>46.64</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -769,10 +773,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D7" s="7">
-        <v>37.991432</v>
+        <v>38.369173</v>
       </c>
       <c r="E7" s="8">
         <v>14400000</v>
@@ -781,10 +785,10 @@
         <v>0</v>
       </c>
       <c r="G7" s="8">
-        <v>547076622.23</v>
+        <v>552516090.61</v>
       </c>
       <c r="H7" s="8">
-        <v>38.11</v>
+        <v>38.21</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -795,10 +799,10 @@
         <v>17</v>
       </c>
       <c r="C8" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D8" s="7">
-        <v>39.614064</v>
+        <v>39.721138</v>
       </c>
       <c r="E8" s="8">
         <v>33700000</v>
@@ -807,10 +811,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="8">
-        <v>1334993969.78</v>
+        <v>1338602365.26</v>
       </c>
       <c r="H8" s="8">
-        <v>39.69</v>
+        <v>39.59</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -821,10 +825,10 @@
         <v>19</v>
       </c>
       <c r="C9" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D9" s="7">
-        <v>56.076353</v>
+        <v>46142</v>
+      </c>
+      <c r="D9" s="10">
+        <v>56.13587</v>
       </c>
       <c r="E9" s="8">
         <v>2550000</v>
@@ -833,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="G9" s="8">
-        <v>142994701.42</v>
+        <v>143146467.73</v>
       </c>
       <c r="H9" s="8">
-        <v>56.16</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -847,10 +851,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D10" s="7">
-        <v>356.455176</v>
+        <v>363.041812</v>
       </c>
       <c r="E10" s="8">
         <v>150000</v>
@@ -859,10 +863,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="8">
-        <v>53468276.33</v>
+        <v>54456271.79</v>
       </c>
       <c r="H10" s="8">
-        <v>356.6</v>
+        <v>363.4</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -873,10 +877,10 @@
         <v>23</v>
       </c>
       <c r="C11" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D11" s="7">
-        <v>555.393707</v>
+        <v>46142</v>
+      </c>
+      <c r="D11" s="10">
+        <v>551.42168</v>
       </c>
       <c r="E11" s="8">
         <v>47850000</v>
@@ -885,10 +889,10 @@
         <v>0</v>
       </c>
       <c r="G11" s="8">
-        <v>26575588877.54</v>
+        <v>26385527400.07</v>
       </c>
       <c r="H11" s="8">
-        <v>555</v>
+        <v>553.25</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -899,10 +903,10 @@
         <v>25</v>
       </c>
       <c r="C12" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D12" s="7">
-        <v>650.541224</v>
+        <v>641.753668</v>
       </c>
       <c r="E12" s="8">
         <v>75300000</v>
@@ -911,10 +915,10 @@
         <v>0</v>
       </c>
       <c r="G12" s="8">
-        <v>48985754171.34</v>
+        <v>48324051196.32</v>
       </c>
       <c r="H12" s="8">
-        <v>655.25</v>
+        <v>652.75</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -925,22 +929,22 @@
         <v>27</v>
       </c>
       <c r="C13" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D13" s="7">
-        <v>4199.416157</v>
+        <v>46142</v>
+      </c>
+      <c r="D13" s="10">
+        <v>4199.40533</v>
       </c>
       <c r="E13" s="8">
-        <v>248000</v>
+        <v>252000</v>
       </c>
       <c r="F13" s="9">
         <v>0</v>
       </c>
       <c r="G13" s="8">
-        <v>1041455206.94</v>
+        <v>1058250143.27</v>
       </c>
       <c r="H13" s="8">
-        <v>4234</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -951,10 +955,10 @@
         <v>29</v>
       </c>
       <c r="C14" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D14" s="7">
-        <v>665.970164</v>
+        <v>663.268568</v>
       </c>
       <c r="E14" s="8">
         <v>113800000</v>
@@ -963,10 +967,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="8">
-        <v>75787404712.09</v>
+        <v>75479963008.89</v>
       </c>
       <c r="H14" s="8">
-        <v>698.5</v>
+        <v>696.75</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -977,10 +981,10 @@
         <v>31</v>
       </c>
       <c r="C15" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D15" s="7">
-        <v>549.429833</v>
+        <v>549.008042</v>
       </c>
       <c r="E15" s="8">
         <v>33450000</v>
@@ -989,10 +993,10 @@
         <v>0</v>
       </c>
       <c r="G15" s="8">
-        <v>18378427920.15</v>
+        <v>18364318990.28</v>
       </c>
       <c r="H15" s="8">
-        <v>555.75</v>
+        <v>545.75</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1003,10 +1007,10 @@
         <v>33</v>
       </c>
       <c r="C16" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D16" s="7">
-        <v>25.628626</v>
+        <v>25.582624</v>
       </c>
       <c r="E16" s="8">
         <v>12300000</v>
@@ -1015,10 +1019,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="8">
-        <v>315232099.88</v>
+        <v>314666274.59</v>
       </c>
       <c r="H16" s="8">
-        <v>25.6</v>
+        <v>25.56</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1029,10 +1033,10 @@
         <v>35</v>
       </c>
       <c r="C17" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D17" s="7">
-        <v>45.376424</v>
+        <v>45.422776</v>
       </c>
       <c r="E17" s="8">
         <v>1625000</v>
@@ -1041,10 +1045,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="8">
-        <v>73736689.26</v>
+        <v>73812011.47</v>
       </c>
       <c r="H17" s="8">
-        <v>45.42</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1055,10 +1059,10 @@
         <v>37</v>
       </c>
       <c r="C18" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D18" s="7">
-        <v>71.006574</v>
+        <v>71.882483</v>
       </c>
       <c r="E18" s="8">
         <v>1140000</v>
@@ -1067,10 +1071,10 @@
         <v>0</v>
       </c>
       <c r="G18" s="8">
-        <v>80947494.22</v>
+        <v>81946030.98</v>
       </c>
       <c r="H18" s="8">
-        <v>71.3</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1081,10 +1085,10 @@
         <v>39</v>
       </c>
       <c r="C19" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D19" s="7">
-        <v>85.222674</v>
+        <v>85.429824</v>
       </c>
       <c r="E19" s="8">
         <v>1155000</v>
@@ -1093,10 +1097,10 @@
         <v>0</v>
       </c>
       <c r="G19" s="8">
-        <v>98432187.99</v>
+        <v>98671446.84</v>
       </c>
       <c r="H19" s="8">
-        <v>85.44</v>
+        <v>85.08</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1107,10 +1111,10 @@
         <v>41</v>
       </c>
       <c r="C20" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D20" s="7">
-        <v>52.219961</v>
+        <v>46142</v>
+      </c>
+      <c r="D20" s="11">
+        <v>52.2106</v>
       </c>
       <c r="E20" s="8">
         <v>2985000</v>
@@ -1119,10 +1123,10 @@
         <v>0</v>
       </c>
       <c r="G20" s="8">
-        <v>155876583.25</v>
+        <v>155848641.04</v>
       </c>
       <c r="H20" s="8">
-        <v>52.28</v>
+        <v>52.08</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1133,10 +1137,10 @@
         <v>43</v>
       </c>
       <c r="C21" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D21" s="7">
-        <v>170.246267</v>
+        <v>169.631592</v>
       </c>
       <c r="E21" s="8">
         <v>600000</v>
@@ -1145,10 +1149,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="8">
-        <v>102147760.18</v>
+        <v>101778955.42</v>
       </c>
       <c r="H21" s="8">
-        <v>170.8</v>
+        <v>170.15</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1159,22 +1163,22 @@
         <v>45</v>
       </c>
       <c r="C22" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D22" s="7">
-        <v>213.972078</v>
+        <v>214.624513</v>
       </c>
       <c r="E22" s="8">
-        <v>133960000</v>
+        <v>134040000</v>
       </c>
       <c r="F22" s="9">
         <v>0</v>
       </c>
       <c r="G22" s="8">
-        <v>28663699559.72</v>
+        <v>28768269730.21</v>
       </c>
       <c r="H22" s="8">
-        <v>214.15</v>
+        <v>214.6</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1185,22 +1189,22 @@
         <v>47</v>
       </c>
       <c r="C23" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D23" s="7">
-        <v>200.879889</v>
+        <v>46142</v>
+      </c>
+      <c r="D23" s="11">
+        <v>197.8555</v>
       </c>
       <c r="E23" s="8">
-        <v>194000000</v>
+        <v>193280000</v>
       </c>
       <c r="F23" s="9">
         <v>0</v>
       </c>
       <c r="G23" s="8">
-        <v>38970698432.82</v>
+        <v>38241511103.11</v>
       </c>
       <c r="H23" s="8">
-        <v>202.1</v>
+        <v>198.9</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1211,10 +1215,10 @@
         <v>49</v>
       </c>
       <c r="C24" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D24" s="7">
-        <v>197.988157</v>
+        <v>197.547529</v>
       </c>
       <c r="E24" s="8">
         <v>320000</v>
@@ -1223,10 +1227,10 @@
         <v>0</v>
       </c>
       <c r="G24" s="8">
-        <v>63356210.16</v>
+        <v>63215209.33</v>
       </c>
       <c r="H24" s="8">
-        <v>198</v>
+        <v>197.55</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1237,10 +1241,10 @@
         <v>51</v>
       </c>
       <c r="C25" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D25" s="7">
-        <v>123.398487</v>
+        <v>122.524028</v>
       </c>
       <c r="E25" s="8">
         <v>600000</v>
@@ -1249,10 +1253,10 @@
         <v>0</v>
       </c>
       <c r="G25" s="8">
-        <v>74039092.05</v>
+        <v>73514417.07</v>
       </c>
       <c r="H25" s="8">
-        <v>124.15</v>
+        <v>122.5</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1263,10 +1267,10 @@
         <v>53</v>
       </c>
       <c r="C26" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D26" s="7">
-        <v>672.917971</v>
+        <v>671.824072</v>
       </c>
       <c r="E26" s="8">
         <v>152040000</v>
@@ -1275,10 +1279,10 @@
         <v>0</v>
       </c>
       <c r="G26" s="8">
-        <v>102310448319.41</v>
+        <v>102144131917.17</v>
       </c>
       <c r="H26" s="8">
-        <v>709.5</v>
+        <v>704.75</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1289,10 +1293,10 @@
         <v>55</v>
       </c>
       <c r="C27" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D27" s="10">
-        <v>170.56434</v>
+        <v>46142</v>
+      </c>
+      <c r="D27" s="7">
+        <v>173.073144</v>
       </c>
       <c r="E27" s="8">
         <v>9400000</v>
@@ -1301,10 +1305,10 @@
         <v>0</v>
       </c>
       <c r="G27" s="8">
-        <v>1603304799</v>
+        <v>1626887558.06</v>
       </c>
       <c r="H27" s="8">
-        <v>172.5</v>
+        <v>172.9</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1315,10 +1319,10 @@
         <v>57</v>
       </c>
       <c r="C28" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D28" s="7">
-        <v>248.760346</v>
+        <v>251.423743</v>
       </c>
       <c r="E28" s="8">
         <v>32720000</v>
@@ -1327,10 +1331,10 @@
         <v>0</v>
       </c>
       <c r="G28" s="8">
-        <v>8139438505.33</v>
+        <v>8226584885.16</v>
       </c>
       <c r="H28" s="8">
-        <v>251</v>
+        <v>251.6</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1341,10 +1345,10 @@
         <v>59</v>
       </c>
       <c r="C29" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D29" s="7">
-        <v>255.392023</v>
+        <v>257.887916</v>
       </c>
       <c r="E29" s="8">
         <v>3200000</v>
@@ -1353,10 +1357,10 @@
         <v>0</v>
       </c>
       <c r="G29" s="8">
-        <v>817254474.07</v>
+        <v>825241331.72</v>
       </c>
       <c r="H29" s="8">
-        <v>255.4</v>
+        <v>257.8</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1367,22 +1371,22 @@
         <v>61</v>
       </c>
       <c r="C30" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D30" s="10">
-        <v>116.70603</v>
+        <v>46142</v>
+      </c>
+      <c r="D30" s="7">
+        <v>117.569705</v>
       </c>
       <c r="E30" s="8">
-        <v>360000</v>
+        <v>440000</v>
       </c>
       <c r="F30" s="9">
         <v>0</v>
       </c>
       <c r="G30" s="8">
-        <v>42014170.96</v>
+        <v>51730670.11</v>
       </c>
       <c r="H30" s="8">
-        <v>114</v>
+        <v>117.55</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1393,10 +1397,10 @@
         <v>63</v>
       </c>
       <c r="C31" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D31" s="7">
-        <v>180.461257</v>
+        <v>180.303075</v>
       </c>
       <c r="E31" s="8">
         <v>400000</v>
@@ -1405,10 +1409,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="8">
-        <v>72184502.69</v>
+        <v>72121229.97</v>
       </c>
       <c r="H31" s="8">
-        <v>180.5</v>
+        <v>180</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1419,10 +1423,10 @@
         <v>65</v>
       </c>
       <c r="C32" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D32" s="7">
-        <v>49.296262</v>
+        <v>49.280059</v>
       </c>
       <c r="E32" s="8">
         <v>1200000</v>
@@ -1431,10 +1435,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="8">
-        <v>59155513.92</v>
+        <v>59136070.64</v>
       </c>
       <c r="H32" s="8">
-        <v>49.29</v>
+        <v>49.28</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1445,10 +1449,10 @@
         <v>67</v>
       </c>
       <c r="C33" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D33" s="7">
-        <v>1207.221567</v>
+        <v>1208.509887</v>
       </c>
       <c r="E33" s="8">
         <v>560000</v>
@@ -1457,10 +1461,10 @@
         <v>0</v>
       </c>
       <c r="G33" s="8">
-        <v>676044077.24</v>
+        <v>676765536.56</v>
       </c>
       <c r="H33" s="8">
-        <v>1209</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -1471,10 +1475,10 @@
         <v>69</v>
       </c>
       <c r="C34" s="6">
-        <v>46141</v>
-      </c>
-      <c r="D34" s="7">
-        <v>185.348155</v>
+        <v>46142</v>
+      </c>
+      <c r="D34" s="11">
+        <v>185.3638</v>
       </c>
       <c r="E34" s="8">
         <v>680000</v>
@@ -1483,7 +1487,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="8">
-        <v>126036745.29</v>
+        <v>126047383.69</v>
       </c>
       <c r="H34" s="8">
         <v>185.35</v>
@@ -1497,22 +1501,22 @@
         <v>71</v>
       </c>
       <c r="C35" s="6">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D35" s="7">
-        <v>1208.365362</v>
+        <v>1209.669553</v>
       </c>
       <c r="E35" s="8">
-        <v>6640000</v>
+        <v>6680000</v>
       </c>
       <c r="F35" s="9">
         <v>0</v>
       </c>
       <c r="G35" s="8">
-        <v>8023546003.64</v>
+        <v>8080592613.03</v>
       </c>
       <c r="H35" s="8">
-        <v>1210</v>
+        <v>1214.5</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>30.04.2026 18:47:30</t>
+    <t>04.05.2026 19:05:28</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -233,13 +233,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="###0.000000;-###0.000000;0"/>
     <numFmt numFmtId="166" formatCode="###0.00;-###0.00;0"/>
     <numFmt numFmtId="167" formatCode="###0;-###0;0"/>
     <numFmt numFmtId="168" formatCode="###0.00000;-###0.00000;0"/>
-    <numFmt numFmtId="169" formatCode="###0.0000;-###0.0000;0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -309,7 +308,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -335,9 +334,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -747,10 +743,10 @@
         <v>13</v>
       </c>
       <c r="C6" s="6">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="D6" s="7">
-        <v>46.611869</v>
+        <v>47.012664</v>
       </c>
       <c r="E6" s="8">
         <v>58000000</v>
@@ -759,10 +755,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="8">
-        <v>2703488409.57</v>
+        <v>2726734532.19</v>
       </c>
       <c r="H6" s="8">
-        <v>46.64</v>
+        <v>48.51</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -773,10 +769,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="6">
-        <v>46142</v>
-      </c>
-      <c r="D7" s="7">
-        <v>38.369173</v>
+        <v>46146</v>
+      </c>
+      <c r="D7" s="10">
+        <v>38.27622</v>
       </c>
       <c r="E7" s="8">
         <v>14400000</v>
@@ -785,10 +781,10 @@
         <v>0</v>
       </c>
       <c r="G7" s="8">
-        <v>552516090.61</v>
+        <v>551177566.41</v>
       </c>
       <c r="H7" s="8">
-        <v>38.21</v>
+        <v>39.03</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -799,10 +795,10 @@
         <v>17</v>
       </c>
       <c r="C8" s="6">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="D8" s="7">
-        <v>39.721138</v>
+        <v>39.869976</v>
       </c>
       <c r="E8" s="8">
         <v>33700000</v>
@@ -811,10 +807,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="8">
-        <v>1338602365.26</v>
+        <v>1343618202.38</v>
       </c>
       <c r="H8" s="8">
-        <v>39.59</v>
+        <v>39.88</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -825,10 +821,10 @@
         <v>19</v>
       </c>
       <c r="C9" s="6">
-        <v>46142</v>
-      </c>
-      <c r="D9" s="10">
-        <v>56.13587</v>
+        <v>46146</v>
+      </c>
+      <c r="D9" s="7">
+        <v>56.353656</v>
       </c>
       <c r="E9" s="8">
         <v>2550000</v>
@@ -837,10 +833,10 @@
         <v>0</v>
       </c>
       <c r="G9" s="8">
-        <v>143146467.73</v>
+        <v>143701821.86</v>
       </c>
       <c r="H9" s="8">
-        <v>56.4</v>
+        <v>56.46</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -851,10 +847,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="6">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="D10" s="7">
-        <v>363.041812</v>
+        <v>366.179515</v>
       </c>
       <c r="E10" s="8">
         <v>150000</v>
@@ -863,10 +859,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="8">
-        <v>54456271.79</v>
+        <v>54926927.19</v>
       </c>
       <c r="H10" s="8">
-        <v>363.4</v>
+        <v>367.1</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -877,10 +873,10 @@
         <v>23</v>
       </c>
       <c r="C11" s="6">
-        <v>46142</v>
-      </c>
-      <c r="D11" s="10">
-        <v>551.42168</v>
+        <v>46146</v>
+      </c>
+      <c r="D11" s="7">
+        <v>563.079256</v>
       </c>
       <c r="E11" s="8">
         <v>47850000</v>
@@ -889,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="G11" s="8">
-        <v>26385527400.07</v>
+        <v>26943342417.52</v>
       </c>
       <c r="H11" s="8">
-        <v>553.25</v>
+        <v>562</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -903,10 +899,10 @@
         <v>25</v>
       </c>
       <c r="C12" s="6">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="D12" s="7">
-        <v>641.753668</v>
+        <v>657.622504</v>
       </c>
       <c r="E12" s="8">
         <v>75300000</v>
@@ -915,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="G12" s="8">
-        <v>48324051196.32</v>
+        <v>49518974528.31</v>
       </c>
       <c r="H12" s="8">
-        <v>652.75</v>
+        <v>666.25</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -929,10 +925,10 @@
         <v>27</v>
       </c>
       <c r="C13" s="6">
-        <v>46142</v>
-      </c>
-      <c r="D13" s="10">
-        <v>4199.40533</v>
+        <v>46146</v>
+      </c>
+      <c r="D13" s="7">
+        <v>4211.156368</v>
       </c>
       <c r="E13" s="8">
         <v>252000</v>
@@ -941,10 +937,10 @@
         <v>0</v>
       </c>
       <c r="G13" s="8">
-        <v>1058250143.27</v>
+        <v>1061211404.65</v>
       </c>
       <c r="H13" s="8">
-        <v>4237</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -955,10 +951,10 @@
         <v>29</v>
       </c>
       <c r="C14" s="6">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="D14" s="7">
-        <v>663.268568</v>
+        <v>672.024055</v>
       </c>
       <c r="E14" s="8">
         <v>113800000</v>
@@ -967,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="8">
-        <v>75479963008.89</v>
+        <v>76476337507.57</v>
       </c>
       <c r="H14" s="8">
-        <v>696.75</v>
+        <v>710</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -981,10 +977,10 @@
         <v>31</v>
       </c>
       <c r="C15" s="6">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="D15" s="7">
-        <v>549.008042</v>
+        <v>551.108706</v>
       </c>
       <c r="E15" s="8">
         <v>33450000</v>
@@ -993,10 +989,10 @@
         <v>0</v>
       </c>
       <c r="G15" s="8">
-        <v>18364318990.28</v>
+        <v>18434586201.37</v>
       </c>
       <c r="H15" s="8">
-        <v>545.75</v>
+        <v>560.25</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1007,10 +1003,10 @@
         <v>33</v>
       </c>
       <c r="C16" s="6">
-        <v>46142</v>
-      </c>
-      <c r="D16" s="7">
-        <v>25.582624</v>
+        <v>46146</v>
+      </c>
+      <c r="D16" s="10">
+        <v>25.82443</v>
       </c>
       <c r="E16" s="8">
         <v>12300000</v>
@@ -1019,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="8">
-        <v>314666274.59</v>
+        <v>317640491.5</v>
       </c>
       <c r="H16" s="8">
-        <v>25.56</v>
+        <v>25.73</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1033,10 +1029,10 @@
         <v>35</v>
       </c>
       <c r="C17" s="6">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="D17" s="7">
-        <v>45.422776</v>
+        <v>45.609579</v>
       </c>
       <c r="E17" s="8">
         <v>1625000</v>
@@ -1045,10 +1041,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="8">
-        <v>73812011.47</v>
+        <v>74115565.25</v>
       </c>
       <c r="H17" s="8">
-        <v>45.62</v>
+        <v>45.65</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1059,10 +1055,10 @@
         <v>37</v>
       </c>
       <c r="C18" s="6">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="D18" s="7">
-        <v>71.882483</v>
+        <v>72.753031</v>
       </c>
       <c r="E18" s="8">
         <v>1140000</v>
@@ -1071,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="G18" s="8">
-        <v>81946030.98</v>
+        <v>82938454.8</v>
       </c>
       <c r="H18" s="8">
-        <v>71.8</v>
+        <v>72.74</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1085,10 +1081,10 @@
         <v>39</v>
       </c>
       <c r="C19" s="6">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="D19" s="7">
-        <v>85.429824</v>
+        <v>85.683189</v>
       </c>
       <c r="E19" s="8">
         <v>1155000</v>
@@ -1097,10 +1093,10 @@
         <v>0</v>
       </c>
       <c r="G19" s="8">
-        <v>98671446.84</v>
+        <v>98964082.86</v>
       </c>
       <c r="H19" s="8">
-        <v>85.08</v>
+        <v>85.52</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1111,10 +1107,10 @@
         <v>41</v>
       </c>
       <c r="C20" s="6">
-        <v>46142</v>
-      </c>
-      <c r="D20" s="11">
-        <v>52.2106</v>
+        <v>46146</v>
+      </c>
+      <c r="D20" s="7">
+        <v>52.705744</v>
       </c>
       <c r="E20" s="8">
         <v>2985000</v>
@@ -1123,10 +1119,10 @@
         <v>0</v>
       </c>
       <c r="G20" s="8">
-        <v>155848641.04</v>
+        <v>157326646.78</v>
       </c>
       <c r="H20" s="8">
-        <v>52.08</v>
+        <v>52.74</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1137,10 +1133,10 @@
         <v>43</v>
       </c>
       <c r="C21" s="6">
-        <v>46142</v>
-      </c>
-      <c r="D21" s="7">
-        <v>169.631592</v>
+        <v>46146</v>
+      </c>
+      <c r="D21" s="10">
+        <v>171.30677</v>
       </c>
       <c r="E21" s="8">
         <v>600000</v>
@@ -1149,10 +1145,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="8">
-        <v>101778955.42</v>
+        <v>102784061.94</v>
       </c>
       <c r="H21" s="8">
-        <v>170.15</v>
+        <v>171.5</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1163,22 +1159,22 @@
         <v>45</v>
       </c>
       <c r="C22" s="6">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="D22" s="7">
-        <v>214.624513</v>
+        <v>215.390282</v>
       </c>
       <c r="E22" s="8">
-        <v>134040000</v>
+        <v>133960000</v>
       </c>
       <c r="F22" s="9">
         <v>0</v>
       </c>
       <c r="G22" s="8">
-        <v>28768269730.21</v>
+        <v>28853682190.1</v>
       </c>
       <c r="H22" s="8">
-        <v>214.6</v>
+        <v>215.75</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1189,22 +1185,22 @@
         <v>47</v>
       </c>
       <c r="C23" s="6">
-        <v>46142</v>
-      </c>
-      <c r="D23" s="11">
-        <v>197.8555</v>
+        <v>46146</v>
+      </c>
+      <c r="D23" s="7">
+        <v>199.652588</v>
       </c>
       <c r="E23" s="8">
-        <v>193280000</v>
+        <v>193400000</v>
       </c>
       <c r="F23" s="9">
         <v>0</v>
       </c>
       <c r="G23" s="8">
-        <v>38241511103.11</v>
+        <v>38612810533.45</v>
       </c>
       <c r="H23" s="8">
-        <v>198.9</v>
+        <v>200.1</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1215,10 +1211,10 @@
         <v>49</v>
       </c>
       <c r="C24" s="6">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="D24" s="7">
-        <v>197.547529</v>
+        <v>199.356872</v>
       </c>
       <c r="E24" s="8">
         <v>320000</v>
@@ -1227,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="G24" s="8">
-        <v>63215209.33</v>
+        <v>63794199.17</v>
       </c>
       <c r="H24" s="8">
-        <v>197.55</v>
+        <v>199.35</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1241,10 +1237,10 @@
         <v>51</v>
       </c>
       <c r="C25" s="6">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="D25" s="7">
-        <v>122.524028</v>
+        <v>123.353601</v>
       </c>
       <c r="E25" s="8">
         <v>600000</v>
@@ -1253,10 +1249,10 @@
         <v>0</v>
       </c>
       <c r="G25" s="8">
-        <v>73514417.07</v>
+        <v>74012160.87</v>
       </c>
       <c r="H25" s="8">
-        <v>122.5</v>
+        <v>123.35</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1267,10 +1263,10 @@
         <v>53</v>
       </c>
       <c r="C26" s="6">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="D26" s="7">
-        <v>671.824072</v>
+        <v>687.134894</v>
       </c>
       <c r="E26" s="8">
         <v>152040000</v>
@@ -1279,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="G26" s="8">
-        <v>102144131917.17</v>
+        <v>104471989326.83</v>
       </c>
       <c r="H26" s="8">
-        <v>704.75</v>
+        <v>712</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1293,10 +1289,10 @@
         <v>55</v>
       </c>
       <c r="C27" s="6">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="D27" s="7">
-        <v>173.073144</v>
+        <v>174.639413</v>
       </c>
       <c r="E27" s="8">
         <v>9400000</v>
@@ -1305,10 +1301,10 @@
         <v>0</v>
       </c>
       <c r="G27" s="8">
-        <v>1626887558.06</v>
+        <v>1641610480.94</v>
       </c>
       <c r="H27" s="8">
-        <v>172.9</v>
+        <v>176.25</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1319,10 +1315,10 @@
         <v>57</v>
       </c>
       <c r="C28" s="6">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="D28" s="7">
-        <v>251.423743</v>
+        <v>254.022105</v>
       </c>
       <c r="E28" s="8">
         <v>32720000</v>
@@ -1331,10 +1327,10 @@
         <v>0</v>
       </c>
       <c r="G28" s="8">
-        <v>8226584885.16</v>
+        <v>8311603288.95</v>
       </c>
       <c r="H28" s="8">
-        <v>251.6</v>
+        <v>253.9</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1345,10 +1341,10 @@
         <v>59</v>
       </c>
       <c r="C29" s="6">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="D29" s="7">
-        <v>257.887916</v>
+        <v>257.246475</v>
       </c>
       <c r="E29" s="8">
         <v>3200000</v>
@@ -1357,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="G29" s="8">
-        <v>825241331.72</v>
+        <v>823188719.77</v>
       </c>
       <c r="H29" s="8">
-        <v>257.8</v>
+        <v>257.6</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1371,10 +1367,10 @@
         <v>61</v>
       </c>
       <c r="C30" s="6">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="D30" s="7">
-        <v>117.569705</v>
+        <v>117.715942</v>
       </c>
       <c r="E30" s="8">
         <v>440000</v>
@@ -1383,10 +1379,10 @@
         <v>0</v>
       </c>
       <c r="G30" s="8">
-        <v>51730670.11</v>
+        <v>51795014.65</v>
       </c>
       <c r="H30" s="8">
-        <v>117.55</v>
+        <v>117.7</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1397,10 +1393,10 @@
         <v>63</v>
       </c>
       <c r="C31" s="6">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="D31" s="7">
-        <v>180.303075</v>
+        <v>182.237306</v>
       </c>
       <c r="E31" s="8">
         <v>400000</v>
@@ -1409,10 +1405,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="8">
-        <v>72121229.97</v>
+        <v>72894922.3</v>
       </c>
       <c r="H31" s="8">
-        <v>180</v>
+        <v>181.8</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1423,10 +1419,10 @@
         <v>65</v>
       </c>
       <c r="C32" s="6">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="D32" s="7">
-        <v>49.280059</v>
+        <v>49.278847</v>
       </c>
       <c r="E32" s="8">
         <v>1200000</v>
@@ -1435,10 +1431,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="8">
-        <v>59136070.64</v>
+        <v>59134616.48</v>
       </c>
       <c r="H32" s="8">
-        <v>49.28</v>
+        <v>49.25</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1449,10 +1445,10 @@
         <v>67</v>
       </c>
       <c r="C33" s="6">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="D33" s="7">
-        <v>1208.509887</v>
+        <v>1213.745987</v>
       </c>
       <c r="E33" s="8">
         <v>560000</v>
@@ -1461,10 +1457,10 @@
         <v>0</v>
       </c>
       <c r="G33" s="8">
-        <v>676765536.56</v>
+        <v>679697752.53</v>
       </c>
       <c r="H33" s="8">
-        <v>1214</v>
+        <v>1215.5</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -1475,10 +1471,10 @@
         <v>69</v>
       </c>
       <c r="C34" s="6">
-        <v>46142</v>
-      </c>
-      <c r="D34" s="11">
-        <v>185.3638</v>
+        <v>46146</v>
+      </c>
+      <c r="D34" s="7">
+        <v>187.146577</v>
       </c>
       <c r="E34" s="8">
         <v>680000</v>
@@ -1487,10 +1483,10 @@
         <v>0</v>
       </c>
       <c r="G34" s="8">
-        <v>126047383.69</v>
+        <v>127259672.31</v>
       </c>
       <c r="H34" s="8">
-        <v>185.35</v>
+        <v>187.2</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -1501,10 +1497,10 @@
         <v>71</v>
       </c>
       <c r="C35" s="6">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="D35" s="7">
-        <v>1209.669553</v>
+        <v>1214.892382</v>
       </c>
       <c r="E35" s="8">
         <v>6680000</v>
@@ -1513,10 +1509,10 @@
         <v>0</v>
       </c>
       <c r="G35" s="8">
-        <v>8080592613.03</v>
+        <v>8115481108.59</v>
       </c>
       <c r="H35" s="8">
-        <v>1214.5</v>
+        <v>1216.5</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>04.05.2026 19:05:28</t>
+    <t>05.05.2026 18:25:30</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -743,10 +743,10 @@
         <v>13</v>
       </c>
       <c r="C6" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D6" s="7">
-        <v>47.012664</v>
+        <v>45.628759</v>
       </c>
       <c r="E6" s="8">
         <v>58000000</v>
@@ -755,10 +755,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="8">
-        <v>2726734532.19</v>
+        <v>2646468042.49</v>
       </c>
       <c r="H6" s="8">
-        <v>48.51</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -769,10 +769,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D7" s="10">
-        <v>38.27622</v>
+        <v>46147</v>
+      </c>
+      <c r="D7" s="7">
+        <v>38.248772</v>
       </c>
       <c r="E7" s="8">
         <v>14400000</v>
@@ -781,10 +781,10 @@
         <v>0</v>
       </c>
       <c r="G7" s="8">
-        <v>551177566.41</v>
+        <v>550782317.86</v>
       </c>
       <c r="H7" s="8">
-        <v>39.03</v>
+        <v>38.35</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -795,10 +795,10 @@
         <v>17</v>
       </c>
       <c r="C8" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D8" s="7">
-        <v>39.869976</v>
+        <v>39.555807</v>
       </c>
       <c r="E8" s="8">
         <v>33700000</v>
@@ -807,10 +807,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="8">
-        <v>1343618202.38</v>
+        <v>1333030696.37</v>
       </c>
       <c r="H8" s="8">
-        <v>39.88</v>
+        <v>39.58</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -821,10 +821,10 @@
         <v>19</v>
       </c>
       <c r="C9" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D9" s="7">
-        <v>56.353656</v>
+        <v>56.413173</v>
       </c>
       <c r="E9" s="8">
         <v>2550000</v>
@@ -833,7 +833,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="8">
-        <v>143701821.86</v>
+        <v>143853590.45</v>
       </c>
       <c r="H9" s="8">
         <v>56.46</v>
@@ -847,10 +847,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D10" s="7">
-        <v>366.179515</v>
+        <v>367.578034</v>
       </c>
       <c r="E10" s="8">
         <v>150000</v>
@@ -859,10 +859,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="8">
-        <v>54926927.19</v>
+        <v>55136705.15</v>
       </c>
       <c r="H10" s="8">
-        <v>367.1</v>
+        <v>368.2</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -873,10 +873,10 @@
         <v>23</v>
       </c>
       <c r="C11" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D11" s="7">
-        <v>563.079256</v>
+        <v>46147</v>
+      </c>
+      <c r="D11" s="10">
+        <v>554.96134</v>
       </c>
       <c r="E11" s="8">
         <v>47850000</v>
@@ -885,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="G11" s="8">
-        <v>26943342417.52</v>
+        <v>26554900132.88</v>
       </c>
       <c r="H11" s="8">
-        <v>562</v>
+        <v>555</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -899,10 +899,10 @@
         <v>25</v>
       </c>
       <c r="C12" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D12" s="7">
-        <v>657.622504</v>
+        <v>662.201349</v>
       </c>
       <c r="E12" s="8">
         <v>75300000</v>
@@ -911,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="G12" s="8">
-        <v>49518974528.31</v>
+        <v>49863761546.18</v>
       </c>
       <c r="H12" s="8">
-        <v>666.25</v>
+        <v>664</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -925,22 +925,22 @@
         <v>27</v>
       </c>
       <c r="C13" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D13" s="7">
-        <v>4211.156368</v>
+        <v>4210.073262</v>
       </c>
       <c r="E13" s="8">
-        <v>252000</v>
+        <v>258000</v>
       </c>
       <c r="F13" s="9">
         <v>0</v>
       </c>
       <c r="G13" s="8">
-        <v>1061211404.65</v>
+        <v>1086198901.49</v>
       </c>
       <c r="H13" s="8">
-        <v>4241</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -951,10 +951,10 @@
         <v>29</v>
       </c>
       <c r="C14" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D14" s="7">
-        <v>672.024055</v>
+        <v>667.500242</v>
       </c>
       <c r="E14" s="8">
         <v>113800000</v>
@@ -963,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="8">
-        <v>76476337507.57</v>
+        <v>75961527530.8</v>
       </c>
       <c r="H14" s="8">
-        <v>710</v>
+        <v>700</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -977,10 +977,10 @@
         <v>31</v>
       </c>
       <c r="C15" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D15" s="7">
-        <v>551.108706</v>
+        <v>551.561422</v>
       </c>
       <c r="E15" s="8">
         <v>33450000</v>
@@ -989,10 +989,10 @@
         <v>0</v>
       </c>
       <c r="G15" s="8">
-        <v>18434586201.37</v>
+        <v>18449729555.43</v>
       </c>
       <c r="H15" s="8">
-        <v>560.25</v>
+        <v>553.5</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1003,10 +1003,10 @@
         <v>33</v>
       </c>
       <c r="C16" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D16" s="10">
-        <v>25.82443</v>
+        <v>46147</v>
+      </c>
+      <c r="D16" s="7">
+        <v>25.467999</v>
       </c>
       <c r="E16" s="8">
         <v>12300000</v>
@@ -1015,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="8">
-        <v>317640491.5</v>
+        <v>313256381.86</v>
       </c>
       <c r="H16" s="8">
-        <v>25.73</v>
+        <v>25.53</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1029,10 +1029,10 @@
         <v>35</v>
       </c>
       <c r="C17" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D17" s="7">
-        <v>45.609579</v>
+        <v>45.654867</v>
       </c>
       <c r="E17" s="8">
         <v>1625000</v>
@@ -1041,10 +1041,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="8">
-        <v>74115565.25</v>
+        <v>74189159.02</v>
       </c>
       <c r="H17" s="8">
-        <v>45.65</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1055,10 +1055,10 @@
         <v>37</v>
       </c>
       <c r="C18" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D18" s="7">
-        <v>72.753031</v>
+        <v>73.200476</v>
       </c>
       <c r="E18" s="8">
         <v>1140000</v>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="G18" s="8">
-        <v>82938454.8</v>
+        <v>83448542.88</v>
       </c>
       <c r="H18" s="8">
-        <v>72.74</v>
+        <v>73.9</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1081,10 +1081,10 @@
         <v>39</v>
       </c>
       <c r="C19" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D19" s="7">
-        <v>85.683189</v>
+        <v>85.154624</v>
       </c>
       <c r="E19" s="8">
         <v>1155000</v>
@@ -1093,10 +1093,10 @@
         <v>0</v>
       </c>
       <c r="G19" s="8">
-        <v>98964082.86</v>
+        <v>98353590.45</v>
       </c>
       <c r="H19" s="8">
-        <v>85.52</v>
+        <v>84.96</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1107,10 +1107,10 @@
         <v>41</v>
       </c>
       <c r="C20" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D20" s="7">
-        <v>52.705744</v>
+        <v>51.826825</v>
       </c>
       <c r="E20" s="8">
         <v>2985000</v>
@@ -1119,10 +1119,10 @@
         <v>0</v>
       </c>
       <c r="G20" s="8">
-        <v>157326646.78</v>
+        <v>154703071.33</v>
       </c>
       <c r="H20" s="8">
-        <v>52.74</v>
+        <v>52.34</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1133,10 +1133,10 @@
         <v>43</v>
       </c>
       <c r="C21" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D21" s="10">
-        <v>171.30677</v>
+        <v>166.62966</v>
       </c>
       <c r="E21" s="8">
         <v>600000</v>
@@ -1145,10 +1145,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="8">
-        <v>102784061.94</v>
+        <v>99977795.85</v>
       </c>
       <c r="H21" s="8">
-        <v>171.5</v>
+        <v>169.9</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1159,22 +1159,22 @@
         <v>45</v>
       </c>
       <c r="C22" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D22" s="7">
-        <v>215.390282</v>
+        <v>213.702668</v>
       </c>
       <c r="E22" s="8">
-        <v>133960000</v>
+        <v>131200000</v>
       </c>
       <c r="F22" s="9">
         <v>0</v>
       </c>
       <c r="G22" s="8">
-        <v>28853682190.1</v>
+        <v>28037790104.13</v>
       </c>
       <c r="H22" s="8">
-        <v>215.75</v>
+        <v>214</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1185,22 +1185,22 @@
         <v>47</v>
       </c>
       <c r="C23" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D23" s="7">
-        <v>199.652588</v>
+        <v>193.704674</v>
       </c>
       <c r="E23" s="8">
-        <v>193400000</v>
+        <v>197400000</v>
       </c>
       <c r="F23" s="9">
         <v>0</v>
       </c>
       <c r="G23" s="8">
-        <v>38612810533.45</v>
+        <v>38237302600.62</v>
       </c>
       <c r="H23" s="8">
-        <v>200.1</v>
+        <v>196.4</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1211,10 +1211,10 @@
         <v>49</v>
       </c>
       <c r="C24" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D24" s="7">
-        <v>199.356872</v>
+        <v>197.090295</v>
       </c>
       <c r="E24" s="8">
         <v>320000</v>
@@ -1223,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="G24" s="8">
-        <v>63794199.17</v>
+        <v>63068894.34</v>
       </c>
       <c r="H24" s="8">
-        <v>199.35</v>
+        <v>197.15</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1237,10 +1237,10 @@
         <v>51</v>
       </c>
       <c r="C25" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D25" s="7">
-        <v>123.353601</v>
+        <v>123.087418</v>
       </c>
       <c r="E25" s="8">
         <v>600000</v>
@@ -1249,10 +1249,10 @@
         <v>0</v>
       </c>
       <c r="G25" s="8">
-        <v>74012160.87</v>
+        <v>73852451</v>
       </c>
       <c r="H25" s="8">
-        <v>123.35</v>
+        <v>122.25</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1263,10 +1263,10 @@
         <v>53</v>
       </c>
       <c r="C26" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D26" s="7">
-        <v>687.134894</v>
+        <v>676.957873</v>
       </c>
       <c r="E26" s="8">
         <v>152040000</v>
@@ -1275,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="G26" s="8">
-        <v>104471989326.83</v>
+        <v>102924675044.16</v>
       </c>
       <c r="H26" s="8">
-        <v>712</v>
+        <v>704.5</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1289,10 +1289,10 @@
         <v>55</v>
       </c>
       <c r="C27" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D27" s="7">
-        <v>174.639413</v>
+        <v>176.098935</v>
       </c>
       <c r="E27" s="8">
         <v>9400000</v>
@@ -1301,10 +1301,10 @@
         <v>0</v>
       </c>
       <c r="G27" s="8">
-        <v>1641610480.94</v>
+        <v>1655329986.14</v>
       </c>
       <c r="H27" s="8">
-        <v>176.25</v>
+        <v>178.8</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1315,22 +1315,22 @@
         <v>57</v>
       </c>
       <c r="C28" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D28" s="7">
-        <v>254.022105</v>
+        <v>255.591219</v>
       </c>
       <c r="E28" s="8">
-        <v>32720000</v>
+        <v>32480000</v>
       </c>
       <c r="F28" s="9">
         <v>0</v>
       </c>
       <c r="G28" s="8">
-        <v>8311603288.95</v>
+        <v>8301602797.12</v>
       </c>
       <c r="H28" s="8">
-        <v>253.9</v>
+        <v>258</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1341,10 +1341,10 @@
         <v>59</v>
       </c>
       <c r="C29" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D29" s="7">
-        <v>257.246475</v>
+        <v>46147</v>
+      </c>
+      <c r="D29" s="10">
+        <v>257.06127</v>
       </c>
       <c r="E29" s="8">
         <v>3200000</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="G29" s="8">
-        <v>823188719.77</v>
+        <v>822596065.17</v>
       </c>
       <c r="H29" s="8">
-        <v>257.6</v>
+        <v>257.5</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1367,10 +1367,10 @@
         <v>61</v>
       </c>
       <c r="C30" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D30" s="7">
-        <v>117.715942</v>
+        <v>118.621413</v>
       </c>
       <c r="E30" s="8">
         <v>440000</v>
@@ -1379,10 +1379,10 @@
         <v>0</v>
       </c>
       <c r="G30" s="8">
-        <v>51795014.65</v>
+        <v>52193421.51</v>
       </c>
       <c r="H30" s="8">
-        <v>117.7</v>
+        <v>123.35</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1393,10 +1393,10 @@
         <v>63</v>
       </c>
       <c r="C31" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D31" s="7">
-        <v>182.237306</v>
+        <v>180.773244</v>
       </c>
       <c r="E31" s="8">
         <v>400000</v>
@@ -1405,10 +1405,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="8">
-        <v>72894922.3</v>
+        <v>72309297.75</v>
       </c>
       <c r="H31" s="8">
-        <v>181.8</v>
+        <v>181.05</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1419,10 +1419,10 @@
         <v>65</v>
       </c>
       <c r="C32" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D32" s="7">
-        <v>49.278847</v>
+        <v>48.691566</v>
       </c>
       <c r="E32" s="8">
         <v>1200000</v>
@@ -1431,10 +1431,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="8">
-        <v>59134616.48</v>
+        <v>58429879.29</v>
       </c>
       <c r="H32" s="8">
-        <v>49.25</v>
+        <v>48.66</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1445,10 +1445,10 @@
         <v>67</v>
       </c>
       <c r="C33" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D33" s="7">
-        <v>1213.745987</v>
+        <v>1215.061727</v>
       </c>
       <c r="E33" s="8">
         <v>560000</v>
@@ -1457,10 +1457,10 @@
         <v>0</v>
       </c>
       <c r="G33" s="8">
-        <v>679697752.53</v>
+        <v>680434567.04</v>
       </c>
       <c r="H33" s="8">
-        <v>1215.5</v>
+        <v>1216.5</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -1471,10 +1471,10 @@
         <v>69</v>
       </c>
       <c r="C34" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="D34" s="7">
-        <v>187.146577</v>
+        <v>185.331861</v>
       </c>
       <c r="E34" s="8">
         <v>680000</v>
@@ -1483,10 +1483,10 @@
         <v>0</v>
       </c>
       <c r="G34" s="8">
-        <v>127259672.31</v>
+        <v>126025665.67</v>
       </c>
       <c r="H34" s="8">
-        <v>187.2</v>
+        <v>185.3</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -1497,10 +1497,10 @@
         <v>71</v>
       </c>
       <c r="C35" s="6">
-        <v>46146</v>
-      </c>
-      <c r="D35" s="7">
-        <v>1214.892382</v>
+        <v>46147</v>
+      </c>
+      <c r="D35" s="10">
+        <v>1216.20383</v>
       </c>
       <c r="E35" s="8">
         <v>6680000</v>
@@ -1509,10 +1509,10 @@
         <v>0</v>
       </c>
       <c r="G35" s="8">
-        <v>8115481108.59</v>
+        <v>8124241585.13</v>
       </c>
       <c r="H35" s="8">
-        <v>1216.5</v>
+        <v>1218</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>05.05.2026 18:25:30</t>
+    <t>06.05.2026 18:20:11</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -743,10 +743,10 @@
         <v>13</v>
       </c>
       <c r="C6" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D6" s="7">
-        <v>45.628759</v>
+        <v>45.666254</v>
       </c>
       <c r="E6" s="8">
         <v>58000000</v>
@@ -755,10 +755,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="8">
-        <v>2646468042.49</v>
+        <v>2648642737.9</v>
       </c>
       <c r="H6" s="8">
-        <v>45.71</v>
+        <v>45.66</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -769,10 +769,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D7" s="7">
-        <v>38.248772</v>
+        <v>38.437878</v>
       </c>
       <c r="E7" s="8">
         <v>14400000</v>
@@ -781,10 +781,10 @@
         <v>0</v>
       </c>
       <c r="G7" s="8">
-        <v>550782317.86</v>
+        <v>553505448.42</v>
       </c>
       <c r="H7" s="8">
-        <v>38.35</v>
+        <v>38.42</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -795,10 +795,10 @@
         <v>17</v>
       </c>
       <c r="C8" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D8" s="7">
-        <v>39.555807</v>
+        <v>39.938036</v>
       </c>
       <c r="E8" s="8">
         <v>33700000</v>
@@ -807,10 +807,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="8">
-        <v>1333030696.37</v>
+        <v>1345911805.73</v>
       </c>
       <c r="H8" s="8">
-        <v>39.58</v>
+        <v>39.95</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -821,10 +821,10 @@
         <v>19</v>
       </c>
       <c r="C9" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D9" s="7">
-        <v>56.413173</v>
+        <v>46148</v>
+      </c>
+      <c r="D9" s="10">
+        <v>56.47212</v>
       </c>
       <c r="E9" s="8">
         <v>2550000</v>
@@ -833,10 +833,10 @@
         <v>0</v>
       </c>
       <c r="G9" s="8">
-        <v>143853590.45</v>
+        <v>144003906.88</v>
       </c>
       <c r="H9" s="8">
-        <v>56.46</v>
+        <v>56.54</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -847,10 +847,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D10" s="7">
-        <v>367.578034</v>
+        <v>370.494106</v>
       </c>
       <c r="E10" s="8">
         <v>150000</v>
@@ -859,10 +859,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="8">
-        <v>55136705.15</v>
+        <v>55574115.92</v>
       </c>
       <c r="H10" s="8">
-        <v>368.2</v>
+        <v>370.9</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -873,10 +873,10 @@
         <v>23</v>
       </c>
       <c r="C11" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D11" s="10">
-        <v>554.96134</v>
+        <v>46148</v>
+      </c>
+      <c r="D11" s="7">
+        <v>558.267049</v>
       </c>
       <c r="E11" s="8">
         <v>47850000</v>
@@ -885,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="G11" s="8">
-        <v>26554900132.88</v>
+        <v>26713078283.92</v>
       </c>
       <c r="H11" s="8">
-        <v>555</v>
+        <v>558.5</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -899,10 +899,10 @@
         <v>25</v>
       </c>
       <c r="C12" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D12" s="7">
-        <v>662.201349</v>
+        <v>661.886826</v>
       </c>
       <c r="E12" s="8">
         <v>75300000</v>
@@ -911,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="G12" s="8">
-        <v>49863761546.18</v>
+        <v>49840078003.79</v>
       </c>
       <c r="H12" s="8">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -925,10 +925,10 @@
         <v>27</v>
       </c>
       <c r="C13" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D13" s="7">
-        <v>4210.073262</v>
+        <v>4214.350775</v>
       </c>
       <c r="E13" s="8">
         <v>258000</v>
@@ -937,7 +937,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="8">
-        <v>1086198901.49</v>
+        <v>1087302499.91</v>
       </c>
       <c r="H13" s="8">
         <v>4239</v>
@@ -951,10 +951,10 @@
         <v>29</v>
       </c>
       <c r="C14" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D14" s="7">
-        <v>667.500242</v>
+        <v>667.631303</v>
       </c>
       <c r="E14" s="8">
         <v>113800000</v>
@@ -963,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="8">
-        <v>75961527530.8</v>
+        <v>75976442227.91</v>
       </c>
       <c r="H14" s="8">
-        <v>700</v>
+        <v>702.25</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -977,10 +977,10 @@
         <v>31</v>
       </c>
       <c r="C15" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D15" s="7">
-        <v>551.561422</v>
+        <v>549.234165</v>
       </c>
       <c r="E15" s="8">
         <v>33450000</v>
@@ -989,10 +989,10 @@
         <v>0</v>
       </c>
       <c r="G15" s="8">
-        <v>18449729555.43</v>
+        <v>18371882830.82</v>
       </c>
       <c r="H15" s="8">
-        <v>553.5</v>
+        <v>553</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1003,22 +1003,22 @@
         <v>33</v>
       </c>
       <c r="C16" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D16" s="7">
-        <v>25.467999</v>
+        <v>25.975645</v>
       </c>
       <c r="E16" s="8">
-        <v>12300000</v>
+        <v>10800000</v>
       </c>
       <c r="F16" s="9">
         <v>0</v>
       </c>
       <c r="G16" s="8">
-        <v>313256381.86</v>
+        <v>280536961.51</v>
       </c>
       <c r="H16" s="8">
-        <v>25.53</v>
+        <v>25.99</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1029,10 +1029,10 @@
         <v>35</v>
       </c>
       <c r="C17" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D17" s="7">
-        <v>45.654867</v>
+        <v>46148</v>
+      </c>
+      <c r="D17" s="10">
+        <v>45.70178</v>
       </c>
       <c r="E17" s="8">
         <v>1625000</v>
@@ -1041,10 +1041,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="8">
-        <v>74189159.02</v>
+        <v>74265393.16</v>
       </c>
       <c r="H17" s="8">
-        <v>45.71</v>
+        <v>45.74</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1055,10 +1055,10 @@
         <v>37</v>
       </c>
       <c r="C18" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D18" s="7">
-        <v>73.200476</v>
+        <v>73.640251</v>
       </c>
       <c r="E18" s="8">
         <v>1140000</v>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="G18" s="8">
-        <v>83448542.88</v>
+        <v>83949886.67</v>
       </c>
       <c r="H18" s="8">
-        <v>73.9</v>
+        <v>74.02</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1081,10 +1081,10 @@
         <v>39</v>
       </c>
       <c r="C19" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D19" s="7">
-        <v>85.154624</v>
+        <v>85.941833</v>
       </c>
       <c r="E19" s="8">
         <v>1155000</v>
@@ -1093,10 +1093,10 @@
         <v>0</v>
       </c>
       <c r="G19" s="8">
-        <v>98353590.45</v>
+        <v>99262817.64</v>
       </c>
       <c r="H19" s="8">
-        <v>84.96</v>
+        <v>85.56</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1107,10 +1107,10 @@
         <v>41</v>
       </c>
       <c r="C20" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D20" s="7">
-        <v>51.826825</v>
+        <v>52.641829</v>
       </c>
       <c r="E20" s="8">
         <v>2985000</v>
@@ -1119,10 +1119,10 @@
         <v>0</v>
       </c>
       <c r="G20" s="8">
-        <v>154703071.33</v>
+        <v>157135858.44</v>
       </c>
       <c r="H20" s="8">
-        <v>52.34</v>
+        <v>51.48</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1133,10 +1133,10 @@
         <v>43</v>
       </c>
       <c r="C21" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D21" s="10">
-        <v>166.62966</v>
+        <v>46148</v>
+      </c>
+      <c r="D21" s="7">
+        <v>169.679913</v>
       </c>
       <c r="E21" s="8">
         <v>600000</v>
@@ -1145,10 +1145,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="8">
-        <v>99977795.85</v>
+        <v>101807947.87</v>
       </c>
       <c r="H21" s="8">
-        <v>169.9</v>
+        <v>169.55</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1159,22 +1159,22 @@
         <v>45</v>
       </c>
       <c r="C22" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D22" s="7">
-        <v>213.702668</v>
+        <v>215.709463</v>
       </c>
       <c r="E22" s="8">
-        <v>131200000</v>
+        <v>128400000</v>
       </c>
       <c r="F22" s="9">
         <v>0</v>
       </c>
       <c r="G22" s="8">
-        <v>28037790104.13</v>
+        <v>27697095065.69</v>
       </c>
       <c r="H22" s="8">
-        <v>214</v>
+        <v>215.65</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1185,22 +1185,22 @@
         <v>47</v>
       </c>
       <c r="C23" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D23" s="7">
-        <v>193.704674</v>
+        <v>193.866394</v>
       </c>
       <c r="E23" s="8">
-        <v>197400000</v>
+        <v>195880000</v>
       </c>
       <c r="F23" s="9">
         <v>0</v>
       </c>
       <c r="G23" s="8">
-        <v>38237302600.62</v>
+        <v>37974549308.44</v>
       </c>
       <c r="H23" s="8">
-        <v>196.4</v>
+        <v>193.95</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1211,10 +1211,10 @@
         <v>49</v>
       </c>
       <c r="C24" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D24" s="7">
-        <v>197.090295</v>
+        <v>46148</v>
+      </c>
+      <c r="D24" s="10">
+        <v>199.81259</v>
       </c>
       <c r="E24" s="8">
         <v>320000</v>
@@ -1223,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="G24" s="8">
-        <v>63068894.34</v>
+        <v>63940028.83</v>
       </c>
       <c r="H24" s="8">
-        <v>197.15</v>
+        <v>200</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1237,10 +1237,10 @@
         <v>51</v>
       </c>
       <c r="C25" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D25" s="7">
-        <v>123.087418</v>
+        <v>123.608584</v>
       </c>
       <c r="E25" s="8">
         <v>600000</v>
@@ -1249,10 +1249,10 @@
         <v>0</v>
       </c>
       <c r="G25" s="8">
-        <v>73852451</v>
+        <v>74165150.62</v>
       </c>
       <c r="H25" s="8">
-        <v>122.25</v>
+        <v>124.15</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1263,10 +1263,10 @@
         <v>53</v>
       </c>
       <c r="C26" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D26" s="7">
-        <v>676.957873</v>
+        <v>681.132932</v>
       </c>
       <c r="E26" s="8">
         <v>152040000</v>
@@ -1275,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="G26" s="8">
-        <v>102924675044.16</v>
+        <v>103559451019.69</v>
       </c>
       <c r="H26" s="8">
-        <v>704.5</v>
+        <v>703.5</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1289,22 +1289,22 @@
         <v>55</v>
       </c>
       <c r="C27" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D27" s="7">
-        <v>176.098935</v>
+        <v>177.584872</v>
       </c>
       <c r="E27" s="8">
-        <v>9400000</v>
+        <v>9760000</v>
       </c>
       <c r="F27" s="9">
         <v>0</v>
       </c>
       <c r="G27" s="8">
-        <v>1655329986.14</v>
+        <v>1733228354.78</v>
       </c>
       <c r="H27" s="8">
-        <v>178.8</v>
+        <v>177.8</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1315,22 +1315,22 @@
         <v>57</v>
       </c>
       <c r="C28" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D28" s="7">
-        <v>255.591219</v>
+        <v>257.438068</v>
       </c>
       <c r="E28" s="8">
-        <v>32480000</v>
+        <v>32960000</v>
       </c>
       <c r="F28" s="9">
         <v>0</v>
       </c>
       <c r="G28" s="8">
-        <v>8301602797.12</v>
+        <v>8485158722.16</v>
       </c>
       <c r="H28" s="8">
-        <v>258</v>
+        <v>257.6</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1341,10 +1341,10 @@
         <v>59</v>
       </c>
       <c r="C29" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D29" s="10">
-        <v>257.06127</v>
+        <v>258.33443</v>
       </c>
       <c r="E29" s="8">
         <v>3200000</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="G29" s="8">
-        <v>822596065.17</v>
+        <v>826670176.5</v>
       </c>
       <c r="H29" s="8">
-        <v>257.5</v>
+        <v>259.7</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1367,10 +1367,10 @@
         <v>61</v>
       </c>
       <c r="C30" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D30" s="7">
-        <v>118.621413</v>
+        <v>122.132712</v>
       </c>
       <c r="E30" s="8">
         <v>440000</v>
@@ -1379,10 +1379,10 @@
         <v>0</v>
       </c>
       <c r="G30" s="8">
-        <v>52193421.51</v>
+        <v>53738393.37</v>
       </c>
       <c r="H30" s="8">
-        <v>123.35</v>
+        <v>127.45</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1393,10 +1393,10 @@
         <v>63</v>
       </c>
       <c r="C31" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D31" s="7">
-        <v>180.773244</v>
+        <v>183.097235</v>
       </c>
       <c r="E31" s="8">
         <v>400000</v>
@@ -1405,10 +1405,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="8">
-        <v>72309297.75</v>
+        <v>73238894.11</v>
       </c>
       <c r="H31" s="8">
-        <v>181.05</v>
+        <v>183.1</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1419,10 +1419,10 @@
         <v>65</v>
       </c>
       <c r="C32" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D32" s="7">
-        <v>48.691566</v>
+        <v>49.088202</v>
       </c>
       <c r="E32" s="8">
         <v>1200000</v>
@@ -1431,10 +1431,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="8">
-        <v>58429879.29</v>
+        <v>58905842.89</v>
       </c>
       <c r="H32" s="8">
-        <v>48.66</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1445,10 +1445,10 @@
         <v>67</v>
       </c>
       <c r="C33" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D33" s="7">
-        <v>1215.061727</v>
+        <v>1216.380048</v>
       </c>
       <c r="E33" s="8">
         <v>560000</v>
@@ -1457,10 +1457,10 @@
         <v>0</v>
       </c>
       <c r="G33" s="8">
-        <v>680434567.04</v>
+        <v>681172826.77</v>
       </c>
       <c r="H33" s="8">
-        <v>1216.5</v>
+        <v>1217.5</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -1471,10 +1471,10 @@
         <v>69</v>
       </c>
       <c r="C34" s="6">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="D34" s="7">
-        <v>185.331861</v>
+        <v>188.382508</v>
       </c>
       <c r="E34" s="8">
         <v>680000</v>
@@ -1483,10 +1483,10 @@
         <v>0</v>
       </c>
       <c r="G34" s="8">
-        <v>126025665.67</v>
+        <v>128100105.26</v>
       </c>
       <c r="H34" s="8">
-        <v>185.3</v>
+        <v>188.7</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -1497,10 +1497,10 @@
         <v>71</v>
       </c>
       <c r="C35" s="6">
-        <v>46147</v>
-      </c>
-      <c r="D35" s="10">
-        <v>1216.20383</v>
+        <v>46148</v>
+      </c>
+      <c r="D35" s="7">
+        <v>1217.516617</v>
       </c>
       <c r="E35" s="8">
         <v>6680000</v>
@@ -1509,10 +1509,10 @@
         <v>0</v>
       </c>
       <c r="G35" s="8">
-        <v>8124241585.13</v>
+        <v>8133010999.27</v>
       </c>
       <c r="H35" s="8">
-        <v>1218</v>
+        <v>1219</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>06.05.2026 18:20:11</t>
+    <t>07.05.2026 18:22:57</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -743,10 +743,10 @@
         <v>13</v>
       </c>
       <c r="C6" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D6" s="7">
-        <v>45.666254</v>
+        <v>47.706149</v>
       </c>
       <c r="E6" s="8">
         <v>58000000</v>
@@ -755,10 +755,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="8">
-        <v>2648642737.9</v>
+        <v>2766956658.17</v>
       </c>
       <c r="H6" s="8">
-        <v>45.66</v>
+        <v>48.49</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -769,10 +769,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D7" s="7">
-        <v>38.437878</v>
+        <v>39.365126</v>
       </c>
       <c r="E7" s="8">
         <v>14400000</v>
@@ -781,10 +781,10 @@
         <v>0</v>
       </c>
       <c r="G7" s="8">
-        <v>553505448.42</v>
+        <v>566857807.21</v>
       </c>
       <c r="H7" s="8">
-        <v>38.42</v>
+        <v>39.41</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -795,10 +795,10 @@
         <v>17</v>
       </c>
       <c r="C8" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D8" s="7">
-        <v>39.938036</v>
+        <v>41.234692</v>
       </c>
       <c r="E8" s="8">
         <v>33700000</v>
@@ -807,10 +807,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="8">
-        <v>1345911805.73</v>
+        <v>1389609125.86</v>
       </c>
       <c r="H8" s="8">
-        <v>39.95</v>
+        <v>41.31</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -821,10 +821,10 @@
         <v>19</v>
       </c>
       <c r="C9" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D9" s="10">
-        <v>56.47212</v>
+        <v>46149</v>
+      </c>
+      <c r="D9" s="7">
+        <v>56.532282</v>
       </c>
       <c r="E9" s="8">
         <v>2550000</v>
@@ -833,10 +833,10 @@
         <v>0</v>
       </c>
       <c r="G9" s="8">
-        <v>144003906.88</v>
+        <v>144157319.25</v>
       </c>
       <c r="H9" s="8">
-        <v>56.54</v>
+        <v>56.56</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -847,22 +847,22 @@
         <v>21</v>
       </c>
       <c r="C10" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D10" s="7">
-        <v>370.494106</v>
+        <v>382.313347</v>
       </c>
       <c r="E10" s="8">
-        <v>150000</v>
+        <v>135000</v>
       </c>
       <c r="F10" s="9">
         <v>0</v>
       </c>
       <c r="G10" s="8">
-        <v>55574115.92</v>
+        <v>51612301.9</v>
       </c>
       <c r="H10" s="8">
-        <v>370.9</v>
+        <v>380.2</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -873,10 +873,10 @@
         <v>23</v>
       </c>
       <c r="C11" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D11" s="7">
-        <v>558.267049</v>
+        <v>572.594063</v>
       </c>
       <c r="E11" s="8">
         <v>47850000</v>
@@ -885,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="G11" s="8">
-        <v>26713078283.92</v>
+        <v>27398625935.68</v>
       </c>
       <c r="H11" s="8">
-        <v>558.5</v>
+        <v>574.75</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -899,22 +899,22 @@
         <v>25</v>
       </c>
       <c r="C12" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D12" s="7">
-        <v>661.886826</v>
+        <v>693.904945</v>
       </c>
       <c r="E12" s="8">
-        <v>75300000</v>
+        <v>74800000</v>
       </c>
       <c r="F12" s="9">
         <v>0</v>
       </c>
       <c r="G12" s="8">
-        <v>49840078003.79</v>
+        <v>51904089858.7</v>
       </c>
       <c r="H12" s="8">
-        <v>665</v>
+        <v>695.75</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -925,22 +925,22 @@
         <v>27</v>
       </c>
       <c r="C13" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D13" s="7">
-        <v>4214.350775</v>
+        <v>4214.246842</v>
       </c>
       <c r="E13" s="8">
-        <v>258000</v>
+        <v>266000</v>
       </c>
       <c r="F13" s="9">
         <v>0</v>
       </c>
       <c r="G13" s="8">
-        <v>1087302499.91</v>
+        <v>1120989660.04</v>
       </c>
       <c r="H13" s="8">
-        <v>4239</v>
+        <v>4238</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -951,10 +951,10 @@
         <v>29</v>
       </c>
       <c r="C14" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D14" s="7">
-        <v>667.631303</v>
+        <v>683.200857</v>
       </c>
       <c r="E14" s="8">
         <v>113800000</v>
@@ -963,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="8">
-        <v>75976442227.91</v>
+        <v>77748257472.22</v>
       </c>
       <c r="H14" s="8">
-        <v>702.25</v>
+        <v>716</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -977,10 +977,10 @@
         <v>31</v>
       </c>
       <c r="C15" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D15" s="7">
-        <v>549.234165</v>
+        <v>563.077605</v>
       </c>
       <c r="E15" s="8">
         <v>33450000</v>
@@ -989,10 +989,10 @@
         <v>0</v>
       </c>
       <c r="G15" s="8">
-        <v>18371882830.82</v>
+        <v>18834945886.21</v>
       </c>
       <c r="H15" s="8">
-        <v>553</v>
+        <v>568</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1003,10 +1003,10 @@
         <v>33</v>
       </c>
       <c r="C16" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D16" s="7">
-        <v>25.975645</v>
+        <v>27.118333</v>
       </c>
       <c r="E16" s="8">
         <v>10800000</v>
@@ -1015,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="8">
-        <v>280536961.51</v>
+        <v>292877997.98</v>
       </c>
       <c r="H16" s="8">
-        <v>25.99</v>
+        <v>27.11</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1029,10 +1029,10 @@
         <v>35</v>
       </c>
       <c r="C17" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D17" s="10">
-        <v>45.70178</v>
+        <v>46149</v>
+      </c>
+      <c r="D17" s="7">
+        <v>45.748704</v>
       </c>
       <c r="E17" s="8">
         <v>1625000</v>
@@ -1041,10 +1041,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="8">
-        <v>74265393.16</v>
+        <v>74341643.76</v>
       </c>
       <c r="H17" s="8">
-        <v>45.74</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1055,10 +1055,10 @@
         <v>37</v>
       </c>
       <c r="C18" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D18" s="7">
-        <v>73.640251</v>
+        <v>74.585417</v>
       </c>
       <c r="E18" s="8">
         <v>1140000</v>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="G18" s="8">
-        <v>83949886.67</v>
+        <v>85027375.5</v>
       </c>
       <c r="H18" s="8">
-        <v>74.02</v>
+        <v>75.46</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1081,10 +1081,10 @@
         <v>39</v>
       </c>
       <c r="C19" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D19" s="7">
-        <v>85.941833</v>
+        <v>88.665536</v>
       </c>
       <c r="E19" s="8">
         <v>1155000</v>
@@ -1093,10 +1093,10 @@
         <v>0</v>
       </c>
       <c r="G19" s="8">
-        <v>99262817.64</v>
+        <v>102408694.01</v>
       </c>
       <c r="H19" s="8">
-        <v>85.56</v>
+        <v>88.86</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1107,10 +1107,10 @@
         <v>41</v>
       </c>
       <c r="C20" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D20" s="7">
-        <v>52.641829</v>
+        <v>54.315573</v>
       </c>
       <c r="E20" s="8">
         <v>2985000</v>
@@ -1119,10 +1119,10 @@
         <v>0</v>
       </c>
       <c r="G20" s="8">
-        <v>157135858.44</v>
+        <v>162131986.08</v>
       </c>
       <c r="H20" s="8">
-        <v>51.48</v>
+        <v>54.36</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1133,10 +1133,10 @@
         <v>43</v>
       </c>
       <c r="C21" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D21" s="7">
-        <v>169.679913</v>
+        <v>174.063814</v>
       </c>
       <c r="E21" s="8">
         <v>600000</v>
@@ -1145,10 +1145,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="8">
-        <v>101807947.87</v>
+        <v>104438288.68</v>
       </c>
       <c r="H21" s="8">
-        <v>169.55</v>
+        <v>174.5</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1159,22 +1159,22 @@
         <v>45</v>
       </c>
       <c r="C22" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D22" s="7">
-        <v>215.709463</v>
+        <v>222.785304</v>
       </c>
       <c r="E22" s="8">
-        <v>128400000</v>
+        <v>129480000</v>
       </c>
       <c r="F22" s="9">
         <v>0</v>
       </c>
       <c r="G22" s="8">
-        <v>27697095065.69</v>
+        <v>28846241173.93</v>
       </c>
       <c r="H22" s="8">
-        <v>215.65</v>
+        <v>223.6</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1185,22 +1185,22 @@
         <v>47</v>
       </c>
       <c r="C23" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D23" s="7">
-        <v>193.866394</v>
+        <v>202.640726</v>
       </c>
       <c r="E23" s="8">
-        <v>195880000</v>
+        <v>197800000</v>
       </c>
       <c r="F23" s="9">
         <v>0</v>
       </c>
       <c r="G23" s="8">
-        <v>37974549308.44</v>
+        <v>40082335566.86</v>
       </c>
       <c r="H23" s="8">
-        <v>193.95</v>
+        <v>203.35</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1211,10 +1211,10 @@
         <v>49</v>
       </c>
       <c r="C24" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D24" s="10">
-        <v>199.81259</v>
+        <v>206.55319</v>
       </c>
       <c r="E24" s="8">
         <v>320000</v>
@@ -1223,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="G24" s="8">
-        <v>63940028.83</v>
+        <v>66097020.67</v>
       </c>
       <c r="H24" s="8">
-        <v>200</v>
+        <v>206.6</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1237,10 +1237,10 @@
         <v>51</v>
       </c>
       <c r="C25" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D25" s="7">
-        <v>123.608584</v>
+        <v>126.962221</v>
       </c>
       <c r="E25" s="8">
         <v>600000</v>
@@ -1249,10 +1249,10 @@
         <v>0</v>
       </c>
       <c r="G25" s="8">
-        <v>74165150.62</v>
+        <v>76177332.33</v>
       </c>
       <c r="H25" s="8">
-        <v>124.15</v>
+        <v>127.6</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1263,10 +1263,10 @@
         <v>53</v>
       </c>
       <c r="C26" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D26" s="7">
-        <v>681.132932</v>
+        <v>46149</v>
+      </c>
+      <c r="D26" s="10">
+        <v>695.81497</v>
       </c>
       <c r="E26" s="8">
         <v>152040000</v>
@@ -1275,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="G26" s="8">
-        <v>103559451019.69</v>
+        <v>105791708057.45</v>
       </c>
       <c r="H26" s="8">
-        <v>703.5</v>
+        <v>719.5</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1289,22 +1289,22 @@
         <v>55</v>
       </c>
       <c r="C27" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D27" s="7">
-        <v>177.584872</v>
+        <v>179.137773</v>
       </c>
       <c r="E27" s="8">
-        <v>9760000</v>
+        <v>10240000</v>
       </c>
       <c r="F27" s="9">
         <v>0</v>
       </c>
       <c r="G27" s="8">
-        <v>1733228354.78</v>
+        <v>1834370798.54</v>
       </c>
       <c r="H27" s="8">
-        <v>177.8</v>
+        <v>179.35</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1315,22 +1315,22 @@
         <v>57</v>
       </c>
       <c r="C28" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D28" s="7">
-        <v>257.438068</v>
+        <v>260.539382</v>
       </c>
       <c r="E28" s="8">
-        <v>32960000</v>
+        <v>33400000</v>
       </c>
       <c r="F28" s="9">
         <v>0</v>
       </c>
       <c r="G28" s="8">
-        <v>8485158722.16</v>
+        <v>8702015347.42</v>
       </c>
       <c r="H28" s="8">
-        <v>257.6</v>
+        <v>255.1</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1341,10 +1341,10 @@
         <v>59</v>
       </c>
       <c r="C29" s="6">
-        <v>46148</v>
-      </c>
-      <c r="D29" s="10">
-        <v>258.33443</v>
+        <v>46149</v>
+      </c>
+      <c r="D29" s="7">
+        <v>264.572342</v>
       </c>
       <c r="E29" s="8">
         <v>3200000</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="G29" s="8">
-        <v>826670176.5</v>
+        <v>846631493</v>
       </c>
       <c r="H29" s="8">
-        <v>259.7</v>
+        <v>265.5</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1367,10 +1367,10 @@
         <v>61</v>
       </c>
       <c r="C30" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D30" s="7">
-        <v>122.132712</v>
+        <v>125.120458</v>
       </c>
       <c r="E30" s="8">
         <v>440000</v>
@@ -1379,10 +1379,10 @@
         <v>0</v>
       </c>
       <c r="G30" s="8">
-        <v>53738393.37</v>
+        <v>55053001.7</v>
       </c>
       <c r="H30" s="8">
-        <v>127.45</v>
+        <v>140.05</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1393,10 +1393,10 @@
         <v>63</v>
       </c>
       <c r="C31" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D31" s="7">
-        <v>183.097235</v>
+        <v>189.004597</v>
       </c>
       <c r="E31" s="8">
         <v>400000</v>
@@ -1405,10 +1405,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="8">
-        <v>73238894.11</v>
+        <v>75601838.85</v>
       </c>
       <c r="H31" s="8">
-        <v>183.1</v>
+        <v>189.05</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1419,10 +1419,10 @@
         <v>65</v>
       </c>
       <c r="C32" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D32" s="7">
-        <v>49.088202</v>
+        <v>50.702467</v>
       </c>
       <c r="E32" s="8">
         <v>1200000</v>
@@ -1431,10 +1431,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="8">
-        <v>58905842.89</v>
+        <v>60842959.9</v>
       </c>
       <c r="H32" s="8">
-        <v>48.98</v>
+        <v>50.66</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1445,22 +1445,22 @@
         <v>67</v>
       </c>
       <c r="C33" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D33" s="7">
-        <v>1216.380048</v>
+        <v>1217.697948</v>
       </c>
       <c r="E33" s="8">
-        <v>560000</v>
+        <v>600000</v>
       </c>
       <c r="F33" s="9">
         <v>0</v>
       </c>
       <c r="G33" s="8">
-        <v>681172826.77</v>
+        <v>730618768.64</v>
       </c>
       <c r="H33" s="8">
-        <v>1217.5</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -1471,10 +1471,10 @@
         <v>69</v>
       </c>
       <c r="C34" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D34" s="7">
-        <v>188.382508</v>
+        <v>194.616092</v>
       </c>
       <c r="E34" s="8">
         <v>680000</v>
@@ -1483,10 +1483,10 @@
         <v>0</v>
       </c>
       <c r="G34" s="8">
-        <v>128100105.26</v>
+        <v>132338942.75</v>
       </c>
       <c r="H34" s="8">
-        <v>188.7</v>
+        <v>194.7</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -1497,10 +1497,10 @@
         <v>71</v>
       </c>
       <c r="C35" s="6">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="D35" s="7">
-        <v>1217.516617</v>
+        <v>1218.831074</v>
       </c>
       <c r="E35" s="8">
         <v>6680000</v>
@@ -1509,10 +1509,10 @@
         <v>0</v>
       </c>
       <c r="G35" s="8">
-        <v>8133010999.27</v>
+        <v>8141791575.35</v>
       </c>
       <c r="H35" s="8">
-        <v>1219</v>
+        <v>1220.5</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>07.05.2026 18:22:57</t>
+    <t>08.05.2026 18:20:22</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -743,10 +743,10 @@
         <v>13</v>
       </c>
       <c r="C6" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D6" s="7">
-        <v>47.706149</v>
+        <v>48.431554</v>
       </c>
       <c r="E6" s="8">
         <v>58000000</v>
@@ -755,10 +755,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="8">
-        <v>2766956658.17</v>
+        <v>2809030125.48</v>
       </c>
       <c r="H6" s="8">
-        <v>48.49</v>
+        <v>48.41</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -769,10 +769,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D7" s="7">
-        <v>39.365126</v>
+        <v>46150</v>
+      </c>
+      <c r="D7" s="10">
+        <v>39.28293</v>
       </c>
       <c r="E7" s="8">
         <v>14400000</v>
@@ -781,10 +781,10 @@
         <v>0</v>
       </c>
       <c r="G7" s="8">
-        <v>566857807.21</v>
+        <v>565674189.15</v>
       </c>
       <c r="H7" s="8">
-        <v>39.41</v>
+        <v>39.18</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -795,10 +795,10 @@
         <v>17</v>
       </c>
       <c r="C8" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D8" s="7">
-        <v>41.234692</v>
+        <v>41.316274</v>
       </c>
       <c r="E8" s="8">
         <v>33700000</v>
@@ -807,10 +807,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="8">
-        <v>1389609125.86</v>
+        <v>1392358419.87</v>
       </c>
       <c r="H8" s="8">
-        <v>41.31</v>
+        <v>41.29</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -821,10 +821,10 @@
         <v>19</v>
       </c>
       <c r="C9" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D9" s="7">
-        <v>56.532282</v>
+        <v>56.592753</v>
       </c>
       <c r="E9" s="8">
         <v>2550000</v>
@@ -833,10 +833,10 @@
         <v>0</v>
       </c>
       <c r="G9" s="8">
-        <v>144157319.25</v>
+        <v>144311520.66</v>
       </c>
       <c r="H9" s="8">
-        <v>56.56</v>
+        <v>56.8</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -847,10 +847,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D10" s="7">
-        <v>382.313347</v>
+        <v>379.753769</v>
       </c>
       <c r="E10" s="8">
         <v>135000</v>
@@ -859,7 +859,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="8">
-        <v>51612301.9</v>
+        <v>51266758.75</v>
       </c>
       <c r="H10" s="8">
         <v>380.2</v>
@@ -873,10 +873,10 @@
         <v>23</v>
       </c>
       <c r="C11" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D11" s="7">
-        <v>572.594063</v>
+        <v>580.434609</v>
       </c>
       <c r="E11" s="8">
         <v>47850000</v>
@@ -885,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="G11" s="8">
-        <v>27398625935.68</v>
+        <v>27773796057.38</v>
       </c>
       <c r="H11" s="8">
-        <v>574.75</v>
+        <v>583</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -899,10 +899,10 @@
         <v>25</v>
       </c>
       <c r="C12" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D12" s="7">
-        <v>693.904945</v>
+        <v>732.960823</v>
       </c>
       <c r="E12" s="8">
         <v>74800000</v>
@@ -911,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="G12" s="8">
-        <v>51904089858.7</v>
+        <v>54825469553.02</v>
       </c>
       <c r="H12" s="8">
-        <v>695.75</v>
+        <v>734.25</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -925,10 +925,10 @@
         <v>27</v>
       </c>
       <c r="C13" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D13" s="7">
-        <v>4214.246842</v>
+        <v>46150</v>
+      </c>
+      <c r="D13" s="10">
+        <v>4217.91859</v>
       </c>
       <c r="E13" s="8">
         <v>266000</v>
@@ -937,10 +937,10 @@
         <v>0</v>
       </c>
       <c r="G13" s="8">
-        <v>1120989660.04</v>
+        <v>1121966345.02</v>
       </c>
       <c r="H13" s="8">
-        <v>4238</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -951,10 +951,10 @@
         <v>29</v>
       </c>
       <c r="C14" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D14" s="7">
-        <v>683.200857</v>
+        <v>689.736093</v>
       </c>
       <c r="E14" s="8">
         <v>113800000</v>
@@ -963,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="8">
-        <v>77748257472.22</v>
+        <v>78491967350.32</v>
       </c>
       <c r="H14" s="8">
-        <v>716</v>
+        <v>730</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -977,10 +977,10 @@
         <v>31</v>
       </c>
       <c r="C15" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D15" s="7">
-        <v>563.077605</v>
+        <v>571.910316</v>
       </c>
       <c r="E15" s="8">
         <v>33450000</v>
@@ -989,10 +989,10 @@
         <v>0</v>
       </c>
       <c r="G15" s="8">
-        <v>18834945886.21</v>
+        <v>19130400071.21</v>
       </c>
       <c r="H15" s="8">
-        <v>568</v>
+        <v>577.5</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1003,10 +1003,10 @@
         <v>33</v>
       </c>
       <c r="C16" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D16" s="7">
-        <v>27.118333</v>
+        <v>27.653654</v>
       </c>
       <c r="E16" s="8">
         <v>10800000</v>
@@ -1015,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="8">
-        <v>292877997.98</v>
+        <v>298659464.13</v>
       </c>
       <c r="H16" s="8">
-        <v>27.11</v>
+        <v>27.63</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1029,10 +1029,10 @@
         <v>35</v>
       </c>
       <c r="C17" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D17" s="7">
-        <v>45.748704</v>
+        <v>45.795704</v>
       </c>
       <c r="E17" s="8">
         <v>1625000</v>
@@ -1041,10 +1041,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="8">
-        <v>74341643.76</v>
+        <v>74418019.07</v>
       </c>
       <c r="H17" s="8">
-        <v>45.8</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1055,10 +1055,10 @@
         <v>37</v>
       </c>
       <c r="C18" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D18" s="7">
-        <v>74.585417</v>
+        <v>74.808795</v>
       </c>
       <c r="E18" s="8">
         <v>1140000</v>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="G18" s="8">
-        <v>85027375.5</v>
+        <v>85282026.81</v>
       </c>
       <c r="H18" s="8">
-        <v>75.46</v>
+        <v>74.64</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1081,10 +1081,10 @@
         <v>39</v>
       </c>
       <c r="C19" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D19" s="7">
-        <v>88.665536</v>
+        <v>88.894782</v>
       </c>
       <c r="E19" s="8">
         <v>1155000</v>
@@ -1093,10 +1093,10 @@
         <v>0</v>
       </c>
       <c r="G19" s="8">
-        <v>102408694.01</v>
+        <v>102673473.66</v>
       </c>
       <c r="H19" s="8">
-        <v>88.86</v>
+        <v>88.92</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1107,10 +1107,10 @@
         <v>41</v>
       </c>
       <c r="C20" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D20" s="7">
-        <v>54.315573</v>
+        <v>46150</v>
+      </c>
+      <c r="D20" s="10">
+        <v>54.60565</v>
       </c>
       <c r="E20" s="8">
         <v>2985000</v>
@@ -1119,10 +1119,10 @@
         <v>0</v>
       </c>
       <c r="G20" s="8">
-        <v>162131986.08</v>
+        <v>162997866.74</v>
       </c>
       <c r="H20" s="8">
-        <v>54.36</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1133,10 +1133,10 @@
         <v>43</v>
       </c>
       <c r="C21" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D21" s="7">
-        <v>174.063814</v>
+        <v>177.508275</v>
       </c>
       <c r="E21" s="8">
         <v>600000</v>
@@ -1145,10 +1145,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="8">
-        <v>104438288.68</v>
+        <v>106504964.74</v>
       </c>
       <c r="H21" s="8">
-        <v>174.5</v>
+        <v>177.6</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1159,22 +1159,22 @@
         <v>45</v>
       </c>
       <c r="C22" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D22" s="7">
-        <v>222.785304</v>
+        <v>223.333959</v>
       </c>
       <c r="E22" s="8">
-        <v>129480000</v>
+        <v>129520000</v>
       </c>
       <c r="F22" s="9">
         <v>0</v>
       </c>
       <c r="G22" s="8">
-        <v>28846241173.93</v>
+        <v>28926214378.97</v>
       </c>
       <c r="H22" s="8">
-        <v>223.6</v>
+        <v>223</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1185,22 +1185,22 @@
         <v>47</v>
       </c>
       <c r="C23" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D23" s="7">
-        <v>202.640726</v>
+        <v>205.785292</v>
       </c>
       <c r="E23" s="8">
-        <v>197800000</v>
+        <v>200400000</v>
       </c>
       <c r="F23" s="9">
         <v>0</v>
       </c>
       <c r="G23" s="8">
-        <v>40082335566.86</v>
+        <v>41239372529.66</v>
       </c>
       <c r="H23" s="8">
-        <v>203.35</v>
+        <v>206.15</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1211,10 +1211,10 @@
         <v>49</v>
       </c>
       <c r="C24" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D24" s="10">
-        <v>206.55319</v>
+        <v>46150</v>
+      </c>
+      <c r="D24" s="7">
+        <v>208.684461</v>
       </c>
       <c r="E24" s="8">
         <v>320000</v>
@@ -1223,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="G24" s="8">
-        <v>66097020.67</v>
+        <v>66779027.58</v>
       </c>
       <c r="H24" s="8">
-        <v>206.6</v>
+        <v>208.25</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1237,10 +1237,10 @@
         <v>51</v>
       </c>
       <c r="C25" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D25" s="7">
-        <v>126.962221</v>
+        <v>130.085841</v>
       </c>
       <c r="E25" s="8">
         <v>600000</v>
@@ -1249,10 +1249,10 @@
         <v>0</v>
       </c>
       <c r="G25" s="8">
-        <v>76177332.33</v>
+        <v>78051504.43</v>
       </c>
       <c r="H25" s="8">
-        <v>127.6</v>
+        <v>130.5</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1263,10 +1263,10 @@
         <v>53</v>
       </c>
       <c r="C26" s="6">
-        <v>46149</v>
-      </c>
-      <c r="D26" s="10">
-        <v>695.81497</v>
+        <v>46150</v>
+      </c>
+      <c r="D26" s="7">
+        <v>705.737256</v>
       </c>
       <c r="E26" s="8">
         <v>152040000</v>
@@ -1275,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="G26" s="8">
-        <v>105791708057.45</v>
+        <v>107300292410.95</v>
       </c>
       <c r="H26" s="8">
-        <v>719.5</v>
+        <v>730.75</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1289,10 +1289,10 @@
         <v>55</v>
       </c>
       <c r="C27" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D27" s="7">
-        <v>179.137773</v>
+        <v>181.162297</v>
       </c>
       <c r="E27" s="8">
         <v>10240000</v>
@@ -1301,10 +1301,10 @@
         <v>0</v>
       </c>
       <c r="G27" s="8">
-        <v>1834370798.54</v>
+        <v>1855101917.47</v>
       </c>
       <c r="H27" s="8">
-        <v>179.35</v>
+        <v>182</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1315,22 +1315,22 @@
         <v>57</v>
       </c>
       <c r="C28" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D28" s="7">
-        <v>260.539382</v>
+        <v>261.608299</v>
       </c>
       <c r="E28" s="8">
-        <v>33400000</v>
+        <v>32680000</v>
       </c>
       <c r="F28" s="9">
         <v>0</v>
       </c>
       <c r="G28" s="8">
-        <v>8702015347.42</v>
+        <v>8549359212.03</v>
       </c>
       <c r="H28" s="8">
-        <v>255.1</v>
+        <v>261.6</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1341,10 +1341,10 @@
         <v>59</v>
       </c>
       <c r="C29" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D29" s="7">
-        <v>264.572342</v>
+        <v>264.017316</v>
       </c>
       <c r="E29" s="8">
         <v>3200000</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="G29" s="8">
-        <v>846631493</v>
+        <v>844855410.86</v>
       </c>
       <c r="H29" s="8">
-        <v>265.5</v>
+        <v>263.5</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1367,10 +1367,10 @@
         <v>61</v>
       </c>
       <c r="C30" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D30" s="7">
-        <v>125.120458</v>
+        <v>127.765986</v>
       </c>
       <c r="E30" s="8">
         <v>440000</v>
@@ -1379,10 +1379,10 @@
         <v>0</v>
       </c>
       <c r="G30" s="8">
-        <v>55053001.7</v>
+        <v>56217033.73</v>
       </c>
       <c r="H30" s="8">
-        <v>140.05</v>
+        <v>127.5</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1393,10 +1393,10 @@
         <v>63</v>
       </c>
       <c r="C31" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D31" s="7">
-        <v>189.004597</v>
+        <v>190.595161</v>
       </c>
       <c r="E31" s="8">
         <v>400000</v>
@@ -1405,10 +1405,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="8">
-        <v>75601838.85</v>
+        <v>76238064.45</v>
       </c>
       <c r="H31" s="8">
-        <v>189.05</v>
+        <v>189.75</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1419,10 +1419,10 @@
         <v>65</v>
       </c>
       <c r="C32" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D32" s="7">
-        <v>50.702467</v>
+        <v>50.740184</v>
       </c>
       <c r="E32" s="8">
         <v>1200000</v>
@@ -1431,10 +1431,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="8">
-        <v>60842959.9</v>
+        <v>60888221.36</v>
       </c>
       <c r="H32" s="8">
-        <v>50.66</v>
+        <v>50.86</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1445,10 +1445,10 @@
         <v>67</v>
       </c>
       <c r="C33" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D33" s="7">
-        <v>1217.697948</v>
+        <v>1219.006981</v>
       </c>
       <c r="E33" s="8">
         <v>600000</v>
@@ -1457,10 +1457,10 @@
         <v>0</v>
       </c>
       <c r="G33" s="8">
-        <v>730618768.64</v>
+        <v>731404188.6</v>
       </c>
       <c r="H33" s="8">
-        <v>1219</v>
+        <v>1223.5</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -1471,10 +1471,10 @@
         <v>69</v>
       </c>
       <c r="C34" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D34" s="7">
-        <v>194.616092</v>
+        <v>195.745908</v>
       </c>
       <c r="E34" s="8">
         <v>680000</v>
@@ -1483,10 +1483,10 @@
         <v>0</v>
       </c>
       <c r="G34" s="8">
-        <v>132338942.75</v>
+        <v>133107217.73</v>
       </c>
       <c r="H34" s="8">
-        <v>194.7</v>
+        <v>195.35</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -1497,10 +1497,10 @@
         <v>71</v>
       </c>
       <c r="C35" s="6">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D35" s="7">
-        <v>1218.831074</v>
+        <v>1220.137904</v>
       </c>
       <c r="E35" s="8">
         <v>6680000</v>
@@ -1509,10 +1509,10 @@
         <v>0</v>
       </c>
       <c r="G35" s="8">
-        <v>8141791575.35</v>
+        <v>8150521198.26</v>
       </c>
       <c r="H35" s="8">
-        <v>1220.5</v>
+        <v>1224.5</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>08.05.2026 18:20:22</t>
+    <t>11.05.2026 18:28:36</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -743,10 +743,10 @@
         <v>13</v>
       </c>
       <c r="C6" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D6" s="7">
-        <v>48.431554</v>
+        <v>48.555556</v>
       </c>
       <c r="E6" s="8">
         <v>58000000</v>
@@ -755,10 +755,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="8">
-        <v>2809030125.48</v>
+        <v>2816222257.64</v>
       </c>
       <c r="H6" s="8">
-        <v>48.41</v>
+        <v>48.43</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -769,10 +769,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D7" s="10">
-        <v>39.28293</v>
+        <v>46153</v>
+      </c>
+      <c r="D7" s="7">
+        <v>39.656054</v>
       </c>
       <c r="E7" s="8">
         <v>14400000</v>
@@ -781,10 +781,10 @@
         <v>0</v>
       </c>
       <c r="G7" s="8">
-        <v>565674189.15</v>
+        <v>571047179.6</v>
       </c>
       <c r="H7" s="8">
-        <v>39.18</v>
+        <v>39.59</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -795,10 +795,10 @@
         <v>17</v>
       </c>
       <c r="C8" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D8" s="7">
-        <v>41.316274</v>
+        <v>46153</v>
+      </c>
+      <c r="D8" s="10">
+        <v>41.59754</v>
       </c>
       <c r="E8" s="8">
         <v>33700000</v>
@@ -807,10 +807,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="8">
-        <v>1392358419.87</v>
+        <v>1401837107.5</v>
       </c>
       <c r="H8" s="8">
-        <v>41.29</v>
+        <v>41.62</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -821,10 +821,10 @@
         <v>19</v>
       </c>
       <c r="C9" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D9" s="7">
-        <v>56.592753</v>
+        <v>56.772861</v>
       </c>
       <c r="E9" s="8">
         <v>2550000</v>
@@ -833,10 +833,10 @@
         <v>0</v>
       </c>
       <c r="G9" s="8">
-        <v>144311520.66</v>
+        <v>144770795.78</v>
       </c>
       <c r="H9" s="8">
-        <v>56.8</v>
+        <v>56.86</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -847,10 +847,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D10" s="7">
-        <v>379.753769</v>
+        <v>385.507462</v>
       </c>
       <c r="E10" s="8">
         <v>135000</v>
@@ -859,10 +859,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="8">
-        <v>51266758.75</v>
+        <v>52043507.42</v>
       </c>
       <c r="H10" s="8">
-        <v>380.2</v>
+        <v>385.9</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -873,10 +873,10 @@
         <v>23</v>
       </c>
       <c r="C11" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D11" s="7">
-        <v>580.434609</v>
+        <v>576.082494</v>
       </c>
       <c r="E11" s="8">
         <v>47850000</v>
@@ -885,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="G11" s="8">
-        <v>27773796057.38</v>
+        <v>27565547356.58</v>
       </c>
       <c r="H11" s="8">
-        <v>583</v>
+        <v>576</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -899,10 +899,10 @@
         <v>25</v>
       </c>
       <c r="C12" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D12" s="7">
-        <v>732.960823</v>
+        <v>725.040141</v>
       </c>
       <c r="E12" s="8">
         <v>74800000</v>
@@ -911,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="G12" s="8">
-        <v>54825469553.02</v>
+        <v>54233002525.78</v>
       </c>
       <c r="H12" s="8">
-        <v>734.25</v>
+        <v>724</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -925,10 +925,10 @@
         <v>27</v>
       </c>
       <c r="C13" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D13" s="10">
-        <v>4217.91859</v>
+        <v>46153</v>
+      </c>
+      <c r="D13" s="7">
+        <v>4223.528036</v>
       </c>
       <c r="E13" s="8">
         <v>266000</v>
@@ -937,10 +937,10 @@
         <v>0</v>
       </c>
       <c r="G13" s="8">
-        <v>1121966345.02</v>
+        <v>1123458457.65</v>
       </c>
       <c r="H13" s="8">
-        <v>4239</v>
+        <v>4244</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -951,10 +951,10 @@
         <v>29</v>
       </c>
       <c r="C14" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D14" s="7">
-        <v>689.736093</v>
+        <v>688.358128</v>
       </c>
       <c r="E14" s="8">
         <v>113800000</v>
@@ -963,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="8">
-        <v>78491967350.32</v>
+        <v>78335154942.13</v>
       </c>
       <c r="H14" s="8">
-        <v>730</v>
+        <v>722</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -977,10 +977,10 @@
         <v>31</v>
       </c>
       <c r="C15" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D15" s="7">
-        <v>571.910316</v>
+        <v>568.604455</v>
       </c>
       <c r="E15" s="8">
         <v>33450000</v>
@@ -989,10 +989,10 @@
         <v>0</v>
       </c>
       <c r="G15" s="8">
-        <v>19130400071.21</v>
+        <v>19019819003.86</v>
       </c>
       <c r="H15" s="8">
-        <v>577.5</v>
+        <v>575.25</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1003,10 +1003,10 @@
         <v>33</v>
       </c>
       <c r="C16" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D16" s="7">
-        <v>27.653654</v>
+        <v>27.743494</v>
       </c>
       <c r="E16" s="8">
         <v>10800000</v>
@@ -1015,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="8">
-        <v>298659464.13</v>
+        <v>299629737.5</v>
       </c>
       <c r="H16" s="8">
-        <v>27.63</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1029,10 +1029,10 @@
         <v>35</v>
       </c>
       <c r="C17" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D17" s="7">
-        <v>45.795704</v>
+        <v>45.936965</v>
       </c>
       <c r="E17" s="8">
         <v>1625000</v>
@@ -1041,10 +1041,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="8">
-        <v>74418019.07</v>
+        <v>74647568.42</v>
       </c>
       <c r="H17" s="8">
-        <v>45.94</v>
+        <v>45.99</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1055,10 +1055,10 @@
         <v>37</v>
       </c>
       <c r="C18" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D18" s="7">
-        <v>74.808795</v>
+        <v>75.873166</v>
       </c>
       <c r="E18" s="8">
         <v>1140000</v>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="G18" s="8">
-        <v>85282026.81</v>
+        <v>86495408.84</v>
       </c>
       <c r="H18" s="8">
-        <v>74.64</v>
+        <v>76.12</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1081,10 +1081,10 @@
         <v>39</v>
       </c>
       <c r="C19" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D19" s="7">
-        <v>88.894782</v>
+        <v>89.602903</v>
       </c>
       <c r="E19" s="8">
         <v>1155000</v>
@@ -1093,10 +1093,10 @@
         <v>0</v>
       </c>
       <c r="G19" s="8">
-        <v>102673473.66</v>
+        <v>103491353.43</v>
       </c>
       <c r="H19" s="8">
-        <v>88.92</v>
+        <v>89.42</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1107,10 +1107,10 @@
         <v>41</v>
       </c>
       <c r="C20" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D20" s="10">
-        <v>54.60565</v>
+        <v>46153</v>
+      </c>
+      <c r="D20" s="7">
+        <v>54.933002</v>
       </c>
       <c r="E20" s="8">
         <v>2985000</v>
@@ -1119,10 +1119,10 @@
         <v>0</v>
       </c>
       <c r="G20" s="8">
-        <v>162997866.74</v>
+        <v>163975012.36</v>
       </c>
       <c r="H20" s="8">
-        <v>54.6</v>
+        <v>54.96</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1133,10 +1133,10 @@
         <v>43</v>
       </c>
       <c r="C21" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D21" s="7">
-        <v>177.508275</v>
+        <v>177.743926</v>
       </c>
       <c r="E21" s="8">
         <v>600000</v>
@@ -1145,10 +1145,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="8">
-        <v>106504964.74</v>
+        <v>106646355.55</v>
       </c>
       <c r="H21" s="8">
-        <v>177.6</v>
+        <v>178.4</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1159,22 +1159,22 @@
         <v>45</v>
       </c>
       <c r="C22" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D22" s="7">
-        <v>223.333959</v>
+        <v>225.029498</v>
       </c>
       <c r="E22" s="8">
-        <v>129520000</v>
+        <v>129400000</v>
       </c>
       <c r="F22" s="9">
         <v>0</v>
       </c>
       <c r="G22" s="8">
-        <v>28926214378.97</v>
+        <v>29118817080.57</v>
       </c>
       <c r="H22" s="8">
-        <v>223</v>
+        <v>224.75</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1185,22 +1185,22 @@
         <v>47</v>
       </c>
       <c r="C23" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D23" s="7">
-        <v>205.785292</v>
+        <v>206.317286</v>
       </c>
       <c r="E23" s="8">
-        <v>200400000</v>
+        <v>203120000</v>
       </c>
       <c r="F23" s="9">
         <v>0</v>
       </c>
       <c r="G23" s="8">
-        <v>41239372529.66</v>
+        <v>41907167060.09</v>
       </c>
       <c r="H23" s="8">
-        <v>206.15</v>
+        <v>205.8</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1211,10 +1211,10 @@
         <v>49</v>
       </c>
       <c r="C24" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D24" s="7">
-        <v>208.684461</v>
+        <v>209.950072</v>
       </c>
       <c r="E24" s="8">
         <v>320000</v>
@@ -1223,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="G24" s="8">
-        <v>66779027.58</v>
+        <v>67184022.93</v>
       </c>
       <c r="H24" s="8">
-        <v>208.25</v>
+        <v>209.85</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1237,10 +1237,10 @@
         <v>51</v>
       </c>
       <c r="C25" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D25" s="7">
-        <v>130.085841</v>
+        <v>129.228103</v>
       </c>
       <c r="E25" s="8">
         <v>600000</v>
@@ -1249,10 +1249,10 @@
         <v>0</v>
       </c>
       <c r="G25" s="8">
-        <v>78051504.43</v>
+        <v>77536861.79</v>
       </c>
       <c r="H25" s="8">
-        <v>130.5</v>
+        <v>128</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1263,10 +1263,10 @@
         <v>53</v>
       </c>
       <c r="C26" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D26" s="7">
-        <v>705.737256</v>
+        <v>699.970335</v>
       </c>
       <c r="E26" s="8">
         <v>152040000</v>
@@ -1275,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="G26" s="8">
-        <v>107300292410.95</v>
+        <v>106423489732.26</v>
       </c>
       <c r="H26" s="8">
-        <v>730.75</v>
+        <v>723</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1289,10 +1289,10 @@
         <v>55</v>
       </c>
       <c r="C27" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D27" s="7">
-        <v>181.162297</v>
+        <v>185.167816</v>
       </c>
       <c r="E27" s="8">
         <v>10240000</v>
@@ -1301,10 +1301,10 @@
         <v>0</v>
       </c>
       <c r="G27" s="8">
-        <v>1855101917.47</v>
+        <v>1896118435.24</v>
       </c>
       <c r="H27" s="8">
-        <v>182</v>
+        <v>186.65</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1315,10 +1315,10 @@
         <v>57</v>
       </c>
       <c r="C28" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D28" s="7">
-        <v>261.608299</v>
+        <v>265.681737</v>
       </c>
       <c r="E28" s="8">
         <v>32680000</v>
@@ -1327,10 +1327,10 @@
         <v>0</v>
       </c>
       <c r="G28" s="8">
-        <v>8549359212.03</v>
+        <v>8682479155.27</v>
       </c>
       <c r="H28" s="8">
-        <v>261.6</v>
+        <v>267.3</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1341,10 +1341,10 @@
         <v>59</v>
       </c>
       <c r="C29" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D29" s="7">
-        <v>264.017316</v>
+        <v>266.504509</v>
       </c>
       <c r="E29" s="8">
         <v>3200000</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="G29" s="8">
-        <v>844855410.86</v>
+        <v>852814427.78</v>
       </c>
       <c r="H29" s="8">
-        <v>263.5</v>
+        <v>266.6</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1367,10 +1367,10 @@
         <v>61</v>
       </c>
       <c r="C30" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D30" s="7">
-        <v>127.765986</v>
+        <v>129.435578</v>
       </c>
       <c r="E30" s="8">
         <v>440000</v>
@@ -1379,10 +1379,10 @@
         <v>0</v>
       </c>
       <c r="G30" s="8">
-        <v>56217033.73</v>
+        <v>56951654.14</v>
       </c>
       <c r="H30" s="8">
-        <v>127.5</v>
+        <v>130</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1393,10 +1393,10 @@
         <v>63</v>
       </c>
       <c r="C31" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D31" s="7">
-        <v>190.595161</v>
+        <v>191.565764</v>
       </c>
       <c r="E31" s="8">
         <v>400000</v>
@@ -1405,10 +1405,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="8">
-        <v>76238064.45</v>
+        <v>76626305.69</v>
       </c>
       <c r="H31" s="8">
-        <v>189.75</v>
+        <v>191.5</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1419,10 +1419,10 @@
         <v>65</v>
       </c>
       <c r="C32" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D32" s="7">
-        <v>50.740184</v>
+        <v>50.845593</v>
       </c>
       <c r="E32" s="8">
         <v>1200000</v>
@@ -1431,10 +1431,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="8">
-        <v>60888221.36</v>
+        <v>61014711</v>
       </c>
       <c r="H32" s="8">
-        <v>50.86</v>
+        <v>50.96</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1445,10 +1445,10 @@
         <v>67</v>
       </c>
       <c r="C33" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D33" s="7">
-        <v>1219.006981</v>
+        <v>1222.945675</v>
       </c>
       <c r="E33" s="8">
         <v>600000</v>
@@ -1457,10 +1457,10 @@
         <v>0</v>
       </c>
       <c r="G33" s="8">
-        <v>731404188.6</v>
+        <v>733767405.25</v>
       </c>
       <c r="H33" s="8">
-        <v>1223.5</v>
+        <v>1224.5</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -1471,10 +1471,10 @@
         <v>69</v>
       </c>
       <c r="C34" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D34" s="7">
-        <v>195.745908</v>
+        <v>196.926357</v>
       </c>
       <c r="E34" s="8">
         <v>680000</v>
@@ -1483,10 +1483,10 @@
         <v>0</v>
       </c>
       <c r="G34" s="8">
-        <v>133107217.73</v>
+        <v>133909922.75</v>
       </c>
       <c r="H34" s="8">
-        <v>195.35</v>
+        <v>197.5</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -1497,10 +1497,10 @@
         <v>71</v>
       </c>
       <c r="C35" s="6">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D35" s="7">
-        <v>1220.137904</v>
+        <v>1224.063666</v>
       </c>
       <c r="E35" s="8">
         <v>6680000</v>
@@ -1509,10 +1509,10 @@
         <v>0</v>
       </c>
       <c r="G35" s="8">
-        <v>8150521198.26</v>
+        <v>8176745286.6</v>
       </c>
       <c r="H35" s="8">
-        <v>1224.5</v>
+        <v>1225.5</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>13.05.2026 10:29:19</t>
+    <t>14.05.2026 21:30:16</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -233,13 +233,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="###0.000000;-###0.000000;0"/>
     <numFmt numFmtId="166" formatCode="###0.00;-###0.00;0"/>
     <numFmt numFmtId="167" formatCode="###0;-###0;0"/>
     <numFmt numFmtId="168" formatCode="###0.00000;-###0.00000;0"/>
-    <numFmt numFmtId="169" formatCode="###0.0000;-###0.0000;0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -309,7 +308,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -335,9 +334,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -747,10 +743,10 @@
         <v>13</v>
       </c>
       <c r="C6" s="6">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="D6" s="7">
-        <v>47.321504</v>
+        <v>46.696462</v>
       </c>
       <c r="E6" s="8">
         <v>58000000</v>
@@ -759,10 +755,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="8">
-        <v>2744647219.4</v>
+        <v>2708394781.43</v>
       </c>
       <c r="H6" s="8">
-        <v>47.42</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -773,10 +769,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="6">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="D7" s="7">
-        <v>38.779193</v>
+        <v>38.647997</v>
       </c>
       <c r="E7" s="8">
         <v>14400000</v>
@@ -785,10 +781,10 @@
         <v>0</v>
       </c>
       <c r="G7" s="8">
-        <v>558420378.16</v>
+        <v>556531162.16</v>
       </c>
       <c r="H7" s="8">
-        <v>38.96</v>
+        <v>38.61</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -799,10 +795,10 @@
         <v>17</v>
       </c>
       <c r="C8" s="6">
-        <v>46155</v>
-      </c>
-      <c r="D8" s="7">
-        <v>40.674662</v>
+        <v>46156</v>
+      </c>
+      <c r="D8" s="10">
+        <v>40.47715</v>
       </c>
       <c r="E8" s="8">
         <v>33700000</v>
@@ -811,10 +807,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="8">
-        <v>1370736119.5</v>
+        <v>1364079948.99</v>
       </c>
       <c r="H8" s="8">
-        <v>40.77</v>
+        <v>40.17</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -825,10 +821,10 @@
         <v>19</v>
       </c>
       <c r="C9" s="6">
-        <v>46155</v>
-      </c>
-      <c r="D9" s="7">
-        <v>56.893307</v>
+        <v>46156</v>
+      </c>
+      <c r="D9" s="10">
+        <v>56.95387</v>
       </c>
       <c r="E9" s="8">
         <v>2550000</v>
@@ -837,10 +833,10 @@
         <v>0</v>
       </c>
       <c r="G9" s="8">
-        <v>145077932.07</v>
+        <v>145232367.76</v>
       </c>
       <c r="H9" s="8">
-        <v>56.96</v>
+        <v>57.02</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -851,10 +847,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="6">
-        <v>46155</v>
-      </c>
-      <c r="D10" s="10">
-        <v>409.11069</v>
+        <v>46156</v>
+      </c>
+      <c r="D10" s="7">
+        <v>408.795157</v>
       </c>
       <c r="E10" s="8">
         <v>135000</v>
@@ -863,10 +859,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="8">
-        <v>55229943.14</v>
+        <v>55187346.2</v>
       </c>
       <c r="H10" s="8">
-        <v>406.8</v>
+        <v>411</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -877,10 +873,10 @@
         <v>23</v>
       </c>
       <c r="C11" s="6">
-        <v>46155</v>
-      </c>
-      <c r="D11" s="7">
-        <v>571.489345</v>
+        <v>46156</v>
+      </c>
+      <c r="D11" s="10">
+        <v>573.59652</v>
       </c>
       <c r="E11" s="8">
         <v>47850000</v>
@@ -889,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="G11" s="8">
-        <v>27345765160.4</v>
+        <v>27446593482.26</v>
       </c>
       <c r="H11" s="8">
-        <v>574.75</v>
+        <v>577</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -903,10 +899,10 @@
         <v>25</v>
       </c>
       <c r="C12" s="6">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="D12" s="7">
-        <v>759.322409</v>
+        <v>795.866893</v>
       </c>
       <c r="E12" s="8">
         <v>73800000</v>
@@ -915,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="G12" s="8">
-        <v>56037993775.06</v>
+        <v>58734976719.88</v>
       </c>
       <c r="H12" s="8">
-        <v>750.75</v>
+        <v>782</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -929,10 +925,10 @@
         <v>27</v>
       </c>
       <c r="C13" s="6">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="D13" s="7">
-        <v>4229.511922</v>
+        <v>4230.853499</v>
       </c>
       <c r="E13" s="8">
         <v>266000</v>
@@ -941,10 +937,10 @@
         <v>0</v>
       </c>
       <c r="G13" s="8">
-        <v>1125050171.12</v>
+        <v>1125407030.67</v>
       </c>
       <c r="H13" s="8">
-        <v>4242</v>
+        <v>4246</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -955,10 +951,10 @@
         <v>29</v>
       </c>
       <c r="C14" s="6">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="D14" s="7">
-        <v>689.326928</v>
+        <v>686.591995</v>
       </c>
       <c r="E14" s="8">
         <v>113800000</v>
@@ -967,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="8">
-        <v>78445404427.73</v>
+        <v>78134169085.78</v>
       </c>
       <c r="H14" s="8">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -981,10 +977,10 @@
         <v>31</v>
       </c>
       <c r="C15" s="6">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="D15" s="7">
-        <v>567.208028</v>
+        <v>567.179994</v>
       </c>
       <c r="E15" s="8">
         <v>33450000</v>
@@ -993,10 +989,10 @@
         <v>0</v>
       </c>
       <c r="G15" s="8">
-        <v>18973108542.01</v>
+        <v>18972170792.74</v>
       </c>
       <c r="H15" s="8">
-        <v>567</v>
+        <v>568.5</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1007,10 +1003,10 @@
         <v>33</v>
       </c>
       <c r="C16" s="6">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="D16" s="7">
-        <v>26.918046</v>
+        <v>26.813912</v>
       </c>
       <c r="E16" s="8">
         <v>10800000</v>
@@ -1019,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="8">
-        <v>290714892.49</v>
+        <v>289590249.88</v>
       </c>
       <c r="H16" s="8">
-        <v>27.05</v>
+        <v>26.93</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1033,10 +1029,10 @@
         <v>35</v>
       </c>
       <c r="C17" s="6">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="D17" s="7">
-        <v>46.031193</v>
+        <v>46.078493</v>
       </c>
       <c r="E17" s="8">
         <v>1625000</v>
@@ -1045,10 +1041,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="8">
-        <v>74800689.27</v>
+        <v>74877551.36</v>
       </c>
       <c r="H17" s="8">
-        <v>46.08</v>
+        <v>46.13</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1059,10 +1055,10 @@
         <v>37</v>
       </c>
       <c r="C18" s="6">
-        <v>46155</v>
-      </c>
-      <c r="D18" s="7">
-        <v>76.141954</v>
+        <v>46156</v>
+      </c>
+      <c r="D18" s="10">
+        <v>75.39835</v>
       </c>
       <c r="E18" s="8">
         <v>1140000</v>
@@ -1071,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="G18" s="8">
-        <v>86801827.29</v>
+        <v>85954118.88</v>
       </c>
       <c r="H18" s="8">
-        <v>76.4</v>
+        <v>75.26</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1085,10 +1081,10 @@
         <v>39</v>
       </c>
       <c r="C19" s="6">
-        <v>46155</v>
-      </c>
-      <c r="D19" s="11">
-        <v>87.6577</v>
+        <v>46156</v>
+      </c>
+      <c r="D19" s="7">
+        <v>87.250411</v>
       </c>
       <c r="E19" s="8">
         <v>1155000</v>
@@ -1097,10 +1093,10 @@
         <v>0</v>
       </c>
       <c r="G19" s="8">
-        <v>101244643.35</v>
+        <v>100774225.13</v>
       </c>
       <c r="H19" s="8">
-        <v>88.18</v>
+        <v>86.98</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1111,10 +1107,10 @@
         <v>41</v>
       </c>
       <c r="C20" s="6">
-        <v>46155</v>
-      </c>
-      <c r="D20" s="7">
-        <v>53.497727</v>
+        <v>46156</v>
+      </c>
+      <c r="D20" s="10">
+        <v>53.51513</v>
       </c>
       <c r="E20" s="8">
         <v>2985000</v>
@@ -1123,10 +1119,10 @@
         <v>0</v>
       </c>
       <c r="G20" s="8">
-        <v>159690715.63</v>
+        <v>159742664.33</v>
       </c>
       <c r="H20" s="8">
-        <v>54.32</v>
+        <v>53.72</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1137,10 +1133,10 @@
         <v>43</v>
       </c>
       <c r="C21" s="6">
-        <v>46155</v>
-      </c>
-      <c r="D21" s="10">
-        <v>174.27058</v>
+        <v>46156</v>
+      </c>
+      <c r="D21" s="7">
+        <v>171.848304</v>
       </c>
       <c r="E21" s="8">
         <v>600000</v>
@@ -1149,10 +1145,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="8">
-        <v>104562348.18</v>
+        <v>103108982.16</v>
       </c>
       <c r="H21" s="8">
-        <v>175.35</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1163,22 +1159,22 @@
         <v>45</v>
       </c>
       <c r="C22" s="6">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="D22" s="7">
-        <v>219.958657</v>
+        <v>218.852391</v>
       </c>
       <c r="E22" s="8">
-        <v>125920000</v>
+        <v>125960000</v>
       </c>
       <c r="F22" s="9">
         <v>0</v>
       </c>
       <c r="G22" s="8">
-        <v>27697194096.9</v>
+        <v>27566647175.96</v>
       </c>
       <c r="H22" s="8">
-        <v>223</v>
+        <v>219.6</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1189,22 +1185,22 @@
         <v>47</v>
       </c>
       <c r="C23" s="6">
-        <v>46155</v>
-      </c>
-      <c r="D23" s="7">
-        <v>201.021726</v>
+        <v>46156</v>
+      </c>
+      <c r="D23" s="10">
+        <v>198.35532</v>
       </c>
       <c r="E23" s="8">
-        <v>204920000</v>
+        <v>205200000</v>
       </c>
       <c r="F23" s="9">
         <v>0</v>
       </c>
       <c r="G23" s="8">
-        <v>41193372120.53</v>
+        <v>40702511753.76</v>
       </c>
       <c r="H23" s="8">
-        <v>203.6</v>
+        <v>199.95</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1215,10 +1211,10 @@
         <v>49</v>
       </c>
       <c r="C24" s="6">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="D24" s="7">
-        <v>206.296585</v>
+        <v>203.730823</v>
       </c>
       <c r="E24" s="8">
         <v>360000</v>
@@ -1227,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="G24" s="8">
-        <v>74266770.69</v>
+        <v>73343096.3</v>
       </c>
       <c r="H24" s="8">
-        <v>206.3</v>
+        <v>204.2</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1241,10 +1237,10 @@
         <v>51</v>
       </c>
       <c r="C25" s="6">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="D25" s="7">
-        <v>129.515406</v>
+        <v>126.602636</v>
       </c>
       <c r="E25" s="8">
         <v>600000</v>
@@ -1253,10 +1249,10 @@
         <v>0</v>
       </c>
       <c r="G25" s="8">
-        <v>77709243.44</v>
+        <v>75961581.77</v>
       </c>
       <c r="H25" s="8">
-        <v>129.5</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1267,10 +1263,10 @@
         <v>53</v>
       </c>
       <c r="C26" s="6">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="D26" s="7">
-        <v>692.575851</v>
+        <v>696.904543</v>
       </c>
       <c r="E26" s="8">
         <v>152040000</v>
@@ -1279,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="G26" s="8">
-        <v>105299232404.42</v>
+        <v>105957366713.32</v>
       </c>
       <c r="H26" s="8">
-        <v>711.75</v>
+        <v>714</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1293,10 +1289,10 @@
         <v>55</v>
       </c>
       <c r="C27" s="6">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="D27" s="7">
-        <v>187.152931</v>
+        <v>183.210298</v>
       </c>
       <c r="E27" s="8">
         <v>10760000</v>
@@ -1305,10 +1301,10 @@
         <v>0</v>
       </c>
       <c r="G27" s="8">
-        <v>2013765538.68</v>
+        <v>1971342802.37</v>
       </c>
       <c r="H27" s="8">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1319,22 +1315,22 @@
         <v>57</v>
       </c>
       <c r="C28" s="6">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="D28" s="7">
-        <v>266.152487</v>
+        <v>262.922315</v>
       </c>
       <c r="E28" s="8">
-        <v>33200000</v>
+        <v>33240000</v>
       </c>
       <c r="F28" s="9">
         <v>0</v>
       </c>
       <c r="G28" s="8">
-        <v>8836262552.83</v>
+        <v>8739537755.74</v>
       </c>
       <c r="H28" s="8">
-        <v>271</v>
+        <v>265.8</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1345,10 +1341,10 @@
         <v>59</v>
       </c>
       <c r="C29" s="6">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="D29" s="7">
-        <v>260.592783</v>
+        <v>259.731148</v>
       </c>
       <c r="E29" s="8">
         <v>3200000</v>
@@ -1357,7 +1353,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="8">
-        <v>833896905.47</v>
+        <v>831139672.27</v>
       </c>
       <c r="H29" s="8">
         <v>260.6</v>
@@ -1371,10 +1367,10 @@
         <v>61</v>
       </c>
       <c r="C30" s="6">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="D30" s="7">
-        <v>124.776816</v>
+        <v>123.772175</v>
       </c>
       <c r="E30" s="8">
         <v>440000</v>
@@ -1383,10 +1379,10 @@
         <v>0</v>
       </c>
       <c r="G30" s="8">
-        <v>54901798.96</v>
+        <v>54459757.19</v>
       </c>
       <c r="H30" s="8">
-        <v>124.75</v>
+        <v>123.9</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1397,10 +1393,10 @@
         <v>63</v>
       </c>
       <c r="C31" s="6">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="D31" s="7">
-        <v>186.287376</v>
+        <v>184.555894</v>
       </c>
       <c r="E31" s="8">
         <v>400000</v>
@@ -1409,10 +1405,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="8">
-        <v>74514950.26</v>
+        <v>73822357.71</v>
       </c>
       <c r="H31" s="8">
-        <v>187</v>
+        <v>185.3</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1423,10 +1419,10 @@
         <v>65</v>
       </c>
       <c r="C32" s="6">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="D32" s="7">
-        <v>49.558906</v>
+        <v>49.377132</v>
       </c>
       <c r="E32" s="8">
         <v>1200000</v>
@@ -1435,10 +1431,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="8">
-        <v>59470687.12</v>
+        <v>59252558.1</v>
       </c>
       <c r="H32" s="8">
-        <v>49.56</v>
+        <v>49.37</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1449,10 +1445,10 @@
         <v>67</v>
       </c>
       <c r="C33" s="6">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="D33" s="7">
-        <v>1225.575622</v>
+        <v>1226.887113</v>
       </c>
       <c r="E33" s="8">
         <v>640000</v>
@@ -1461,10 +1457,10 @@
         <v>0</v>
       </c>
       <c r="G33" s="8">
-        <v>784368398.04</v>
+        <v>785207752.3</v>
       </c>
       <c r="H33" s="8">
-        <v>1227</v>
+        <v>1228.5</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -1475,10 +1471,10 @@
         <v>69</v>
       </c>
       <c r="C34" s="6">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="D34" s="7">
-        <v>191.514891</v>
+        <v>191.529637</v>
       </c>
       <c r="E34" s="8">
         <v>680000</v>
@@ -1487,7 +1483,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="8">
-        <v>130230125.62</v>
+        <v>130240153.37</v>
       </c>
       <c r="H34" s="8">
         <v>191.5</v>
@@ -1501,22 +1497,22 @@
         <v>71</v>
       </c>
       <c r="C35" s="6">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="D35" s="7">
-        <v>1226.690981</v>
+        <v>1228.004784</v>
       </c>
       <c r="E35" s="8">
-        <v>6680000</v>
+        <v>6640000</v>
       </c>
       <c r="F35" s="9">
         <v>0</v>
       </c>
       <c r="G35" s="8">
-        <v>8194295752.24</v>
+        <v>8153951767.16</v>
       </c>
       <c r="H35" s="8">
-        <v>1228.5</v>
+        <v>1229.5</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>14.05.2026 21:30:16</t>
+    <t>15.05.2026 18:52:26</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -743,10 +743,10 @@
         <v>13</v>
       </c>
       <c r="C6" s="6">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="D6" s="7">
-        <v>46.696462</v>
+        <v>47.238507</v>
       </c>
       <c r="E6" s="8">
         <v>58000000</v>
@@ -755,10 +755,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="8">
-        <v>2708394781.43</v>
+        <v>2739833419.27</v>
       </c>
       <c r="H6" s="8">
-        <v>46.8</v>
+        <v>47.26</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -769,10 +769,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="6">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="D7" s="7">
-        <v>38.647997</v>
+        <v>38.954287</v>
       </c>
       <c r="E7" s="8">
         <v>14400000</v>
@@ -781,10 +781,10 @@
         <v>0</v>
       </c>
       <c r="G7" s="8">
-        <v>556531162.16</v>
+        <v>560941725.95</v>
       </c>
       <c r="H7" s="8">
-        <v>38.61</v>
+        <v>38.97</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -795,10 +795,10 @@
         <v>17</v>
       </c>
       <c r="C8" s="6">
-        <v>46156</v>
-      </c>
-      <c r="D8" s="10">
-        <v>40.47715</v>
+        <v>46157</v>
+      </c>
+      <c r="D8" s="7">
+        <v>40.746065</v>
       </c>
       <c r="E8" s="8">
         <v>33700000</v>
@@ -807,10 +807,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="8">
-        <v>1364079948.99</v>
+        <v>1373142405.73</v>
       </c>
       <c r="H8" s="8">
-        <v>40.17</v>
+        <v>40.81</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -821,10 +821,10 @@
         <v>19</v>
       </c>
       <c r="C9" s="6">
-        <v>46156</v>
-      </c>
-      <c r="D9" s="10">
-        <v>56.95387</v>
+        <v>46157</v>
+      </c>
+      <c r="D9" s="7">
+        <v>57.014327</v>
       </c>
       <c r="E9" s="8">
         <v>2550000</v>
@@ -833,10 +833,10 @@
         <v>0</v>
       </c>
       <c r="G9" s="8">
-        <v>145232367.76</v>
+        <v>145386534.76</v>
       </c>
       <c r="H9" s="8">
-        <v>57.02</v>
+        <v>57.22</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -847,10 +847,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="6">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="D10" s="7">
-        <v>408.795157</v>
+        <v>408.567514</v>
       </c>
       <c r="E10" s="8">
         <v>135000</v>
@@ -859,10 +859,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="8">
-        <v>55187346.2</v>
+        <v>55156614.38</v>
       </c>
       <c r="H10" s="8">
-        <v>411</v>
+        <v>408.6</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -873,10 +873,10 @@
         <v>23</v>
       </c>
       <c r="C11" s="6">
-        <v>46156</v>
-      </c>
-      <c r="D11" s="10">
-        <v>573.59652</v>
+        <v>46157</v>
+      </c>
+      <c r="D11" s="7">
+        <v>573.250355</v>
       </c>
       <c r="E11" s="8">
         <v>47850000</v>
@@ -885,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="G11" s="8">
-        <v>27446593482.26</v>
+        <v>27430029501.58</v>
       </c>
       <c r="H11" s="8">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -899,22 +899,22 @@
         <v>25</v>
       </c>
       <c r="C12" s="6">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="D12" s="7">
-        <v>795.866893</v>
+        <v>762.419857</v>
       </c>
       <c r="E12" s="8">
-        <v>73800000</v>
+        <v>73550000</v>
       </c>
       <c r="F12" s="9">
         <v>0</v>
       </c>
       <c r="G12" s="8">
-        <v>58734976719.88</v>
+        <v>56075980517.37</v>
       </c>
       <c r="H12" s="8">
-        <v>782</v>
+        <v>758.5</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -925,10 +925,10 @@
         <v>27</v>
       </c>
       <c r="C13" s="6">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="D13" s="7">
-        <v>4230.853499</v>
+        <v>4232.703574</v>
       </c>
       <c r="E13" s="8">
         <v>266000</v>
@@ -937,10 +937,10 @@
         <v>0</v>
       </c>
       <c r="G13" s="8">
-        <v>1125407030.67</v>
+        <v>1125899150.73</v>
       </c>
       <c r="H13" s="8">
-        <v>4246</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -951,10 +951,10 @@
         <v>29</v>
       </c>
       <c r="C14" s="6">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="D14" s="7">
-        <v>686.591995</v>
+        <v>686.416883</v>
       </c>
       <c r="E14" s="8">
         <v>113800000</v>
@@ -963,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="8">
-        <v>78134169085.78</v>
+        <v>78114241338.66</v>
       </c>
       <c r="H14" s="8">
-        <v>710</v>
+        <v>706</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -977,10 +977,10 @@
         <v>31</v>
       </c>
       <c r="C15" s="6">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="D15" s="7">
-        <v>567.179994</v>
+        <v>566.712993</v>
       </c>
       <c r="E15" s="8">
         <v>33450000</v>
@@ -989,10 +989,10 @@
         <v>0</v>
       </c>
       <c r="G15" s="8">
-        <v>18972170792.74</v>
+        <v>18956549610.56</v>
       </c>
       <c r="H15" s="8">
-        <v>568.5</v>
+        <v>564.75</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1003,10 +1003,10 @@
         <v>33</v>
       </c>
       <c r="C16" s="6">
-        <v>46156</v>
-      </c>
-      <c r="D16" s="7">
-        <v>26.813912</v>
+        <v>46157</v>
+      </c>
+      <c r="D16" s="10">
+        <v>27.11587</v>
       </c>
       <c r="E16" s="8">
         <v>10800000</v>
@@ -1015,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="8">
-        <v>289590249.88</v>
+        <v>292851396.07</v>
       </c>
       <c r="H16" s="8">
-        <v>26.93</v>
+        <v>27.15</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1029,10 +1029,10 @@
         <v>35</v>
       </c>
       <c r="C17" s="6">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="D17" s="7">
-        <v>46.078493</v>
+        <v>46.125844</v>
       </c>
       <c r="E17" s="8">
         <v>1625000</v>
@@ -1041,10 +1041,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="8">
-        <v>74877551.36</v>
+        <v>74954496.99</v>
       </c>
       <c r="H17" s="8">
-        <v>46.13</v>
+        <v>46.27</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1055,10 +1055,10 @@
         <v>37</v>
       </c>
       <c r="C18" s="6">
-        <v>46156</v>
-      </c>
-      <c r="D18" s="10">
-        <v>75.39835</v>
+        <v>46157</v>
+      </c>
+      <c r="D18" s="7">
+        <v>76.030114</v>
       </c>
       <c r="E18" s="8">
         <v>1140000</v>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="G18" s="8">
-        <v>85954118.88</v>
+        <v>86674329.72</v>
       </c>
       <c r="H18" s="8">
-        <v>75.26</v>
+        <v>76.04</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1081,10 +1081,10 @@
         <v>39</v>
       </c>
       <c r="C19" s="6">
-        <v>46156</v>
-      </c>
-      <c r="D19" s="7">
-        <v>87.250411</v>
+        <v>46157</v>
+      </c>
+      <c r="D19" s="10">
+        <v>87.86944</v>
       </c>
       <c r="E19" s="8">
         <v>1155000</v>
@@ -1093,10 +1093,10 @@
         <v>0</v>
       </c>
       <c r="G19" s="8">
-        <v>100774225.13</v>
+        <v>101489203.55</v>
       </c>
       <c r="H19" s="8">
-        <v>86.98</v>
+        <v>87.58</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1107,10 +1107,10 @@
         <v>41</v>
       </c>
       <c r="C20" s="6">
-        <v>46156</v>
-      </c>
-      <c r="D20" s="10">
-        <v>53.51513</v>
+        <v>46157</v>
+      </c>
+      <c r="D20" s="7">
+        <v>53.853741</v>
       </c>
       <c r="E20" s="8">
         <v>2985000</v>
@@ -1119,10 +1119,10 @@
         <v>0</v>
       </c>
       <c r="G20" s="8">
-        <v>159742664.33</v>
+        <v>160753417.03</v>
       </c>
       <c r="H20" s="8">
-        <v>53.72</v>
+        <v>53.96</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1133,10 +1133,10 @@
         <v>43</v>
       </c>
       <c r="C21" s="6">
-        <v>46156</v>
-      </c>
-      <c r="D21" s="7">
-        <v>171.848304</v>
+        <v>46157</v>
+      </c>
+      <c r="D21" s="10">
+        <v>173.59879</v>
       </c>
       <c r="E21" s="8">
         <v>600000</v>
@@ -1145,10 +1145,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="8">
-        <v>103108982.16</v>
+        <v>104159274.19</v>
       </c>
       <c r="H21" s="8">
-        <v>172</v>
+        <v>173.85</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1159,22 +1159,22 @@
         <v>45</v>
       </c>
       <c r="C22" s="6">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="D22" s="7">
-        <v>218.852391</v>
+        <v>220.419434</v>
       </c>
       <c r="E22" s="8">
-        <v>125960000</v>
+        <v>125680000</v>
       </c>
       <c r="F22" s="9">
         <v>0</v>
       </c>
       <c r="G22" s="8">
-        <v>27566647175.96</v>
+        <v>27702314447.7</v>
       </c>
       <c r="H22" s="8">
-        <v>219.6</v>
+        <v>221</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1185,22 +1185,22 @@
         <v>47</v>
       </c>
       <c r="C23" s="6">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="D23" s="10">
-        <v>198.35532</v>
+        <v>200.69398</v>
       </c>
       <c r="E23" s="8">
-        <v>205200000</v>
+        <v>202840000</v>
       </c>
       <c r="F23" s="9">
         <v>0</v>
       </c>
       <c r="G23" s="8">
-        <v>40702511753.76</v>
+        <v>40708766946.24</v>
       </c>
       <c r="H23" s="8">
-        <v>199.95</v>
+        <v>201</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1211,10 +1211,10 @@
         <v>49</v>
       </c>
       <c r="C24" s="6">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="D24" s="7">
-        <v>203.730823</v>
+        <v>204.174778</v>
       </c>
       <c r="E24" s="8">
         <v>360000</v>
@@ -1223,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="G24" s="8">
-        <v>73343096.3</v>
+        <v>73502920.05</v>
       </c>
       <c r="H24" s="8">
-        <v>204.2</v>
+        <v>204.15</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1237,10 +1237,10 @@
         <v>51</v>
       </c>
       <c r="C25" s="6">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="D25" s="7">
-        <v>126.602636</v>
+        <v>127.744876</v>
       </c>
       <c r="E25" s="8">
         <v>600000</v>
@@ -1249,10 +1249,10 @@
         <v>0</v>
       </c>
       <c r="G25" s="8">
-        <v>75961581.77</v>
+        <v>76646925.4</v>
       </c>
       <c r="H25" s="8">
-        <v>127</v>
+        <v>127.55</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1263,10 +1263,10 @@
         <v>53</v>
       </c>
       <c r="C26" s="6">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="D26" s="7">
-        <v>696.904543</v>
+        <v>695.843121</v>
       </c>
       <c r="E26" s="8">
         <v>152040000</v>
@@ -1275,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="G26" s="8">
-        <v>105957366713.32</v>
+        <v>105795988083.69</v>
       </c>
       <c r="H26" s="8">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1289,22 +1289,22 @@
         <v>55</v>
       </c>
       <c r="C27" s="6">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="D27" s="7">
-        <v>183.210298</v>
+        <v>184.857652</v>
       </c>
       <c r="E27" s="8">
-        <v>10760000</v>
+        <v>10800000</v>
       </c>
       <c r="F27" s="9">
         <v>0</v>
       </c>
       <c r="G27" s="8">
-        <v>1971342802.37</v>
+        <v>1996462641.97</v>
       </c>
       <c r="H27" s="8">
-        <v>187</v>
+        <v>184.65</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1315,22 +1315,22 @@
         <v>57</v>
       </c>
       <c r="C28" s="6">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="D28" s="7">
-        <v>262.922315</v>
+        <v>264.632714</v>
       </c>
       <c r="E28" s="8">
-        <v>33240000</v>
+        <v>33280000</v>
       </c>
       <c r="F28" s="9">
         <v>0</v>
       </c>
       <c r="G28" s="8">
-        <v>8739537755.74</v>
+        <v>8806976722.55</v>
       </c>
       <c r="H28" s="8">
-        <v>265.8</v>
+        <v>264.6</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1341,10 +1341,10 @@
         <v>59</v>
       </c>
       <c r="C29" s="6">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="D29" s="7">
-        <v>259.731148</v>
+        <v>261.784375</v>
       </c>
       <c r="E29" s="8">
         <v>3200000</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="G29" s="8">
-        <v>831139672.27</v>
+        <v>837710000.31</v>
       </c>
       <c r="H29" s="8">
-        <v>260.6</v>
+        <v>261.7</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1367,10 +1367,10 @@
         <v>61</v>
       </c>
       <c r="C30" s="6">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="D30" s="7">
-        <v>123.772175</v>
+        <v>126.190293</v>
       </c>
       <c r="E30" s="8">
         <v>440000</v>
@@ -1379,10 +1379,10 @@
         <v>0</v>
       </c>
       <c r="G30" s="8">
-        <v>54459757.19</v>
+        <v>55523729.11</v>
       </c>
       <c r="H30" s="8">
-        <v>123.9</v>
+        <v>126.2</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1393,10 +1393,10 @@
         <v>63</v>
       </c>
       <c r="C31" s="6">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="D31" s="7">
-        <v>184.555894</v>
+        <v>184.765863</v>
       </c>
       <c r="E31" s="8">
         <v>400000</v>
@@ -1405,10 +1405,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="8">
-        <v>73822357.71</v>
+        <v>73906345.32</v>
       </c>
       <c r="H31" s="8">
-        <v>185.3</v>
+        <v>184.8</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1419,10 +1419,10 @@
         <v>65</v>
       </c>
       <c r="C32" s="6">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="D32" s="7">
-        <v>49.377132</v>
+        <v>49.773887</v>
       </c>
       <c r="E32" s="8">
         <v>1200000</v>
@@ -1431,10 +1431,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="8">
-        <v>59252558.1</v>
+        <v>59728664.51</v>
       </c>
       <c r="H32" s="8">
-        <v>49.37</v>
+        <v>49.74</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1445,10 +1445,10 @@
         <v>67</v>
       </c>
       <c r="C33" s="6">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="D33" s="7">
-        <v>1226.887113</v>
+        <v>1228.205954</v>
       </c>
       <c r="E33" s="8">
         <v>640000</v>
@@ -1457,10 +1457,10 @@
         <v>0</v>
       </c>
       <c r="G33" s="8">
-        <v>785207752.3</v>
+        <v>786051810.3</v>
       </c>
       <c r="H33" s="8">
-        <v>1228.5</v>
+        <v>1232.5</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -1471,10 +1471,10 @@
         <v>69</v>
       </c>
       <c r="C34" s="6">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="D34" s="7">
-        <v>191.529637</v>
+        <v>192.824723</v>
       </c>
       <c r="E34" s="8">
         <v>680000</v>
@@ -1483,10 +1483,10 @@
         <v>0</v>
       </c>
       <c r="G34" s="8">
-        <v>130240153.37</v>
+        <v>131120811.76</v>
       </c>
       <c r="H34" s="8">
-        <v>191.5</v>
+        <v>192.6</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -1497,22 +1497,22 @@
         <v>71</v>
       </c>
       <c r="C35" s="6">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="D35" s="7">
-        <v>1228.004784</v>
+        <v>1229.322086</v>
       </c>
       <c r="E35" s="8">
-        <v>6640000</v>
+        <v>6520000</v>
       </c>
       <c r="F35" s="9">
         <v>0</v>
       </c>
       <c r="G35" s="8">
-        <v>8153951767.16</v>
+        <v>8015180000.15</v>
       </c>
       <c r="H35" s="8">
-        <v>1229.5</v>
+        <v>1233.5</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>15.05.2026 18:52:26</t>
+    <t>18.05.2026 12:26:33</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -743,10 +743,10 @@
         <v>13</v>
       </c>
       <c r="C6" s="6">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="D6" s="7">
-        <v>47.238507</v>
+        <v>45.971312</v>
       </c>
       <c r="E6" s="8">
         <v>58000000</v>
@@ -755,10 +755,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="8">
-        <v>2739833419.27</v>
+        <v>2666336105.44</v>
       </c>
       <c r="H6" s="8">
-        <v>47.26</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -769,10 +769,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="6">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="D7" s="7">
-        <v>38.954287</v>
+        <v>38.632538</v>
       </c>
       <c r="E7" s="8">
         <v>14400000</v>
@@ -781,10 +781,10 @@
         <v>0</v>
       </c>
       <c r="G7" s="8">
-        <v>560941725.95</v>
+        <v>556308551.74</v>
       </c>
       <c r="H7" s="8">
-        <v>38.97</v>
+        <v>38.46</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -795,10 +795,10 @@
         <v>17</v>
       </c>
       <c r="C8" s="6">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="D8" s="7">
-        <v>40.746065</v>
+        <v>40.030002</v>
       </c>
       <c r="E8" s="8">
         <v>33700000</v>
@@ -807,10 +807,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="8">
-        <v>1373142405.73</v>
+        <v>1349011081.75</v>
       </c>
       <c r="H8" s="8">
-        <v>40.81</v>
+        <v>40.45</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -821,10 +821,10 @@
         <v>19</v>
       </c>
       <c r="C9" s="6">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="D9" s="7">
-        <v>57.014327</v>
+        <v>57.195913</v>
       </c>
       <c r="E9" s="8">
         <v>2550000</v>
@@ -833,10 +833,10 @@
         <v>0</v>
       </c>
       <c r="G9" s="8">
-        <v>145386534.76</v>
+        <v>145849579.27</v>
       </c>
       <c r="H9" s="8">
-        <v>57.22</v>
+        <v>57.34</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -847,10 +847,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="6">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="D10" s="7">
-        <v>408.567514</v>
+        <v>394.214373</v>
       </c>
       <c r="E10" s="8">
         <v>135000</v>
@@ -859,10 +859,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="8">
-        <v>55156614.38</v>
+        <v>53218940.31</v>
       </c>
       <c r="H10" s="8">
-        <v>408.6</v>
+        <v>395.2</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -873,10 +873,10 @@
         <v>23</v>
       </c>
       <c r="C11" s="6">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="D11" s="7">
-        <v>573.250355</v>
+        <v>559.282833</v>
       </c>
       <c r="E11" s="8">
         <v>47850000</v>
@@ -885,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="G11" s="8">
-        <v>27430029501.58</v>
+        <v>26761683563.46</v>
       </c>
       <c r="H11" s="8">
-        <v>574</v>
+        <v>559</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -899,22 +899,22 @@
         <v>25</v>
       </c>
       <c r="C12" s="6">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="D12" s="7">
-        <v>762.419857</v>
+        <v>693.360033</v>
       </c>
       <c r="E12" s="8">
-        <v>73550000</v>
+        <v>73300000</v>
       </c>
       <c r="F12" s="9">
         <v>0</v>
       </c>
       <c r="G12" s="8">
-        <v>56075980517.37</v>
+        <v>50823290407.92</v>
       </c>
       <c r="H12" s="8">
-        <v>758.5</v>
+        <v>702.5</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -925,10 +925,10 @@
         <v>27</v>
       </c>
       <c r="C13" s="6">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="D13" s="7">
-        <v>4232.703574</v>
+        <v>4242.832521</v>
       </c>
       <c r="E13" s="8">
         <v>266000</v>
@@ -937,10 +937,10 @@
         <v>0</v>
       </c>
       <c r="G13" s="8">
-        <v>1125899150.73</v>
+        <v>1128593450.5</v>
       </c>
       <c r="H13" s="8">
-        <v>4247</v>
+        <v>4252</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -951,10 +951,10 @@
         <v>29</v>
       </c>
       <c r="C14" s="6">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="D14" s="7">
-        <v>686.416883</v>
+        <v>667.838977</v>
       </c>
       <c r="E14" s="8">
         <v>113800000</v>
@@ -963,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="8">
-        <v>78114241338.66</v>
+        <v>76000075547.86</v>
       </c>
       <c r="H14" s="8">
-        <v>706</v>
+        <v>683.25</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -977,10 +977,10 @@
         <v>31</v>
       </c>
       <c r="C15" s="6">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="D15" s="7">
-        <v>566.712993</v>
+        <v>551.036988</v>
       </c>
       <c r="E15" s="8">
         <v>33450000</v>
@@ -989,10 +989,10 @@
         <v>0</v>
       </c>
       <c r="G15" s="8">
-        <v>18956549610.56</v>
+        <v>18432187257.65</v>
       </c>
       <c r="H15" s="8">
-        <v>564.75</v>
+        <v>555.5</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1003,10 +1003,10 @@
         <v>33</v>
       </c>
       <c r="C16" s="6">
-        <v>46157</v>
-      </c>
-      <c r="D16" s="10">
-        <v>27.11587</v>
+        <v>46160</v>
+      </c>
+      <c r="D16" s="7">
+        <v>26.475274</v>
       </c>
       <c r="E16" s="8">
         <v>10800000</v>
@@ -1015,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="8">
-        <v>292851396.07</v>
+        <v>285932963.89</v>
       </c>
       <c r="H16" s="8">
-        <v>27.15</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1029,10 +1029,10 @@
         <v>35</v>
       </c>
       <c r="C17" s="6">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="D17" s="7">
-        <v>46.125844</v>
+        <v>46.267937</v>
       </c>
       <c r="E17" s="8">
         <v>1625000</v>
@@ -1041,10 +1041,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="8">
-        <v>74954496.99</v>
+        <v>75185398.01</v>
       </c>
       <c r="H17" s="8">
-        <v>46.27</v>
+        <v>46.37</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1055,10 +1055,10 @@
         <v>37</v>
       </c>
       <c r="C18" s="6">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="D18" s="7">
-        <v>76.030114</v>
+        <v>75.195216</v>
       </c>
       <c r="E18" s="8">
         <v>1140000</v>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="G18" s="8">
-        <v>86674329.72</v>
+        <v>85722546.71</v>
       </c>
       <c r="H18" s="8">
-        <v>76.04</v>
+        <v>75.18</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1081,10 +1081,10 @@
         <v>39</v>
       </c>
       <c r="C19" s="6">
-        <v>46157</v>
-      </c>
-      <c r="D19" s="10">
-        <v>87.86944</v>
+        <v>46160</v>
+      </c>
+      <c r="D19" s="7">
+        <v>86.309078</v>
       </c>
       <c r="E19" s="8">
         <v>1155000</v>
@@ -1093,10 +1093,10 @@
         <v>0</v>
       </c>
       <c r="G19" s="8">
-        <v>101489203.55</v>
+        <v>99686985.23</v>
       </c>
       <c r="H19" s="8">
-        <v>87.58</v>
+        <v>86.14</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1107,10 +1107,10 @@
         <v>41</v>
       </c>
       <c r="C20" s="6">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="D20" s="7">
-        <v>53.853741</v>
+        <v>52.807499</v>
       </c>
       <c r="E20" s="8">
         <v>2985000</v>
@@ -1119,10 +1119,10 @@
         <v>0</v>
       </c>
       <c r="G20" s="8">
-        <v>160753417.03</v>
+        <v>157630385.14</v>
       </c>
       <c r="H20" s="8">
-        <v>53.96</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1133,10 +1133,10 @@
         <v>43</v>
       </c>
       <c r="C21" s="6">
-        <v>46157</v>
-      </c>
-      <c r="D21" s="10">
-        <v>173.59879</v>
+        <v>46160</v>
+      </c>
+      <c r="D21" s="7">
+        <v>172.675625</v>
       </c>
       <c r="E21" s="8">
         <v>600000</v>
@@ -1145,10 +1145,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="8">
-        <v>104159274.19</v>
+        <v>103605374.95</v>
       </c>
       <c r="H21" s="8">
-        <v>173.85</v>
+        <v>171.8</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1159,22 +1159,22 @@
         <v>45</v>
       </c>
       <c r="C22" s="6">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="D22" s="7">
-        <v>220.419434</v>
+        <v>216.446044</v>
       </c>
       <c r="E22" s="8">
-        <v>125680000</v>
+        <v>123000000</v>
       </c>
       <c r="F22" s="9">
         <v>0</v>
       </c>
       <c r="G22" s="8">
-        <v>27702314447.7</v>
+        <v>26622863386.9</v>
       </c>
       <c r="H22" s="8">
-        <v>221</v>
+        <v>216.3</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1185,22 +1185,22 @@
         <v>47</v>
       </c>
       <c r="C23" s="6">
-        <v>46157</v>
-      </c>
-      <c r="D23" s="10">
-        <v>200.69398</v>
+        <v>46160</v>
+      </c>
+      <c r="D23" s="7">
+        <v>195.223885</v>
       </c>
       <c r="E23" s="8">
-        <v>202840000</v>
+        <v>204000000</v>
       </c>
       <c r="F23" s="9">
         <v>0</v>
       </c>
       <c r="G23" s="8">
-        <v>40708766946.24</v>
+        <v>39825672477.86</v>
       </c>
       <c r="H23" s="8">
-        <v>201</v>
+        <v>196.55</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1211,10 +1211,10 @@
         <v>49</v>
       </c>
       <c r="C24" s="6">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="D24" s="7">
-        <v>204.174778</v>
+        <v>199.589345</v>
       </c>
       <c r="E24" s="8">
         <v>360000</v>
@@ -1223,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="G24" s="8">
-        <v>73502920.05</v>
+        <v>71852164.03</v>
       </c>
       <c r="H24" s="8">
-        <v>204.15</v>
+        <v>199.6</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1237,10 +1237,10 @@
         <v>51</v>
       </c>
       <c r="C25" s="6">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="D25" s="7">
-        <v>127.744876</v>
+        <v>124.199348</v>
       </c>
       <c r="E25" s="8">
         <v>600000</v>
@@ -1249,10 +1249,10 @@
         <v>0</v>
       </c>
       <c r="G25" s="8">
-        <v>76646925.4</v>
+        <v>74519608.54</v>
       </c>
       <c r="H25" s="8">
-        <v>127.55</v>
+        <v>124.2</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1263,10 +1263,10 @@
         <v>53</v>
       </c>
       <c r="C26" s="6">
-        <v>46157</v>
-      </c>
-      <c r="D26" s="7">
-        <v>695.843121</v>
+        <v>46160</v>
+      </c>
+      <c r="D26" s="10">
+        <v>675.05834</v>
       </c>
       <c r="E26" s="8">
         <v>152040000</v>
@@ -1275,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="G26" s="8">
-        <v>105795988083.69</v>
+        <v>102635870030.72</v>
       </c>
       <c r="H26" s="8">
-        <v>712</v>
+        <v>697</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1289,22 +1289,22 @@
         <v>55</v>
       </c>
       <c r="C27" s="6">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="D27" s="7">
-        <v>184.857652</v>
+        <v>181.741706</v>
       </c>
       <c r="E27" s="8">
-        <v>10800000</v>
+        <v>10760000</v>
       </c>
       <c r="F27" s="9">
         <v>0</v>
       </c>
       <c r="G27" s="8">
-        <v>1996462641.97</v>
+        <v>1955540754.73</v>
       </c>
       <c r="H27" s="8">
-        <v>184.65</v>
+        <v>181.6</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1315,22 +1315,22 @@
         <v>57</v>
       </c>
       <c r="C28" s="6">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="D28" s="7">
-        <v>264.632714</v>
+        <v>261.311111</v>
       </c>
       <c r="E28" s="8">
-        <v>33280000</v>
+        <v>33200000</v>
       </c>
       <c r="F28" s="9">
         <v>0</v>
       </c>
       <c r="G28" s="8">
-        <v>8806976722.55</v>
+        <v>8675528873.41</v>
       </c>
       <c r="H28" s="8">
-        <v>264.6</v>
+        <v>260.6</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1341,10 +1341,10 @@
         <v>59</v>
       </c>
       <c r="C29" s="6">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="D29" s="7">
-        <v>261.784375</v>
+        <v>259.598346</v>
       </c>
       <c r="E29" s="8">
         <v>3200000</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="G29" s="8">
-        <v>837710000.31</v>
+        <v>830714706.2</v>
       </c>
       <c r="H29" s="8">
-        <v>261.7</v>
+        <v>259.6</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1367,10 +1367,10 @@
         <v>61</v>
       </c>
       <c r="C30" s="6">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="D30" s="7">
-        <v>126.190293</v>
+        <v>123.267522</v>
       </c>
       <c r="E30" s="8">
         <v>440000</v>
@@ -1379,10 +1379,10 @@
         <v>0</v>
       </c>
       <c r="G30" s="8">
-        <v>55523729.11</v>
+        <v>54237709.64</v>
       </c>
       <c r="H30" s="8">
-        <v>126.2</v>
+        <v>123.25</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1393,10 +1393,10 @@
         <v>63</v>
       </c>
       <c r="C31" s="6">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="D31" s="7">
-        <v>184.765863</v>
+        <v>181.075384</v>
       </c>
       <c r="E31" s="8">
         <v>400000</v>
@@ -1405,10 +1405,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="8">
-        <v>73906345.32</v>
+        <v>72430153.46</v>
       </c>
       <c r="H31" s="8">
-        <v>184.8</v>
+        <v>181.1</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1419,10 +1419,10 @@
         <v>65</v>
       </c>
       <c r="C32" s="6">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="D32" s="7">
-        <v>49.773887</v>
+        <v>48.828749</v>
       </c>
       <c r="E32" s="8">
         <v>1200000</v>
@@ -1431,10 +1431,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="8">
-        <v>59728664.51</v>
+        <v>58594499.04</v>
       </c>
       <c r="H32" s="8">
-        <v>49.74</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1445,10 +1445,10 @@
         <v>67</v>
       </c>
       <c r="C33" s="6">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="D33" s="7">
-        <v>1228.205954</v>
+        <v>1232.168009</v>
       </c>
       <c r="E33" s="8">
         <v>640000</v>
@@ -1457,10 +1457,10 @@
         <v>0</v>
       </c>
       <c r="G33" s="8">
-        <v>786051810.3</v>
+        <v>788587526.03</v>
       </c>
       <c r="H33" s="8">
-        <v>1232.5</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -1471,10 +1471,10 @@
         <v>69</v>
       </c>
       <c r="C34" s="6">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="D34" s="7">
-        <v>192.824723</v>
+        <v>188.905705</v>
       </c>
       <c r="E34" s="8">
         <v>680000</v>
@@ -1483,10 +1483,10 @@
         <v>0</v>
       </c>
       <c r="G34" s="8">
-        <v>131120811.76</v>
+        <v>128455879.16</v>
       </c>
       <c r="H34" s="8">
-        <v>192.6</v>
+        <v>188.9</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -1497,22 +1497,22 @@
         <v>71</v>
       </c>
       <c r="C35" s="6">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="D35" s="7">
-        <v>1229.322086</v>
+        <v>1233.278156</v>
       </c>
       <c r="E35" s="8">
-        <v>6520000</v>
+        <v>6400000</v>
       </c>
       <c r="F35" s="9">
         <v>0</v>
       </c>
       <c r="G35" s="8">
-        <v>8015180000.15</v>
+        <v>7892980198.67</v>
       </c>
       <c r="H35" s="8">
-        <v>1233.5</v>
+        <v>1236.5</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>18.05.2026 12:26:33</t>
+    <t>20.05.2026 16:12:23</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -233,12 +233,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="###0.000000;-###0.000000;0"/>
     <numFmt numFmtId="166" formatCode="###0.00;-###0.00;0"/>
     <numFmt numFmtId="167" formatCode="###0;-###0;0"/>
     <numFmt numFmtId="168" formatCode="###0.00000;-###0.00000;0"/>
+    <numFmt numFmtId="169" formatCode="###0.0000;-###0.0000;0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -308,7 +309,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -334,6 +335,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -743,10 +747,10 @@
         <v>13</v>
       </c>
       <c r="C6" s="6">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="D6" s="7">
-        <v>45.971312</v>
+        <v>45.639355</v>
       </c>
       <c r="E6" s="8">
         <v>58000000</v>
@@ -755,10 +759,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="8">
-        <v>2666336105.44</v>
+        <v>2647082596.52</v>
       </c>
       <c r="H6" s="8">
-        <v>46.1</v>
+        <v>45.86</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -769,10 +773,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="6">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="D7" s="7">
-        <v>38.632538</v>
+        <v>37.615161</v>
       </c>
       <c r="E7" s="8">
         <v>14400000</v>
@@ -781,10 +785,10 @@
         <v>0</v>
       </c>
       <c r="G7" s="8">
-        <v>556308551.74</v>
+        <v>541658323.52</v>
       </c>
       <c r="H7" s="8">
-        <v>38.46</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -795,10 +799,10 @@
         <v>17</v>
       </c>
       <c r="C8" s="6">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="D8" s="7">
-        <v>40.030002</v>
+        <v>39.099067</v>
       </c>
       <c r="E8" s="8">
         <v>33700000</v>
@@ -807,10 +811,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="8">
-        <v>1349011081.75</v>
+        <v>1325458380.41</v>
       </c>
       <c r="H8" s="8">
-        <v>40.45</v>
+        <v>39.19</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -821,10 +825,10 @@
         <v>19</v>
       </c>
       <c r="C9" s="6">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="D9" s="7">
-        <v>57.195913</v>
+        <v>57.316476</v>
       </c>
       <c r="E9" s="8">
         <v>2550000</v>
@@ -833,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="G9" s="8">
-        <v>145849579.27</v>
+        <v>146157012.59</v>
       </c>
       <c r="H9" s="8">
-        <v>57.34</v>
+        <v>57.4</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -847,10 +851,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="6">
-        <v>46160</v>
-      </c>
-      <c r="D10" s="7">
-        <v>394.214373</v>
+        <v>46162</v>
+      </c>
+      <c r="D10" s="10">
+        <v>378.89284</v>
       </c>
       <c r="E10" s="8">
         <v>135000</v>
@@ -859,10 +863,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="8">
-        <v>53218940.31</v>
+        <v>51150533.38</v>
       </c>
       <c r="H10" s="8">
-        <v>395.2</v>
+        <v>379.6</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -873,22 +877,22 @@
         <v>23</v>
       </c>
       <c r="C11" s="6">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="D11" s="7">
-        <v>559.282833</v>
+        <v>556.481302</v>
       </c>
       <c r="E11" s="8">
-        <v>47850000</v>
+        <v>46600000</v>
       </c>
       <c r="F11" s="9">
         <v>0</v>
       </c>
       <c r="G11" s="8">
-        <v>26761683563.46</v>
+        <v>25932028674.76</v>
       </c>
       <c r="H11" s="8">
-        <v>559</v>
+        <v>557.75</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -899,22 +903,22 @@
         <v>25</v>
       </c>
       <c r="C12" s="6">
-        <v>46160</v>
-      </c>
-      <c r="D12" s="7">
-        <v>693.360033</v>
+        <v>46162</v>
+      </c>
+      <c r="D12" s="11">
+        <v>689.3382</v>
       </c>
       <c r="E12" s="8">
-        <v>73300000</v>
+        <v>73050000</v>
       </c>
       <c r="F12" s="9">
         <v>0</v>
       </c>
       <c r="G12" s="8">
-        <v>50823290407.92</v>
+        <v>50356155526.74</v>
       </c>
       <c r="H12" s="8">
-        <v>702.5</v>
+        <v>703</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -925,10 +929,10 @@
         <v>27</v>
       </c>
       <c r="C13" s="6">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="D13" s="7">
-        <v>4242.832521</v>
+        <v>4241.228195</v>
       </c>
       <c r="E13" s="8">
         <v>266000</v>
@@ -937,10 +941,10 @@
         <v>0</v>
       </c>
       <c r="G13" s="8">
-        <v>1128593450.5</v>
+        <v>1128166700</v>
       </c>
       <c r="H13" s="8">
-        <v>4252</v>
+        <v>4260</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -951,10 +955,10 @@
         <v>29</v>
       </c>
       <c r="C14" s="6">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="D14" s="7">
-        <v>667.838977</v>
+        <v>670.986874</v>
       </c>
       <c r="E14" s="8">
         <v>113800000</v>
@@ -963,10 +967,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="8">
-        <v>76000075547.86</v>
+        <v>76358306209.97</v>
       </c>
       <c r="H14" s="8">
-        <v>683.25</v>
+        <v>681</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -977,10 +981,10 @@
         <v>31</v>
       </c>
       <c r="C15" s="6">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="D15" s="7">
-        <v>551.036988</v>
+        <v>551.485633</v>
       </c>
       <c r="E15" s="8">
         <v>33450000</v>
@@ -989,10 +993,10 @@
         <v>0</v>
       </c>
       <c r="G15" s="8">
-        <v>18432187257.65</v>
+        <v>18447194429.98</v>
       </c>
       <c r="H15" s="8">
-        <v>555.5</v>
+        <v>553.75</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1003,10 +1007,10 @@
         <v>33</v>
       </c>
       <c r="C16" s="6">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="D16" s="7">
-        <v>26.475274</v>
+        <v>25.756076</v>
       </c>
       <c r="E16" s="8">
         <v>10800000</v>
@@ -1015,10 +1019,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="8">
-        <v>285932963.89</v>
+        <v>278165618.93</v>
       </c>
       <c r="H16" s="8">
-        <v>26.4</v>
+        <v>25.83</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1029,10 +1033,10 @@
         <v>35</v>
       </c>
       <c r="C17" s="6">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="D17" s="7">
-        <v>46.267937</v>
+        <v>46.362446</v>
       </c>
       <c r="E17" s="8">
         <v>1625000</v>
@@ -1041,10 +1045,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="8">
-        <v>75185398.01</v>
+        <v>75338975.1</v>
       </c>
       <c r="H17" s="8">
-        <v>46.37</v>
+        <v>46.42</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1055,10 +1059,10 @@
         <v>37</v>
       </c>
       <c r="C18" s="6">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="D18" s="7">
-        <v>75.195216</v>
+        <v>73.460148</v>
       </c>
       <c r="E18" s="8">
         <v>1140000</v>
@@ -1067,10 +1071,10 @@
         <v>0</v>
       </c>
       <c r="G18" s="8">
-        <v>85722546.71</v>
+        <v>83744568.71</v>
       </c>
       <c r="H18" s="8">
-        <v>75.18</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1081,10 +1085,10 @@
         <v>39</v>
       </c>
       <c r="C19" s="6">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="D19" s="7">
-        <v>86.309078</v>
+        <v>84.390019</v>
       </c>
       <c r="E19" s="8">
         <v>1155000</v>
@@ -1093,10 +1097,10 @@
         <v>0</v>
       </c>
       <c r="G19" s="8">
-        <v>99686985.23</v>
+        <v>97470471.68</v>
       </c>
       <c r="H19" s="8">
-        <v>86.14</v>
+        <v>84.68</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1107,10 +1111,10 @@
         <v>41</v>
       </c>
       <c r="C20" s="6">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="D20" s="7">
-        <v>52.807499</v>
+        <v>51.699128</v>
       </c>
       <c r="E20" s="8">
         <v>2985000</v>
@@ -1119,10 +1123,10 @@
         <v>0</v>
       </c>
       <c r="G20" s="8">
-        <v>157630385.14</v>
+        <v>154321896.96</v>
       </c>
       <c r="H20" s="8">
-        <v>53.7</v>
+        <v>51.92</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1133,10 +1137,10 @@
         <v>43</v>
       </c>
       <c r="C21" s="6">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="D21" s="7">
-        <v>172.675625</v>
+        <v>167.274031</v>
       </c>
       <c r="E21" s="8">
         <v>600000</v>
@@ -1145,10 +1149,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="8">
-        <v>103605374.95</v>
+        <v>100364418.46</v>
       </c>
       <c r="H21" s="8">
-        <v>171.8</v>
+        <v>167.65</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1159,22 +1163,22 @@
         <v>45</v>
       </c>
       <c r="C22" s="6">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="D22" s="7">
-        <v>216.446044</v>
+        <v>211.352011</v>
       </c>
       <c r="E22" s="8">
-        <v>123000000</v>
+        <v>119560000</v>
       </c>
       <c r="F22" s="9">
         <v>0</v>
       </c>
       <c r="G22" s="8">
-        <v>26622863386.9</v>
+        <v>25269246470.11</v>
       </c>
       <c r="H22" s="8">
-        <v>216.3</v>
+        <v>212.25</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1185,22 +1189,22 @@
         <v>47</v>
       </c>
       <c r="C23" s="6">
-        <v>46160</v>
-      </c>
-      <c r="D23" s="7">
-        <v>195.223885</v>
+        <v>46162</v>
+      </c>
+      <c r="D23" s="10">
+        <v>193.76411</v>
       </c>
       <c r="E23" s="8">
-        <v>204000000</v>
+        <v>205440000</v>
       </c>
       <c r="F23" s="9">
         <v>0</v>
       </c>
       <c r="G23" s="8">
-        <v>39825672477.86</v>
+        <v>39806898696.16</v>
       </c>
       <c r="H23" s="8">
-        <v>196.55</v>
+        <v>196</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1211,10 +1215,10 @@
         <v>49</v>
       </c>
       <c r="C24" s="6">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="D24" s="7">
-        <v>199.589345</v>
+        <v>194.864693</v>
       </c>
       <c r="E24" s="8">
         <v>360000</v>
@@ -1223,10 +1227,10 @@
         <v>0</v>
       </c>
       <c r="G24" s="8">
-        <v>71852164.03</v>
+        <v>70151289.41</v>
       </c>
       <c r="H24" s="8">
-        <v>199.6</v>
+        <v>195.5</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1237,10 +1241,10 @@
         <v>51</v>
       </c>
       <c r="C25" s="6">
-        <v>46160</v>
-      </c>
-      <c r="D25" s="7">
-        <v>124.199348</v>
+        <v>46162</v>
+      </c>
+      <c r="D25" s="10">
+        <v>120.72158</v>
       </c>
       <c r="E25" s="8">
         <v>600000</v>
@@ -1249,10 +1253,10 @@
         <v>0</v>
       </c>
       <c r="G25" s="8">
-        <v>74519608.54</v>
+        <v>72432948.02</v>
       </c>
       <c r="H25" s="8">
-        <v>124.2</v>
+        <v>121.45</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1263,10 +1267,10 @@
         <v>53</v>
       </c>
       <c r="C26" s="6">
-        <v>46160</v>
-      </c>
-      <c r="D26" s="10">
-        <v>675.05834</v>
+        <v>46162</v>
+      </c>
+      <c r="D26" s="7">
+        <v>677.964379</v>
       </c>
       <c r="E26" s="8">
         <v>152040000</v>
@@ -1275,10 +1279,10 @@
         <v>0</v>
       </c>
       <c r="G26" s="8">
-        <v>102635870030.72</v>
+        <v>103077704167.22</v>
       </c>
       <c r="H26" s="8">
-        <v>697</v>
+        <v>691</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1289,22 +1293,22 @@
         <v>55</v>
       </c>
       <c r="C27" s="6">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="D27" s="7">
-        <v>181.741706</v>
+        <v>178.347806</v>
       </c>
       <c r="E27" s="8">
-        <v>10760000</v>
+        <v>10680000</v>
       </c>
       <c r="F27" s="9">
         <v>0</v>
       </c>
       <c r="G27" s="8">
-        <v>1955540754.73</v>
+        <v>1904754570.75</v>
       </c>
       <c r="H27" s="8">
-        <v>181.6</v>
+        <v>182.2</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1315,22 +1319,22 @@
         <v>57</v>
       </c>
       <c r="C28" s="6">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="D28" s="7">
-        <v>261.311111</v>
+        <v>255.173599</v>
       </c>
       <c r="E28" s="8">
-        <v>33200000</v>
+        <v>33120000</v>
       </c>
       <c r="F28" s="9">
         <v>0</v>
       </c>
       <c r="G28" s="8">
-        <v>8675528873.41</v>
+        <v>8451349584.94</v>
       </c>
       <c r="H28" s="8">
-        <v>260.6</v>
+        <v>256.5</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1341,10 +1345,10 @@
         <v>59</v>
       </c>
       <c r="C29" s="6">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="D29" s="7">
-        <v>259.598346</v>
+        <v>252.734894</v>
       </c>
       <c r="E29" s="8">
         <v>3200000</v>
@@ -1353,10 +1357,10 @@
         <v>0</v>
       </c>
       <c r="G29" s="8">
-        <v>830714706.2</v>
+        <v>808751660.45</v>
       </c>
       <c r="H29" s="8">
-        <v>259.6</v>
+        <v>253</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1367,10 +1371,10 @@
         <v>61</v>
       </c>
       <c r="C30" s="6">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="D30" s="7">
-        <v>123.267522</v>
+        <v>121.083465</v>
       </c>
       <c r="E30" s="8">
         <v>440000</v>
@@ -1379,10 +1383,10 @@
         <v>0</v>
       </c>
       <c r="G30" s="8">
-        <v>54237709.64</v>
+        <v>53276724.77</v>
       </c>
       <c r="H30" s="8">
-        <v>123.25</v>
+        <v>121.2</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1393,10 +1397,10 @@
         <v>63</v>
       </c>
       <c r="C31" s="6">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="D31" s="7">
-        <v>181.075384</v>
+        <v>176.431593</v>
       </c>
       <c r="E31" s="8">
         <v>400000</v>
@@ -1405,10 +1409,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="8">
-        <v>72430153.46</v>
+        <v>70572637.14</v>
       </c>
       <c r="H31" s="8">
-        <v>181.1</v>
+        <v>177</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1419,10 +1423,10 @@
         <v>65</v>
       </c>
       <c r="C32" s="6">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="D32" s="7">
-        <v>48.828749</v>
+        <v>47.802429</v>
       </c>
       <c r="E32" s="8">
         <v>1200000</v>
@@ -1431,10 +1435,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="8">
-        <v>58594499.04</v>
+        <v>57362915.27</v>
       </c>
       <c r="H32" s="8">
-        <v>48.8</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1445,10 +1449,10 @@
         <v>67</v>
       </c>
       <c r="C33" s="6">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="D33" s="7">
-        <v>1232.168009</v>
+        <v>1234.817137</v>
       </c>
       <c r="E33" s="8">
         <v>640000</v>
@@ -1457,10 +1461,10 @@
         <v>0</v>
       </c>
       <c r="G33" s="8">
-        <v>788587526.03</v>
+        <v>790282967.38</v>
       </c>
       <c r="H33" s="8">
-        <v>1235</v>
+        <v>1236.5</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -1471,10 +1475,10 @@
         <v>69</v>
       </c>
       <c r="C34" s="6">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="D34" s="7">
-        <v>188.905705</v>
+        <v>184.741462</v>
       </c>
       <c r="E34" s="8">
         <v>680000</v>
@@ -1483,10 +1487,10 @@
         <v>0</v>
       </c>
       <c r="G34" s="8">
-        <v>128455879.16</v>
+        <v>125624193.98</v>
       </c>
       <c r="H34" s="8">
-        <v>188.9</v>
+        <v>185.65</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -1497,22 +1501,22 @@
         <v>71</v>
       </c>
       <c r="C35" s="6">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="D35" s="7">
-        <v>1233.278156</v>
+        <v>1235.924168</v>
       </c>
       <c r="E35" s="8">
-        <v>6400000</v>
+        <v>6240000</v>
       </c>
       <c r="F35" s="9">
         <v>0</v>
       </c>
       <c r="G35" s="8">
-        <v>7892980198.67</v>
+        <v>7712166805.82</v>
       </c>
       <c r="H35" s="8">
-        <v>1236.5</v>
+        <v>1237.5</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>20.05.2026 16:12:23</t>
+    <t>21.05.2026 16:42:51</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -238,8 +238,8 @@
     <numFmt numFmtId="165" formatCode="###0.000000;-###0.000000;0"/>
     <numFmt numFmtId="166" formatCode="###0.00;-###0.00;0"/>
     <numFmt numFmtId="167" formatCode="###0;-###0;0"/>
-    <numFmt numFmtId="168" formatCode="###0.00000;-###0.00000;0"/>
-    <numFmt numFmtId="169" formatCode="###0.0000;-###0.0000;0"/>
+    <numFmt numFmtId="168" formatCode="###0.0000;-###0.0000;0"/>
+    <numFmt numFmtId="169" formatCode="###0.00000;-###0.00000;0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -747,10 +747,10 @@
         <v>13</v>
       </c>
       <c r="C6" s="6">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="D6" s="7">
-        <v>45.639355</v>
+        <v>45.176996</v>
       </c>
       <c r="E6" s="8">
         <v>58000000</v>
@@ -759,10 +759,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="8">
-        <v>2647082596.52</v>
+        <v>2620265762.88</v>
       </c>
       <c r="H6" s="8">
-        <v>45.86</v>
+        <v>45.25</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -773,10 +773,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="6">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="D7" s="7">
-        <v>37.615161</v>
+        <v>37.359764</v>
       </c>
       <c r="E7" s="8">
         <v>14400000</v>
@@ -785,10 +785,10 @@
         <v>0</v>
       </c>
       <c r="G7" s="8">
-        <v>541658323.52</v>
+        <v>537980604.89</v>
       </c>
       <c r="H7" s="8">
-        <v>37.8</v>
+        <v>37.37</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -799,22 +799,22 @@
         <v>17</v>
       </c>
       <c r="C8" s="6">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="D8" s="7">
-        <v>39.099067</v>
+        <v>39.081368</v>
       </c>
       <c r="E8" s="8">
-        <v>33700000</v>
+        <v>33900000</v>
       </c>
       <c r="F8" s="9">
         <v>0</v>
       </c>
       <c r="G8" s="8">
-        <v>1325458380.41</v>
+        <v>1324858390.21</v>
       </c>
       <c r="H8" s="8">
-        <v>39.19</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -825,10 +825,10 @@
         <v>19</v>
       </c>
       <c r="C9" s="6">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="D9" s="7">
-        <v>57.316476</v>
+        <v>57.376913</v>
       </c>
       <c r="E9" s="8">
         <v>2550000</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="G9" s="8">
-        <v>146157012.59</v>
+        <v>146311127.01</v>
       </c>
       <c r="H9" s="8">
-        <v>57.4</v>
+        <v>57.46</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -851,10 +851,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="6">
-        <v>46162</v>
-      </c>
-      <c r="D10" s="10">
-        <v>378.89284</v>
+        <v>46163</v>
+      </c>
+      <c r="D10" s="7">
+        <v>381.360109</v>
       </c>
       <c r="E10" s="8">
         <v>135000</v>
@@ -863,10 +863,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="8">
-        <v>51150533.38</v>
+        <v>51483614.71</v>
       </c>
       <c r="H10" s="8">
-        <v>379.6</v>
+        <v>381.5</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -877,10 +877,10 @@
         <v>23</v>
       </c>
       <c r="C11" s="6">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="D11" s="7">
-        <v>556.481302</v>
+        <v>555.644007</v>
       </c>
       <c r="E11" s="8">
         <v>46600000</v>
@@ -889,10 +889,10 @@
         <v>0</v>
       </c>
       <c r="G11" s="8">
-        <v>25932028674.76</v>
+        <v>25893010709.74</v>
       </c>
       <c r="H11" s="8">
-        <v>557.75</v>
+        <v>557</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -903,10 +903,10 @@
         <v>25</v>
       </c>
       <c r="C12" s="6">
-        <v>46162</v>
-      </c>
-      <c r="D12" s="11">
-        <v>689.3382</v>
+        <v>46163</v>
+      </c>
+      <c r="D12" s="7">
+        <v>685.567697</v>
       </c>
       <c r="E12" s="8">
         <v>73050000</v>
@@ -915,10 +915,10 @@
         <v>0</v>
       </c>
       <c r="G12" s="8">
-        <v>50356155526.74</v>
+        <v>50080720248.64</v>
       </c>
       <c r="H12" s="8">
-        <v>703</v>
+        <v>696.5</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -929,10 +929,10 @@
         <v>27</v>
       </c>
       <c r="C13" s="6">
-        <v>46162</v>
-      </c>
-      <c r="D13" s="7">
-        <v>4241.228195</v>
+        <v>46163</v>
+      </c>
+      <c r="D13" s="10">
+        <v>4244.9462</v>
       </c>
       <c r="E13" s="8">
         <v>266000</v>
@@ -941,7 +941,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="8">
-        <v>1128166700</v>
+        <v>1129155689.21</v>
       </c>
       <c r="H13" s="8">
         <v>4260</v>
@@ -955,10 +955,10 @@
         <v>29</v>
       </c>
       <c r="C14" s="6">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="D14" s="7">
-        <v>670.986874</v>
+        <v>662.944614</v>
       </c>
       <c r="E14" s="8">
         <v>113800000</v>
@@ -967,10 +967,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="8">
-        <v>76358306209.97</v>
+        <v>75443097073.74</v>
       </c>
       <c r="H14" s="8">
-        <v>681</v>
+        <v>687</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -981,10 +981,10 @@
         <v>31</v>
       </c>
       <c r="C15" s="6">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="D15" s="7">
-        <v>551.485633</v>
+        <v>544.398099</v>
       </c>
       <c r="E15" s="8">
         <v>33450000</v>
@@ -993,10 +993,10 @@
         <v>0</v>
       </c>
       <c r="G15" s="8">
-        <v>18447194429.98</v>
+        <v>18210116405.2</v>
       </c>
       <c r="H15" s="8">
-        <v>553.75</v>
+        <v>552</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1007,10 +1007,10 @@
         <v>33</v>
       </c>
       <c r="C16" s="6">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="D16" s="7">
-        <v>25.756076</v>
+        <v>25.964799</v>
       </c>
       <c r="E16" s="8">
         <v>10800000</v>
@@ -1019,10 +1019,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="8">
-        <v>278165618.93</v>
+        <v>280419827.01</v>
       </c>
       <c r="H16" s="8">
-        <v>25.83</v>
+        <v>25.99</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1033,10 +1033,10 @@
         <v>35</v>
       </c>
       <c r="C17" s="6">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="D17" s="7">
-        <v>46.362446</v>
+        <v>46.410104</v>
       </c>
       <c r="E17" s="8">
         <v>1625000</v>
@@ -1045,10 +1045,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="8">
-        <v>75338975.1</v>
+        <v>75416419.76</v>
       </c>
       <c r="H17" s="8">
-        <v>46.42</v>
+        <v>46.46</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1059,10 +1059,10 @@
         <v>37</v>
       </c>
       <c r="C18" s="6">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="D18" s="7">
-        <v>73.460148</v>
+        <v>72.955811</v>
       </c>
       <c r="E18" s="8">
         <v>1140000</v>
@@ -1071,10 +1071,10 @@
         <v>0</v>
       </c>
       <c r="G18" s="8">
-        <v>83744568.71</v>
+        <v>83169624.91</v>
       </c>
       <c r="H18" s="8">
-        <v>73.5</v>
+        <v>73.48</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1085,10 +1085,10 @@
         <v>39</v>
       </c>
       <c r="C19" s="6">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="D19" s="7">
-        <v>84.390019</v>
+        <v>84.408036</v>
       </c>
       <c r="E19" s="8">
         <v>1155000</v>
@@ -1097,10 +1097,10 @@
         <v>0</v>
       </c>
       <c r="G19" s="8">
-        <v>97470471.68</v>
+        <v>97491281.25</v>
       </c>
       <c r="H19" s="8">
-        <v>84.68</v>
+        <v>84.26</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1111,10 +1111,10 @@
         <v>41</v>
       </c>
       <c r="C20" s="6">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="D20" s="7">
-        <v>51.699128</v>
+        <v>51.792717</v>
       </c>
       <c r="E20" s="8">
         <v>2985000</v>
@@ -1123,10 +1123,10 @@
         <v>0</v>
       </c>
       <c r="G20" s="8">
-        <v>154321896.96</v>
+        <v>154601260.09</v>
       </c>
       <c r="H20" s="8">
-        <v>51.92</v>
+        <v>51.82</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1137,10 +1137,10 @@
         <v>43</v>
       </c>
       <c r="C21" s="6">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="D21" s="7">
-        <v>167.274031</v>
+        <v>166.731039</v>
       </c>
       <c r="E21" s="8">
         <v>600000</v>
@@ -1149,10 +1149,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="8">
-        <v>100364418.46</v>
+        <v>100038623.34</v>
       </c>
       <c r="H21" s="8">
-        <v>167.65</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1163,22 +1163,22 @@
         <v>45</v>
       </c>
       <c r="C22" s="6">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="D22" s="7">
-        <v>211.352011</v>
+        <v>211.384291</v>
       </c>
       <c r="E22" s="8">
-        <v>119560000</v>
+        <v>119840000</v>
       </c>
       <c r="F22" s="9">
         <v>0</v>
       </c>
       <c r="G22" s="8">
-        <v>25269246470.11</v>
+        <v>25332293435.73</v>
       </c>
       <c r="H22" s="8">
-        <v>212.25</v>
+        <v>212.55</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1189,22 +1189,22 @@
         <v>47</v>
       </c>
       <c r="C23" s="6">
-        <v>46162</v>
-      </c>
-      <c r="D23" s="10">
-        <v>193.76411</v>
+        <v>46163</v>
+      </c>
+      <c r="D23" s="11">
+        <v>191.78358</v>
       </c>
       <c r="E23" s="8">
-        <v>205440000</v>
+        <v>206680000</v>
       </c>
       <c r="F23" s="9">
         <v>0</v>
       </c>
       <c r="G23" s="8">
-        <v>39806898696.16</v>
+        <v>39637830374.58</v>
       </c>
       <c r="H23" s="8">
-        <v>196</v>
+        <v>193.25</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1215,10 +1215,10 @@
         <v>49</v>
       </c>
       <c r="C24" s="6">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="D24" s="7">
-        <v>194.864693</v>
+        <v>195.600529</v>
       </c>
       <c r="E24" s="8">
         <v>360000</v>
@@ -1227,10 +1227,10 @@
         <v>0</v>
       </c>
       <c r="G24" s="8">
-        <v>70151289.41</v>
+        <v>70416190.27</v>
       </c>
       <c r="H24" s="8">
-        <v>195.5</v>
+        <v>194</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1241,10 +1241,10 @@
         <v>51</v>
       </c>
       <c r="C25" s="6">
-        <v>46162</v>
-      </c>
-      <c r="D25" s="10">
-        <v>120.72158</v>
+        <v>46163</v>
+      </c>
+      <c r="D25" s="7">
+        <v>121.127096</v>
       </c>
       <c r="E25" s="8">
         <v>600000</v>
@@ -1253,10 +1253,10 @@
         <v>0</v>
       </c>
       <c r="G25" s="8">
-        <v>72432948.02</v>
+        <v>72676257.66</v>
       </c>
       <c r="H25" s="8">
-        <v>121.45</v>
+        <v>124</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1267,10 +1267,10 @@
         <v>53</v>
       </c>
       <c r="C26" s="6">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="D26" s="7">
-        <v>677.964379</v>
+        <v>677.333893</v>
       </c>
       <c r="E26" s="8">
         <v>152040000</v>
@@ -1279,10 +1279,10 @@
         <v>0</v>
       </c>
       <c r="G26" s="8">
-        <v>103077704167.22</v>
+        <v>102981845066.3</v>
       </c>
       <c r="H26" s="8">
-        <v>691</v>
+        <v>695</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1293,10 +1293,10 @@
         <v>55</v>
       </c>
       <c r="C27" s="6">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="D27" s="7">
-        <v>178.347806</v>
+        <v>178.479879</v>
       </c>
       <c r="E27" s="8">
         <v>10680000</v>
@@ -1305,10 +1305,10 @@
         <v>0</v>
       </c>
       <c r="G27" s="8">
-        <v>1904754570.75</v>
+        <v>1906165107.31</v>
       </c>
       <c r="H27" s="8">
-        <v>182.2</v>
+        <v>179.25</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1319,10 +1319,10 @@
         <v>57</v>
       </c>
       <c r="C28" s="6">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="D28" s="7">
-        <v>255.173599</v>
+        <v>253.258086</v>
       </c>
       <c r="E28" s="8">
         <v>33120000</v>
@@ -1331,10 +1331,10 @@
         <v>0</v>
       </c>
       <c r="G28" s="8">
-        <v>8451349584.94</v>
+        <v>8387907809.72</v>
       </c>
       <c r="H28" s="8">
-        <v>256.5</v>
+        <v>254</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1345,10 +1345,10 @@
         <v>59</v>
       </c>
       <c r="C29" s="6">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="D29" s="7">
-        <v>252.734894</v>
+        <v>251.010158</v>
       </c>
       <c r="E29" s="8">
         <v>3200000</v>
@@ -1357,10 +1357,10 @@
         <v>0</v>
       </c>
       <c r="G29" s="8">
-        <v>808751660.45</v>
+        <v>803232506</v>
       </c>
       <c r="H29" s="8">
-        <v>253</v>
+        <v>251.6</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1371,10 +1371,10 @@
         <v>61</v>
       </c>
       <c r="C30" s="6">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="D30" s="7">
-        <v>121.083465</v>
+        <v>120.899815</v>
       </c>
       <c r="E30" s="8">
         <v>440000</v>
@@ -1383,10 +1383,10 @@
         <v>0</v>
       </c>
       <c r="G30" s="8">
-        <v>53276724.77</v>
+        <v>53195918.62</v>
       </c>
       <c r="H30" s="8">
-        <v>121.2</v>
+        <v>121.05</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1397,10 +1397,10 @@
         <v>63</v>
       </c>
       <c r="C31" s="6">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="D31" s="7">
-        <v>176.431593</v>
+        <v>177.907201</v>
       </c>
       <c r="E31" s="8">
         <v>400000</v>
@@ -1409,10 +1409,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="8">
-        <v>70572637.14</v>
+        <v>71162880.26</v>
       </c>
       <c r="H31" s="8">
-        <v>177</v>
+        <v>177.65</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1423,10 +1423,10 @@
         <v>65</v>
       </c>
       <c r="C32" s="6">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="D32" s="7">
-        <v>47.802429</v>
+        <v>47.668278</v>
       </c>
       <c r="E32" s="8">
         <v>1200000</v>
@@ -1435,7 +1435,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="8">
-        <v>57362915.27</v>
+        <v>57201933.1</v>
       </c>
       <c r="H32" s="8">
         <v>48</v>
@@ -1449,10 +1449,10 @@
         <v>67</v>
       </c>
       <c r="C33" s="6">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="D33" s="7">
-        <v>1234.817137</v>
+        <v>1236.142226</v>
       </c>
       <c r="E33" s="8">
         <v>640000</v>
@@ -1461,10 +1461,10 @@
         <v>0</v>
       </c>
       <c r="G33" s="8">
-        <v>790282967.38</v>
+        <v>791131024.43</v>
       </c>
       <c r="H33" s="8">
-        <v>1236.5</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -1475,10 +1475,10 @@
         <v>69</v>
       </c>
       <c r="C34" s="6">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="D34" s="7">
-        <v>184.741462</v>
+        <v>185.095677</v>
       </c>
       <c r="E34" s="8">
         <v>680000</v>
@@ -1487,10 +1487,10 @@
         <v>0</v>
       </c>
       <c r="G34" s="8">
-        <v>125624193.98</v>
+        <v>125865060.61</v>
       </c>
       <c r="H34" s="8">
-        <v>185.65</v>
+        <v>185.5</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -1501,10 +1501,10 @@
         <v>71</v>
       </c>
       <c r="C35" s="6">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="D35" s="7">
-        <v>1235.924168</v>
+        <v>1237.249655</v>
       </c>
       <c r="E35" s="8">
         <v>6240000</v>
@@ -1513,10 +1513,10 @@
         <v>0</v>
       </c>
       <c r="G35" s="8">
-        <v>7712166805.82</v>
+        <v>7720437847.55</v>
       </c>
       <c r="H35" s="8">
-        <v>1237.5</v>
+        <v>1238.5</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>21.05.2026 16:42:51</t>
+    <t>22.05.2026 17:23:38</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -233,13 +233,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="###0.000000;-###0.000000;0"/>
     <numFmt numFmtId="166" formatCode="###0.00;-###0.00;0"/>
     <numFmt numFmtId="167" formatCode="###0;-###0;0"/>
-    <numFmt numFmtId="168" formatCode="###0.0000;-###0.0000;0"/>
-    <numFmt numFmtId="169" formatCode="###0.00000;-###0.00000;0"/>
+    <numFmt numFmtId="168" formatCode="###0.00000;-###0.00000;0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -309,7 +308,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -335,9 +334,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -747,10 +743,10 @@
         <v>13</v>
       </c>
       <c r="C6" s="6">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="D6" s="7">
-        <v>45.176996</v>
+        <v>41.325645</v>
       </c>
       <c r="E6" s="8">
         <v>58000000</v>
@@ -759,10 +755,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="8">
-        <v>2620265762.88</v>
+        <v>2396887428.76</v>
       </c>
       <c r="H6" s="8">
-        <v>45.25</v>
+        <v>43.35</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -773,10 +769,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="6">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="D7" s="7">
-        <v>37.359764</v>
+        <v>35.364116</v>
       </c>
       <c r="E7" s="8">
         <v>14400000</v>
@@ -785,10 +781,10 @@
         <v>0</v>
       </c>
       <c r="G7" s="8">
-        <v>537980604.89</v>
+        <v>509243272.12</v>
       </c>
       <c r="H7" s="8">
-        <v>37.37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -799,10 +795,10 @@
         <v>17</v>
       </c>
       <c r="C8" s="6">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="D8" s="7">
-        <v>39.081368</v>
+        <v>36.767812</v>
       </c>
       <c r="E8" s="8">
         <v>33900000</v>
@@ -811,10 +807,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="8">
-        <v>1324858390.21</v>
+        <v>1246428815.58</v>
       </c>
       <c r="H8" s="8">
-        <v>39.5</v>
+        <v>36.99</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -825,22 +821,22 @@
         <v>19</v>
       </c>
       <c r="C9" s="6">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="D9" s="7">
-        <v>57.376913</v>
+        <v>57.437827</v>
       </c>
       <c r="E9" s="8">
-        <v>2550000</v>
+        <v>2250000</v>
       </c>
       <c r="F9" s="9">
         <v>0</v>
       </c>
       <c r="G9" s="8">
-        <v>146311127.01</v>
+        <v>129235109.65</v>
       </c>
       <c r="H9" s="8">
-        <v>57.46</v>
+        <v>57.62</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -851,10 +847,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="6">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="D10" s="7">
-        <v>381.360109</v>
+        <v>347.153213</v>
       </c>
       <c r="E10" s="8">
         <v>135000</v>
@@ -863,10 +859,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="8">
-        <v>51483614.71</v>
+        <v>46865683.69</v>
       </c>
       <c r="H10" s="8">
-        <v>381.5</v>
+        <v>350</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -877,10 +873,10 @@
         <v>23</v>
       </c>
       <c r="C11" s="6">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="D11" s="7">
-        <v>555.644007</v>
+        <v>553.018911</v>
       </c>
       <c r="E11" s="8">
         <v>46600000</v>
@@ -889,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="G11" s="8">
-        <v>25893010709.74</v>
+        <v>25770681251.58</v>
       </c>
       <c r="H11" s="8">
-        <v>557</v>
+        <v>555.25</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -903,10 +899,10 @@
         <v>25</v>
       </c>
       <c r="C12" s="6">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="D12" s="7">
-        <v>685.567697</v>
+        <v>678.851357</v>
       </c>
       <c r="E12" s="8">
         <v>73050000</v>
@@ -915,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="G12" s="8">
-        <v>50080720248.64</v>
+        <v>49590091617.3</v>
       </c>
       <c r="H12" s="8">
-        <v>696.5</v>
+        <v>686</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -929,10 +925,10 @@
         <v>27</v>
       </c>
       <c r="C13" s="6">
-        <v>46163</v>
-      </c>
-      <c r="D13" s="10">
-        <v>4244.9462</v>
+        <v>46164</v>
+      </c>
+      <c r="D13" s="7">
+        <v>4248.320871</v>
       </c>
       <c r="E13" s="8">
         <v>266000</v>
@@ -941,10 +937,10 @@
         <v>0</v>
       </c>
       <c r="G13" s="8">
-        <v>1129155689.21</v>
+        <v>1130053351.63</v>
       </c>
       <c r="H13" s="8">
-        <v>4260</v>
+        <v>4283</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -955,10 +951,10 @@
         <v>29</v>
       </c>
       <c r="C14" s="6">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="D14" s="7">
-        <v>662.944614</v>
+        <v>664.622753</v>
       </c>
       <c r="E14" s="8">
         <v>113800000</v>
@@ -967,7 +963,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="8">
-        <v>75443097073.74</v>
+        <v>75634069267.1</v>
       </c>
       <c r="H14" s="8">
         <v>687</v>
@@ -981,10 +977,10 @@
         <v>31</v>
       </c>
       <c r="C15" s="6">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="D15" s="7">
-        <v>544.398099</v>
+        <v>547.638977</v>
       </c>
       <c r="E15" s="8">
         <v>33450000</v>
@@ -993,10 +989,10 @@
         <v>0</v>
       </c>
       <c r="G15" s="8">
-        <v>18210116405.2</v>
+        <v>18318523765.32</v>
       </c>
       <c r="H15" s="8">
-        <v>552</v>
+        <v>549.75</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1007,10 +1003,10 @@
         <v>33</v>
       </c>
       <c r="C16" s="6">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="D16" s="7">
-        <v>25.964799</v>
+        <v>24.500774</v>
       </c>
       <c r="E16" s="8">
         <v>10800000</v>
@@ -1019,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="8">
-        <v>280419827.01</v>
+        <v>264608355.01</v>
       </c>
       <c r="H16" s="8">
-        <v>25.99</v>
+        <v>25.01</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1033,10 +1029,10 @@
         <v>35</v>
       </c>
       <c r="C17" s="6">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="D17" s="7">
-        <v>46.410104</v>
+        <v>46.457824</v>
       </c>
       <c r="E17" s="8">
         <v>1625000</v>
@@ -1045,10 +1041,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="8">
-        <v>75416419.76</v>
+        <v>75493964.49</v>
       </c>
       <c r="H17" s="8">
-        <v>46.46</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1059,10 +1055,10 @@
         <v>37</v>
       </c>
       <c r="C18" s="6">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="D18" s="7">
-        <v>72.955811</v>
+        <v>68.588167</v>
       </c>
       <c r="E18" s="8">
         <v>1140000</v>
@@ -1071,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="G18" s="8">
-        <v>83169624.91</v>
+        <v>78190509.98</v>
       </c>
       <c r="H18" s="8">
-        <v>73.48</v>
+        <v>70.18</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1085,10 +1081,10 @@
         <v>39</v>
       </c>
       <c r="C19" s="6">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="D19" s="7">
-        <v>84.408036</v>
+        <v>79.547411</v>
       </c>
       <c r="E19" s="8">
         <v>1155000</v>
@@ -1097,10 +1093,10 @@
         <v>0</v>
       </c>
       <c r="G19" s="8">
-        <v>97491281.25</v>
+        <v>91877259.39</v>
       </c>
       <c r="H19" s="8">
-        <v>84.26</v>
+        <v>82.9</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1111,10 +1107,10 @@
         <v>41</v>
       </c>
       <c r="C20" s="6">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="D20" s="7">
-        <v>51.792717</v>
+        <v>48.932791</v>
       </c>
       <c r="E20" s="8">
         <v>2985000</v>
@@ -1123,10 +1119,10 @@
         <v>0</v>
       </c>
       <c r="G20" s="8">
-        <v>154601260.09</v>
+        <v>146064379.82</v>
       </c>
       <c r="H20" s="8">
-        <v>51.82</v>
+        <v>49.44</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1137,10 +1133,10 @@
         <v>43</v>
       </c>
       <c r="C21" s="6">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="D21" s="7">
-        <v>166.731039</v>
+        <v>158.721131</v>
       </c>
       <c r="E21" s="8">
         <v>600000</v>
@@ -1149,10 +1145,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="8">
-        <v>100038623.34</v>
+        <v>95232678.5</v>
       </c>
       <c r="H21" s="8">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1163,22 +1159,22 @@
         <v>45</v>
       </c>
       <c r="C22" s="6">
-        <v>46163</v>
-      </c>
-      <c r="D22" s="7">
-        <v>211.384291</v>
+        <v>46164</v>
+      </c>
+      <c r="D22" s="10">
+        <v>198.73814</v>
       </c>
       <c r="E22" s="8">
-        <v>119840000</v>
+        <v>119800000</v>
       </c>
       <c r="F22" s="9">
         <v>0</v>
       </c>
       <c r="G22" s="8">
-        <v>25332293435.73</v>
+        <v>23808829224.64</v>
       </c>
       <c r="H22" s="8">
-        <v>212.55</v>
+        <v>200</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1189,22 +1185,22 @@
         <v>47</v>
       </c>
       <c r="C23" s="6">
-        <v>46163</v>
-      </c>
-      <c r="D23" s="11">
-        <v>191.78358</v>
+        <v>46164</v>
+      </c>
+      <c r="D23" s="7">
+        <v>175.216873</v>
       </c>
       <c r="E23" s="8">
-        <v>206680000</v>
+        <v>207000000</v>
       </c>
       <c r="F23" s="9">
         <v>0</v>
       </c>
       <c r="G23" s="8">
-        <v>39637830374.58</v>
+        <v>36269892629.67</v>
       </c>
       <c r="H23" s="8">
-        <v>193.25</v>
+        <v>173.95</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1215,10 +1211,10 @@
         <v>49</v>
       </c>
       <c r="C24" s="6">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="D24" s="7">
-        <v>195.600529</v>
+        <v>183.434305</v>
       </c>
       <c r="E24" s="8">
         <v>360000</v>
@@ -1227,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="G24" s="8">
-        <v>70416190.27</v>
+        <v>66036349.69</v>
       </c>
       <c r="H24" s="8">
-        <v>194</v>
+        <v>183.85</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1241,10 +1237,10 @@
         <v>51</v>
       </c>
       <c r="C25" s="6">
-        <v>46163</v>
-      </c>
-      <c r="D25" s="7">
-        <v>121.127096</v>
+        <v>46164</v>
+      </c>
+      <c r="D25" s="10">
+        <v>112.76042</v>
       </c>
       <c r="E25" s="8">
         <v>600000</v>
@@ -1253,10 +1249,10 @@
         <v>0</v>
       </c>
       <c r="G25" s="8">
-        <v>72676257.66</v>
+        <v>67656251.73</v>
       </c>
       <c r="H25" s="8">
-        <v>124</v>
+        <v>118.95</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1267,10 +1263,10 @@
         <v>53</v>
       </c>
       <c r="C26" s="6">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="D26" s="7">
-        <v>677.333893</v>
+        <v>672.546978</v>
       </c>
       <c r="E26" s="8">
         <v>152040000</v>
@@ -1279,7 +1275,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="8">
-        <v>102981845066.3</v>
+        <v>102254042485.1</v>
       </c>
       <c r="H26" s="8">
         <v>695</v>
@@ -1293,10 +1289,10 @@
         <v>55</v>
       </c>
       <c r="C27" s="6">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="D27" s="7">
-        <v>178.479879</v>
+        <v>166.398498</v>
       </c>
       <c r="E27" s="8">
         <v>10680000</v>
@@ -1305,10 +1301,10 @@
         <v>0</v>
       </c>
       <c r="G27" s="8">
-        <v>1906165107.31</v>
+        <v>1777135962.97</v>
       </c>
       <c r="H27" s="8">
-        <v>179.25</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1319,22 +1315,22 @@
         <v>57</v>
       </c>
       <c r="C28" s="6">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="D28" s="7">
-        <v>253.258086</v>
+        <v>237.411038</v>
       </c>
       <c r="E28" s="8">
-        <v>33120000</v>
+        <v>32440000</v>
       </c>
       <c r="F28" s="9">
         <v>0</v>
       </c>
       <c r="G28" s="8">
-        <v>8387907809.72</v>
+        <v>7701614075.86</v>
       </c>
       <c r="H28" s="8">
-        <v>254</v>
+        <v>237.1</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1345,10 +1341,10 @@
         <v>59</v>
       </c>
       <c r="C29" s="6">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="D29" s="7">
-        <v>251.010158</v>
+        <v>237.580892</v>
       </c>
       <c r="E29" s="8">
         <v>3200000</v>
@@ -1357,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="G29" s="8">
-        <v>803232506</v>
+        <v>760258855.61</v>
       </c>
       <c r="H29" s="8">
-        <v>251.6</v>
+        <v>237.55</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1371,10 +1367,10 @@
         <v>61</v>
       </c>
       <c r="C30" s="6">
-        <v>46163</v>
-      </c>
-      <c r="D30" s="7">
-        <v>120.899815</v>
+        <v>46164</v>
+      </c>
+      <c r="D30" s="10">
+        <v>113.69428</v>
       </c>
       <c r="E30" s="8">
         <v>440000</v>
@@ -1383,10 +1379,10 @@
         <v>0</v>
       </c>
       <c r="G30" s="8">
-        <v>53195918.62</v>
+        <v>50025483.32</v>
       </c>
       <c r="H30" s="8">
-        <v>121.05</v>
+        <v>114.75</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1397,10 +1393,10 @@
         <v>63</v>
       </c>
       <c r="C31" s="6">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="D31" s="7">
-        <v>177.907201</v>
+        <v>167.465568</v>
       </c>
       <c r="E31" s="8">
         <v>400000</v>
@@ -1409,10 +1405,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="8">
-        <v>71162880.26</v>
+        <v>66986227.34</v>
       </c>
       <c r="H31" s="8">
-        <v>177.65</v>
+        <v>172.45</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1423,10 +1419,10 @@
         <v>65</v>
       </c>
       <c r="C32" s="6">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="D32" s="7">
-        <v>47.668278</v>
+        <v>44.931846</v>
       </c>
       <c r="E32" s="8">
         <v>1200000</v>
@@ -1435,10 +1431,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="8">
-        <v>57201933.1</v>
+        <v>53918215.32</v>
       </c>
       <c r="H32" s="8">
-        <v>48</v>
+        <v>46.47</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1449,10 +1445,10 @@
         <v>67</v>
       </c>
       <c r="C33" s="6">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="D33" s="7">
-        <v>1236.142226</v>
+        <v>1237.467062</v>
       </c>
       <c r="E33" s="8">
         <v>640000</v>
@@ -1461,10 +1457,10 @@
         <v>0</v>
       </c>
       <c r="G33" s="8">
-        <v>791131024.43</v>
+        <v>791978919.84</v>
       </c>
       <c r="H33" s="8">
-        <v>1238</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -1475,10 +1471,10 @@
         <v>69</v>
       </c>
       <c r="C34" s="6">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="D34" s="7">
-        <v>185.095677</v>
+        <v>174.565008</v>
       </c>
       <c r="E34" s="8">
         <v>680000</v>
@@ -1487,10 +1483,10 @@
         <v>0</v>
       </c>
       <c r="G34" s="8">
-        <v>125865060.61</v>
+        <v>118704205.28</v>
       </c>
       <c r="H34" s="8">
-        <v>185.5</v>
+        <v>174.55</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -1501,10 +1497,10 @@
         <v>71</v>
       </c>
       <c r="C35" s="6">
-        <v>46163</v>
-      </c>
-      <c r="D35" s="7">
-        <v>1237.249655</v>
+        <v>46164</v>
+      </c>
+      <c r="D35" s="10">
+        <v>1238.57683</v>
       </c>
       <c r="E35" s="8">
         <v>6240000</v>
@@ -1513,10 +1509,10 @@
         <v>0</v>
       </c>
       <c r="G35" s="8">
-        <v>7720437847.55</v>
+        <v>7728719418.48</v>
       </c>
       <c r="H35" s="8">
-        <v>1238.5</v>
+        <v>1243</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>22.05.2026 17:23:38</t>
+    <t>25.05.2026 13:29:13</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -743,10 +743,10 @@
         <v>13</v>
       </c>
       <c r="C6" s="6">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="D6" s="7">
-        <v>41.325645</v>
+        <v>42.495237</v>
       </c>
       <c r="E6" s="8">
         <v>58000000</v>
@@ -755,10 +755,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="8">
-        <v>2396887428.76</v>
+        <v>2464723741.76</v>
       </c>
       <c r="H6" s="8">
-        <v>43.35</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -769,10 +769,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="6">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="D7" s="7">
-        <v>35.364116</v>
+        <v>37.300952</v>
       </c>
       <c r="E7" s="8">
         <v>14400000</v>
@@ -781,10 +781,10 @@
         <v>0</v>
       </c>
       <c r="G7" s="8">
-        <v>509243272.12</v>
+        <v>537133708.75</v>
       </c>
       <c r="H7" s="8">
-        <v>35</v>
+        <v>37.3</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -795,10 +795,10 @@
         <v>17</v>
       </c>
       <c r="C8" s="6">
-        <v>46164</v>
-      </c>
-      <c r="D8" s="7">
-        <v>36.767812</v>
+        <v>46167</v>
+      </c>
+      <c r="D8" s="10">
+        <v>38.51606</v>
       </c>
       <c r="E8" s="8">
         <v>33900000</v>
@@ -807,10 +807,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="8">
-        <v>1246428815.58</v>
+        <v>1305694445.03</v>
       </c>
       <c r="H8" s="8">
-        <v>36.99</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -821,10 +821,10 @@
         <v>19</v>
       </c>
       <c r="C9" s="6">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="D9" s="7">
-        <v>57.437827</v>
+        <v>57.620562</v>
       </c>
       <c r="E9" s="8">
         <v>2250000</v>
@@ -833,10 +833,10 @@
         <v>0</v>
       </c>
       <c r="G9" s="8">
-        <v>129235109.65</v>
+        <v>129646265.09</v>
       </c>
       <c r="H9" s="8">
-        <v>57.62</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -847,10 +847,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="6">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="D10" s="7">
-        <v>347.153213</v>
+        <v>363.777193</v>
       </c>
       <c r="E10" s="8">
         <v>135000</v>
@@ -859,10 +859,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="8">
-        <v>46865683.69</v>
+        <v>49109921.04</v>
       </c>
       <c r="H10" s="8">
-        <v>350</v>
+        <v>364.2</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -873,22 +873,22 @@
         <v>23</v>
       </c>
       <c r="C11" s="6">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="D11" s="7">
-        <v>553.018911</v>
+        <v>555.861887</v>
       </c>
       <c r="E11" s="8">
-        <v>46600000</v>
+        <v>46350000</v>
       </c>
       <c r="F11" s="9">
         <v>0</v>
       </c>
       <c r="G11" s="8">
-        <v>25770681251.58</v>
+        <v>25764198442.16</v>
       </c>
       <c r="H11" s="8">
-        <v>555.25</v>
+        <v>562</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -899,22 +899,22 @@
         <v>25</v>
       </c>
       <c r="C12" s="6">
-        <v>46164</v>
-      </c>
-      <c r="D12" s="7">
-        <v>678.851357</v>
+        <v>46167</v>
+      </c>
+      <c r="D12" s="10">
+        <v>685.92583</v>
       </c>
       <c r="E12" s="8">
-        <v>73050000</v>
+        <v>73300000</v>
       </c>
       <c r="F12" s="9">
         <v>0</v>
       </c>
       <c r="G12" s="8">
-        <v>49590091617.3</v>
+        <v>50278363332.4</v>
       </c>
       <c r="H12" s="8">
-        <v>686</v>
+        <v>697.75</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -925,22 +925,22 @@
         <v>27</v>
       </c>
       <c r="C13" s="6">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="D13" s="7">
-        <v>4248.320871</v>
+        <v>4261.086389</v>
       </c>
       <c r="E13" s="8">
-        <v>266000</v>
+        <v>280000</v>
       </c>
       <c r="F13" s="9">
         <v>0</v>
       </c>
       <c r="G13" s="8">
-        <v>1130053351.63</v>
+        <v>1193104188.86</v>
       </c>
       <c r="H13" s="8">
-        <v>4283</v>
+        <v>4337</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -951,10 +951,10 @@
         <v>29</v>
       </c>
       <c r="C14" s="6">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="D14" s="7">
-        <v>664.622753</v>
+        <v>665.969802</v>
       </c>
       <c r="E14" s="8">
         <v>113800000</v>
@@ -963,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="8">
-        <v>75634069267.1</v>
+        <v>75787363413.9</v>
       </c>
       <c r="H14" s="8">
-        <v>687</v>
+        <v>690</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -977,10 +977,10 @@
         <v>31</v>
       </c>
       <c r="C15" s="6">
-        <v>46164</v>
-      </c>
-      <c r="D15" s="7">
-        <v>547.638977</v>
+        <v>46167</v>
+      </c>
+      <c r="D15" s="10">
+        <v>547.36196</v>
       </c>
       <c r="E15" s="8">
         <v>33450000</v>
@@ -989,10 +989,10 @@
         <v>0</v>
       </c>
       <c r="G15" s="8">
-        <v>18318523765.32</v>
+        <v>18309257571.24</v>
       </c>
       <c r="H15" s="8">
-        <v>549.75</v>
+        <v>555.25</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1003,10 +1003,10 @@
         <v>33</v>
       </c>
       <c r="C16" s="6">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="D16" s="7">
-        <v>24.500774</v>
+        <v>25.585236</v>
       </c>
       <c r="E16" s="8">
         <v>10800000</v>
@@ -1015,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="8">
-        <v>264608355.01</v>
+        <v>276320549.59</v>
       </c>
       <c r="H16" s="8">
-        <v>25.01</v>
+        <v>25.64</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1029,10 +1029,10 @@
         <v>35</v>
       </c>
       <c r="C17" s="6">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="D17" s="7">
-        <v>46.457824</v>
+        <v>46.602175</v>
       </c>
       <c r="E17" s="8">
         <v>1625000</v>
@@ -1041,10 +1041,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="8">
-        <v>75493964.49</v>
+        <v>75728534.47</v>
       </c>
       <c r="H17" s="8">
-        <v>46.6</v>
+        <v>46.94</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1055,10 +1055,10 @@
         <v>37</v>
       </c>
       <c r="C18" s="6">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="D18" s="7">
-        <v>68.588167</v>
+        <v>72.084101</v>
       </c>
       <c r="E18" s="8">
         <v>1140000</v>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="G18" s="8">
-        <v>78190509.98</v>
+        <v>82175875.61</v>
       </c>
       <c r="H18" s="8">
-        <v>70.18</v>
+        <v>71.72</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1081,10 +1081,10 @@
         <v>39</v>
       </c>
       <c r="C19" s="6">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="D19" s="7">
-        <v>79.547411</v>
+        <v>83.189759</v>
       </c>
       <c r="E19" s="8">
         <v>1155000</v>
@@ -1093,10 +1093,10 @@
         <v>0</v>
       </c>
       <c r="G19" s="8">
-        <v>91877259.39</v>
+        <v>96084171.67</v>
       </c>
       <c r="H19" s="8">
-        <v>82.9</v>
+        <v>82.74</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1107,10 +1107,10 @@
         <v>41</v>
       </c>
       <c r="C20" s="6">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="D20" s="7">
-        <v>48.932791</v>
+        <v>50.764988</v>
       </c>
       <c r="E20" s="8">
         <v>2985000</v>
@@ -1119,10 +1119,10 @@
         <v>0</v>
       </c>
       <c r="G20" s="8">
-        <v>146064379.82</v>
+        <v>151533489.02</v>
       </c>
       <c r="H20" s="8">
-        <v>49.44</v>
+        <v>51.24</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1133,10 +1133,10 @@
         <v>43</v>
       </c>
       <c r="C21" s="6">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="D21" s="7">
-        <v>158.721131</v>
+        <v>163.312905</v>
       </c>
       <c r="E21" s="8">
         <v>600000</v>
@@ -1145,10 +1145,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="8">
-        <v>95232678.5</v>
+        <v>97987743.02</v>
       </c>
       <c r="H21" s="8">
-        <v>163</v>
+        <v>163.8</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1159,22 +1159,22 @@
         <v>45</v>
       </c>
       <c r="C22" s="6">
-        <v>46164</v>
-      </c>
-      <c r="D22" s="10">
-        <v>198.73814</v>
+        <v>46167</v>
+      </c>
+      <c r="D22" s="7">
+        <v>208.230328</v>
       </c>
       <c r="E22" s="8">
-        <v>119800000</v>
+        <v>116840000</v>
       </c>
       <c r="F22" s="9">
         <v>0</v>
       </c>
       <c r="G22" s="8">
-        <v>23808829224.64</v>
+        <v>24329631512.58</v>
       </c>
       <c r="H22" s="8">
-        <v>200</v>
+        <v>209.8</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1185,22 +1185,22 @@
         <v>47</v>
       </c>
       <c r="C23" s="6">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="D23" s="7">
-        <v>175.216873</v>
+        <v>180.280965</v>
       </c>
       <c r="E23" s="8">
-        <v>207000000</v>
+        <v>207320000</v>
       </c>
       <c r="F23" s="9">
         <v>0</v>
       </c>
       <c r="G23" s="8">
-        <v>36269892629.67</v>
+        <v>37375849600</v>
       </c>
       <c r="H23" s="8">
-        <v>173.95</v>
+        <v>181.45</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1211,10 +1211,10 @@
         <v>49</v>
       </c>
       <c r="C24" s="6">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="D24" s="7">
-        <v>183.434305</v>
+        <v>191.998632</v>
       </c>
       <c r="E24" s="8">
         <v>360000</v>
@@ -1223,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="G24" s="8">
-        <v>66036349.69</v>
+        <v>69119507.55</v>
       </c>
       <c r="H24" s="8">
-        <v>183.85</v>
+        <v>193.6</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1237,10 +1237,10 @@
         <v>51</v>
       </c>
       <c r="C25" s="6">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="D25" s="10">
-        <v>112.76042</v>
+        <v>118.00706</v>
       </c>
       <c r="E25" s="8">
         <v>600000</v>
@@ -1249,10 +1249,10 @@
         <v>0</v>
       </c>
       <c r="G25" s="8">
-        <v>67656251.73</v>
+        <v>70804236.12</v>
       </c>
       <c r="H25" s="8">
-        <v>118.95</v>
+        <v>121.5</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1263,10 +1263,10 @@
         <v>53</v>
       </c>
       <c r="C26" s="6">
-        <v>46164</v>
-      </c>
-      <c r="D26" s="7">
-        <v>672.546978</v>
+        <v>46167</v>
+      </c>
+      <c r="D26" s="10">
+        <v>675.78871</v>
       </c>
       <c r="E26" s="8">
         <v>152040000</v>
@@ -1275,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="G26" s="8">
-        <v>102254042485.1</v>
+        <v>102746915446.59</v>
       </c>
       <c r="H26" s="8">
-        <v>695</v>
+        <v>699</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1289,10 +1289,10 @@
         <v>55</v>
       </c>
       <c r="C27" s="6">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="D27" s="7">
-        <v>166.398498</v>
+        <v>175.768456</v>
       </c>
       <c r="E27" s="8">
         <v>10680000</v>
@@ -1301,10 +1301,10 @@
         <v>0</v>
       </c>
       <c r="G27" s="8">
-        <v>1777135962.97</v>
+        <v>1877207106.06</v>
       </c>
       <c r="H27" s="8">
-        <v>174</v>
+        <v>180</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1315,10 +1315,10 @@
         <v>57</v>
       </c>
       <c r="C28" s="6">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="D28" s="7">
-        <v>237.411038</v>
+        <v>250.060048</v>
       </c>
       <c r="E28" s="8">
         <v>32440000</v>
@@ -1327,10 +1327,10 @@
         <v>0</v>
       </c>
       <c r="G28" s="8">
-        <v>7701614075.86</v>
+        <v>8111947946.71</v>
       </c>
       <c r="H28" s="8">
-        <v>237.1</v>
+        <v>252.4</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1341,10 +1341,10 @@
         <v>59</v>
       </c>
       <c r="C29" s="6">
-        <v>46164</v>
-      </c>
-      <c r="D29" s="7">
-        <v>237.580892</v>
+        <v>46167</v>
+      </c>
+      <c r="D29" s="10">
+        <v>250.58659</v>
       </c>
       <c r="E29" s="8">
         <v>3200000</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="G29" s="8">
-        <v>760258855.61</v>
+        <v>801877088.17</v>
       </c>
       <c r="H29" s="8">
-        <v>237.55</v>
+        <v>253</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1367,10 +1367,10 @@
         <v>61</v>
       </c>
       <c r="C30" s="6">
-        <v>46164</v>
-      </c>
-      <c r="D30" s="10">
-        <v>113.69428</v>
+        <v>46167</v>
+      </c>
+      <c r="D30" s="7">
+        <v>118.985864</v>
       </c>
       <c r="E30" s="8">
         <v>440000</v>
@@ -1379,10 +1379,10 @@
         <v>0</v>
       </c>
       <c r="G30" s="8">
-        <v>50025483.32</v>
+        <v>52353779.95</v>
       </c>
       <c r="H30" s="8">
-        <v>114.75</v>
+        <v>119.55</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1393,10 +1393,10 @@
         <v>63</v>
       </c>
       <c r="C31" s="6">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="D31" s="7">
-        <v>167.465568</v>
+        <v>175.916244</v>
       </c>
       <c r="E31" s="8">
         <v>400000</v>
@@ -1405,10 +1405,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="8">
-        <v>66986227.34</v>
+        <v>70366497.75</v>
       </c>
       <c r="H31" s="8">
-        <v>172.45</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1419,10 +1419,10 @@
         <v>65</v>
       </c>
       <c r="C32" s="6">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="D32" s="7">
-        <v>44.931846</v>
+        <v>46.584875</v>
       </c>
       <c r="E32" s="8">
         <v>1200000</v>
@@ -1431,10 +1431,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="8">
-        <v>53918215.32</v>
+        <v>55901850.32</v>
       </c>
       <c r="H32" s="8">
-        <v>46.47</v>
+        <v>46.14</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1445,22 +1445,22 @@
         <v>67</v>
       </c>
       <c r="C33" s="6">
-        <v>46164</v>
-      </c>
-      <c r="D33" s="7">
-        <v>1237.467062</v>
+        <v>46167</v>
+      </c>
+      <c r="D33" s="10">
+        <v>1241.45609</v>
       </c>
       <c r="E33" s="8">
-        <v>640000</v>
+        <v>600000</v>
       </c>
       <c r="F33" s="9">
         <v>0</v>
       </c>
       <c r="G33" s="8">
-        <v>791978919.84</v>
+        <v>744873654.11</v>
       </c>
       <c r="H33" s="8">
-        <v>1242</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -1471,10 +1471,10 @@
         <v>69</v>
       </c>
       <c r="C34" s="6">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="D34" s="7">
-        <v>174.565008</v>
+        <v>181.380916</v>
       </c>
       <c r="E34" s="8">
         <v>680000</v>
@@ -1483,10 +1483,10 @@
         <v>0</v>
       </c>
       <c r="G34" s="8">
-        <v>118704205.28</v>
+        <v>123339023.18</v>
       </c>
       <c r="H34" s="8">
-        <v>174.55</v>
+        <v>183.7</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -1497,10 +1497,10 @@
         <v>71</v>
       </c>
       <c r="C35" s="6">
-        <v>46164</v>
-      </c>
-      <c r="D35" s="10">
-        <v>1238.57683</v>
+        <v>46167</v>
+      </c>
+      <c r="D35" s="7">
+        <v>1242.562642</v>
       </c>
       <c r="E35" s="8">
         <v>6240000</v>
@@ -1509,10 +1509,10 @@
         <v>0</v>
       </c>
       <c r="G35" s="8">
-        <v>7728719418.48</v>
+        <v>7753590886.05</v>
       </c>
       <c r="H35" s="8">
-        <v>1243</v>
+        <v>1252.5</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>25.05.2026 13:29:13</t>
+    <t>26.05.2026 11:06:59</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -743,10 +743,10 @@
         <v>13</v>
       </c>
       <c r="C6" s="6">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="D6" s="7">
-        <v>42.495237</v>
+        <v>43.482932</v>
       </c>
       <c r="E6" s="8">
         <v>58000000</v>
@@ -755,10 +755,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="8">
-        <v>2464723741.76</v>
+        <v>2522010042.27</v>
       </c>
       <c r="H6" s="8">
-        <v>42.5</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -769,10 +769,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="6">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="D7" s="7">
-        <v>37.300952</v>
+        <v>36.951468</v>
       </c>
       <c r="E7" s="8">
         <v>14400000</v>
@@ -781,10 +781,10 @@
         <v>0</v>
       </c>
       <c r="G7" s="8">
-        <v>537133708.75</v>
+        <v>532101142.31</v>
       </c>
       <c r="H7" s="8">
-        <v>37.3</v>
+        <v>36.94</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -795,10 +795,10 @@
         <v>17</v>
       </c>
       <c r="C8" s="6">
-        <v>46167</v>
-      </c>
-      <c r="D8" s="10">
-        <v>38.51606</v>
+        <v>46168</v>
+      </c>
+      <c r="D8" s="7">
+        <v>38.494457</v>
       </c>
       <c r="E8" s="8">
         <v>33900000</v>
@@ -807,10 +807,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="8">
-        <v>1305694445.03</v>
+        <v>1304962079.6</v>
       </c>
       <c r="H8" s="8">
-        <v>38.4</v>
+        <v>38.41</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -821,10 +821,10 @@
         <v>19</v>
       </c>
       <c r="C9" s="6">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="D9" s="7">
-        <v>57.620562</v>
+        <v>57.677818</v>
       </c>
       <c r="E9" s="8">
         <v>2250000</v>
@@ -833,10 +833,10 @@
         <v>0</v>
       </c>
       <c r="G9" s="8">
-        <v>129646265.09</v>
+        <v>129775089.71</v>
       </c>
       <c r="H9" s="8">
-        <v>58.08</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -847,10 +847,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="6">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="D10" s="7">
-        <v>363.777193</v>
+        <v>376.992129</v>
       </c>
       <c r="E10" s="8">
         <v>135000</v>
@@ -859,10 +859,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="8">
-        <v>49109921.04</v>
+        <v>50893937.47</v>
       </c>
       <c r="H10" s="8">
-        <v>364.2</v>
+        <v>377</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -873,10 +873,10 @@
         <v>23</v>
       </c>
       <c r="C11" s="6">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="D11" s="7">
-        <v>555.861887</v>
+        <v>561.843673</v>
       </c>
       <c r="E11" s="8">
         <v>46350000</v>
@@ -885,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="G11" s="8">
-        <v>25764198442.16</v>
+        <v>26041454241.95</v>
       </c>
       <c r="H11" s="8">
-        <v>562</v>
+        <v>571.25</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -899,22 +899,22 @@
         <v>25</v>
       </c>
       <c r="C12" s="6">
-        <v>46167</v>
-      </c>
-      <c r="D12" s="10">
-        <v>685.92583</v>
+        <v>46168</v>
+      </c>
+      <c r="D12" s="7">
+        <v>704.444133</v>
       </c>
       <c r="E12" s="8">
-        <v>73300000</v>
+        <v>73550000</v>
       </c>
       <c r="F12" s="9">
         <v>0</v>
       </c>
       <c r="G12" s="8">
-        <v>50278363332.4</v>
+        <v>51811866004.96</v>
       </c>
       <c r="H12" s="8">
-        <v>697.75</v>
+        <v>721</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -925,10 +925,10 @@
         <v>27</v>
       </c>
       <c r="C13" s="6">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="D13" s="7">
-        <v>4261.086389</v>
+        <v>4254.652424</v>
       </c>
       <c r="E13" s="8">
         <v>280000</v>
@@ -937,10 +937,10 @@
         <v>0</v>
       </c>
       <c r="G13" s="8">
-        <v>1193104188.86</v>
+        <v>1191302678.82</v>
       </c>
       <c r="H13" s="8">
-        <v>4337</v>
+        <v>4305</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -951,10 +951,10 @@
         <v>29</v>
       </c>
       <c r="C14" s="6">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="D14" s="7">
-        <v>665.969802</v>
+        <v>674.069554</v>
       </c>
       <c r="E14" s="8">
         <v>113800000</v>
@@ -963,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="8">
-        <v>75787363413.9</v>
+        <v>76709115215.56</v>
       </c>
       <c r="H14" s="8">
-        <v>690</v>
+        <v>700</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -977,10 +977,10 @@
         <v>31</v>
       </c>
       <c r="C15" s="6">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="D15" s="10">
-        <v>547.36196</v>
+        <v>555.30926</v>
       </c>
       <c r="E15" s="8">
         <v>33450000</v>
@@ -989,10 +989,10 @@
         <v>0</v>
       </c>
       <c r="G15" s="8">
-        <v>18309257571.24</v>
+        <v>18575094748.72</v>
       </c>
       <c r="H15" s="8">
-        <v>555.25</v>
+        <v>559.5</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1003,10 +1003,10 @@
         <v>33</v>
       </c>
       <c r="C16" s="6">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="D16" s="7">
-        <v>25.585236</v>
+        <v>25.552387</v>
       </c>
       <c r="E16" s="8">
         <v>10800000</v>
@@ -1015,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="8">
-        <v>276320549.59</v>
+        <v>275965781.76</v>
       </c>
       <c r="H16" s="8">
-        <v>25.64</v>
+        <v>25.54</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1029,10 +1029,10 @@
         <v>35</v>
       </c>
       <c r="C17" s="6">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="D17" s="7">
-        <v>46.602175</v>
+        <v>46.650105</v>
       </c>
       <c r="E17" s="8">
         <v>1625000</v>
@@ -1041,10 +1041,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="8">
-        <v>75728534.47</v>
+        <v>75806420.84</v>
       </c>
       <c r="H17" s="8">
-        <v>46.94</v>
+        <v>46.99</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1055,10 +1055,10 @@
         <v>37</v>
       </c>
       <c r="C18" s="6">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="D18" s="7">
-        <v>72.084101</v>
+        <v>72.553847</v>
       </c>
       <c r="E18" s="8">
         <v>1140000</v>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="G18" s="8">
-        <v>82175875.61</v>
+        <v>82711386.03</v>
       </c>
       <c r="H18" s="8">
-        <v>71.72</v>
+        <v>72.56</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1081,10 +1081,10 @@
         <v>39</v>
       </c>
       <c r="C19" s="6">
-        <v>46167</v>
-      </c>
-      <c r="D19" s="7">
-        <v>83.189759</v>
+        <v>46168</v>
+      </c>
+      <c r="D19" s="10">
+        <v>83.09385</v>
       </c>
       <c r="E19" s="8">
         <v>1155000</v>
@@ -1093,10 +1093,10 @@
         <v>0</v>
       </c>
       <c r="G19" s="8">
-        <v>96084171.67</v>
+        <v>95973397.06</v>
       </c>
       <c r="H19" s="8">
-        <v>82.74</v>
+        <v>82.86</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1107,10 +1107,10 @@
         <v>41</v>
       </c>
       <c r="C20" s="6">
-        <v>46167</v>
-      </c>
-      <c r="D20" s="7">
-        <v>50.764988</v>
+        <v>46168</v>
+      </c>
+      <c r="D20" s="10">
+        <v>50.71088</v>
       </c>
       <c r="E20" s="8">
         <v>2985000</v>
@@ -1119,10 +1119,10 @@
         <v>0</v>
       </c>
       <c r="G20" s="8">
-        <v>151533489.02</v>
+        <v>151371976.78</v>
       </c>
       <c r="H20" s="8">
-        <v>51.24</v>
+        <v>50.78</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1133,10 +1133,10 @@
         <v>43</v>
       </c>
       <c r="C21" s="6">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="D21" s="7">
-        <v>163.312905</v>
+        <v>165.328979</v>
       </c>
       <c r="E21" s="8">
         <v>600000</v>
@@ -1145,10 +1145,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="8">
-        <v>97987743.02</v>
+        <v>99197387.21</v>
       </c>
       <c r="H21" s="8">
-        <v>163.8</v>
+        <v>165.1</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1159,22 +1159,22 @@
         <v>45</v>
       </c>
       <c r="C22" s="6">
-        <v>46167</v>
-      </c>
-      <c r="D22" s="7">
-        <v>208.230328</v>
+        <v>46168</v>
+      </c>
+      <c r="D22" s="10">
+        <v>208.09019</v>
       </c>
       <c r="E22" s="8">
-        <v>116840000</v>
+        <v>116880000</v>
       </c>
       <c r="F22" s="9">
         <v>0</v>
       </c>
       <c r="G22" s="8">
-        <v>24329631512.58</v>
+        <v>24321581457.19</v>
       </c>
       <c r="H22" s="8">
-        <v>209.8</v>
+        <v>207.8</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1185,22 +1185,22 @@
         <v>47</v>
       </c>
       <c r="C23" s="6">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="D23" s="7">
-        <v>180.280965</v>
+        <v>184.525624</v>
       </c>
       <c r="E23" s="8">
-        <v>207320000</v>
+        <v>207280000</v>
       </c>
       <c r="F23" s="9">
         <v>0</v>
       </c>
       <c r="G23" s="8">
-        <v>37375849600</v>
+        <v>38248471407.85</v>
       </c>
       <c r="H23" s="8">
-        <v>181.45</v>
+        <v>184.5</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1211,10 +1211,10 @@
         <v>49</v>
       </c>
       <c r="C24" s="6">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="D24" s="7">
-        <v>191.998632</v>
+        <v>193.790995</v>
       </c>
       <c r="E24" s="8">
         <v>360000</v>
@@ -1223,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="G24" s="8">
-        <v>69119507.55</v>
+        <v>69764758.33</v>
       </c>
       <c r="H24" s="8">
-        <v>193.6</v>
+        <v>193.8</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1237,10 +1237,10 @@
         <v>51</v>
       </c>
       <c r="C25" s="6">
-        <v>46167</v>
-      </c>
-      <c r="D25" s="10">
-        <v>118.00706</v>
+        <v>46168</v>
+      </c>
+      <c r="D25" s="7">
+        <v>120.929132</v>
       </c>
       <c r="E25" s="8">
         <v>600000</v>
@@ -1249,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="8">
-        <v>70804236.12</v>
+        <v>72557478.95</v>
       </c>
       <c r="H25" s="8">
         <v>121.5</v>
@@ -1263,10 +1263,10 @@
         <v>53</v>
       </c>
       <c r="C26" s="6">
-        <v>46167</v>
-      </c>
-      <c r="D26" s="10">
-        <v>675.78871</v>
+        <v>46168</v>
+      </c>
+      <c r="D26" s="7">
+        <v>685.352233</v>
       </c>
       <c r="E26" s="8">
         <v>152040000</v>
@@ -1275,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="G26" s="8">
-        <v>102746915446.59</v>
+        <v>104200953477.31</v>
       </c>
       <c r="H26" s="8">
-        <v>699</v>
+        <v>712.75</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1289,10 +1289,10 @@
         <v>55</v>
       </c>
       <c r="C27" s="6">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="D27" s="7">
-        <v>175.768456</v>
+        <v>180.509106</v>
       </c>
       <c r="E27" s="8">
         <v>10680000</v>
@@ -1301,10 +1301,10 @@
         <v>0</v>
       </c>
       <c r="G27" s="8">
-        <v>1877207106.06</v>
+        <v>1927837248.39</v>
       </c>
       <c r="H27" s="8">
-        <v>180</v>
+        <v>183.15</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1315,10 +1315,10 @@
         <v>57</v>
       </c>
       <c r="C28" s="6">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="D28" s="7">
-        <v>250.060048</v>
+        <v>252.353248</v>
       </c>
       <c r="E28" s="8">
         <v>32440000</v>
@@ -1327,10 +1327,10 @@
         <v>0</v>
       </c>
       <c r="G28" s="8">
-        <v>8111947946.71</v>
+        <v>8186339349.58</v>
       </c>
       <c r="H28" s="8">
-        <v>252.4</v>
+        <v>251.6</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1341,10 +1341,10 @@
         <v>59</v>
       </c>
       <c r="C29" s="6">
-        <v>46167</v>
-      </c>
-      <c r="D29" s="10">
-        <v>250.58659</v>
+        <v>46168</v>
+      </c>
+      <c r="D29" s="7">
+        <v>248.228633</v>
       </c>
       <c r="E29" s="8">
         <v>3200000</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="G29" s="8">
-        <v>801877088.17</v>
+        <v>794331626.11</v>
       </c>
       <c r="H29" s="8">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1367,10 +1367,10 @@
         <v>61</v>
       </c>
       <c r="C30" s="6">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="D30" s="7">
-        <v>118.985864</v>
+        <v>122.312568</v>
       </c>
       <c r="E30" s="8">
         <v>440000</v>
@@ -1379,10 +1379,10 @@
         <v>0</v>
       </c>
       <c r="G30" s="8">
-        <v>52353779.95</v>
+        <v>53817530.02</v>
       </c>
       <c r="H30" s="8">
-        <v>119.55</v>
+        <v>122.3</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1393,10 +1393,10 @@
         <v>63</v>
       </c>
       <c r="C31" s="6">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="D31" s="7">
-        <v>175.916244</v>
+        <v>177.142157</v>
       </c>
       <c r="E31" s="8">
         <v>400000</v>
@@ -1405,10 +1405,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="8">
-        <v>70366497.75</v>
+        <v>70856862.77</v>
       </c>
       <c r="H31" s="8">
-        <v>176</v>
+        <v>177.15</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1419,10 +1419,10 @@
         <v>65</v>
       </c>
       <c r="C32" s="6">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="D32" s="7">
-        <v>46.584875</v>
+        <v>46.591109</v>
       </c>
       <c r="E32" s="8">
         <v>1200000</v>
@@ -1431,10 +1431,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="8">
-        <v>55901850.32</v>
+        <v>55909331.22</v>
       </c>
       <c r="H32" s="8">
-        <v>46.14</v>
+        <v>46.57</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1445,10 +1445,10 @@
         <v>67</v>
       </c>
       <c r="C33" s="6">
-        <v>46167</v>
-      </c>
-      <c r="D33" s="10">
-        <v>1241.45609</v>
+        <v>46168</v>
+      </c>
+      <c r="D33" s="7">
+        <v>1242.791878</v>
       </c>
       <c r="E33" s="8">
         <v>600000</v>
@@ -1457,10 +1457,10 @@
         <v>0</v>
       </c>
       <c r="G33" s="8">
-        <v>744873654.11</v>
+        <v>745675126.54</v>
       </c>
       <c r="H33" s="8">
-        <v>1251</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -1471,10 +1471,10 @@
         <v>69</v>
       </c>
       <c r="C34" s="6">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="D34" s="7">
-        <v>181.380916</v>
+        <v>181.184628</v>
       </c>
       <c r="E34" s="8">
         <v>680000</v>
@@ -1483,10 +1483,10 @@
         <v>0</v>
       </c>
       <c r="G34" s="8">
-        <v>123339023.18</v>
+        <v>123205547.12</v>
       </c>
       <c r="H34" s="8">
-        <v>183.7</v>
+        <v>181.5</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -1497,10 +1497,10 @@
         <v>71</v>
       </c>
       <c r="C35" s="6">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="D35" s="7">
-        <v>1242.562642</v>
+        <v>1243.895646</v>
       </c>
       <c r="E35" s="8">
         <v>6240000</v>
@@ -1509,10 +1509,10 @@
         <v>0</v>
       </c>
       <c r="G35" s="8">
-        <v>7753590886.05</v>
+        <v>7761908832.49</v>
       </c>
       <c r="H35" s="8">
-        <v>1252.5</v>
+        <v>1253.5</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>26.05.2026 11:06:59</t>
+    <t>01.06.2026 17:43:30</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -233,12 +233,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="###0.000000;-###0.000000;0"/>
     <numFmt numFmtId="166" formatCode="###0.00;-###0.00;0"/>
     <numFmt numFmtId="167" formatCode="###0;-###0;0"/>
-    <numFmt numFmtId="168" formatCode="###0.00000;-###0.00000;0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -308,7 +307,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -331,9 +330,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -743,10 +739,10 @@
         <v>13</v>
       </c>
       <c r="C6" s="6">
-        <v>46168</v>
+        <v>46174</v>
       </c>
       <c r="D6" s="7">
-        <v>43.482932</v>
+        <v>42.939369</v>
       </c>
       <c r="E6" s="8">
         <v>58000000</v>
@@ -755,10 +751,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="8">
-        <v>2522010042.27</v>
+        <v>2490483408.9</v>
       </c>
       <c r="H6" s="8">
-        <v>43.5</v>
+        <v>43.12</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -769,10 +765,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="6">
-        <v>46168</v>
+        <v>46174</v>
       </c>
       <c r="D7" s="7">
-        <v>36.951468</v>
+        <v>36.161903</v>
       </c>
       <c r="E7" s="8">
         <v>14400000</v>
@@ -781,10 +777,10 @@
         <v>0</v>
       </c>
       <c r="G7" s="8">
-        <v>532101142.31</v>
+        <v>520731407.21</v>
       </c>
       <c r="H7" s="8">
-        <v>36.94</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -795,10 +791,10 @@
         <v>17</v>
       </c>
       <c r="C8" s="6">
-        <v>46168</v>
+        <v>46174</v>
       </c>
       <c r="D8" s="7">
-        <v>38.494457</v>
+        <v>37.651059</v>
       </c>
       <c r="E8" s="8">
         <v>33900000</v>
@@ -807,10 +803,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="8">
-        <v>1304962079.6</v>
+        <v>1276370909.75</v>
       </c>
       <c r="H8" s="8">
-        <v>38.41</v>
+        <v>37.96</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -821,10 +817,10 @@
         <v>19</v>
       </c>
       <c r="C9" s="6">
-        <v>46168</v>
+        <v>46174</v>
       </c>
       <c r="D9" s="7">
-        <v>57.677818</v>
+        <v>58.052416</v>
       </c>
       <c r="E9" s="8">
         <v>2250000</v>
@@ -833,10 +829,10 @@
         <v>0</v>
       </c>
       <c r="G9" s="8">
-        <v>129775089.71</v>
+        <v>130617935.32</v>
       </c>
       <c r="H9" s="8">
-        <v>58.1</v>
+        <v>58.14</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -847,10 +843,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="6">
-        <v>46168</v>
+        <v>46174</v>
       </c>
       <c r="D10" s="7">
-        <v>376.992129</v>
+        <v>374.470944</v>
       </c>
       <c r="E10" s="8">
         <v>135000</v>
@@ -859,10 +855,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="8">
-        <v>50893937.47</v>
+        <v>50553577.49</v>
       </c>
       <c r="H10" s="8">
-        <v>377</v>
+        <v>373.7</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -873,10 +869,10 @@
         <v>23</v>
       </c>
       <c r="C11" s="6">
-        <v>46168</v>
+        <v>46174</v>
       </c>
       <c r="D11" s="7">
-        <v>561.843673</v>
+        <v>557.268496</v>
       </c>
       <c r="E11" s="8">
         <v>46350000</v>
@@ -885,10 +881,10 @@
         <v>0</v>
       </c>
       <c r="G11" s="8">
-        <v>26041454241.95</v>
+        <v>25829394785.65</v>
       </c>
       <c r="H11" s="8">
-        <v>571.25</v>
+        <v>565.5</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -899,10 +895,10 @@
         <v>25</v>
       </c>
       <c r="C12" s="6">
-        <v>46168</v>
+        <v>46174</v>
       </c>
       <c r="D12" s="7">
-        <v>704.444133</v>
+        <v>690.187281</v>
       </c>
       <c r="E12" s="8">
         <v>73550000</v>
@@ -911,10 +907,10 @@
         <v>0</v>
       </c>
       <c r="G12" s="8">
-        <v>51811866004.96</v>
+        <v>50763274491.2</v>
       </c>
       <c r="H12" s="8">
-        <v>721</v>
+        <v>707.25</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -925,10 +921,10 @@
         <v>27</v>
       </c>
       <c r="C13" s="6">
-        <v>46168</v>
+        <v>46174</v>
       </c>
       <c r="D13" s="7">
-        <v>4254.652424</v>
+        <v>4252.823352</v>
       </c>
       <c r="E13" s="8">
         <v>280000</v>
@@ -937,10 +933,10 @@
         <v>0</v>
       </c>
       <c r="G13" s="8">
-        <v>1191302678.82</v>
+        <v>1190790538.65</v>
       </c>
       <c r="H13" s="8">
-        <v>4305</v>
+        <v>4319</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -951,10 +947,10 @@
         <v>29</v>
       </c>
       <c r="C14" s="6">
-        <v>46168</v>
+        <v>46174</v>
       </c>
       <c r="D14" s="7">
-        <v>674.069554</v>
+        <v>674.046895</v>
       </c>
       <c r="E14" s="8">
         <v>113800000</v>
@@ -963,10 +959,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="8">
-        <v>76709115215.56</v>
+        <v>76706536641.45</v>
       </c>
       <c r="H14" s="8">
-        <v>700</v>
+        <v>691</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -977,10 +973,10 @@
         <v>31</v>
       </c>
       <c r="C15" s="6">
-        <v>46168</v>
-      </c>
-      <c r="D15" s="10">
-        <v>555.30926</v>
+        <v>46174</v>
+      </c>
+      <c r="D15" s="7">
+        <v>554.861777</v>
       </c>
       <c r="E15" s="8">
         <v>33450000</v>
@@ -989,10 +985,10 @@
         <v>0</v>
       </c>
       <c r="G15" s="8">
-        <v>18575094748.72</v>
+        <v>18560126430.54</v>
       </c>
       <c r="H15" s="8">
-        <v>559.5</v>
+        <v>558.25</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1003,10 +999,10 @@
         <v>33</v>
       </c>
       <c r="C16" s="6">
-        <v>46168</v>
+        <v>46174</v>
       </c>
       <c r="D16" s="7">
-        <v>25.552387</v>
+        <v>25.216979</v>
       </c>
       <c r="E16" s="8">
         <v>10800000</v>
@@ -1015,10 +1011,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="8">
-        <v>275965781.76</v>
+        <v>272343375.34</v>
       </c>
       <c r="H16" s="8">
-        <v>25.54</v>
+        <v>25.33</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1029,10 +1025,10 @@
         <v>35</v>
       </c>
       <c r="C17" s="6">
-        <v>46168</v>
+        <v>46174</v>
       </c>
       <c r="D17" s="7">
-        <v>46.650105</v>
+        <v>46.938987</v>
       </c>
       <c r="E17" s="8">
         <v>1625000</v>
@@ -1041,7 +1037,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="8">
-        <v>75806420.84</v>
+        <v>76275853.88</v>
       </c>
       <c r="H17" s="8">
         <v>46.99</v>
@@ -1055,10 +1051,10 @@
         <v>37</v>
       </c>
       <c r="C18" s="6">
-        <v>46168</v>
+        <v>46174</v>
       </c>
       <c r="D18" s="7">
-        <v>72.553847</v>
+        <v>71.826977</v>
       </c>
       <c r="E18" s="8">
         <v>1140000</v>
@@ -1067,10 +1063,10 @@
         <v>0</v>
       </c>
       <c r="G18" s="8">
-        <v>82711386.03</v>
+        <v>81882753.71</v>
       </c>
       <c r="H18" s="8">
-        <v>72.56</v>
+        <v>71.66</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1081,10 +1077,10 @@
         <v>39</v>
       </c>
       <c r="C19" s="6">
-        <v>46168</v>
-      </c>
-      <c r="D19" s="10">
-        <v>83.09385</v>
+        <v>46174</v>
+      </c>
+      <c r="D19" s="7">
+        <v>81.311668</v>
       </c>
       <c r="E19" s="8">
         <v>1155000</v>
@@ -1093,10 +1089,10 @@
         <v>0</v>
       </c>
       <c r="G19" s="8">
-        <v>95973397.06</v>
+        <v>93914977.05</v>
       </c>
       <c r="H19" s="8">
-        <v>82.86</v>
+        <v>81.88</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1107,10 +1103,10 @@
         <v>41</v>
       </c>
       <c r="C20" s="6">
-        <v>46168</v>
-      </c>
-      <c r="D20" s="10">
-        <v>50.71088</v>
+        <v>46174</v>
+      </c>
+      <c r="D20" s="7">
+        <v>50.034176</v>
       </c>
       <c r="E20" s="8">
         <v>2985000</v>
@@ -1119,10 +1115,10 @@
         <v>0</v>
       </c>
       <c r="G20" s="8">
-        <v>151371976.78</v>
+        <v>149352015.71</v>
       </c>
       <c r="H20" s="8">
-        <v>50.78</v>
+        <v>50.24</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1133,10 +1129,10 @@
         <v>43</v>
       </c>
       <c r="C21" s="6">
-        <v>46168</v>
+        <v>46174</v>
       </c>
       <c r="D21" s="7">
-        <v>165.328979</v>
+        <v>165.177628</v>
       </c>
       <c r="E21" s="8">
         <v>600000</v>
@@ -1145,10 +1141,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="8">
-        <v>99197387.21</v>
+        <v>99106576.69</v>
       </c>
       <c r="H21" s="8">
-        <v>165.1</v>
+        <v>166.75</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1159,22 +1155,22 @@
         <v>45</v>
       </c>
       <c r="C22" s="6">
-        <v>46168</v>
-      </c>
-      <c r="D22" s="10">
-        <v>208.09019</v>
+        <v>46174</v>
+      </c>
+      <c r="D22" s="7">
+        <v>203.435872</v>
       </c>
       <c r="E22" s="8">
-        <v>116880000</v>
+        <v>114680000</v>
       </c>
       <c r="F22" s="9">
         <v>0</v>
       </c>
       <c r="G22" s="8">
-        <v>24321581457.19</v>
+        <v>23330025848.09</v>
       </c>
       <c r="H22" s="8">
-        <v>207.8</v>
+        <v>205.15</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1185,22 +1181,22 @@
         <v>47</v>
       </c>
       <c r="C23" s="6">
-        <v>46168</v>
+        <v>46174</v>
       </c>
       <c r="D23" s="7">
-        <v>184.525624</v>
+        <v>182.197631</v>
       </c>
       <c r="E23" s="8">
-        <v>207280000</v>
+        <v>209760000</v>
       </c>
       <c r="F23" s="9">
         <v>0</v>
       </c>
       <c r="G23" s="8">
-        <v>38248471407.85</v>
+        <v>38217775075.98</v>
       </c>
       <c r="H23" s="8">
-        <v>184.5</v>
+        <v>183.05</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1211,10 +1207,10 @@
         <v>49</v>
       </c>
       <c r="C24" s="6">
-        <v>46168</v>
+        <v>46174</v>
       </c>
       <c r="D24" s="7">
-        <v>193.790995</v>
+        <v>189.999238</v>
       </c>
       <c r="E24" s="8">
         <v>360000</v>
@@ -1223,10 +1219,10 @@
         <v>0</v>
       </c>
       <c r="G24" s="8">
-        <v>69764758.33</v>
+        <v>68399725.57</v>
       </c>
       <c r="H24" s="8">
-        <v>193.8</v>
+        <v>190</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1237,10 +1233,10 @@
         <v>51</v>
       </c>
       <c r="C25" s="6">
-        <v>46168</v>
+        <v>46174</v>
       </c>
       <c r="D25" s="7">
-        <v>120.929132</v>
+        <v>119.215549</v>
       </c>
       <c r="E25" s="8">
         <v>600000</v>
@@ -1249,10 +1245,10 @@
         <v>0</v>
       </c>
       <c r="G25" s="8">
-        <v>72557478.95</v>
+        <v>71529329.62</v>
       </c>
       <c r="H25" s="8">
-        <v>121.5</v>
+        <v>119.2</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1263,10 +1259,10 @@
         <v>53</v>
       </c>
       <c r="C26" s="6">
-        <v>46168</v>
+        <v>46174</v>
       </c>
       <c r="D26" s="7">
-        <v>685.352233</v>
+        <v>681.178811</v>
       </c>
       <c r="E26" s="8">
         <v>152040000</v>
@@ -1275,10 +1271,10 @@
         <v>0</v>
       </c>
       <c r="G26" s="8">
-        <v>104200953477.31</v>
+        <v>103566426495.91</v>
       </c>
       <c r="H26" s="8">
-        <v>712.75</v>
+        <v>702</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1289,22 +1285,22 @@
         <v>55</v>
       </c>
       <c r="C27" s="6">
-        <v>46168</v>
+        <v>46174</v>
       </c>
       <c r="D27" s="7">
-        <v>180.509106</v>
+        <v>178.178658</v>
       </c>
       <c r="E27" s="8">
-        <v>10680000</v>
+        <v>10960000</v>
       </c>
       <c r="F27" s="9">
         <v>0</v>
       </c>
       <c r="G27" s="8">
-        <v>1927837248.39</v>
+        <v>1952838095.12</v>
       </c>
       <c r="H27" s="8">
-        <v>183.15</v>
+        <v>178.9</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1315,22 +1311,22 @@
         <v>57</v>
       </c>
       <c r="C28" s="6">
-        <v>46168</v>
+        <v>46174</v>
       </c>
       <c r="D28" s="7">
-        <v>252.353248</v>
+        <v>250.242649</v>
       </c>
       <c r="E28" s="8">
-        <v>32440000</v>
+        <v>32080000</v>
       </c>
       <c r="F28" s="9">
         <v>0</v>
       </c>
       <c r="G28" s="8">
-        <v>8186339349.58</v>
+        <v>8027784176.64</v>
       </c>
       <c r="H28" s="8">
-        <v>251.6</v>
+        <v>250.2</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1341,10 +1337,10 @@
         <v>59</v>
       </c>
       <c r="C29" s="6">
-        <v>46168</v>
+        <v>46174</v>
       </c>
       <c r="D29" s="7">
-        <v>248.228633</v>
+        <v>242.887091</v>
       </c>
       <c r="E29" s="8">
         <v>3200000</v>
@@ -1353,10 +1349,10 @@
         <v>0</v>
       </c>
       <c r="G29" s="8">
-        <v>794331626.11</v>
+        <v>777238691.81</v>
       </c>
       <c r="H29" s="8">
-        <v>252</v>
+        <v>244.55</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1367,10 +1363,10 @@
         <v>61</v>
       </c>
       <c r="C30" s="6">
-        <v>46168</v>
+        <v>46174</v>
       </c>
       <c r="D30" s="7">
-        <v>122.312568</v>
+        <v>121.845333</v>
       </c>
       <c r="E30" s="8">
         <v>440000</v>
@@ -1379,10 +1375,10 @@
         <v>0</v>
       </c>
       <c r="G30" s="8">
-        <v>53817530.02</v>
+        <v>53611946.69</v>
       </c>
       <c r="H30" s="8">
-        <v>122.3</v>
+        <v>126.05</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1393,10 +1389,10 @@
         <v>63</v>
       </c>
       <c r="C31" s="6">
-        <v>46168</v>
+        <v>46174</v>
       </c>
       <c r="D31" s="7">
-        <v>177.142157</v>
+        <v>173.202339</v>
       </c>
       <c r="E31" s="8">
         <v>400000</v>
@@ -1405,10 +1401,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="8">
-        <v>70856862.77</v>
+        <v>69280935.68</v>
       </c>
       <c r="H31" s="8">
-        <v>177.15</v>
+        <v>173.95</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1419,10 +1415,10 @@
         <v>65</v>
       </c>
       <c r="C32" s="6">
-        <v>46168</v>
+        <v>46174</v>
       </c>
       <c r="D32" s="7">
-        <v>46.591109</v>
+        <v>45.853794</v>
       </c>
       <c r="E32" s="8">
         <v>1200000</v>
@@ -1431,10 +1427,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="8">
-        <v>55909331.22</v>
+        <v>55024553.26</v>
       </c>
       <c r="H32" s="8">
-        <v>46.57</v>
+        <v>45.87</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1445,10 +1441,10 @@
         <v>67</v>
       </c>
       <c r="C33" s="6">
-        <v>46168</v>
+        <v>46174</v>
       </c>
       <c r="D33" s="7">
-        <v>1242.791878</v>
+        <v>1250.804156</v>
       </c>
       <c r="E33" s="8">
         <v>600000</v>
@@ -1457,10 +1453,10 @@
         <v>0</v>
       </c>
       <c r="G33" s="8">
-        <v>745675126.54</v>
+        <v>750482493.67</v>
       </c>
       <c r="H33" s="8">
-        <v>1252</v>
+        <v>1252.5</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -1471,10 +1467,10 @@
         <v>69</v>
       </c>
       <c r="C34" s="6">
-        <v>46168</v>
+        <v>46174</v>
       </c>
       <c r="D34" s="7">
-        <v>181.184628</v>
+        <v>178.701382</v>
       </c>
       <c r="E34" s="8">
         <v>680000</v>
@@ -1483,10 +1479,10 @@
         <v>0</v>
       </c>
       <c r="G34" s="8">
-        <v>123205547.12</v>
+        <v>121516940.09</v>
       </c>
       <c r="H34" s="8">
-        <v>181.5</v>
+        <v>178.7</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -1497,10 +1493,10 @@
         <v>71</v>
       </c>
       <c r="C35" s="6">
-        <v>46168</v>
+        <v>46174</v>
       </c>
       <c r="D35" s="7">
-        <v>1243.895646</v>
+        <v>1251.901332</v>
       </c>
       <c r="E35" s="8">
         <v>6240000</v>
@@ -1509,10 +1505,10 @@
         <v>0</v>
       </c>
       <c r="G35" s="8">
-        <v>7761908832.49</v>
+        <v>7811864313.42</v>
       </c>
       <c r="H35" s="8">
-        <v>1253.5</v>
+        <v>1253</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>01.06.2026 17:43:30</t>
+    <t>02.06.2026 11:24:59</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -233,11 +233,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="###0.000000;-###0.000000;0"/>
     <numFmt numFmtId="166" formatCode="###0.00;-###0.00;0"/>
     <numFmt numFmtId="167" formatCode="###0;-###0;0"/>
+    <numFmt numFmtId="168" formatCode="###0.00000;-###0.00000;0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -307,7 +308,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -330,6 +331,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -739,22 +743,22 @@
         <v>13</v>
       </c>
       <c r="C6" s="6">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="D6" s="7">
-        <v>42.939369</v>
+        <v>43.051018</v>
       </c>
       <c r="E6" s="8">
-        <v>58000000</v>
+        <v>58200000</v>
       </c>
       <c r="F6" s="9">
         <v>0</v>
       </c>
       <c r="G6" s="8">
-        <v>2490483408.9</v>
+        <v>2505569269.46</v>
       </c>
       <c r="H6" s="8">
-        <v>43.12</v>
+        <v>43.16</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -765,10 +769,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="6">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="D7" s="7">
-        <v>36.161903</v>
+        <v>36.370775</v>
       </c>
       <c r="E7" s="8">
         <v>14400000</v>
@@ -777,10 +781,10 @@
         <v>0</v>
       </c>
       <c r="G7" s="8">
-        <v>520731407.21</v>
+        <v>523739156.76</v>
       </c>
       <c r="H7" s="8">
-        <v>36.4</v>
+        <v>36.36</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -791,10 +795,10 @@
         <v>17</v>
       </c>
       <c r="C8" s="6">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="D8" s="7">
-        <v>37.651059</v>
+        <v>37.844204</v>
       </c>
       <c r="E8" s="8">
         <v>33900000</v>
@@ -803,10 +807,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="8">
-        <v>1276370909.75</v>
+        <v>1282918509.91</v>
       </c>
       <c r="H8" s="8">
-        <v>37.96</v>
+        <v>37.88</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -817,10 +821,10 @@
         <v>19</v>
       </c>
       <c r="C9" s="6">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="D9" s="7">
-        <v>58.052416</v>
+        <v>58.110247</v>
       </c>
       <c r="E9" s="8">
         <v>2250000</v>
@@ -829,10 +833,10 @@
         <v>0</v>
       </c>
       <c r="G9" s="8">
-        <v>130617935.32</v>
+        <v>130748055.11</v>
       </c>
       <c r="H9" s="8">
-        <v>58.14</v>
+        <v>58.18</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -843,10 +847,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="6">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="D10" s="7">
-        <v>374.470944</v>
+        <v>388.080673</v>
       </c>
       <c r="E10" s="8">
         <v>135000</v>
@@ -855,10 +859,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="8">
-        <v>50553577.49</v>
+        <v>52390890.91</v>
       </c>
       <c r="H10" s="8">
-        <v>373.7</v>
+        <v>386.2</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -869,10 +873,10 @@
         <v>23</v>
       </c>
       <c r="C11" s="6">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="D11" s="7">
-        <v>557.268496</v>
+        <v>551.802152</v>
       </c>
       <c r="E11" s="8">
         <v>46350000</v>
@@ -881,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="G11" s="8">
-        <v>25829394785.65</v>
+        <v>25576029761.96</v>
       </c>
       <c r="H11" s="8">
-        <v>565.5</v>
+        <v>555.75</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -895,10 +899,10 @@
         <v>25</v>
       </c>
       <c r="C12" s="6">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="D12" s="7">
-        <v>690.187281</v>
+        <v>678.444963</v>
       </c>
       <c r="E12" s="8">
         <v>73550000</v>
@@ -907,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="G12" s="8">
-        <v>50763274491.2</v>
+        <v>49899627018.41</v>
       </c>
       <c r="H12" s="8">
-        <v>707.25</v>
+        <v>692.25</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -921,10 +925,10 @@
         <v>27</v>
       </c>
       <c r="C13" s="6">
-        <v>46174</v>
-      </c>
-      <c r="D13" s="7">
-        <v>4252.823352</v>
+        <v>46175</v>
+      </c>
+      <c r="D13" s="10">
+        <v>4276.69324</v>
       </c>
       <c r="E13" s="8">
         <v>280000</v>
@@ -933,10 +937,10 @@
         <v>0</v>
       </c>
       <c r="G13" s="8">
-        <v>1190790538.65</v>
+        <v>1197474107.18</v>
       </c>
       <c r="H13" s="8">
-        <v>4319</v>
+        <v>4305</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -947,10 +951,10 @@
         <v>29</v>
       </c>
       <c r="C14" s="6">
-        <v>46174</v>
-      </c>
-      <c r="D14" s="7">
-        <v>674.046895</v>
+        <v>46175</v>
+      </c>
+      <c r="D14" s="10">
+        <v>664.65998</v>
       </c>
       <c r="E14" s="8">
         <v>113800000</v>
@@ -959,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="8">
-        <v>76706536641.45</v>
+        <v>75638305701.3</v>
       </c>
       <c r="H14" s="8">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -973,10 +977,10 @@
         <v>31</v>
       </c>
       <c r="C15" s="6">
-        <v>46174</v>
-      </c>
-      <c r="D15" s="7">
-        <v>554.861777</v>
+        <v>46175</v>
+      </c>
+      <c r="D15" s="10">
+        <v>550.69728</v>
       </c>
       <c r="E15" s="8">
         <v>33450000</v>
@@ -985,10 +989,10 @@
         <v>0</v>
       </c>
       <c r="G15" s="8">
-        <v>18560126430.54</v>
+        <v>18420824024.02</v>
       </c>
       <c r="H15" s="8">
-        <v>558.25</v>
+        <v>549.75</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -999,10 +1003,10 @@
         <v>33</v>
       </c>
       <c r="C16" s="6">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="D16" s="7">
-        <v>25.216979</v>
+        <v>25.306508</v>
       </c>
       <c r="E16" s="8">
         <v>10800000</v>
@@ -1011,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="8">
-        <v>272343375.34</v>
+        <v>273310285.27</v>
       </c>
       <c r="H16" s="8">
-        <v>25.33</v>
+        <v>25.36</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1025,10 +1029,10 @@
         <v>35</v>
       </c>
       <c r="C17" s="6">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="D17" s="7">
-        <v>46.938987</v>
+        <v>46.988929</v>
       </c>
       <c r="E17" s="8">
         <v>1625000</v>
@@ -1037,10 +1041,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="8">
-        <v>76275853.88</v>
+        <v>76357009.94</v>
       </c>
       <c r="H17" s="8">
-        <v>46.99</v>
+        <v>47.04</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1051,10 +1055,10 @@
         <v>37</v>
       </c>
       <c r="C18" s="6">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="D18" s="7">
-        <v>71.826977</v>
+        <v>72.516824</v>
       </c>
       <c r="E18" s="8">
         <v>1140000</v>
@@ -1063,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="G18" s="8">
-        <v>81882753.71</v>
+        <v>82669179.29</v>
       </c>
       <c r="H18" s="8">
-        <v>71.66</v>
+        <v>72.42</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1077,10 +1081,10 @@
         <v>39</v>
       </c>
       <c r="C19" s="6">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="D19" s="7">
-        <v>81.311668</v>
+        <v>81.841137</v>
       </c>
       <c r="E19" s="8">
         <v>1155000</v>
@@ -1089,10 +1093,10 @@
         <v>0</v>
       </c>
       <c r="G19" s="8">
-        <v>93914977.05</v>
+        <v>94526513.33</v>
       </c>
       <c r="H19" s="8">
-        <v>81.88</v>
+        <v>81.9</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1103,10 +1107,10 @@
         <v>41</v>
       </c>
       <c r="C20" s="6">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="D20" s="7">
-        <v>50.034176</v>
+        <v>50.135808</v>
       </c>
       <c r="E20" s="8">
         <v>2985000</v>
@@ -1115,10 +1119,10 @@
         <v>0</v>
       </c>
       <c r="G20" s="8">
-        <v>149352015.71</v>
+        <v>149655386.89</v>
       </c>
       <c r="H20" s="8">
-        <v>50.24</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1129,10 +1133,10 @@
         <v>43</v>
       </c>
       <c r="C21" s="6">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="D21" s="7">
-        <v>165.177628</v>
+        <v>164.145424</v>
       </c>
       <c r="E21" s="8">
         <v>600000</v>
@@ -1141,10 +1145,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="8">
-        <v>99106576.69</v>
+        <v>98487254.42</v>
       </c>
       <c r="H21" s="8">
-        <v>166.75</v>
+        <v>165.7</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1155,22 +1159,22 @@
         <v>45</v>
       </c>
       <c r="C22" s="6">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="D22" s="7">
-        <v>203.435872</v>
+        <v>204.583432</v>
       </c>
       <c r="E22" s="8">
-        <v>114680000</v>
+        <v>117040000</v>
       </c>
       <c r="F22" s="9">
         <v>0</v>
       </c>
       <c r="G22" s="8">
-        <v>23330025848.09</v>
+        <v>23944444926.87</v>
       </c>
       <c r="H22" s="8">
-        <v>205.15</v>
+        <v>204.65</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1181,22 +1185,22 @@
         <v>47</v>
       </c>
       <c r="C23" s="6">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="D23" s="7">
-        <v>182.197631</v>
+        <v>182.705717</v>
       </c>
       <c r="E23" s="8">
-        <v>209760000</v>
+        <v>209040000</v>
       </c>
       <c r="F23" s="9">
         <v>0</v>
       </c>
       <c r="G23" s="8">
-        <v>38217775075.98</v>
+        <v>38192803078.41</v>
       </c>
       <c r="H23" s="8">
-        <v>183.05</v>
+        <v>182.85</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1207,10 +1211,10 @@
         <v>49</v>
       </c>
       <c r="C24" s="6">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="D24" s="7">
-        <v>189.999238</v>
+        <v>190.696228</v>
       </c>
       <c r="E24" s="8">
         <v>360000</v>
@@ -1219,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="G24" s="8">
-        <v>68399725.57</v>
+        <v>68650642.05</v>
       </c>
       <c r="H24" s="8">
-        <v>190</v>
+        <v>190.7</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1233,10 +1237,10 @@
         <v>51</v>
       </c>
       <c r="C25" s="6">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="D25" s="7">
-        <v>119.215549</v>
+        <v>120.512358</v>
       </c>
       <c r="E25" s="8">
         <v>600000</v>
@@ -1245,10 +1249,10 @@
         <v>0</v>
       </c>
       <c r="G25" s="8">
-        <v>71529329.62</v>
+        <v>72307415.01</v>
       </c>
       <c r="H25" s="8">
-        <v>119.2</v>
+        <v>120.5</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1259,10 +1263,10 @@
         <v>53</v>
       </c>
       <c r="C26" s="6">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="D26" s="7">
-        <v>681.178811</v>
+        <v>672.680335</v>
       </c>
       <c r="E26" s="8">
         <v>152040000</v>
@@ -1271,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="G26" s="8">
-        <v>103566426495.91</v>
+        <v>102274318087.14</v>
       </c>
       <c r="H26" s="8">
-        <v>702</v>
+        <v>690.75</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1285,10 +1289,10 @@
         <v>55</v>
       </c>
       <c r="C27" s="6">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="D27" s="7">
-        <v>178.178658</v>
+        <v>179.041922</v>
       </c>
       <c r="E27" s="8">
         <v>10960000</v>
@@ -1297,10 +1301,10 @@
         <v>0</v>
       </c>
       <c r="G27" s="8">
-        <v>1952838095.12</v>
+        <v>1962299468.06</v>
       </c>
       <c r="H27" s="8">
-        <v>178.9</v>
+        <v>181</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1311,22 +1315,22 @@
         <v>57</v>
       </c>
       <c r="C28" s="6">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="D28" s="7">
-        <v>250.242649</v>
+        <v>251.208047</v>
       </c>
       <c r="E28" s="8">
-        <v>32080000</v>
+        <v>32040000</v>
       </c>
       <c r="F28" s="9">
         <v>0</v>
       </c>
       <c r="G28" s="8">
-        <v>8027784176.64</v>
+        <v>8048705818.6</v>
       </c>
       <c r="H28" s="8">
-        <v>250.2</v>
+        <v>253</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1337,10 +1341,10 @@
         <v>59</v>
       </c>
       <c r="C29" s="6">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="D29" s="7">
-        <v>242.887091</v>
+        <v>244.306183</v>
       </c>
       <c r="E29" s="8">
         <v>3200000</v>
@@ -1349,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="G29" s="8">
-        <v>777238691.81</v>
+        <v>781779785.67</v>
       </c>
       <c r="H29" s="8">
-        <v>244.55</v>
+        <v>244.35</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1363,10 +1367,10 @@
         <v>61</v>
       </c>
       <c r="C30" s="6">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="D30" s="7">
-        <v>121.845333</v>
+        <v>124.762224</v>
       </c>
       <c r="E30" s="8">
         <v>440000</v>
@@ -1375,10 +1379,10 @@
         <v>0</v>
       </c>
       <c r="G30" s="8">
-        <v>53611946.69</v>
+        <v>54895378.51</v>
       </c>
       <c r="H30" s="8">
-        <v>126.05</v>
+        <v>124.85</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1389,10 +1393,10 @@
         <v>63</v>
       </c>
       <c r="C31" s="6">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="D31" s="7">
-        <v>173.202339</v>
+        <v>173.887556</v>
       </c>
       <c r="E31" s="8">
         <v>400000</v>
@@ -1401,10 +1405,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="8">
-        <v>69280935.68</v>
+        <v>69555022.58</v>
       </c>
       <c r="H31" s="8">
-        <v>173.95</v>
+        <v>173.9</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1415,10 +1419,10 @@
         <v>65</v>
       </c>
       <c r="C32" s="6">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="D32" s="7">
-        <v>45.853794</v>
+        <v>45.905788</v>
       </c>
       <c r="E32" s="8">
         <v>1200000</v>
@@ -1427,10 +1431,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="8">
-        <v>55024553.26</v>
+        <v>55086945.64</v>
       </c>
       <c r="H32" s="8">
-        <v>45.87</v>
+        <v>45.91</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1441,10 +1445,10 @@
         <v>67</v>
       </c>
       <c r="C33" s="6">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="D33" s="7">
-        <v>1250.804156</v>
+        <v>1252.151149</v>
       </c>
       <c r="E33" s="8">
         <v>600000</v>
@@ -1453,10 +1457,10 @@
         <v>0</v>
       </c>
       <c r="G33" s="8">
-        <v>750482493.67</v>
+        <v>751290689.19</v>
       </c>
       <c r="H33" s="8">
-        <v>1252.5</v>
+        <v>1253.5</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -1467,10 +1471,10 @@
         <v>69</v>
       </c>
       <c r="C34" s="6">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="D34" s="7">
-        <v>178.701382</v>
+        <v>179.386816</v>
       </c>
       <c r="E34" s="8">
         <v>680000</v>
@@ -1479,10 +1483,10 @@
         <v>0</v>
       </c>
       <c r="G34" s="8">
-        <v>121516940.09</v>
+        <v>121983034.65</v>
       </c>
       <c r="H34" s="8">
-        <v>178.7</v>
+        <v>179.4</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -1493,10 +1497,10 @@
         <v>71</v>
       </c>
       <c r="C35" s="6">
-        <v>46174</v>
-      </c>
-      <c r="D35" s="7">
-        <v>1251.901332</v>
+        <v>46175</v>
+      </c>
+      <c r="D35" s="10">
+        <v>1253.24462</v>
       </c>
       <c r="E35" s="8">
         <v>6240000</v>
@@ -1505,10 +1509,10 @@
         <v>0</v>
       </c>
       <c r="G35" s="8">
-        <v>7811864313.42</v>
+        <v>7820246431.51</v>
       </c>
       <c r="H35" s="8">
-        <v>1253</v>
+        <v>1255</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>02.06.2026 11:24:59</t>
+    <t>03.06.2026 17:45:40</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -743,10 +743,10 @@
         <v>13</v>
       </c>
       <c r="C6" s="6">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="D6" s="7">
-        <v>43.051018</v>
+        <v>45.057766</v>
       </c>
       <c r="E6" s="8">
         <v>58200000</v>
@@ -755,10 +755,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="8">
-        <v>2505569269.46</v>
+        <v>2622361992.16</v>
       </c>
       <c r="H6" s="8">
-        <v>43.16</v>
+        <v>45.06</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -769,10 +769,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="6">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="D7" s="7">
-        <v>36.370775</v>
+        <v>37.712341</v>
       </c>
       <c r="E7" s="8">
         <v>14400000</v>
@@ -781,10 +781,10 @@
         <v>0</v>
       </c>
       <c r="G7" s="8">
-        <v>523739156.76</v>
+        <v>543057708.72</v>
       </c>
       <c r="H7" s="8">
-        <v>36.36</v>
+        <v>37.53</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -795,10 +795,10 @@
         <v>17</v>
       </c>
       <c r="C8" s="6">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="D8" s="7">
-        <v>37.844204</v>
+        <v>39.355076</v>
       </c>
       <c r="E8" s="8">
         <v>33900000</v>
@@ -807,10 +807,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="8">
-        <v>1282918509.91</v>
+        <v>1334137067.52</v>
       </c>
       <c r="H8" s="8">
-        <v>37.88</v>
+        <v>39.33</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -821,10 +821,10 @@
         <v>19</v>
       </c>
       <c r="C9" s="6">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="D9" s="7">
-        <v>58.110247</v>
+        <v>58.171889</v>
       </c>
       <c r="E9" s="8">
         <v>2250000</v>
@@ -833,10 +833,10 @@
         <v>0</v>
       </c>
       <c r="G9" s="8">
-        <v>130748055.11</v>
+        <v>130886750.78</v>
       </c>
       <c r="H9" s="8">
-        <v>58.18</v>
+        <v>58.24</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -847,10 +847,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="6">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="D10" s="7">
-        <v>388.080673</v>
+        <v>402.315931</v>
       </c>
       <c r="E10" s="8">
         <v>135000</v>
@@ -859,10 +859,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="8">
-        <v>52390890.91</v>
+        <v>54312650.72</v>
       </c>
       <c r="H10" s="8">
-        <v>386.2</v>
+        <v>401.8</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -873,22 +873,22 @@
         <v>23</v>
       </c>
       <c r="C11" s="6">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="D11" s="7">
-        <v>551.802152</v>
+        <v>557.657078</v>
       </c>
       <c r="E11" s="8">
-        <v>46350000</v>
+        <v>44850000</v>
       </c>
       <c r="F11" s="9">
         <v>0</v>
       </c>
       <c r="G11" s="8">
-        <v>25576029761.96</v>
+        <v>25010919960.99</v>
       </c>
       <c r="H11" s="8">
-        <v>555.75</v>
+        <v>560.5</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -899,10 +899,10 @@
         <v>25</v>
       </c>
       <c r="C12" s="6">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="D12" s="7">
-        <v>678.444963</v>
+        <v>691.644856</v>
       </c>
       <c r="E12" s="8">
         <v>73550000</v>
@@ -911,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="G12" s="8">
-        <v>49899627018.41</v>
+        <v>50870479183.75</v>
       </c>
       <c r="H12" s="8">
-        <v>692.25</v>
+        <v>700</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -925,10 +925,10 @@
         <v>27</v>
       </c>
       <c r="C13" s="6">
-        <v>46175</v>
-      </c>
-      <c r="D13" s="10">
-        <v>4276.69324</v>
+        <v>46176</v>
+      </c>
+      <c r="D13" s="7">
+        <v>4279.056939</v>
       </c>
       <c r="E13" s="8">
         <v>280000</v>
@@ -937,10 +937,10 @@
         <v>0</v>
       </c>
       <c r="G13" s="8">
-        <v>1197474107.18</v>
+        <v>1198135942.95</v>
       </c>
       <c r="H13" s="8">
-        <v>4305</v>
+        <v>4308</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -951,10 +951,10 @@
         <v>29</v>
       </c>
       <c r="C14" s="6">
-        <v>46175</v>
-      </c>
-      <c r="D14" s="10">
-        <v>664.65998</v>
+        <v>46176</v>
+      </c>
+      <c r="D14" s="7">
+        <v>667.550348</v>
       </c>
       <c r="E14" s="8">
         <v>113800000</v>
@@ -963,7 +963,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="8">
-        <v>75638305701.3</v>
+        <v>75967229620.71</v>
       </c>
       <c r="H14" s="8">
         <v>690</v>
@@ -977,10 +977,10 @@
         <v>31</v>
       </c>
       <c r="C15" s="6">
-        <v>46175</v>
-      </c>
-      <c r="D15" s="10">
-        <v>550.69728</v>
+        <v>46176</v>
+      </c>
+      <c r="D15" s="7">
+        <v>551.601699</v>
       </c>
       <c r="E15" s="8">
         <v>33450000</v>
@@ -989,10 +989,10 @@
         <v>0</v>
       </c>
       <c r="G15" s="8">
-        <v>18420824024.02</v>
+        <v>18451076822.24</v>
       </c>
       <c r="H15" s="8">
-        <v>549.75</v>
+        <v>552.5</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1003,10 +1003,10 @@
         <v>33</v>
       </c>
       <c r="C16" s="6">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="D16" s="7">
-        <v>25.306508</v>
+        <v>25.917302</v>
       </c>
       <c r="E16" s="8">
         <v>10800000</v>
@@ -1015,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="8">
-        <v>273310285.27</v>
+        <v>279906861.03</v>
       </c>
       <c r="H16" s="8">
-        <v>25.36</v>
+        <v>25.92</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1029,10 +1029,10 @@
         <v>35</v>
       </c>
       <c r="C17" s="6">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="D17" s="7">
-        <v>46.988929</v>
+        <v>47.038943</v>
       </c>
       <c r="E17" s="8">
         <v>1625000</v>
@@ -1041,10 +1041,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="8">
-        <v>76357009.94</v>
+        <v>76438282.02</v>
       </c>
       <c r="H17" s="8">
-        <v>47.04</v>
+        <v>47.09</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1055,10 +1055,10 @@
         <v>37</v>
       </c>
       <c r="C18" s="6">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="D18" s="7">
-        <v>72.516824</v>
+        <v>74.516853</v>
       </c>
       <c r="E18" s="8">
         <v>1140000</v>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="G18" s="8">
-        <v>82669179.29</v>
+        <v>84949212.94</v>
       </c>
       <c r="H18" s="8">
-        <v>72.42</v>
+        <v>74.02</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1081,10 +1081,10 @@
         <v>39</v>
       </c>
       <c r="C19" s="6">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="D19" s="7">
-        <v>81.841137</v>
+        <v>85.029019</v>
       </c>
       <c r="E19" s="8">
         <v>1155000</v>
@@ -1093,10 +1093,10 @@
         <v>0</v>
       </c>
       <c r="G19" s="8">
-        <v>94526513.33</v>
+        <v>98208517.52</v>
       </c>
       <c r="H19" s="8">
-        <v>81.9</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1107,10 +1107,10 @@
         <v>41</v>
       </c>
       <c r="C20" s="6">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="D20" s="7">
-        <v>50.135808</v>
+        <v>51.717816</v>
       </c>
       <c r="E20" s="8">
         <v>2985000</v>
@@ -1119,10 +1119,10 @@
         <v>0</v>
       </c>
       <c r="G20" s="8">
-        <v>149655386.89</v>
+        <v>154377681.86</v>
       </c>
       <c r="H20" s="8">
-        <v>50.3</v>
+        <v>51.38</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1133,10 +1133,10 @@
         <v>43</v>
       </c>
       <c r="C21" s="6">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="D21" s="7">
-        <v>164.145424</v>
+        <v>167.964946</v>
       </c>
       <c r="E21" s="8">
         <v>600000</v>
@@ -1145,10 +1145,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="8">
-        <v>98487254.42</v>
+        <v>100778967.31</v>
       </c>
       <c r="H21" s="8">
-        <v>165.7</v>
+        <v>168.25</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1159,22 +1159,22 @@
         <v>45</v>
       </c>
       <c r="C22" s="6">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="D22" s="7">
-        <v>204.583432</v>
+        <v>212.773988</v>
       </c>
       <c r="E22" s="8">
-        <v>117040000</v>
+        <v>116520000</v>
       </c>
       <c r="F22" s="9">
         <v>0</v>
       </c>
       <c r="G22" s="8">
-        <v>23944444926.87</v>
+        <v>24792425083.51</v>
       </c>
       <c r="H22" s="8">
-        <v>204.65</v>
+        <v>212.95</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1185,22 +1185,22 @@
         <v>47</v>
       </c>
       <c r="C23" s="6">
-        <v>46175</v>
-      </c>
-      <c r="D23" s="7">
-        <v>182.705717</v>
+        <v>46176</v>
+      </c>
+      <c r="D23" s="10">
+        <v>191.41267</v>
       </c>
       <c r="E23" s="8">
-        <v>209040000</v>
+        <v>209120000</v>
       </c>
       <c r="F23" s="9">
         <v>0</v>
       </c>
       <c r="G23" s="8">
-        <v>38192803078.41</v>
+        <v>40028217477.27</v>
       </c>
       <c r="H23" s="8">
-        <v>182.85</v>
+        <v>192.7</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1211,22 +1211,22 @@
         <v>49</v>
       </c>
       <c r="C24" s="6">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="D24" s="7">
-        <v>190.696228</v>
+        <v>197.977912</v>
       </c>
       <c r="E24" s="8">
-        <v>360000</v>
+        <v>400000</v>
       </c>
       <c r="F24" s="9">
         <v>0</v>
       </c>
       <c r="G24" s="8">
-        <v>68650642.05</v>
+        <v>79191164.78</v>
       </c>
       <c r="H24" s="8">
-        <v>190.7</v>
+        <v>198.6</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1237,10 +1237,10 @@
         <v>51</v>
       </c>
       <c r="C25" s="6">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="D25" s="7">
-        <v>120.512358</v>
+        <v>124.569457</v>
       </c>
       <c r="E25" s="8">
         <v>600000</v>
@@ -1249,10 +1249,10 @@
         <v>0</v>
       </c>
       <c r="G25" s="8">
-        <v>72307415.01</v>
+        <v>74741674.16</v>
       </c>
       <c r="H25" s="8">
-        <v>120.5</v>
+        <v>124.55</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1263,10 +1263,10 @@
         <v>53</v>
       </c>
       <c r="C26" s="6">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="D26" s="7">
-        <v>672.680335</v>
+        <v>677.853002</v>
       </c>
       <c r="E26" s="8">
         <v>152040000</v>
@@ -1275,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="G26" s="8">
-        <v>102274318087.14</v>
+        <v>103060770397.04</v>
       </c>
       <c r="H26" s="8">
-        <v>690.75</v>
+        <v>695.5</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1289,10 +1289,10 @@
         <v>55</v>
       </c>
       <c r="C27" s="6">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="D27" s="7">
-        <v>179.041922</v>
+        <v>184.180659</v>
       </c>
       <c r="E27" s="8">
         <v>10960000</v>
@@ -1301,10 +1301,10 @@
         <v>0</v>
       </c>
       <c r="G27" s="8">
-        <v>1962299468.06</v>
+        <v>2018620018.91</v>
       </c>
       <c r="H27" s="8">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1315,10 +1315,10 @@
         <v>57</v>
       </c>
       <c r="C28" s="6">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="D28" s="7">
-        <v>251.208047</v>
+        <v>257.493924</v>
       </c>
       <c r="E28" s="8">
         <v>32040000</v>
@@ -1327,10 +1327,10 @@
         <v>0</v>
       </c>
       <c r="G28" s="8">
-        <v>8048705818.6</v>
+        <v>8250105316.33</v>
       </c>
       <c r="H28" s="8">
-        <v>253</v>
+        <v>257.5</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1341,10 +1341,10 @@
         <v>59</v>
       </c>
       <c r="C29" s="6">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="D29" s="7">
-        <v>244.306183</v>
+        <v>253.300715</v>
       </c>
       <c r="E29" s="8">
         <v>3200000</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="G29" s="8">
-        <v>781779785.67</v>
+        <v>810562288.94</v>
       </c>
       <c r="H29" s="8">
-        <v>244.35</v>
+        <v>253.2</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1367,10 +1367,10 @@
         <v>61</v>
       </c>
       <c r="C30" s="6">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="D30" s="7">
-        <v>124.762224</v>
+        <v>130.729924</v>
       </c>
       <c r="E30" s="8">
         <v>440000</v>
@@ -1379,10 +1379,10 @@
         <v>0</v>
       </c>
       <c r="G30" s="8">
-        <v>54895378.51</v>
+        <v>57521166.76</v>
       </c>
       <c r="H30" s="8">
-        <v>124.85</v>
+        <v>130.75</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1393,10 +1393,10 @@
         <v>63</v>
       </c>
       <c r="C31" s="6">
-        <v>46175</v>
-      </c>
-      <c r="D31" s="7">
-        <v>173.887556</v>
+        <v>46176</v>
+      </c>
+      <c r="D31" s="10">
+        <v>180.55125</v>
       </c>
       <c r="E31" s="8">
         <v>400000</v>
@@ -1405,10 +1405,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="8">
-        <v>69555022.58</v>
+        <v>72220499.92</v>
       </c>
       <c r="H31" s="8">
-        <v>173.9</v>
+        <v>180.55</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1419,10 +1419,10 @@
         <v>65</v>
       </c>
       <c r="C32" s="6">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="D32" s="7">
-        <v>45.905788</v>
+        <v>47.595469</v>
       </c>
       <c r="E32" s="8">
         <v>1200000</v>
@@ -1431,10 +1431,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="8">
-        <v>55086945.64</v>
+        <v>57114562.27</v>
       </c>
       <c r="H32" s="8">
-        <v>45.91</v>
+        <v>47.57</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1445,10 +1445,10 @@
         <v>67</v>
       </c>
       <c r="C33" s="6">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="D33" s="7">
-        <v>1252.151149</v>
+        <v>1253.498582</v>
       </c>
       <c r="E33" s="8">
         <v>600000</v>
@@ -1457,10 +1457,10 @@
         <v>0</v>
       </c>
       <c r="G33" s="8">
-        <v>751290689.19</v>
+        <v>752099148.94</v>
       </c>
       <c r="H33" s="8">
-        <v>1253.5</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -1471,10 +1471,10 @@
         <v>69</v>
       </c>
       <c r="C34" s="6">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="D34" s="7">
-        <v>179.386816</v>
+        <v>185.230666</v>
       </c>
       <c r="E34" s="8">
         <v>680000</v>
@@ -1483,10 +1483,10 @@
         <v>0</v>
       </c>
       <c r="G34" s="8">
-        <v>121983034.65</v>
+        <v>125956853.08</v>
       </c>
       <c r="H34" s="8">
-        <v>179.4</v>
+        <v>186.6</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -1497,10 +1497,10 @@
         <v>71</v>
       </c>
       <c r="C35" s="6">
-        <v>46175</v>
-      </c>
-      <c r="D35" s="10">
-        <v>1253.24462</v>
+        <v>46176</v>
+      </c>
+      <c r="D35" s="7">
+        <v>1254.589213</v>
       </c>
       <c r="E35" s="8">
         <v>6240000</v>
@@ -1509,10 +1509,10 @@
         <v>0</v>
       </c>
       <c r="G35" s="8">
-        <v>7820246431.51</v>
+        <v>7828636690.81</v>
       </c>
       <c r="H35" s="8">
-        <v>1255</v>
+        <v>1255.5</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>03.06.2026 17:45:40</t>
+    <t>04.06.2026 10:50:42</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -743,10 +743,10 @@
         <v>13</v>
       </c>
       <c r="C6" s="6">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="D6" s="7">
-        <v>45.057766</v>
+        <v>44.224491</v>
       </c>
       <c r="E6" s="8">
         <v>58200000</v>
@@ -755,10 +755,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="8">
-        <v>2622361992.16</v>
+        <v>2573865376.68</v>
       </c>
       <c r="H6" s="8">
-        <v>45.06</v>
+        <v>44.27</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -769,10 +769,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="6">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="D7" s="7">
-        <v>37.712341</v>
+        <v>36.660975</v>
       </c>
       <c r="E7" s="8">
         <v>14400000</v>
@@ -781,10 +781,10 @@
         <v>0</v>
       </c>
       <c r="G7" s="8">
-        <v>543057708.72</v>
+        <v>527918037.01</v>
       </c>
       <c r="H7" s="8">
-        <v>37.53</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -795,10 +795,10 @@
         <v>17</v>
       </c>
       <c r="C8" s="6">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="D8" s="7">
-        <v>39.355076</v>
+        <v>38.445755</v>
       </c>
       <c r="E8" s="8">
         <v>33900000</v>
@@ -807,10 +807,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="8">
-        <v>1334137067.52</v>
+        <v>1303311100.32</v>
       </c>
       <c r="H8" s="8">
-        <v>39.33</v>
+        <v>38.42</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -821,10 +821,10 @@
         <v>19</v>
       </c>
       <c r="C9" s="6">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="D9" s="7">
-        <v>58.171889</v>
+        <v>58.233602</v>
       </c>
       <c r="E9" s="8">
         <v>2250000</v>
@@ -833,10 +833,10 @@
         <v>0</v>
       </c>
       <c r="G9" s="8">
-        <v>130886750.78</v>
+        <v>131025605.12</v>
       </c>
       <c r="H9" s="8">
-        <v>58.24</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -847,10 +847,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="6">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="D10" s="7">
-        <v>402.315931</v>
+        <v>386.261664</v>
       </c>
       <c r="E10" s="8">
         <v>135000</v>
@@ -859,10 +859,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="8">
-        <v>54312650.72</v>
+        <v>52145324.69</v>
       </c>
       <c r="H10" s="8">
-        <v>401.8</v>
+        <v>385.2</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -873,10 +873,10 @@
         <v>23</v>
       </c>
       <c r="C11" s="6">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="D11" s="7">
-        <v>557.657078</v>
+        <v>550.683482</v>
       </c>
       <c r="E11" s="8">
         <v>44850000</v>
@@ -885,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="G11" s="8">
-        <v>25010919960.99</v>
+        <v>24698154185.31</v>
       </c>
       <c r="H11" s="8">
-        <v>560.5</v>
+        <v>552</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -899,10 +899,10 @@
         <v>25</v>
       </c>
       <c r="C12" s="6">
-        <v>46176</v>
-      </c>
-      <c r="D12" s="7">
-        <v>691.644856</v>
+        <v>46177</v>
+      </c>
+      <c r="D12" s="10">
+        <v>670.67724</v>
       </c>
       <c r="E12" s="8">
         <v>73550000</v>
@@ -911,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="G12" s="8">
-        <v>50870479183.75</v>
+        <v>49328310971.41</v>
       </c>
       <c r="H12" s="8">
-        <v>700</v>
+        <v>681</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -925,10 +925,10 @@
         <v>27</v>
       </c>
       <c r="C13" s="6">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="D13" s="7">
-        <v>4279.056939</v>
+        <v>4280.024122</v>
       </c>
       <c r="E13" s="8">
         <v>280000</v>
@@ -937,10 +937,10 @@
         <v>0</v>
       </c>
       <c r="G13" s="8">
-        <v>1198135942.95</v>
+        <v>1198406754.22</v>
       </c>
       <c r="H13" s="8">
-        <v>4308</v>
+        <v>4299</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -951,10 +951,10 @@
         <v>29</v>
       </c>
       <c r="C14" s="6">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="D14" s="7">
-        <v>667.550348</v>
+        <v>662.834764</v>
       </c>
       <c r="E14" s="8">
         <v>113800000</v>
@@ -963,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="8">
-        <v>75967229620.71</v>
+        <v>75430596137.72</v>
       </c>
       <c r="H14" s="8">
-        <v>690</v>
+        <v>675.75</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -977,10 +977,10 @@
         <v>31</v>
       </c>
       <c r="C15" s="6">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="D15" s="7">
-        <v>551.601699</v>
+        <v>545.208946</v>
       </c>
       <c r="E15" s="8">
         <v>33450000</v>
@@ -989,10 +989,10 @@
         <v>0</v>
       </c>
       <c r="G15" s="8">
-        <v>18451076822.24</v>
+        <v>18237239254.2</v>
       </c>
       <c r="H15" s="8">
-        <v>552.5</v>
+        <v>550</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1003,10 +1003,10 @@
         <v>33</v>
       </c>
       <c r="C16" s="6">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="D16" s="7">
-        <v>25.917302</v>
+        <v>25.434187</v>
       </c>
       <c r="E16" s="8">
         <v>10800000</v>
@@ -1015,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="8">
-        <v>279906861.03</v>
+        <v>274689223.79</v>
       </c>
       <c r="H16" s="8">
-        <v>25.92</v>
+        <v>25.38</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1029,10 +1029,10 @@
         <v>35</v>
       </c>
       <c r="C17" s="6">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="D17" s="7">
-        <v>47.038943</v>
+        <v>47.088979</v>
       </c>
       <c r="E17" s="8">
         <v>1625000</v>
@@ -1041,10 +1041,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="8">
-        <v>76438282.02</v>
+        <v>76519590.75</v>
       </c>
       <c r="H17" s="8">
-        <v>47.09</v>
+        <v>47.15</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1055,10 +1055,10 @@
         <v>37</v>
       </c>
       <c r="C18" s="6">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="D18" s="7">
-        <v>74.516853</v>
+        <v>73.311705</v>
       </c>
       <c r="E18" s="8">
         <v>1140000</v>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="G18" s="8">
-        <v>84949212.94</v>
+        <v>83575343.45</v>
       </c>
       <c r="H18" s="8">
-        <v>74.02</v>
+        <v>73.42</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1081,10 +1081,10 @@
         <v>39</v>
       </c>
       <c r="C19" s="6">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="D19" s="7">
-        <v>85.029019</v>
+        <v>83.056153</v>
       </c>
       <c r="E19" s="8">
         <v>1155000</v>
@@ -1093,10 +1093,10 @@
         <v>0</v>
       </c>
       <c r="G19" s="8">
-        <v>98208517.52</v>
+        <v>95929856.64</v>
       </c>
       <c r="H19" s="8">
-        <v>85.2</v>
+        <v>82.9</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1107,10 +1107,10 @@
         <v>41</v>
       </c>
       <c r="C20" s="6">
-        <v>46176</v>
-      </c>
-      <c r="D20" s="7">
-        <v>51.717816</v>
+        <v>46177</v>
+      </c>
+      <c r="D20" s="10">
+        <v>50.75021</v>
       </c>
       <c r="E20" s="8">
         <v>2985000</v>
@@ -1119,10 +1119,10 @@
         <v>0</v>
       </c>
       <c r="G20" s="8">
-        <v>154377681.86</v>
+        <v>151489376.54</v>
       </c>
       <c r="H20" s="8">
-        <v>51.38</v>
+        <v>50.78</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1133,10 +1133,10 @@
         <v>43</v>
       </c>
       <c r="C21" s="6">
-        <v>46176</v>
-      </c>
-      <c r="D21" s="7">
-        <v>167.964946</v>
+        <v>46177</v>
+      </c>
+      <c r="D21" s="10">
+        <v>163.78796</v>
       </c>
       <c r="E21" s="8">
         <v>600000</v>
@@ -1145,10 +1145,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="8">
-        <v>100778967.31</v>
+        <v>98272775.84</v>
       </c>
       <c r="H21" s="8">
-        <v>168.25</v>
+        <v>164.3</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1159,22 +1159,22 @@
         <v>45</v>
       </c>
       <c r="C22" s="6">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="D22" s="7">
-        <v>212.773988</v>
+        <v>207.745132</v>
       </c>
       <c r="E22" s="8">
-        <v>116520000</v>
+        <v>116960000</v>
       </c>
       <c r="F22" s="9">
         <v>0</v>
       </c>
       <c r="G22" s="8">
-        <v>24792425083.51</v>
+        <v>24297870683</v>
       </c>
       <c r="H22" s="8">
-        <v>212.95</v>
+        <v>207.6</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1185,22 +1185,22 @@
         <v>47</v>
       </c>
       <c r="C23" s="6">
-        <v>46176</v>
-      </c>
-      <c r="D23" s="10">
-        <v>191.41267</v>
+        <v>46177</v>
+      </c>
+      <c r="D23" s="7">
+        <v>187.805384</v>
       </c>
       <c r="E23" s="8">
-        <v>209120000</v>
+        <v>210840000</v>
       </c>
       <c r="F23" s="9">
         <v>0</v>
       </c>
       <c r="G23" s="8">
-        <v>40028217477.27</v>
+        <v>39596887129.95</v>
       </c>
       <c r="H23" s="8">
-        <v>192.7</v>
+        <v>187.9</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1211,10 +1211,10 @@
         <v>49</v>
       </c>
       <c r="C24" s="6">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="D24" s="7">
-        <v>197.977912</v>
+        <v>195.065434</v>
       </c>
       <c r="E24" s="8">
         <v>400000</v>
@@ -1223,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="G24" s="8">
-        <v>79191164.78</v>
+        <v>78026173.55</v>
       </c>
       <c r="H24" s="8">
-        <v>198.6</v>
+        <v>195.05</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1237,10 +1237,10 @@
         <v>51</v>
       </c>
       <c r="C25" s="6">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="D25" s="7">
-        <v>124.569457</v>
+        <v>122.729259</v>
       </c>
       <c r="E25" s="8">
         <v>600000</v>
@@ -1249,10 +1249,10 @@
         <v>0</v>
       </c>
       <c r="G25" s="8">
-        <v>74741674.16</v>
+        <v>73637555.6</v>
       </c>
       <c r="H25" s="8">
-        <v>124.55</v>
+        <v>122.7</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1263,10 +1263,10 @@
         <v>53</v>
       </c>
       <c r="C26" s="6">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="D26" s="7">
-        <v>677.853002</v>
+        <v>670.530458</v>
       </c>
       <c r="E26" s="8">
         <v>152040000</v>
@@ -1275,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="G26" s="8">
-        <v>103060770397.04</v>
+        <v>101947450785.01</v>
       </c>
       <c r="H26" s="8">
-        <v>695.5</v>
+        <v>680.75</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1289,22 +1289,22 @@
         <v>55</v>
       </c>
       <c r="C27" s="6">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="D27" s="7">
-        <v>184.180659</v>
+        <v>181.871808</v>
       </c>
       <c r="E27" s="8">
-        <v>10960000</v>
+        <v>11000000</v>
       </c>
       <c r="F27" s="9">
         <v>0</v>
       </c>
       <c r="G27" s="8">
-        <v>2018620018.91</v>
+        <v>2000589888.59</v>
       </c>
       <c r="H27" s="8">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1315,10 +1315,10 @@
         <v>57</v>
       </c>
       <c r="C28" s="6">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="D28" s="7">
-        <v>257.493924</v>
+        <v>253.343179</v>
       </c>
       <c r="E28" s="8">
         <v>32040000</v>
@@ -1327,10 +1327,10 @@
         <v>0</v>
       </c>
       <c r="G28" s="8">
-        <v>8250105316.33</v>
+        <v>8117115446.52</v>
       </c>
       <c r="H28" s="8">
-        <v>257.5</v>
+        <v>260</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1341,10 +1341,10 @@
         <v>59</v>
       </c>
       <c r="C29" s="6">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="D29" s="7">
-        <v>253.300715</v>
+        <v>246.215377</v>
       </c>
       <c r="E29" s="8">
         <v>3200000</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="G29" s="8">
-        <v>810562288.94</v>
+        <v>787889206.16</v>
       </c>
       <c r="H29" s="8">
-        <v>253.2</v>
+        <v>246.2</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1367,10 +1367,10 @@
         <v>61</v>
       </c>
       <c r="C30" s="6">
-        <v>46176</v>
-      </c>
-      <c r="D30" s="7">
-        <v>130.729924</v>
+        <v>46177</v>
+      </c>
+      <c r="D30" s="10">
+        <v>126.76356</v>
       </c>
       <c r="E30" s="8">
         <v>440000</v>
@@ -1379,10 +1379,10 @@
         <v>0</v>
       </c>
       <c r="G30" s="8">
-        <v>57521166.76</v>
+        <v>55775966.55</v>
       </c>
       <c r="H30" s="8">
-        <v>130.75</v>
+        <v>126.75</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1393,10 +1393,10 @@
         <v>63</v>
       </c>
       <c r="C31" s="6">
-        <v>46176</v>
-      </c>
-      <c r="D31" s="10">
-        <v>180.55125</v>
+        <v>46177</v>
+      </c>
+      <c r="D31" s="7">
+        <v>178.126239</v>
       </c>
       <c r="E31" s="8">
         <v>400000</v>
@@ -1405,10 +1405,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="8">
-        <v>72220499.92</v>
+        <v>71250495.66</v>
       </c>
       <c r="H31" s="8">
-        <v>180.55</v>
+        <v>178.15</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1419,10 +1419,10 @@
         <v>65</v>
       </c>
       <c r="C32" s="6">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="D32" s="7">
-        <v>47.595469</v>
+        <v>46.440807</v>
       </c>
       <c r="E32" s="8">
         <v>1200000</v>
@@ -1431,10 +1431,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="8">
-        <v>57114562.27</v>
+        <v>55728967.98</v>
       </c>
       <c r="H32" s="8">
-        <v>47.57</v>
+        <v>46.45</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1445,10 +1445,10 @@
         <v>67</v>
       </c>
       <c r="C33" s="6">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="D33" s="7">
-        <v>1253.498582</v>
+        <v>1254.847454</v>
       </c>
       <c r="E33" s="8">
         <v>600000</v>
@@ -1457,10 +1457,10 @@
         <v>0</v>
       </c>
       <c r="G33" s="8">
-        <v>752099148.94</v>
+        <v>752908472.39</v>
       </c>
       <c r="H33" s="8">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -1471,10 +1471,10 @@
         <v>69</v>
       </c>
       <c r="C34" s="6">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="D34" s="7">
-        <v>185.230666</v>
+        <v>181.630992</v>
       </c>
       <c r="E34" s="8">
         <v>680000</v>
@@ -1483,10 +1483,10 @@
         <v>0</v>
       </c>
       <c r="G34" s="8">
-        <v>125956853.08</v>
+        <v>123509074.78</v>
       </c>
       <c r="H34" s="8">
-        <v>186.6</v>
+        <v>181.65</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -1497,10 +1497,10 @@
         <v>71</v>
       </c>
       <c r="C35" s="6">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="D35" s="7">
-        <v>1254.589213</v>
+        <v>1255.935441</v>
       </c>
       <c r="E35" s="8">
         <v>6240000</v>
@@ -1509,10 +1509,10 @@
         <v>0</v>
       </c>
       <c r="G35" s="8">
-        <v>7828636690.81</v>
+        <v>7837037152.61</v>
       </c>
       <c r="H35" s="8">
-        <v>1255.5</v>
+        <v>1257</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>04.06.2026 10:50:42</t>
+    <t>05.06.2026 11:21:20</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -743,10 +743,10 @@
         <v>13</v>
       </c>
       <c r="C6" s="6">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="D6" s="7">
-        <v>44.224491</v>
+        <v>45.219878</v>
       </c>
       <c r="E6" s="8">
         <v>58200000</v>
@@ -755,10 +755,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="8">
-        <v>2573865376.68</v>
+        <v>2631796889.42</v>
       </c>
       <c r="H6" s="8">
-        <v>44.27</v>
+        <v>45.19</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -769,10 +769,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="6">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="D7" s="7">
-        <v>36.660975</v>
+        <v>35.929718</v>
       </c>
       <c r="E7" s="8">
         <v>14400000</v>
@@ -781,10 +781,10 @@
         <v>0</v>
       </c>
       <c r="G7" s="8">
-        <v>527918037.01</v>
+        <v>517387938.09</v>
       </c>
       <c r="H7" s="8">
-        <v>36.6</v>
+        <v>36.08</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -795,10 +795,10 @@
         <v>17</v>
       </c>
       <c r="C8" s="6">
-        <v>46177</v>
-      </c>
-      <c r="D8" s="7">
-        <v>38.445755</v>
+        <v>46178</v>
+      </c>
+      <c r="D8" s="10">
+        <v>38.01235</v>
       </c>
       <c r="E8" s="8">
         <v>33900000</v>
@@ -807,10 +807,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="8">
-        <v>1303311100.32</v>
+        <v>1288618667.89</v>
       </c>
       <c r="H8" s="8">
-        <v>38.42</v>
+        <v>37.97</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -821,10 +821,10 @@
         <v>19</v>
       </c>
       <c r="C9" s="6">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="D9" s="7">
-        <v>58.233602</v>
+        <v>58.295414</v>
       </c>
       <c r="E9" s="8">
         <v>2250000</v>
@@ -833,10 +833,10 @@
         <v>0</v>
       </c>
       <c r="G9" s="8">
-        <v>131025605.12</v>
+        <v>131164682.42</v>
       </c>
       <c r="H9" s="8">
-        <v>58.3</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -847,10 +847,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="6">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="D10" s="7">
-        <v>386.261664</v>
+        <v>375.146204</v>
       </c>
       <c r="E10" s="8">
         <v>135000</v>
@@ -859,10 +859,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="8">
-        <v>52145324.69</v>
+        <v>50644737.51</v>
       </c>
       <c r="H10" s="8">
-        <v>385.2</v>
+        <v>375.9</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -873,10 +873,10 @@
         <v>23</v>
       </c>
       <c r="C11" s="6">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="D11" s="7">
-        <v>550.683482</v>
+        <v>553.700623</v>
       </c>
       <c r="E11" s="8">
         <v>44850000</v>
@@ -885,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="G11" s="8">
-        <v>24698154185.31</v>
+        <v>24833472937.93</v>
       </c>
       <c r="H11" s="8">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -899,10 +899,10 @@
         <v>25</v>
       </c>
       <c r="C12" s="6">
-        <v>46177</v>
-      </c>
-      <c r="D12" s="10">
-        <v>670.67724</v>
+        <v>46178</v>
+      </c>
+      <c r="D12" s="7">
+        <v>671.559685</v>
       </c>
       <c r="E12" s="8">
         <v>73550000</v>
@@ -911,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="G12" s="8">
-        <v>49328310971.41</v>
+        <v>49393214849.73</v>
       </c>
       <c r="H12" s="8">
-        <v>681</v>
+        <v>682.5</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -925,10 +925,10 @@
         <v>27</v>
       </c>
       <c r="C13" s="6">
-        <v>46177</v>
-      </c>
-      <c r="D13" s="7">
-        <v>4280.024122</v>
+        <v>46178</v>
+      </c>
+      <c r="D13" s="10">
+        <v>4283.27222</v>
       </c>
       <c r="E13" s="8">
         <v>280000</v>
@@ -937,10 +937,10 @@
         <v>0</v>
       </c>
       <c r="G13" s="8">
-        <v>1198406754.22</v>
+        <v>1199316221.67</v>
       </c>
       <c r="H13" s="8">
-        <v>4299</v>
+        <v>4300</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -951,10 +951,10 @@
         <v>29</v>
       </c>
       <c r="C14" s="6">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="D14" s="7">
-        <v>662.834764</v>
+        <v>667.728526</v>
       </c>
       <c r="E14" s="8">
         <v>113800000</v>
@@ -963,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="8">
-        <v>75430596137.72</v>
+        <v>75987506238.66</v>
       </c>
       <c r="H14" s="8">
-        <v>675.75</v>
+        <v>672</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -977,10 +977,10 @@
         <v>31</v>
       </c>
       <c r="C15" s="6">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="D15" s="7">
-        <v>545.208946</v>
+        <v>544.996458</v>
       </c>
       <c r="E15" s="8">
         <v>33450000</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="8">
-        <v>18237239254.2</v>
+        <v>18230131531.92</v>
       </c>
       <c r="H15" s="8">
         <v>550</v>
@@ -1003,10 +1003,10 @@
         <v>33</v>
       </c>
       <c r="C16" s="6">
-        <v>46177</v>
-      </c>
-      <c r="D16" s="7">
-        <v>25.434187</v>
+        <v>46178</v>
+      </c>
+      <c r="D16" s="10">
+        <v>25.38445</v>
       </c>
       <c r="E16" s="8">
         <v>10800000</v>
@@ -1015,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="8">
-        <v>274689223.79</v>
+        <v>274152060.17</v>
       </c>
       <c r="H16" s="8">
-        <v>25.38</v>
+        <v>25.36</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1029,10 +1029,10 @@
         <v>35</v>
       </c>
       <c r="C17" s="6">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="D17" s="7">
-        <v>47.088979</v>
+        <v>47.139071</v>
       </c>
       <c r="E17" s="8">
         <v>1625000</v>
@@ -1041,10 +1041,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="8">
-        <v>76519590.75</v>
+        <v>76600990.97</v>
       </c>
       <c r="H17" s="8">
-        <v>47.15</v>
+        <v>47.28</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1055,10 +1055,10 @@
         <v>37</v>
       </c>
       <c r="C18" s="6">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="D18" s="7">
-        <v>73.311705</v>
+        <v>72.961483</v>
       </c>
       <c r="E18" s="8">
         <v>1140000</v>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="G18" s="8">
-        <v>83575343.45</v>
+        <v>83176090.83</v>
       </c>
       <c r="H18" s="8">
-        <v>73.42</v>
+        <v>72.84</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1081,10 +1081,10 @@
         <v>39</v>
       </c>
       <c r="C19" s="6">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="D19" s="7">
-        <v>83.056153</v>
+        <v>82.131734</v>
       </c>
       <c r="E19" s="8">
         <v>1155000</v>
@@ -1093,10 +1093,10 @@
         <v>0</v>
       </c>
       <c r="G19" s="8">
-        <v>95929856.64</v>
+        <v>94862152.68</v>
       </c>
       <c r="H19" s="8">
-        <v>82.9</v>
+        <v>82.24</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1107,10 +1107,10 @@
         <v>41</v>
       </c>
       <c r="C20" s="6">
-        <v>46177</v>
-      </c>
-      <c r="D20" s="10">
-        <v>50.75021</v>
+        <v>46178</v>
+      </c>
+      <c r="D20" s="7">
+        <v>50.825642</v>
       </c>
       <c r="E20" s="8">
         <v>2985000</v>
@@ -1119,10 +1119,10 @@
         <v>0</v>
       </c>
       <c r="G20" s="8">
-        <v>151489376.54</v>
+        <v>151714541.47</v>
       </c>
       <c r="H20" s="8">
-        <v>50.78</v>
+        <v>50.74</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1133,10 +1133,10 @@
         <v>43</v>
       </c>
       <c r="C21" s="6">
-        <v>46177</v>
-      </c>
-      <c r="D21" s="10">
-        <v>163.78796</v>
+        <v>46178</v>
+      </c>
+      <c r="D21" s="7">
+        <v>164.854504</v>
       </c>
       <c r="E21" s="8">
         <v>600000</v>
@@ -1145,10 +1145,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="8">
-        <v>98272775.84</v>
+        <v>98912702.52</v>
       </c>
       <c r="H21" s="8">
-        <v>164.3</v>
+        <v>165.05</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1159,22 +1159,22 @@
         <v>45</v>
       </c>
       <c r="C22" s="6">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="D22" s="7">
-        <v>207.745132</v>
+        <v>205.293137</v>
       </c>
       <c r="E22" s="8">
-        <v>116960000</v>
+        <v>118560000</v>
       </c>
       <c r="F22" s="9">
         <v>0</v>
       </c>
       <c r="G22" s="8">
-        <v>24297870683</v>
+        <v>24339554358.76</v>
       </c>
       <c r="H22" s="8">
-        <v>207.6</v>
+        <v>205.2</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1185,22 +1185,22 @@
         <v>47</v>
       </c>
       <c r="C23" s="6">
-        <v>46177</v>
-      </c>
-      <c r="D23" s="7">
-        <v>187.805384</v>
+        <v>46178</v>
+      </c>
+      <c r="D23" s="10">
+        <v>192.05286</v>
       </c>
       <c r="E23" s="8">
-        <v>210840000</v>
+        <v>210000000</v>
       </c>
       <c r="F23" s="9">
         <v>0</v>
       </c>
       <c r="G23" s="8">
-        <v>39596887129.95</v>
+        <v>40331100676.47</v>
       </c>
       <c r="H23" s="8">
-        <v>187.9</v>
+        <v>191.9</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1211,10 +1211,10 @@
         <v>49</v>
       </c>
       <c r="C24" s="6">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="D24" s="7">
-        <v>195.065434</v>
+        <v>193.996085</v>
       </c>
       <c r="E24" s="8">
         <v>400000</v>
@@ -1223,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="G24" s="8">
-        <v>78026173.55</v>
+        <v>77598433.8</v>
       </c>
       <c r="H24" s="8">
-        <v>195.05</v>
+        <v>194</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1237,10 +1237,10 @@
         <v>51</v>
       </c>
       <c r="C25" s="6">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="D25" s="7">
-        <v>122.729259</v>
+        <v>121.722121</v>
       </c>
       <c r="E25" s="8">
         <v>600000</v>
@@ -1249,10 +1249,10 @@
         <v>0</v>
       </c>
       <c r="G25" s="8">
-        <v>73637555.6</v>
+        <v>73033272.35</v>
       </c>
       <c r="H25" s="8">
-        <v>122.7</v>
+        <v>121.7</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1263,10 +1263,10 @@
         <v>53</v>
       </c>
       <c r="C26" s="6">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="D26" s="7">
-        <v>670.530458</v>
+        <v>673.578291</v>
       </c>
       <c r="E26" s="8">
         <v>152040000</v>
@@ -1275,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="G26" s="8">
-        <v>101947450785.01</v>
+        <v>102410843349.01</v>
       </c>
       <c r="H26" s="8">
-        <v>680.75</v>
+        <v>679.5</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1289,10 +1289,10 @@
         <v>55</v>
       </c>
       <c r="C27" s="6">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="D27" s="7">
-        <v>181.871808</v>
+        <v>180.851874</v>
       </c>
       <c r="E27" s="8">
         <v>11000000</v>
@@ -1301,10 +1301,10 @@
         <v>0</v>
       </c>
       <c r="G27" s="8">
-        <v>2000589888.59</v>
+        <v>1989370612.75</v>
       </c>
       <c r="H27" s="8">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1315,22 +1315,22 @@
         <v>57</v>
       </c>
       <c r="C28" s="6">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="D28" s="7">
-        <v>253.343179</v>
+        <v>252.290086</v>
       </c>
       <c r="E28" s="8">
-        <v>32040000</v>
+        <v>32200000</v>
       </c>
       <c r="F28" s="9">
         <v>0</v>
       </c>
       <c r="G28" s="8">
-        <v>8117115446.52</v>
+        <v>8123740760.29</v>
       </c>
       <c r="H28" s="8">
-        <v>260</v>
+        <v>255</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1341,10 +1341,10 @@
         <v>59</v>
       </c>
       <c r="C29" s="6">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="D29" s="7">
-        <v>246.215377</v>
+        <v>241.307528</v>
       </c>
       <c r="E29" s="8">
         <v>3200000</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="G29" s="8">
-        <v>787889206.16</v>
+        <v>772184088.53</v>
       </c>
       <c r="H29" s="8">
-        <v>246.2</v>
+        <v>241.15</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1367,10 +1367,10 @@
         <v>61</v>
       </c>
       <c r="C30" s="6">
-        <v>46177</v>
-      </c>
-      <c r="D30" s="10">
-        <v>126.76356</v>
+        <v>46178</v>
+      </c>
+      <c r="D30" s="7">
+        <v>124.423041</v>
       </c>
       <c r="E30" s="8">
         <v>440000</v>
@@ -1379,10 +1379,10 @@
         <v>0</v>
       </c>
       <c r="G30" s="8">
-        <v>55775966.55</v>
+        <v>54746138.17</v>
       </c>
       <c r="H30" s="8">
-        <v>126.75</v>
+        <v>124.7</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1393,10 +1393,10 @@
         <v>63</v>
       </c>
       <c r="C31" s="6">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="D31" s="7">
-        <v>178.126239</v>
+        <v>176.569277</v>
       </c>
       <c r="E31" s="8">
         <v>400000</v>
@@ -1405,10 +1405,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="8">
-        <v>71250495.66</v>
+        <v>70627710.65</v>
       </c>
       <c r="H31" s="8">
-        <v>178.15</v>
+        <v>176.6</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1419,10 +1419,10 @@
         <v>65</v>
       </c>
       <c r="C32" s="6">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="D32" s="7">
-        <v>46.440807</v>
+        <v>46.312369</v>
       </c>
       <c r="E32" s="8">
         <v>1200000</v>
@@ -1431,10 +1431,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="8">
-        <v>55728967.98</v>
+        <v>55574842.3</v>
       </c>
       <c r="H32" s="8">
-        <v>46.45</v>
+        <v>46.33</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1445,10 +1445,10 @@
         <v>67</v>
       </c>
       <c r="C33" s="6">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="D33" s="7">
-        <v>1254.847454</v>
+        <v>1256.191301</v>
       </c>
       <c r="E33" s="8">
         <v>600000</v>
@@ -1457,10 +1457,10 @@
         <v>0</v>
       </c>
       <c r="G33" s="8">
-        <v>752908472.39</v>
+        <v>753714780.67</v>
       </c>
       <c r="H33" s="8">
-        <v>1256</v>
+        <v>1260.5</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -1471,10 +1471,10 @@
         <v>69</v>
       </c>
       <c r="C34" s="6">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="D34" s="7">
-        <v>181.630992</v>
+        <v>181.878602</v>
       </c>
       <c r="E34" s="8">
         <v>680000</v>
@@ -1483,10 +1483,10 @@
         <v>0</v>
       </c>
       <c r="G34" s="8">
-        <v>123509074.78</v>
+        <v>123677449.6</v>
       </c>
       <c r="H34" s="8">
-        <v>181.65</v>
+        <v>181.25</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -1497,10 +1497,10 @@
         <v>71</v>
       </c>
       <c r="C35" s="6">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="D35" s="7">
-        <v>1255.935441</v>
+        <v>1257.282161</v>
       </c>
       <c r="E35" s="8">
         <v>6240000</v>
@@ -1509,10 +1509,10 @@
         <v>0</v>
       </c>
       <c r="G35" s="8">
-        <v>7837037152.61</v>
+        <v>7845440683.95</v>
       </c>
       <c r="H35" s="8">
-        <v>1257</v>
+        <v>1261.5</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>05.06.2026 11:21:20</t>
+    <t>08.06.2026 10:37:37</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -743,10 +743,10 @@
         <v>13</v>
       </c>
       <c r="C6" s="6">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="D6" s="7">
-        <v>45.219878</v>
+        <v>43.545027</v>
       </c>
       <c r="E6" s="8">
         <v>58200000</v>
@@ -755,10 +755,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="8">
-        <v>2631796889.42</v>
+        <v>2534320556.6</v>
       </c>
       <c r="H6" s="8">
-        <v>45.19</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -769,10 +769,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="6">
-        <v>46178</v>
-      </c>
-      <c r="D7" s="7">
-        <v>35.929718</v>
+        <v>46181</v>
+      </c>
+      <c r="D7" s="10">
+        <v>35.89398</v>
       </c>
       <c r="E7" s="8">
         <v>14400000</v>
@@ -781,10 +781,10 @@
         <v>0</v>
       </c>
       <c r="G7" s="8">
-        <v>517387938.09</v>
+        <v>516873309.25</v>
       </c>
       <c r="H7" s="8">
-        <v>36.08</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -795,10 +795,10 @@
         <v>17</v>
       </c>
       <c r="C8" s="6">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="D8" s="10">
-        <v>38.01235</v>
+        <v>37.53686</v>
       </c>
       <c r="E8" s="8">
         <v>33900000</v>
@@ -807,10 +807,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="8">
-        <v>1288618667.89</v>
+        <v>1272499562.86</v>
       </c>
       <c r="H8" s="8">
-        <v>37.97</v>
+        <v>37.48</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -821,10 +821,10 @@
         <v>19</v>
       </c>
       <c r="C9" s="6">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="D9" s="7">
-        <v>58.295414</v>
+        <v>58.480908</v>
       </c>
       <c r="E9" s="8">
         <v>2250000</v>
@@ -833,10 +833,10 @@
         <v>0</v>
       </c>
       <c r="G9" s="8">
-        <v>131164682.42</v>
+        <v>131582042.46</v>
       </c>
       <c r="H9" s="8">
-        <v>58.5</v>
+        <v>58.56</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -847,10 +847,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="6">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="D10" s="7">
-        <v>375.146204</v>
+        <v>372.180089</v>
       </c>
       <c r="E10" s="8">
         <v>135000</v>
@@ -859,10 +859,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="8">
-        <v>50644737.51</v>
+        <v>50244311.96</v>
       </c>
       <c r="H10" s="8">
-        <v>375.9</v>
+        <v>372.4</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -873,10 +873,10 @@
         <v>23</v>
       </c>
       <c r="C11" s="6">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="D11" s="7">
-        <v>553.700623</v>
+        <v>541.509852</v>
       </c>
       <c r="E11" s="8">
         <v>44850000</v>
@@ -885,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="G11" s="8">
-        <v>24833472937.93</v>
+        <v>24286716868.59</v>
       </c>
       <c r="H11" s="8">
-        <v>553</v>
+        <v>545</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -899,22 +899,22 @@
         <v>25</v>
       </c>
       <c r="C12" s="6">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="D12" s="7">
-        <v>671.559685</v>
+        <v>633.032262</v>
       </c>
       <c r="E12" s="8">
-        <v>73550000</v>
+        <v>73800000</v>
       </c>
       <c r="F12" s="9">
         <v>0</v>
       </c>
       <c r="G12" s="8">
-        <v>49393214849.73</v>
+        <v>46717780950.63</v>
       </c>
       <c r="H12" s="8">
-        <v>682.5</v>
+        <v>657.25</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -925,10 +925,10 @@
         <v>27</v>
       </c>
       <c r="C13" s="6">
-        <v>46178</v>
-      </c>
-      <c r="D13" s="10">
-        <v>4283.27222</v>
+        <v>46181</v>
+      </c>
+      <c r="D13" s="7">
+        <v>4292.643807</v>
       </c>
       <c r="E13" s="8">
         <v>280000</v>
@@ -937,10 +937,10 @@
         <v>0</v>
       </c>
       <c r="G13" s="8">
-        <v>1199316221.67</v>
+        <v>1201940265.87</v>
       </c>
       <c r="H13" s="8">
-        <v>4300</v>
+        <v>4326</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -951,10 +951,10 @@
         <v>29</v>
       </c>
       <c r="C14" s="6">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="D14" s="7">
-        <v>667.728526</v>
+        <v>657.433559</v>
       </c>
       <c r="E14" s="8">
         <v>113800000</v>
@@ -963,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="8">
-        <v>75987506238.66</v>
+        <v>74815939046.85</v>
       </c>
       <c r="H14" s="8">
-        <v>672</v>
+        <v>663.75</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -977,10 +977,10 @@
         <v>31</v>
       </c>
       <c r="C15" s="6">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="D15" s="7">
-        <v>544.996458</v>
+        <v>545.355633</v>
       </c>
       <c r="E15" s="8">
         <v>33450000</v>
@@ -989,10 +989,10 @@
         <v>0</v>
       </c>
       <c r="G15" s="8">
-        <v>18230131531.92</v>
+        <v>18242145937.64</v>
       </c>
       <c r="H15" s="8">
-        <v>550</v>
+        <v>539.5</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1003,10 +1003,10 @@
         <v>33</v>
       </c>
       <c r="C16" s="6">
-        <v>46178</v>
-      </c>
-      <c r="D16" s="10">
-        <v>25.38445</v>
+        <v>46181</v>
+      </c>
+      <c r="D16" s="7">
+        <v>24.926192</v>
       </c>
       <c r="E16" s="8">
         <v>10800000</v>
@@ -1015,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="8">
-        <v>274152060.17</v>
+        <v>269202878.64</v>
       </c>
       <c r="H16" s="8">
-        <v>25.36</v>
+        <v>25.25</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1029,22 +1029,22 @@
         <v>35</v>
       </c>
       <c r="C17" s="6">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="D17" s="7">
-        <v>47.139071</v>
+        <v>47.289829</v>
       </c>
       <c r="E17" s="8">
-        <v>1625000</v>
+        <v>1575000</v>
       </c>
       <c r="F17" s="9">
         <v>0</v>
       </c>
       <c r="G17" s="8">
-        <v>76600990.97</v>
+        <v>74481480.7</v>
       </c>
       <c r="H17" s="8">
-        <v>47.28</v>
+        <v>47.35</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1055,10 +1055,10 @@
         <v>37</v>
       </c>
       <c r="C18" s="6">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="D18" s="7">
-        <v>72.961483</v>
+        <v>72.336068</v>
       </c>
       <c r="E18" s="8">
         <v>1140000</v>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="G18" s="8">
-        <v>83176090.83</v>
+        <v>82463118.06</v>
       </c>
       <c r="H18" s="8">
-        <v>72.84</v>
+        <v>72.34</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1081,10 +1081,10 @@
         <v>39</v>
       </c>
       <c r="C19" s="6">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="D19" s="7">
-        <v>82.131734</v>
+        <v>81.094826</v>
       </c>
       <c r="E19" s="8">
         <v>1155000</v>
@@ -1093,10 +1093,10 @@
         <v>0</v>
       </c>
       <c r="G19" s="8">
-        <v>94862152.68</v>
+        <v>93664524.04</v>
       </c>
       <c r="H19" s="8">
-        <v>82.24</v>
+        <v>81.16</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1107,10 +1107,10 @@
         <v>41</v>
       </c>
       <c r="C20" s="6">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="D20" s="7">
-        <v>50.825642</v>
+        <v>50.175027</v>
       </c>
       <c r="E20" s="8">
         <v>2985000</v>
@@ -1119,10 +1119,10 @@
         <v>0</v>
       </c>
       <c r="G20" s="8">
-        <v>151714541.47</v>
+        <v>149772456.09</v>
       </c>
       <c r="H20" s="8">
-        <v>50.74</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1133,10 +1133,10 @@
         <v>43</v>
       </c>
       <c r="C21" s="6">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="D21" s="7">
-        <v>164.854504</v>
+        <v>162.939282</v>
       </c>
       <c r="E21" s="8">
         <v>600000</v>
@@ -1145,10 +1145,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="8">
-        <v>98912702.52</v>
+        <v>97763568.95</v>
       </c>
       <c r="H21" s="8">
-        <v>165.05</v>
+        <v>163.3</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1159,22 +1159,22 @@
         <v>45</v>
       </c>
       <c r="C22" s="6">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="D22" s="7">
-        <v>205.293137</v>
+        <v>202.640642</v>
       </c>
       <c r="E22" s="8">
-        <v>118560000</v>
+        <v>118520000</v>
       </c>
       <c r="F22" s="9">
         <v>0</v>
       </c>
       <c r="G22" s="8">
-        <v>24339554358.76</v>
+        <v>24016968875.84</v>
       </c>
       <c r="H22" s="8">
-        <v>205.2</v>
+        <v>202.65</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1185,22 +1185,22 @@
         <v>47</v>
       </c>
       <c r="C23" s="6">
-        <v>46178</v>
-      </c>
-      <c r="D23" s="10">
-        <v>192.05286</v>
+        <v>46181</v>
+      </c>
+      <c r="D23" s="7">
+        <v>184.828792</v>
       </c>
       <c r="E23" s="8">
-        <v>210000000</v>
+        <v>210040000</v>
       </c>
       <c r="F23" s="9">
         <v>0</v>
       </c>
       <c r="G23" s="8">
-        <v>40331100676.47</v>
+        <v>38821439525.04</v>
       </c>
       <c r="H23" s="8">
-        <v>191.9</v>
+        <v>184.85</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1211,10 +1211,10 @@
         <v>49</v>
       </c>
       <c r="C24" s="6">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="D24" s="7">
-        <v>193.996085</v>
+        <v>190.108708</v>
       </c>
       <c r="E24" s="8">
         <v>400000</v>
@@ -1223,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="G24" s="8">
-        <v>77598433.8</v>
+        <v>76043483.33</v>
       </c>
       <c r="H24" s="8">
-        <v>194</v>
+        <v>190.1</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1237,10 +1237,10 @@
         <v>51</v>
       </c>
       <c r="C25" s="6">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="D25" s="7">
-        <v>121.722121</v>
+        <v>119.958065</v>
       </c>
       <c r="E25" s="8">
         <v>600000</v>
@@ -1249,10 +1249,10 @@
         <v>0</v>
       </c>
       <c r="G25" s="8">
-        <v>73033272.35</v>
+        <v>71974838.76</v>
       </c>
       <c r="H25" s="8">
-        <v>121.7</v>
+        <v>119.95</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1263,10 +1263,10 @@
         <v>53</v>
       </c>
       <c r="C26" s="6">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="D26" s="7">
-        <v>673.578291</v>
+        <v>660.784578</v>
       </c>
       <c r="E26" s="8">
         <v>152040000</v>
@@ -1275,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="G26" s="8">
-        <v>102410843349.01</v>
+        <v>100465687252.66</v>
       </c>
       <c r="H26" s="8">
-        <v>679.5</v>
+        <v>669</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1289,10 +1289,10 @@
         <v>55</v>
       </c>
       <c r="C27" s="6">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="D27" s="7">
-        <v>180.851874</v>
+        <v>178.659262</v>
       </c>
       <c r="E27" s="8">
         <v>11000000</v>
@@ -1301,10 +1301,10 @@
         <v>0</v>
       </c>
       <c r="G27" s="8">
-        <v>1989370612.75</v>
+        <v>1965251886.45</v>
       </c>
       <c r="H27" s="8">
-        <v>184</v>
+        <v>182.75</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1315,10 +1315,10 @@
         <v>57</v>
       </c>
       <c r="C28" s="6">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="D28" s="7">
-        <v>252.290086</v>
+        <v>250.026853</v>
       </c>
       <c r="E28" s="8">
         <v>32200000</v>
@@ -1327,10 +1327,10 @@
         <v>0</v>
       </c>
       <c r="G28" s="8">
-        <v>8123740760.29</v>
+        <v>8050864655.69</v>
       </c>
       <c r="H28" s="8">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1341,10 +1341,10 @@
         <v>59</v>
       </c>
       <c r="C29" s="6">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="D29" s="7">
-        <v>241.307528</v>
+        <v>241.018782</v>
       </c>
       <c r="E29" s="8">
         <v>3200000</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="G29" s="8">
-        <v>772184088.53</v>
+        <v>771260103</v>
       </c>
       <c r="H29" s="8">
-        <v>241.15</v>
+        <v>241</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1367,10 +1367,10 @@
         <v>61</v>
       </c>
       <c r="C30" s="6">
-        <v>46178</v>
-      </c>
-      <c r="D30" s="7">
-        <v>124.423041</v>
+        <v>46181</v>
+      </c>
+      <c r="D30" s="10">
+        <v>123.17619</v>
       </c>
       <c r="E30" s="8">
         <v>440000</v>
@@ -1379,10 +1379,10 @@
         <v>0</v>
       </c>
       <c r="G30" s="8">
-        <v>54746138.17</v>
+        <v>54197523.75</v>
       </c>
       <c r="H30" s="8">
-        <v>124.7</v>
+        <v>122.9</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1393,10 +1393,10 @@
         <v>63</v>
       </c>
       <c r="C31" s="6">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="D31" s="7">
-        <v>176.569277</v>
+        <v>174.037986</v>
       </c>
       <c r="E31" s="8">
         <v>400000</v>
@@ -1405,10 +1405,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="8">
-        <v>70627710.65</v>
+        <v>69615194.53</v>
       </c>
       <c r="H31" s="8">
-        <v>176.6</v>
+        <v>174.05</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1419,10 +1419,10 @@
         <v>65</v>
       </c>
       <c r="C32" s="6">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="D32" s="7">
-        <v>46.312369</v>
+        <v>45.808603</v>
       </c>
       <c r="E32" s="8">
         <v>1200000</v>
@@ -1431,10 +1431,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="8">
-        <v>55574842.3</v>
+        <v>54970323.08</v>
       </c>
       <c r="H32" s="8">
-        <v>46.33</v>
+        <v>45.82</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1445,10 +1445,10 @@
         <v>67</v>
       </c>
       <c r="C33" s="6">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="D33" s="7">
-        <v>1256.191301</v>
+        <v>1260.250273</v>
       </c>
       <c r="E33" s="8">
         <v>600000</v>
@@ -1457,10 +1457,10 @@
         <v>0</v>
       </c>
       <c r="G33" s="8">
-        <v>753714780.67</v>
+        <v>756150163.66</v>
       </c>
       <c r="H33" s="8">
-        <v>1260.5</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -1471,10 +1471,10 @@
         <v>69</v>
       </c>
       <c r="C34" s="6">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="D34" s="7">
-        <v>181.878602</v>
+        <v>179.472305</v>
       </c>
       <c r="E34" s="8">
         <v>680000</v>
@@ -1483,10 +1483,10 @@
         <v>0</v>
       </c>
       <c r="G34" s="8">
-        <v>123677449.6</v>
+        <v>122041167.1</v>
       </c>
       <c r="H34" s="8">
-        <v>181.25</v>
+        <v>179.55</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -1497,10 +1497,10 @@
         <v>71</v>
       </c>
       <c r="C35" s="6">
-        <v>46178</v>
-      </c>
-      <c r="D35" s="7">
-        <v>1257.282161</v>
+        <v>46181</v>
+      </c>
+      <c r="D35" s="10">
+        <v>1261.32767</v>
       </c>
       <c r="E35" s="8">
         <v>6240000</v>
@@ -1509,10 +1509,10 @@
         <v>0</v>
       </c>
       <c r="G35" s="8">
-        <v>7845440683.95</v>
+        <v>7870684661.21</v>
       </c>
       <c r="H35" s="8">
-        <v>1261.5</v>
+        <v>1263</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>08.06.2026 10:37:37</t>
+    <t>09.06.2026 10:05:07</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -684,7 +684,7 @@
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="24" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="7" max="7" width="19" customWidth="1"/>
     <col min="8" max="8" width="21" customWidth="1"/>
   </cols>
   <sheetData>
@@ -743,10 +743,10 @@
         <v>13</v>
       </c>
       <c r="C6" s="6">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="D6" s="7">
-        <v>43.545027</v>
+        <v>45.159116</v>
       </c>
       <c r="E6" s="8">
         <v>58200000</v>
@@ -755,10 +755,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="8">
-        <v>2534320556.6</v>
+        <v>2628260537.48</v>
       </c>
       <c r="H6" s="8">
-        <v>43.6</v>
+        <v>45.31</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -769,10 +769,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="6">
-        <v>46181</v>
-      </c>
-      <c r="D7" s="10">
-        <v>35.89398</v>
+        <v>46182</v>
+      </c>
+      <c r="D7" s="7">
+        <v>36.080649</v>
       </c>
       <c r="E7" s="8">
         <v>14400000</v>
@@ -781,10 +781,10 @@
         <v>0</v>
       </c>
       <c r="G7" s="8">
-        <v>516873309.25</v>
+        <v>519561349.81</v>
       </c>
       <c r="H7" s="8">
-        <v>35.8</v>
+        <v>36.16</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -795,10 +795,10 @@
         <v>17</v>
       </c>
       <c r="C8" s="6">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="D8" s="10">
-        <v>37.53686</v>
+        <v>37.93958</v>
       </c>
       <c r="E8" s="8">
         <v>33900000</v>
@@ -807,10 +807,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="8">
-        <v>1272499562.86</v>
+        <v>1286151777.67</v>
       </c>
       <c r="H8" s="8">
-        <v>37.48</v>
+        <v>37.99</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -821,10 +821,10 @@
         <v>19</v>
       </c>
       <c r="C9" s="6">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="D9" s="7">
-        <v>58.480908</v>
+        <v>58.542922</v>
       </c>
       <c r="E9" s="8">
         <v>2250000</v>
@@ -833,10 +833,10 @@
         <v>0</v>
       </c>
       <c r="G9" s="8">
-        <v>131582042.46</v>
+        <v>131721573.99</v>
       </c>
       <c r="H9" s="8">
-        <v>58.56</v>
+        <v>58.62</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -847,10 +847,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="6">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="D10" s="7">
-        <v>372.180089</v>
+        <v>366.370314</v>
       </c>
       <c r="E10" s="8">
         <v>135000</v>
@@ -859,10 +859,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="8">
-        <v>50244311.96</v>
+        <v>49459992.36</v>
       </c>
       <c r="H10" s="8">
-        <v>372.4</v>
+        <v>367</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -873,10 +873,10 @@
         <v>23</v>
       </c>
       <c r="C11" s="6">
-        <v>46181</v>
-      </c>
-      <c r="D11" s="7">
-        <v>541.509852</v>
+        <v>46182</v>
+      </c>
+      <c r="D11" s="10">
+        <v>537.51575</v>
       </c>
       <c r="E11" s="8">
         <v>44850000</v>
@@ -885,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="G11" s="8">
-        <v>24286716868.59</v>
+        <v>24107581371.42</v>
       </c>
       <c r="H11" s="8">
-        <v>545</v>
+        <v>539</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -899,22 +899,22 @@
         <v>25</v>
       </c>
       <c r="C12" s="6">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="D12" s="7">
-        <v>633.032262</v>
+        <v>625.577831</v>
       </c>
       <c r="E12" s="8">
-        <v>73800000</v>
+        <v>74050000</v>
       </c>
       <c r="F12" s="9">
         <v>0</v>
       </c>
       <c r="G12" s="8">
-        <v>46717780950.63</v>
+        <v>46324038419.07</v>
       </c>
       <c r="H12" s="8">
-        <v>657.25</v>
+        <v>638</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -925,10 +925,10 @@
         <v>27</v>
       </c>
       <c r="C13" s="6">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="D13" s="7">
-        <v>4292.643807</v>
+        <v>4293.983213</v>
       </c>
       <c r="E13" s="8">
         <v>280000</v>
@@ -937,10 +937,10 @@
         <v>0</v>
       </c>
       <c r="G13" s="8">
-        <v>1201940265.87</v>
+        <v>1202315299.73</v>
       </c>
       <c r="H13" s="8">
-        <v>4326</v>
+        <v>4307</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -951,10 +951,10 @@
         <v>29</v>
       </c>
       <c r="C14" s="6">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="D14" s="7">
-        <v>657.433559</v>
+        <v>646.535692</v>
       </c>
       <c r="E14" s="8">
         <v>113800000</v>
@@ -963,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="8">
-        <v>74815939046.85</v>
+        <v>73575761694.69</v>
       </c>
       <c r="H14" s="8">
-        <v>663.75</v>
+        <v>660</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -977,10 +977,10 @@
         <v>31</v>
       </c>
       <c r="C15" s="6">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="D15" s="7">
-        <v>545.355633</v>
+        <v>529.280124</v>
       </c>
       <c r="E15" s="8">
         <v>33450000</v>
@@ -989,10 +989,10 @@
         <v>0</v>
       </c>
       <c r="G15" s="8">
-        <v>18242145937.64</v>
+        <v>17704420145.16</v>
       </c>
       <c r="H15" s="8">
-        <v>539.5</v>
+        <v>535.5</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1003,10 +1003,10 @@
         <v>33</v>
       </c>
       <c r="C16" s="6">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="D16" s="7">
-        <v>24.926192</v>
+        <v>25.208312</v>
       </c>
       <c r="E16" s="8">
         <v>10800000</v>
@@ -1015,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="8">
-        <v>269202878.64</v>
+        <v>272249774.61</v>
       </c>
       <c r="H16" s="8">
-        <v>25.25</v>
+        <v>25.24</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1029,10 +1029,10 @@
         <v>35</v>
       </c>
       <c r="C17" s="6">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="D17" s="7">
-        <v>47.289829</v>
+        <v>47.340122</v>
       </c>
       <c r="E17" s="8">
         <v>1575000</v>
@@ -1041,10 +1041,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="8">
-        <v>74481480.7</v>
+        <v>74560692.25</v>
       </c>
       <c r="H17" s="8">
-        <v>47.35</v>
+        <v>47.38</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1055,10 +1055,10 @@
         <v>37</v>
       </c>
       <c r="C18" s="6">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="D18" s="7">
-        <v>72.336068</v>
+        <v>73.181921</v>
       </c>
       <c r="E18" s="8">
         <v>1140000</v>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="G18" s="8">
-        <v>82463118.06</v>
+        <v>83427389.45</v>
       </c>
       <c r="H18" s="8">
-        <v>72.34</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1081,10 +1081,10 @@
         <v>39</v>
       </c>
       <c r="C19" s="6">
-        <v>46181</v>
-      </c>
-      <c r="D19" s="7">
-        <v>81.094826</v>
+        <v>46182</v>
+      </c>
+      <c r="D19" s="10">
+        <v>81.94462</v>
       </c>
       <c r="E19" s="8">
         <v>1155000</v>
@@ -1093,10 +1093,10 @@
         <v>0</v>
       </c>
       <c r="G19" s="8">
-        <v>93664524.04</v>
+        <v>94646036.43</v>
       </c>
       <c r="H19" s="8">
-        <v>81.16</v>
+        <v>81.96</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1107,10 +1107,10 @@
         <v>41</v>
       </c>
       <c r="C20" s="6">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="D20" s="7">
-        <v>50.175027</v>
+        <v>50.831426</v>
       </c>
       <c r="E20" s="8">
         <v>2985000</v>
@@ -1119,10 +1119,10 @@
         <v>0</v>
       </c>
       <c r="G20" s="8">
-        <v>149772456.09</v>
+        <v>151731806.01</v>
       </c>
       <c r="H20" s="8">
-        <v>50.16</v>
+        <v>50.96</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1133,10 +1133,10 @@
         <v>43</v>
       </c>
       <c r="C21" s="6">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="D21" s="7">
-        <v>162.939282</v>
+        <v>164.513272</v>
       </c>
       <c r="E21" s="8">
         <v>600000</v>
@@ -1145,10 +1145,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="8">
-        <v>97763568.95</v>
+        <v>98707963.26</v>
       </c>
       <c r="H21" s="8">
-        <v>163.3</v>
+        <v>164.3</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1159,22 +1159,22 @@
         <v>45</v>
       </c>
       <c r="C22" s="6">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="D22" s="7">
-        <v>202.640642</v>
+        <v>204.800515</v>
       </c>
       <c r="E22" s="8">
-        <v>118520000</v>
+        <v>119560000</v>
       </c>
       <c r="F22" s="9">
         <v>0</v>
       </c>
       <c r="G22" s="8">
-        <v>24016968875.84</v>
+        <v>24485949574.4</v>
       </c>
       <c r="H22" s="8">
-        <v>202.65</v>
+        <v>205.25</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1185,22 +1185,22 @@
         <v>47</v>
       </c>
       <c r="C23" s="6">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="D23" s="7">
-        <v>184.828792</v>
+        <v>191.796276</v>
       </c>
       <c r="E23" s="8">
-        <v>210040000</v>
+        <v>212120000</v>
       </c>
       <c r="F23" s="9">
         <v>0</v>
       </c>
       <c r="G23" s="8">
-        <v>38821439525.04</v>
+        <v>40683826041.45</v>
       </c>
       <c r="H23" s="8">
-        <v>184.85</v>
+        <v>192.05</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1211,10 +1211,10 @@
         <v>49</v>
       </c>
       <c r="C24" s="6">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="D24" s="7">
-        <v>190.108708</v>
+        <v>192.546583</v>
       </c>
       <c r="E24" s="8">
         <v>400000</v>
@@ -1223,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="G24" s="8">
-        <v>76043483.33</v>
+        <v>77018633.05</v>
       </c>
       <c r="H24" s="8">
-        <v>190.1</v>
+        <v>192.85</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1237,10 +1237,10 @@
         <v>51</v>
       </c>
       <c r="C25" s="6">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="D25" s="7">
-        <v>119.958065</v>
+        <v>121.256783</v>
       </c>
       <c r="E25" s="8">
         <v>600000</v>
@@ -1249,10 +1249,10 @@
         <v>0</v>
       </c>
       <c r="G25" s="8">
-        <v>71974838.76</v>
+        <v>72754069.94</v>
       </c>
       <c r="H25" s="8">
-        <v>119.95</v>
+        <v>121.25</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1263,10 +1263,10 @@
         <v>53</v>
       </c>
       <c r="C26" s="6">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="D26" s="7">
-        <v>660.784578</v>
+        <v>654.583535</v>
       </c>
       <c r="E26" s="8">
         <v>152040000</v>
@@ -1275,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="G26" s="8">
-        <v>100465687252.66</v>
+        <v>99522880700.89</v>
       </c>
       <c r="H26" s="8">
-        <v>669</v>
+        <v>664</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1289,10 +1289,10 @@
         <v>55</v>
       </c>
       <c r="C27" s="6">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="D27" s="7">
-        <v>178.659262</v>
+        <v>179.858317</v>
       </c>
       <c r="E27" s="8">
         <v>11000000</v>
@@ -1301,10 +1301,10 @@
         <v>0</v>
       </c>
       <c r="G27" s="8">
-        <v>1965251886.45</v>
+        <v>1978441491.47</v>
       </c>
       <c r="H27" s="8">
-        <v>182.75</v>
+        <v>180.1</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1315,10 +1315,10 @@
         <v>57</v>
       </c>
       <c r="C28" s="6">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="D28" s="7">
-        <v>250.026853</v>
+        <v>252.920473</v>
       </c>
       <c r="E28" s="8">
         <v>32200000</v>
@@ -1327,10 +1327,10 @@
         <v>0</v>
       </c>
       <c r="G28" s="8">
-        <v>8050864655.69</v>
+        <v>8144039244.97</v>
       </c>
       <c r="H28" s="8">
-        <v>253</v>
+        <v>252.4</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1341,10 +1341,10 @@
         <v>59</v>
       </c>
       <c r="C29" s="6">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="D29" s="7">
-        <v>241.018782</v>
+        <v>242.314491</v>
       </c>
       <c r="E29" s="8">
         <v>3200000</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="G29" s="8">
-        <v>771260103</v>
+        <v>775406372.53</v>
       </c>
       <c r="H29" s="8">
-        <v>241</v>
+        <v>243.6</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1367,10 +1367,10 @@
         <v>61</v>
       </c>
       <c r="C30" s="6">
-        <v>46181</v>
-      </c>
-      <c r="D30" s="10">
-        <v>123.17619</v>
+        <v>46182</v>
+      </c>
+      <c r="D30" s="7">
+        <v>123.358237</v>
       </c>
       <c r="E30" s="8">
         <v>440000</v>
@@ -1379,10 +1379,10 @@
         <v>0</v>
       </c>
       <c r="G30" s="8">
-        <v>54197523.75</v>
+        <v>54277624.15</v>
       </c>
       <c r="H30" s="8">
-        <v>122.9</v>
+        <v>124</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1393,10 +1393,10 @@
         <v>63</v>
       </c>
       <c r="C31" s="6">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="D31" s="7">
-        <v>174.037986</v>
+        <v>175.450115</v>
       </c>
       <c r="E31" s="8">
         <v>400000</v>
@@ -1405,10 +1405,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="8">
-        <v>69615194.53</v>
+        <v>70180046</v>
       </c>
       <c r="H31" s="8">
-        <v>174.05</v>
+        <v>175.2</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1419,10 +1419,10 @@
         <v>65</v>
       </c>
       <c r="C32" s="6">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="D32" s="7">
-        <v>45.808603</v>
+        <v>46.403215</v>
       </c>
       <c r="E32" s="8">
         <v>1200000</v>
@@ -1431,10 +1431,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="8">
-        <v>54970323.08</v>
+        <v>55683857.98</v>
       </c>
       <c r="H32" s="8">
-        <v>45.82</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1445,22 +1445,22 @@
         <v>67</v>
       </c>
       <c r="C33" s="6">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="D33" s="7">
-        <v>1260.250273</v>
+        <v>1261.704294</v>
       </c>
       <c r="E33" s="8">
-        <v>600000</v>
+        <v>560000</v>
       </c>
       <c r="F33" s="9">
         <v>0</v>
       </c>
       <c r="G33" s="8">
-        <v>756150163.66</v>
+        <v>706554404.85</v>
       </c>
       <c r="H33" s="8">
-        <v>1262</v>
+        <v>1263.5</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -1471,10 +1471,10 @@
         <v>69</v>
       </c>
       <c r="C34" s="6">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="D34" s="7">
-        <v>179.472305</v>
+        <v>181.860913</v>
       </c>
       <c r="E34" s="8">
         <v>680000</v>
@@ -1483,10 +1483,10 @@
         <v>0</v>
       </c>
       <c r="G34" s="8">
-        <v>122041167.1</v>
+        <v>123665420.55</v>
       </c>
       <c r="H34" s="8">
-        <v>179.55</v>
+        <v>181.75</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -1497,22 +1497,22 @@
         <v>71</v>
       </c>
       <c r="C35" s="6">
-        <v>46181</v>
-      </c>
-      <c r="D35" s="10">
-        <v>1261.32767</v>
+        <v>46182</v>
+      </c>
+      <c r="D35" s="7">
+        <v>1262.689464</v>
       </c>
       <c r="E35" s="8">
-        <v>6240000</v>
+        <v>6200000</v>
       </c>
       <c r="F35" s="9">
         <v>0</v>
       </c>
       <c r="G35" s="8">
-        <v>7870684661.21</v>
+        <v>7828674678.94</v>
       </c>
       <c r="H35" s="8">
-        <v>1263</v>
+        <v>1264</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>09.06.2026 10:05:07</t>
+    <t>10.06.2026 10:58:56</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -235,10 +235,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="165" formatCode="###0.000000;-###0.000000;0"/>
+    <numFmt numFmtId="165" formatCode="###0.00000;-###0.00000;0"/>
     <numFmt numFmtId="166" formatCode="###0.00;-###0.00;0"/>
     <numFmt numFmtId="167" formatCode="###0;-###0;0"/>
-    <numFmt numFmtId="168" formatCode="###0.00000;-###0.00000;0"/>
+    <numFmt numFmtId="168" formatCode="###0.000000;-###0.000000;0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -743,10 +743,10 @@
         <v>13</v>
       </c>
       <c r="C6" s="6">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="D6" s="7">
-        <v>45.159116</v>
+        <v>45.52466</v>
       </c>
       <c r="E6" s="8">
         <v>58200000</v>
@@ -755,10 +755,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="8">
-        <v>2628260537.48</v>
+        <v>2649535187.51</v>
       </c>
       <c r="H6" s="8">
-        <v>45.31</v>
+        <v>45.54</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -769,10 +769,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="6">
-        <v>46182</v>
-      </c>
-      <c r="D7" s="7">
-        <v>36.080649</v>
+        <v>46183</v>
+      </c>
+      <c r="D7" s="10">
+        <v>35.523088</v>
       </c>
       <c r="E7" s="8">
         <v>14400000</v>
@@ -781,10 +781,10 @@
         <v>0</v>
       </c>
       <c r="G7" s="8">
-        <v>519561349.81</v>
+        <v>511532471.44</v>
       </c>
       <c r="H7" s="8">
-        <v>36.16</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -795,10 +795,10 @@
         <v>17</v>
       </c>
       <c r="C8" s="6">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="D8" s="10">
-        <v>37.93958</v>
+        <v>37.579246</v>
       </c>
       <c r="E8" s="8">
         <v>33900000</v>
@@ -807,10 +807,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="8">
-        <v>1286151777.67</v>
+        <v>1273936437.05</v>
       </c>
       <c r="H8" s="8">
-        <v>37.99</v>
+        <v>37.58</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -821,10 +821,10 @@
         <v>19</v>
       </c>
       <c r="C9" s="6">
-        <v>46182</v>
-      </c>
-      <c r="D9" s="7">
-        <v>58.542922</v>
+        <v>46183</v>
+      </c>
+      <c r="D9" s="10">
+        <v>58.605007</v>
       </c>
       <c r="E9" s="8">
         <v>2250000</v>
@@ -833,10 +833,10 @@
         <v>0</v>
       </c>
       <c r="G9" s="8">
-        <v>131721573.99</v>
+        <v>131861266.2</v>
       </c>
       <c r="H9" s="8">
-        <v>58.62</v>
+        <v>58.7</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -847,10 +847,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="6">
-        <v>46182</v>
-      </c>
-      <c r="D10" s="7">
-        <v>366.370314</v>
+        <v>46183</v>
+      </c>
+      <c r="D10" s="10">
+        <v>355.484977</v>
       </c>
       <c r="E10" s="8">
         <v>135000</v>
@@ -859,10 +859,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="8">
-        <v>49459992.36</v>
+        <v>47990471.87</v>
       </c>
       <c r="H10" s="8">
-        <v>367</v>
+        <v>356.5</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -873,10 +873,10 @@
         <v>23</v>
       </c>
       <c r="C11" s="6">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="D11" s="10">
-        <v>537.51575</v>
+        <v>533.813189</v>
       </c>
       <c r="E11" s="8">
         <v>44850000</v>
@@ -885,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="G11" s="8">
-        <v>24107581371.42</v>
+        <v>23941521522.95</v>
       </c>
       <c r="H11" s="8">
-        <v>539</v>
+        <v>533</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -899,22 +899,22 @@
         <v>25</v>
       </c>
       <c r="C12" s="6">
-        <v>46182</v>
-      </c>
-      <c r="D12" s="7">
-        <v>625.577831</v>
+        <v>46183</v>
+      </c>
+      <c r="D12" s="10">
+        <v>605.959495</v>
       </c>
       <c r="E12" s="8">
-        <v>74050000</v>
+        <v>74550000</v>
       </c>
       <c r="F12" s="9">
         <v>0</v>
       </c>
       <c r="G12" s="8">
-        <v>46324038419.07</v>
+        <v>45174280346.51</v>
       </c>
       <c r="H12" s="8">
-        <v>638</v>
+        <v>608</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -925,10 +925,10 @@
         <v>27</v>
       </c>
       <c r="C13" s="6">
-        <v>46182</v>
-      </c>
-      <c r="D13" s="7">
-        <v>4293.983213</v>
+        <v>46183</v>
+      </c>
+      <c r="D13" s="10">
+        <v>4296.806784</v>
       </c>
       <c r="E13" s="8">
         <v>280000</v>
@@ -937,10 +937,10 @@
         <v>0</v>
       </c>
       <c r="G13" s="8">
-        <v>1202315299.73</v>
+        <v>1203105899.5</v>
       </c>
       <c r="H13" s="8">
-        <v>4307</v>
+        <v>4306</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -951,10 +951,10 @@
         <v>29</v>
       </c>
       <c r="C14" s="6">
-        <v>46182</v>
-      </c>
-      <c r="D14" s="7">
-        <v>646.535692</v>
+        <v>46183</v>
+      </c>
+      <c r="D14" s="10">
+        <v>647.630187</v>
       </c>
       <c r="E14" s="8">
         <v>113800000</v>
@@ -963,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="8">
-        <v>73575761694.69</v>
+        <v>73700315291.9</v>
       </c>
       <c r="H14" s="8">
-        <v>660</v>
+        <v>650</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -977,10 +977,10 @@
         <v>31</v>
       </c>
       <c r="C15" s="6">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="D15" s="7">
-        <v>529.280124</v>
+        <v>531.78997</v>
       </c>
       <c r="E15" s="8">
         <v>33450000</v>
@@ -989,10 +989,10 @@
         <v>0</v>
       </c>
       <c r="G15" s="8">
-        <v>17704420145.16</v>
+        <v>17788374499.57</v>
       </c>
       <c r="H15" s="8">
-        <v>535.5</v>
+        <v>532.75</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1003,10 +1003,10 @@
         <v>33</v>
       </c>
       <c r="C16" s="6">
-        <v>46182</v>
-      </c>
-      <c r="D16" s="7">
-        <v>25.208312</v>
+        <v>46183</v>
+      </c>
+      <c r="D16" s="10">
+        <v>25.367583</v>
       </c>
       <c r="E16" s="8">
         <v>10800000</v>
@@ -1015,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="8">
-        <v>272249774.61</v>
+        <v>273969896.48</v>
       </c>
       <c r="H16" s="8">
-        <v>25.24</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1029,10 +1029,10 @@
         <v>35</v>
       </c>
       <c r="C17" s="6">
-        <v>46182</v>
-      </c>
-      <c r="D17" s="7">
-        <v>47.340122</v>
+        <v>46183</v>
+      </c>
+      <c r="D17" s="10">
+        <v>47.390472</v>
       </c>
       <c r="E17" s="8">
         <v>1575000</v>
@@ -1041,10 +1041,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="8">
-        <v>74560692.25</v>
+        <v>74639994.03</v>
       </c>
       <c r="H17" s="8">
-        <v>47.38</v>
+        <v>47.45</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1055,10 +1055,10 @@
         <v>37</v>
       </c>
       <c r="C18" s="6">
-        <v>46182</v>
-      </c>
-      <c r="D18" s="7">
-        <v>73.181921</v>
+        <v>46183</v>
+      </c>
+      <c r="D18" s="10">
+        <v>72.485289</v>
       </c>
       <c r="E18" s="8">
         <v>1140000</v>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="G18" s="8">
-        <v>83427389.45</v>
+        <v>82633229.43</v>
       </c>
       <c r="H18" s="8">
-        <v>74</v>
+        <v>72.54</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1081,10 +1081,10 @@
         <v>39</v>
       </c>
       <c r="C19" s="6">
-        <v>46182</v>
-      </c>
-      <c r="D19" s="10">
-        <v>81.94462</v>
+        <v>46183</v>
+      </c>
+      <c r="D19" s="7">
+        <v>81.17022</v>
       </c>
       <c r="E19" s="8">
         <v>1155000</v>
@@ -1093,10 +1093,10 @@
         <v>0</v>
       </c>
       <c r="G19" s="8">
-        <v>94646036.43</v>
+        <v>93751603.95</v>
       </c>
       <c r="H19" s="8">
-        <v>81.96</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1107,10 +1107,10 @@
         <v>41</v>
       </c>
       <c r="C20" s="6">
-        <v>46182</v>
-      </c>
-      <c r="D20" s="7">
-        <v>50.831426</v>
+        <v>46183</v>
+      </c>
+      <c r="D20" s="10">
+        <v>50.595129</v>
       </c>
       <c r="E20" s="8">
         <v>2985000</v>
@@ -1119,10 +1119,10 @@
         <v>0</v>
       </c>
       <c r="G20" s="8">
-        <v>151731806.01</v>
+        <v>151026460.11</v>
       </c>
       <c r="H20" s="8">
-        <v>50.96</v>
+        <v>50.68</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1133,10 +1133,10 @@
         <v>43</v>
       </c>
       <c r="C21" s="6">
-        <v>46182</v>
-      </c>
-      <c r="D21" s="7">
-        <v>164.513272</v>
+        <v>46183</v>
+      </c>
+      <c r="D21" s="10">
+        <v>164.744818</v>
       </c>
       <c r="E21" s="8">
         <v>600000</v>
@@ -1145,10 +1145,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="8">
-        <v>98707963.26</v>
+        <v>98846890.78</v>
       </c>
       <c r="H21" s="8">
-        <v>164.3</v>
+        <v>164.85</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1159,10 +1159,10 @@
         <v>45</v>
       </c>
       <c r="C22" s="6">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="D22" s="7">
-        <v>204.800515</v>
+        <v>202.75779</v>
       </c>
       <c r="E22" s="8">
         <v>119560000</v>
@@ -1171,10 +1171,10 @@
         <v>0</v>
       </c>
       <c r="G22" s="8">
-        <v>24485949574.4</v>
+        <v>24241721363.62</v>
       </c>
       <c r="H22" s="8">
-        <v>205.25</v>
+        <v>203</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1185,22 +1185,22 @@
         <v>47</v>
       </c>
       <c r="C23" s="6">
-        <v>46182</v>
-      </c>
-      <c r="D23" s="7">
-        <v>191.796276</v>
+        <v>46183</v>
+      </c>
+      <c r="D23" s="10">
+        <v>193.389698</v>
       </c>
       <c r="E23" s="8">
-        <v>212120000</v>
+        <v>211920000</v>
       </c>
       <c r="F23" s="9">
         <v>0</v>
       </c>
       <c r="G23" s="8">
-        <v>40683826041.45</v>
+        <v>40983144706.63</v>
       </c>
       <c r="H23" s="8">
-        <v>192.05</v>
+        <v>193.05</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1211,10 +1211,10 @@
         <v>49</v>
       </c>
       <c r="C24" s="6">
-        <v>46182</v>
-      </c>
-      <c r="D24" s="7">
-        <v>192.546583</v>
+        <v>46183</v>
+      </c>
+      <c r="D24" s="10">
+        <v>191.038894</v>
       </c>
       <c r="E24" s="8">
         <v>400000</v>
@@ -1223,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="G24" s="8">
-        <v>77018633.05</v>
+        <v>76415557.55</v>
       </c>
       <c r="H24" s="8">
-        <v>192.85</v>
+        <v>191.05</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1237,10 +1237,10 @@
         <v>51</v>
       </c>
       <c r="C25" s="6">
-        <v>46182</v>
-      </c>
-      <c r="D25" s="7">
-        <v>121.256783</v>
+        <v>46183</v>
+      </c>
+      <c r="D25" s="10">
+        <v>120.225207</v>
       </c>
       <c r="E25" s="8">
         <v>600000</v>
@@ -1249,10 +1249,10 @@
         <v>0</v>
       </c>
       <c r="G25" s="8">
-        <v>72754069.94</v>
+        <v>72135124.07</v>
       </c>
       <c r="H25" s="8">
-        <v>121.25</v>
+        <v>120.3</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1263,10 +1263,10 @@
         <v>53</v>
       </c>
       <c r="C26" s="6">
-        <v>46182</v>
-      </c>
-      <c r="D26" s="7">
-        <v>654.583535</v>
+        <v>46183</v>
+      </c>
+      <c r="D26" s="10">
+        <v>649.469422</v>
       </c>
       <c r="E26" s="8">
         <v>152040000</v>
@@ -1275,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="G26" s="8">
-        <v>99522880700.89</v>
+        <v>98745330859.94</v>
       </c>
       <c r="H26" s="8">
-        <v>664</v>
+        <v>661.25</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1289,10 +1289,10 @@
         <v>55</v>
       </c>
       <c r="C27" s="6">
-        <v>46182</v>
-      </c>
-      <c r="D27" s="7">
-        <v>179.858317</v>
+        <v>46183</v>
+      </c>
+      <c r="D27" s="10">
+        <v>177.957885</v>
       </c>
       <c r="E27" s="8">
         <v>11000000</v>
@@ -1301,10 +1301,10 @@
         <v>0</v>
       </c>
       <c r="G27" s="8">
-        <v>1978441491.47</v>
+        <v>1957536737.25</v>
       </c>
       <c r="H27" s="8">
-        <v>180.1</v>
+        <v>176.05</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1315,10 +1315,10 @@
         <v>57</v>
       </c>
       <c r="C28" s="6">
-        <v>46182</v>
-      </c>
-      <c r="D28" s="7">
-        <v>252.920473</v>
+        <v>46183</v>
+      </c>
+      <c r="D28" s="10">
+        <v>251.066025</v>
       </c>
       <c r="E28" s="8">
         <v>32200000</v>
@@ -1327,10 +1327,10 @@
         <v>0</v>
       </c>
       <c r="G28" s="8">
-        <v>8144039244.97</v>
+        <v>8084326013.68</v>
       </c>
       <c r="H28" s="8">
-        <v>252.4</v>
+        <v>250.2</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1341,10 +1341,10 @@
         <v>59</v>
       </c>
       <c r="C29" s="6">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="D29" s="7">
-        <v>242.314491</v>
+        <v>238.54436</v>
       </c>
       <c r="E29" s="8">
         <v>3200000</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="G29" s="8">
-        <v>775406372.53</v>
+        <v>763341951.34</v>
       </c>
       <c r="H29" s="8">
-        <v>243.6</v>
+        <v>238.8</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1367,10 +1367,10 @@
         <v>61</v>
       </c>
       <c r="C30" s="6">
-        <v>46182</v>
-      </c>
-      <c r="D30" s="7">
-        <v>123.358237</v>
+        <v>46183</v>
+      </c>
+      <c r="D30" s="10">
+        <v>121.865556</v>
       </c>
       <c r="E30" s="8">
         <v>440000</v>
@@ -1379,10 +1379,10 @@
         <v>0</v>
       </c>
       <c r="G30" s="8">
-        <v>54277624.15</v>
+        <v>53620844.81</v>
       </c>
       <c r="H30" s="8">
-        <v>124</v>
+        <v>121.9</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1393,10 +1393,10 @@
         <v>63</v>
       </c>
       <c r="C31" s="6">
-        <v>46182</v>
-      </c>
-      <c r="D31" s="7">
-        <v>175.450115</v>
+        <v>46183</v>
+      </c>
+      <c r="D31" s="10">
+        <v>173.665556</v>
       </c>
       <c r="E31" s="8">
         <v>400000</v>
@@ -1405,10 +1405,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="8">
-        <v>70180046</v>
+        <v>69466222.35</v>
       </c>
       <c r="H31" s="8">
-        <v>175.2</v>
+        <v>173.9</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1419,10 +1419,10 @@
         <v>65</v>
       </c>
       <c r="C32" s="6">
-        <v>46182</v>
-      </c>
-      <c r="D32" s="7">
-        <v>46.403215</v>
+        <v>46183</v>
+      </c>
+      <c r="D32" s="10">
+        <v>46.157421</v>
       </c>
       <c r="E32" s="8">
         <v>1200000</v>
@@ -1431,10 +1431,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="8">
-        <v>55683857.98</v>
+        <v>55388905.08</v>
       </c>
       <c r="H32" s="8">
-        <v>46.4</v>
+        <v>46.41</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1445,10 +1445,10 @@
         <v>67</v>
       </c>
       <c r="C33" s="6">
-        <v>46182</v>
-      </c>
-      <c r="D33" s="7">
-        <v>1261.704294</v>
+        <v>46183</v>
+      </c>
+      <c r="D33" s="10">
+        <v>1263.062466</v>
       </c>
       <c r="E33" s="8">
         <v>560000</v>
@@ -1457,10 +1457,10 @@
         <v>0</v>
       </c>
       <c r="G33" s="8">
-        <v>706554404.85</v>
+        <v>707314980.95</v>
       </c>
       <c r="H33" s="8">
-        <v>1263.5</v>
+        <v>1264.5</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -1471,10 +1471,10 @@
         <v>69</v>
       </c>
       <c r="C34" s="6">
-        <v>46182</v>
-      </c>
-      <c r="D34" s="7">
-        <v>181.860913</v>
+        <v>46183</v>
+      </c>
+      <c r="D34" s="10">
+        <v>181.000497</v>
       </c>
       <c r="E34" s="8">
         <v>680000</v>
@@ -1483,10 +1483,10 @@
         <v>0</v>
       </c>
       <c r="G34" s="8">
-        <v>123665420.55</v>
+        <v>123080337.94</v>
       </c>
       <c r="H34" s="8">
-        <v>181.75</v>
+        <v>181</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -1497,22 +1497,22 @@
         <v>71</v>
       </c>
       <c r="C35" s="6">
-        <v>46182</v>
-      </c>
-      <c r="D35" s="7">
-        <v>1262.689464</v>
+        <v>46183</v>
+      </c>
+      <c r="D35" s="10">
+        <v>1264.044881</v>
       </c>
       <c r="E35" s="8">
-        <v>6200000</v>
+        <v>4440000</v>
       </c>
       <c r="F35" s="9">
         <v>0</v>
       </c>
       <c r="G35" s="8">
-        <v>7828674678.94</v>
+        <v>5612359271.04</v>
       </c>
       <c r="H35" s="8">
-        <v>1264</v>
+        <v>1265.5</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>10.06.2026 10:58:56</t>
+    <t>11.06.2026 10:19:16</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -233,12 +233,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="165" formatCode="###0.00000;-###0.00000;0"/>
+    <numFmt numFmtId="165" formatCode="###0.000000;-###0.000000;0"/>
     <numFmt numFmtId="166" formatCode="###0.00;-###0.00;0"/>
     <numFmt numFmtId="167" formatCode="###0;-###0;0"/>
-    <numFmt numFmtId="168" formatCode="###0.000000;-###0.000000;0"/>
+    <numFmt numFmtId="168" formatCode="###0.0000;-###0.0000;0"/>
+    <numFmt numFmtId="169" formatCode="###0.00000;-###0.00000;0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -308,7 +309,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -334,6 +335,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -743,10 +747,10 @@
         <v>13</v>
       </c>
       <c r="C6" s="6">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="D6" s="7">
-        <v>45.52466</v>
+        <v>44.774199</v>
       </c>
       <c r="E6" s="8">
         <v>58200000</v>
@@ -755,10 +759,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="8">
-        <v>2649535187.51</v>
+        <v>2605858366.33</v>
       </c>
       <c r="H6" s="8">
-        <v>45.54</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -769,10 +773,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="6">
-        <v>46183</v>
-      </c>
-      <c r="D7" s="10">
-        <v>35.523088</v>
+        <v>46184</v>
+      </c>
+      <c r="D7" s="7">
+        <v>36.011392</v>
       </c>
       <c r="E7" s="8">
         <v>14400000</v>
@@ -781,10 +785,10 @@
         <v>0</v>
       </c>
       <c r="G7" s="8">
-        <v>511532471.44</v>
+        <v>518564042.67</v>
       </c>
       <c r="H7" s="8">
-        <v>35.8</v>
+        <v>36.17</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -795,10 +799,10 @@
         <v>17</v>
       </c>
       <c r="C8" s="6">
-        <v>46183</v>
-      </c>
-      <c r="D8" s="10">
-        <v>37.579246</v>
+        <v>46184</v>
+      </c>
+      <c r="D8" s="7">
+        <v>37.628159</v>
       </c>
       <c r="E8" s="8">
         <v>33900000</v>
@@ -807,10 +811,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="8">
-        <v>1273936437.05</v>
+        <v>1275594595.65</v>
       </c>
       <c r="H8" s="8">
-        <v>37.58</v>
+        <v>37.71</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -821,10 +825,10 @@
         <v>19</v>
       </c>
       <c r="C9" s="6">
-        <v>46183</v>
-      </c>
-      <c r="D9" s="10">
-        <v>58.605007</v>
+        <v>46184</v>
+      </c>
+      <c r="D9" s="7">
+        <v>58.666942</v>
       </c>
       <c r="E9" s="8">
         <v>2250000</v>
@@ -833,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="G9" s="8">
-        <v>131861266.2</v>
+        <v>132000618.78</v>
       </c>
       <c r="H9" s="8">
-        <v>58.7</v>
+        <v>58.74</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -847,10 +851,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="6">
-        <v>46183</v>
-      </c>
-      <c r="D10" s="10">
-        <v>355.484977</v>
+        <v>46184</v>
+      </c>
+      <c r="D10" s="7">
+        <v>347.800491</v>
       </c>
       <c r="E10" s="8">
         <v>135000</v>
@@ -859,10 +863,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="8">
-        <v>47990471.87</v>
+        <v>46953066.35</v>
       </c>
       <c r="H10" s="8">
-        <v>356.5</v>
+        <v>348.6</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -873,22 +877,22 @@
         <v>23</v>
       </c>
       <c r="C11" s="6">
-        <v>46183</v>
-      </c>
-      <c r="D11" s="10">
-        <v>533.813189</v>
+        <v>46184</v>
+      </c>
+      <c r="D11" s="7">
+        <v>512.667338</v>
       </c>
       <c r="E11" s="8">
-        <v>44850000</v>
+        <v>44600000</v>
       </c>
       <c r="F11" s="9">
         <v>0</v>
       </c>
       <c r="G11" s="8">
-        <v>23941521522.95</v>
+        <v>22864963289.91</v>
       </c>
       <c r="H11" s="8">
-        <v>533</v>
+        <v>515.25</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -899,22 +903,22 @@
         <v>25</v>
       </c>
       <c r="C12" s="6">
-        <v>46183</v>
-      </c>
-      <c r="D12" s="10">
-        <v>605.959495</v>
+        <v>46184</v>
+      </c>
+      <c r="D12" s="7">
+        <v>590.800688</v>
       </c>
       <c r="E12" s="8">
-        <v>74550000</v>
+        <v>74800000</v>
       </c>
       <c r="F12" s="9">
         <v>0</v>
       </c>
       <c r="G12" s="8">
-        <v>45174280346.51</v>
+        <v>44191891438.78</v>
       </c>
       <c r="H12" s="8">
-        <v>608</v>
+        <v>593.5</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -925,10 +929,10 @@
         <v>27</v>
       </c>
       <c r="C13" s="6">
-        <v>46183</v>
-      </c>
-      <c r="D13" s="10">
-        <v>4296.806784</v>
+        <v>46184</v>
+      </c>
+      <c r="D13" s="7">
+        <v>4296.191057</v>
       </c>
       <c r="E13" s="8">
         <v>280000</v>
@@ -937,10 +941,10 @@
         <v>0</v>
       </c>
       <c r="G13" s="8">
-        <v>1203105899.5</v>
+        <v>1202933496.02</v>
       </c>
       <c r="H13" s="8">
-        <v>4306</v>
+        <v>4301</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -951,10 +955,10 @@
         <v>29</v>
       </c>
       <c r="C14" s="6">
-        <v>46183</v>
-      </c>
-      <c r="D14" s="10">
-        <v>647.630187</v>
+        <v>46184</v>
+      </c>
+      <c r="D14" s="7">
+        <v>622.424491</v>
       </c>
       <c r="E14" s="8">
         <v>113800000</v>
@@ -963,10 +967,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="8">
-        <v>73700315291.9</v>
+        <v>70831907084.01</v>
       </c>
       <c r="H14" s="8">
-        <v>650</v>
+        <v>635.5</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -977,10 +981,10 @@
         <v>31</v>
       </c>
       <c r="C15" s="6">
-        <v>46183</v>
-      </c>
-      <c r="D15" s="7">
-        <v>531.78997</v>
+        <v>46184</v>
+      </c>
+      <c r="D15" s="10">
+        <v>516.1139</v>
       </c>
       <c r="E15" s="8">
         <v>33450000</v>
@@ -989,10 +993,10 @@
         <v>0</v>
       </c>
       <c r="G15" s="8">
-        <v>17788374499.57</v>
+        <v>17264009956.43</v>
       </c>
       <c r="H15" s="8">
-        <v>532.75</v>
+        <v>512</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1003,10 +1007,10 @@
         <v>33</v>
       </c>
       <c r="C16" s="6">
-        <v>46183</v>
-      </c>
-      <c r="D16" s="10">
-        <v>25.367583</v>
+        <v>46184</v>
+      </c>
+      <c r="D16" s="7">
+        <v>25.009499</v>
       </c>
       <c r="E16" s="8">
         <v>10800000</v>
@@ -1015,10 +1019,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="8">
-        <v>273969896.48</v>
+        <v>270102585.3</v>
       </c>
       <c r="H16" s="8">
-        <v>25.4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1029,10 +1033,10 @@
         <v>35</v>
       </c>
       <c r="C17" s="6">
-        <v>46183</v>
-      </c>
-      <c r="D17" s="10">
-        <v>47.390472</v>
+        <v>46184</v>
+      </c>
+      <c r="D17" s="7">
+        <v>47.431728</v>
       </c>
       <c r="E17" s="8">
         <v>1575000</v>
@@ -1041,10 +1045,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="8">
-        <v>74639994.03</v>
+        <v>74704971.76</v>
       </c>
       <c r="H17" s="8">
-        <v>47.45</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1055,10 +1059,10 @@
         <v>37</v>
       </c>
       <c r="C18" s="6">
-        <v>46183</v>
-      </c>
-      <c r="D18" s="10">
-        <v>72.485289</v>
+        <v>46184</v>
+      </c>
+      <c r="D18" s="7">
+        <v>72.924961</v>
       </c>
       <c r="E18" s="8">
         <v>1140000</v>
@@ -1067,10 +1071,10 @@
         <v>0</v>
       </c>
       <c r="G18" s="8">
-        <v>82633229.43</v>
+        <v>83134456.05</v>
       </c>
       <c r="H18" s="8">
-        <v>72.54</v>
+        <v>72.98</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1081,10 +1085,10 @@
         <v>39</v>
       </c>
       <c r="C19" s="6">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="D19" s="7">
-        <v>81.17022</v>
+        <v>81.277241</v>
       </c>
       <c r="E19" s="8">
         <v>1155000</v>
@@ -1093,10 +1097,10 @@
         <v>0</v>
       </c>
       <c r="G19" s="8">
-        <v>93751603.95</v>
+        <v>93875213.08</v>
       </c>
       <c r="H19" s="8">
-        <v>81.2</v>
+        <v>81.4</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1107,10 +1111,10 @@
         <v>41</v>
       </c>
       <c r="C20" s="6">
-        <v>46183</v>
-      </c>
-      <c r="D20" s="10">
-        <v>50.595129</v>
+        <v>46184</v>
+      </c>
+      <c r="D20" s="7">
+        <v>50.376768</v>
       </c>
       <c r="E20" s="8">
         <v>2985000</v>
@@ -1119,10 +1123,10 @@
         <v>0</v>
       </c>
       <c r="G20" s="8">
-        <v>151026460.11</v>
+        <v>150374653.49</v>
       </c>
       <c r="H20" s="8">
-        <v>50.68</v>
+        <v>50.46</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1133,10 +1137,10 @@
         <v>43</v>
       </c>
       <c r="C21" s="6">
-        <v>46183</v>
-      </c>
-      <c r="D21" s="10">
-        <v>164.744818</v>
+        <v>46184</v>
+      </c>
+      <c r="D21" s="11">
+        <v>163.60817</v>
       </c>
       <c r="E21" s="8">
         <v>600000</v>
@@ -1145,10 +1149,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="8">
-        <v>98846890.78</v>
+        <v>98164901.83</v>
       </c>
       <c r="H21" s="8">
-        <v>164.85</v>
+        <v>164.15</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1159,22 +1163,22 @@
         <v>45</v>
       </c>
       <c r="C22" s="6">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="D22" s="7">
-        <v>202.75779</v>
+        <v>202.979865</v>
       </c>
       <c r="E22" s="8">
-        <v>119560000</v>
+        <v>117360000</v>
       </c>
       <c r="F22" s="9">
         <v>0</v>
       </c>
       <c r="G22" s="8">
-        <v>24241721363.62</v>
+        <v>23821716957.86</v>
       </c>
       <c r="H22" s="8">
-        <v>203</v>
+        <v>203.35</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1185,22 +1189,22 @@
         <v>47</v>
       </c>
       <c r="C23" s="6">
-        <v>46183</v>
-      </c>
-      <c r="D23" s="10">
-        <v>193.389698</v>
+        <v>46184</v>
+      </c>
+      <c r="D23" s="7">
+        <v>190.144977</v>
       </c>
       <c r="E23" s="8">
-        <v>211920000</v>
+        <v>214920000</v>
       </c>
       <c r="F23" s="9">
         <v>0</v>
       </c>
       <c r="G23" s="8">
-        <v>40983144706.63</v>
+        <v>40865958386.28</v>
       </c>
       <c r="H23" s="8">
-        <v>193.05</v>
+        <v>191.4</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1211,10 +1215,10 @@
         <v>49</v>
       </c>
       <c r="C24" s="6">
-        <v>46183</v>
-      </c>
-      <c r="D24" s="10">
-        <v>191.038894</v>
+        <v>46184</v>
+      </c>
+      <c r="D24" s="7">
+        <v>189.404815</v>
       </c>
       <c r="E24" s="8">
         <v>400000</v>
@@ -1223,10 +1227,10 @@
         <v>0</v>
       </c>
       <c r="G24" s="8">
-        <v>76415557.55</v>
+        <v>75761926.06</v>
       </c>
       <c r="H24" s="8">
-        <v>191.05</v>
+        <v>189.7</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1237,10 +1241,10 @@
         <v>51</v>
       </c>
       <c r="C25" s="6">
-        <v>46183</v>
-      </c>
-      <c r="D25" s="10">
-        <v>120.225207</v>
+        <v>46184</v>
+      </c>
+      <c r="D25" s="7">
+        <v>120.071234</v>
       </c>
       <c r="E25" s="8">
         <v>600000</v>
@@ -1249,10 +1253,10 @@
         <v>0</v>
       </c>
       <c r="G25" s="8">
-        <v>72135124.07</v>
+        <v>72042740.38</v>
       </c>
       <c r="H25" s="8">
-        <v>120.3</v>
+        <v>120.05</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1263,10 +1267,10 @@
         <v>53</v>
       </c>
       <c r="C26" s="6">
-        <v>46183</v>
-      </c>
-      <c r="D26" s="10">
-        <v>649.469422</v>
+        <v>46184</v>
+      </c>
+      <c r="D26" s="7">
+        <v>627.110664</v>
       </c>
       <c r="E26" s="8">
         <v>152040000</v>
@@ -1275,10 +1279,10 @@
         <v>0</v>
       </c>
       <c r="G26" s="8">
-        <v>98745330859.94</v>
+        <v>95345905302.57</v>
       </c>
       <c r="H26" s="8">
-        <v>661.25</v>
+        <v>640</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1289,10 +1293,10 @@
         <v>55</v>
       </c>
       <c r="C27" s="6">
-        <v>46183</v>
-      </c>
-      <c r="D27" s="10">
-        <v>177.957885</v>
+        <v>46184</v>
+      </c>
+      <c r="D27" s="11">
+        <v>178.43187</v>
       </c>
       <c r="E27" s="8">
         <v>11000000</v>
@@ -1301,10 +1305,10 @@
         <v>0</v>
       </c>
       <c r="G27" s="8">
-        <v>1957536737.25</v>
+        <v>1962750566.77</v>
       </c>
       <c r="H27" s="8">
-        <v>176.05</v>
+        <v>179.1</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1315,10 +1319,10 @@
         <v>57</v>
       </c>
       <c r="C28" s="6">
-        <v>46183</v>
-      </c>
-      <c r="D28" s="10">
-        <v>251.066025</v>
+        <v>46184</v>
+      </c>
+      <c r="D28" s="11">
+        <v>252.47451</v>
       </c>
       <c r="E28" s="8">
         <v>32200000</v>
@@ -1327,10 +1331,10 @@
         <v>0</v>
       </c>
       <c r="G28" s="8">
-        <v>8084326013.68</v>
+        <v>8129679233.01</v>
       </c>
       <c r="H28" s="8">
-        <v>250.2</v>
+        <v>257</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1341,10 +1345,10 @@
         <v>59</v>
       </c>
       <c r="C29" s="6">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="D29" s="7">
-        <v>238.54436</v>
+        <v>241.806891</v>
       </c>
       <c r="E29" s="8">
         <v>3200000</v>
@@ -1353,10 +1357,10 @@
         <v>0</v>
       </c>
       <c r="G29" s="8">
-        <v>763341951.34</v>
+        <v>773782051.76</v>
       </c>
       <c r="H29" s="8">
-        <v>238.8</v>
+        <v>242.85</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1367,10 +1371,10 @@
         <v>61</v>
       </c>
       <c r="C30" s="6">
-        <v>46183</v>
-      </c>
-      <c r="D30" s="10">
-        <v>121.865556</v>
+        <v>46184</v>
+      </c>
+      <c r="D30" s="7">
+        <v>123.289307</v>
       </c>
       <c r="E30" s="8">
         <v>440000</v>
@@ -1379,10 +1383,10 @@
         <v>0</v>
       </c>
       <c r="G30" s="8">
-        <v>53620844.81</v>
+        <v>54247294.87</v>
       </c>
       <c r="H30" s="8">
-        <v>121.9</v>
+        <v>123.25</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1393,10 +1397,10 @@
         <v>63</v>
       </c>
       <c r="C31" s="6">
-        <v>46183</v>
-      </c>
-      <c r="D31" s="10">
-        <v>173.665556</v>
+        <v>46184</v>
+      </c>
+      <c r="D31" s="7">
+        <v>173.430449</v>
       </c>
       <c r="E31" s="8">
         <v>400000</v>
@@ -1405,10 +1409,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="8">
-        <v>69466222.35</v>
+        <v>69372179.4</v>
       </c>
       <c r="H31" s="8">
-        <v>173.9</v>
+        <v>174.1</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1419,10 +1423,10 @@
         <v>65</v>
       </c>
       <c r="C32" s="6">
-        <v>46183</v>
-      </c>
-      <c r="D32" s="10">
-        <v>46.157421</v>
+        <v>46184</v>
+      </c>
+      <c r="D32" s="7">
+        <v>46.193199</v>
       </c>
       <c r="E32" s="8">
         <v>1200000</v>
@@ -1431,10 +1435,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="8">
-        <v>55388905.08</v>
+        <v>55431838.94</v>
       </c>
       <c r="H32" s="8">
-        <v>46.41</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1445,10 +1449,10 @@
         <v>67</v>
       </c>
       <c r="C33" s="6">
-        <v>46183</v>
-      </c>
-      <c r="D33" s="10">
-        <v>1263.062466</v>
+        <v>46184</v>
+      </c>
+      <c r="D33" s="7">
+        <v>1264.423865</v>
       </c>
       <c r="E33" s="8">
         <v>560000</v>
@@ -1457,10 +1461,10 @@
         <v>0</v>
       </c>
       <c r="G33" s="8">
-        <v>707314980.95</v>
+        <v>708077364.51</v>
       </c>
       <c r="H33" s="8">
-        <v>1264.5</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -1471,10 +1475,10 @@
         <v>69</v>
       </c>
       <c r="C34" s="6">
-        <v>46183</v>
-      </c>
-      <c r="D34" s="10">
-        <v>181.000497</v>
+        <v>46184</v>
+      </c>
+      <c r="D34" s="7">
+        <v>180.160379</v>
       </c>
       <c r="E34" s="8">
         <v>680000</v>
@@ -1483,10 +1487,10 @@
         <v>0</v>
       </c>
       <c r="G34" s="8">
-        <v>123080337.94</v>
+        <v>122509057.91</v>
       </c>
       <c r="H34" s="8">
-        <v>181</v>
+        <v>180.6</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -1497,10 +1501,10 @@
         <v>71</v>
       </c>
       <c r="C35" s="6">
-        <v>46183</v>
-      </c>
-      <c r="D35" s="10">
-        <v>1264.044881</v>
+        <v>46184</v>
+      </c>
+      <c r="D35" s="7">
+        <v>1265.401736</v>
       </c>
       <c r="E35" s="8">
         <v>4440000</v>
@@ -1509,10 +1513,10 @@
         <v>0</v>
       </c>
       <c r="G35" s="8">
-        <v>5612359271.04</v>
+        <v>5618383708.4</v>
       </c>
       <c r="H35" s="8">
-        <v>1265.5</v>
+        <v>1267</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>11.06.2026 10:19:16</t>
+    <t>12.06.2026 12:03:47</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -233,13 +233,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="###0.000000;-###0.000000;0"/>
     <numFmt numFmtId="166" formatCode="###0.00;-###0.00;0"/>
     <numFmt numFmtId="167" formatCode="###0;-###0;0"/>
-    <numFmt numFmtId="168" formatCode="###0.0000;-###0.0000;0"/>
-    <numFmt numFmtId="169" formatCode="###0.00000;-###0.00000;0"/>
+    <numFmt numFmtId="168" formatCode="###0.00000;-###0.00000;0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -309,7 +308,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -335,9 +334,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -747,10 +743,10 @@
         <v>13</v>
       </c>
       <c r="C6" s="6">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="D6" s="7">
-        <v>44.774199</v>
+        <v>45.027594</v>
       </c>
       <c r="E6" s="8">
         <v>58200000</v>
@@ -759,10 +755,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="8">
-        <v>2605858366.33</v>
+        <v>2620605951.61</v>
       </c>
       <c r="H6" s="8">
-        <v>45.3</v>
+        <v>45.12</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -773,10 +769,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="6">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="D7" s="7">
-        <v>36.011392</v>
+        <v>36.042632</v>
       </c>
       <c r="E7" s="8">
         <v>14400000</v>
@@ -785,10 +781,10 @@
         <v>0</v>
       </c>
       <c r="G7" s="8">
-        <v>518564042.67</v>
+        <v>519013897.97</v>
       </c>
       <c r="H7" s="8">
-        <v>36.17</v>
+        <v>36.05</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -799,10 +795,10 @@
         <v>17</v>
       </c>
       <c r="C8" s="6">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="D8" s="7">
-        <v>37.628159</v>
+        <v>37.731087</v>
       </c>
       <c r="E8" s="8">
         <v>33900000</v>
@@ -811,10 +807,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="8">
-        <v>1275594595.65</v>
+        <v>1279083864.2</v>
       </c>
       <c r="H8" s="8">
-        <v>37.71</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -825,10 +821,10 @@
         <v>19</v>
       </c>
       <c r="C9" s="6">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="D9" s="7">
-        <v>58.666942</v>
+        <v>58.728889</v>
       </c>
       <c r="E9" s="8">
         <v>2250000</v>
@@ -837,10 +833,10 @@
         <v>0</v>
       </c>
       <c r="G9" s="8">
-        <v>132000618.78</v>
+        <v>132139999.95</v>
       </c>
       <c r="H9" s="8">
-        <v>58.74</v>
+        <v>58.92</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -851,10 +847,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="6">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="D10" s="7">
-        <v>347.800491</v>
+        <v>344.960037</v>
       </c>
       <c r="E10" s="8">
         <v>135000</v>
@@ -863,10 +859,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="8">
-        <v>46953066.35</v>
+        <v>46569605.05</v>
       </c>
       <c r="H10" s="8">
-        <v>348.6</v>
+        <v>345.3</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -877,22 +873,22 @@
         <v>23</v>
       </c>
       <c r="C11" s="6">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="D11" s="7">
-        <v>512.667338</v>
+        <v>507.504756</v>
       </c>
       <c r="E11" s="8">
-        <v>44600000</v>
+        <v>44350000</v>
       </c>
       <c r="F11" s="9">
         <v>0</v>
       </c>
       <c r="G11" s="8">
-        <v>22864963289.91</v>
+        <v>22507835914.12</v>
       </c>
       <c r="H11" s="8">
-        <v>515.25</v>
+        <v>510.75</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -903,10 +899,10 @@
         <v>25</v>
       </c>
       <c r="C12" s="6">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="D12" s="7">
-        <v>590.800688</v>
+        <v>587.455858</v>
       </c>
       <c r="E12" s="8">
         <v>74800000</v>
@@ -915,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="G12" s="8">
-        <v>44191891438.78</v>
+        <v>43941698153.88</v>
       </c>
       <c r="H12" s="8">
-        <v>593.5</v>
+        <v>590</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -929,10 +925,10 @@
         <v>27</v>
       </c>
       <c r="C13" s="6">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="D13" s="7">
-        <v>4296.191057</v>
+        <v>4299.715422</v>
       </c>
       <c r="E13" s="8">
         <v>280000</v>
@@ -941,10 +937,10 @@
         <v>0</v>
       </c>
       <c r="G13" s="8">
-        <v>1202933496.02</v>
+        <v>1203920318.14</v>
       </c>
       <c r="H13" s="8">
-        <v>4301</v>
+        <v>4318</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -955,10 +951,10 @@
         <v>29</v>
       </c>
       <c r="C14" s="6">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="D14" s="7">
-        <v>622.424491</v>
+        <v>614.207023</v>
       </c>
       <c r="E14" s="8">
         <v>113800000</v>
@@ -967,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="8">
-        <v>70831907084.01</v>
+        <v>69896759219.93</v>
       </c>
       <c r="H14" s="8">
-        <v>635.5</v>
+        <v>640</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -981,10 +977,10 @@
         <v>31</v>
       </c>
       <c r="C15" s="6">
-        <v>46184</v>
-      </c>
-      <c r="D15" s="10">
-        <v>516.1139</v>
+        <v>46185</v>
+      </c>
+      <c r="D15" s="7">
+        <v>504.616511</v>
       </c>
       <c r="E15" s="8">
         <v>33450000</v>
@@ -993,10 +989,10 @@
         <v>0</v>
       </c>
       <c r="G15" s="8">
-        <v>17264009956.43</v>
+        <v>16879422303.66</v>
       </c>
       <c r="H15" s="8">
-        <v>512</v>
+        <v>504</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1007,10 +1003,10 @@
         <v>33</v>
       </c>
       <c r="C16" s="6">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="D16" s="7">
-        <v>25.009499</v>
+        <v>24.848576</v>
       </c>
       <c r="E16" s="8">
         <v>10800000</v>
@@ -1019,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="8">
-        <v>270102585.3</v>
+        <v>268364617.72</v>
       </c>
       <c r="H16" s="8">
-        <v>25</v>
+        <v>24.85</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1033,10 +1029,10 @@
         <v>35</v>
       </c>
       <c r="C17" s="6">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="D17" s="7">
-        <v>47.431728</v>
+        <v>47.482181</v>
       </c>
       <c r="E17" s="8">
         <v>1575000</v>
@@ -1045,10 +1041,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="8">
-        <v>74704971.76</v>
+        <v>74784434.99</v>
       </c>
       <c r="H17" s="8">
-        <v>47.5</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1059,10 +1055,10 @@
         <v>37</v>
       </c>
       <c r="C18" s="6">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="D18" s="7">
-        <v>72.924961</v>
+        <v>72.897474</v>
       </c>
       <c r="E18" s="8">
         <v>1140000</v>
@@ -1071,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="G18" s="8">
-        <v>83134456.05</v>
+        <v>83103120.73</v>
       </c>
       <c r="H18" s="8">
-        <v>72.98</v>
+        <v>72.9</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1085,10 +1081,10 @@
         <v>39</v>
       </c>
       <c r="C19" s="6">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="D19" s="7">
-        <v>81.277241</v>
+        <v>81.529607</v>
       </c>
       <c r="E19" s="8">
         <v>1155000</v>
@@ -1097,10 +1093,10 @@
         <v>0</v>
       </c>
       <c r="G19" s="8">
-        <v>93875213.08</v>
+        <v>94166696.64</v>
       </c>
       <c r="H19" s="8">
-        <v>81.4</v>
+        <v>81.32</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1111,22 +1107,22 @@
         <v>41</v>
       </c>
       <c r="C20" s="6">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="D20" s="7">
-        <v>50.376768</v>
+        <v>50.440511</v>
       </c>
       <c r="E20" s="8">
-        <v>2985000</v>
+        <v>3135000</v>
       </c>
       <c r="F20" s="9">
         <v>0</v>
       </c>
       <c r="G20" s="8">
-        <v>150374653.49</v>
+        <v>158131001.16</v>
       </c>
       <c r="H20" s="8">
-        <v>50.46</v>
+        <v>50.44</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1137,10 +1133,10 @@
         <v>43</v>
       </c>
       <c r="C21" s="6">
-        <v>46184</v>
-      </c>
-      <c r="D21" s="11">
-        <v>163.60817</v>
+        <v>46185</v>
+      </c>
+      <c r="D21" s="7">
+        <v>163.548985</v>
       </c>
       <c r="E21" s="8">
         <v>600000</v>
@@ -1149,10 +1145,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="8">
-        <v>98164901.83</v>
+        <v>98129391.2</v>
       </c>
       <c r="H21" s="8">
-        <v>164.15</v>
+        <v>164</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1163,22 +1159,22 @@
         <v>45</v>
       </c>
       <c r="C22" s="6">
-        <v>46184</v>
-      </c>
-      <c r="D22" s="7">
-        <v>202.979865</v>
+        <v>46185</v>
+      </c>
+      <c r="D22" s="10">
+        <v>203.66368</v>
       </c>
       <c r="E22" s="8">
-        <v>117360000</v>
+        <v>116160000</v>
       </c>
       <c r="F22" s="9">
         <v>0</v>
       </c>
       <c r="G22" s="8">
-        <v>23821716957.86</v>
+        <v>23657573091.21</v>
       </c>
       <c r="H22" s="8">
-        <v>203.35</v>
+        <v>202.45</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1189,22 +1185,22 @@
         <v>47</v>
       </c>
       <c r="C23" s="6">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="D23" s="7">
-        <v>190.144977</v>
+        <v>191.218539</v>
       </c>
       <c r="E23" s="8">
-        <v>214920000</v>
+        <v>216120000</v>
       </c>
       <c r="F23" s="9">
         <v>0</v>
       </c>
       <c r="G23" s="8">
-        <v>40865958386.28</v>
+        <v>41326150645.63</v>
       </c>
       <c r="H23" s="8">
-        <v>191.4</v>
+        <v>192.5</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1215,10 +1211,10 @@
         <v>49</v>
       </c>
       <c r="C24" s="6">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="D24" s="7">
-        <v>189.404815</v>
+        <v>190.020607</v>
       </c>
       <c r="E24" s="8">
         <v>400000</v>
@@ -1227,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="G24" s="8">
-        <v>75761926.06</v>
+        <v>76008242.85</v>
       </c>
       <c r="H24" s="8">
-        <v>189.7</v>
+        <v>190.1</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1241,10 +1237,10 @@
         <v>51</v>
       </c>
       <c r="C25" s="6">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="D25" s="7">
-        <v>120.071234</v>
+        <v>119.381809</v>
       </c>
       <c r="E25" s="8">
         <v>600000</v>
@@ -1253,10 +1249,10 @@
         <v>0</v>
       </c>
       <c r="G25" s="8">
-        <v>72042740.38</v>
+        <v>71629085.35</v>
       </c>
       <c r="H25" s="8">
-        <v>120.05</v>
+        <v>119.15</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1267,10 +1263,10 @@
         <v>53</v>
       </c>
       <c r="C26" s="6">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="D26" s="7">
-        <v>627.110664</v>
+        <v>618.834845</v>
       </c>
       <c r="E26" s="8">
         <v>152040000</v>
@@ -1279,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="G26" s="8">
-        <v>95345905302.57</v>
+        <v>94087649878.92</v>
       </c>
       <c r="H26" s="8">
-        <v>640</v>
+        <v>644.25</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1293,22 +1289,22 @@
         <v>55</v>
       </c>
       <c r="C27" s="6">
-        <v>46184</v>
-      </c>
-      <c r="D27" s="11">
-        <v>178.43187</v>
+        <v>46185</v>
+      </c>
+      <c r="D27" s="7">
+        <v>176.168699</v>
       </c>
       <c r="E27" s="8">
-        <v>11000000</v>
+        <v>10960000</v>
       </c>
       <c r="F27" s="9">
         <v>0</v>
       </c>
       <c r="G27" s="8">
-        <v>1962750566.77</v>
+        <v>1930808938.51</v>
       </c>
       <c r="H27" s="8">
-        <v>179.1</v>
+        <v>177.75</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1319,10 +1315,10 @@
         <v>57</v>
       </c>
       <c r="C28" s="6">
-        <v>46184</v>
-      </c>
-      <c r="D28" s="11">
-        <v>252.47451</v>
+        <v>46185</v>
+      </c>
+      <c r="D28" s="7">
+        <v>251.152008</v>
       </c>
       <c r="E28" s="8">
         <v>32200000</v>
@@ -1331,10 +1327,10 @@
         <v>0</v>
       </c>
       <c r="G28" s="8">
-        <v>8129679233.01</v>
+        <v>8087094645.7</v>
       </c>
       <c r="H28" s="8">
-        <v>257</v>
+        <v>248.15</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1345,10 +1341,10 @@
         <v>59</v>
       </c>
       <c r="C29" s="6">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="D29" s="7">
-        <v>241.806891</v>
+        <v>242.114057</v>
       </c>
       <c r="E29" s="8">
         <v>3200000</v>
@@ -1357,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="G29" s="8">
-        <v>773782051.76</v>
+        <v>774764982.12</v>
       </c>
       <c r="H29" s="8">
-        <v>242.85</v>
+        <v>241.65</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1371,10 +1367,10 @@
         <v>61</v>
       </c>
       <c r="C30" s="6">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="D30" s="7">
-        <v>123.289307</v>
+        <v>124.499899</v>
       </c>
       <c r="E30" s="8">
         <v>440000</v>
@@ -1383,10 +1379,10 @@
         <v>0</v>
       </c>
       <c r="G30" s="8">
-        <v>54247294.87</v>
+        <v>54779955.43</v>
       </c>
       <c r="H30" s="8">
-        <v>123.25</v>
+        <v>122.95</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1397,10 +1393,10 @@
         <v>63</v>
       </c>
       <c r="C31" s="6">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="D31" s="7">
-        <v>173.430449</v>
+        <v>174.017504</v>
       </c>
       <c r="E31" s="8">
         <v>400000</v>
@@ -1409,10 +1405,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="8">
-        <v>69372179.4</v>
+        <v>69607001.64</v>
       </c>
       <c r="H31" s="8">
-        <v>174.1</v>
+        <v>174.05</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1423,10 +1419,10 @@
         <v>65</v>
       </c>
       <c r="C32" s="6">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="D32" s="7">
-        <v>46.193199</v>
+        <v>46.244261</v>
       </c>
       <c r="E32" s="8">
         <v>1200000</v>
@@ -1435,10 +1431,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="8">
-        <v>55431838.94</v>
+        <v>55493113.79</v>
       </c>
       <c r="H32" s="8">
-        <v>46.4</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1449,10 +1445,10 @@
         <v>67</v>
       </c>
       <c r="C33" s="6">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="D33" s="7">
-        <v>1264.423865</v>
+        <v>1265.780564</v>
       </c>
       <c r="E33" s="8">
         <v>560000</v>
@@ -1461,10 +1457,10 @@
         <v>0</v>
       </c>
       <c r="G33" s="8">
-        <v>708077364.51</v>
+        <v>708837115.8</v>
       </c>
       <c r="H33" s="8">
-        <v>1266</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -1475,10 +1471,10 @@
         <v>69</v>
       </c>
       <c r="C34" s="6">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="D34" s="7">
-        <v>180.160379</v>
+        <v>180.354754</v>
       </c>
       <c r="E34" s="8">
         <v>680000</v>
@@ -1487,10 +1483,10 @@
         <v>0</v>
       </c>
       <c r="G34" s="8">
-        <v>122509057.91</v>
+        <v>122641232.59</v>
       </c>
       <c r="H34" s="8">
-        <v>180.6</v>
+        <v>179.35</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -1501,22 +1497,22 @@
         <v>71</v>
       </c>
       <c r="C35" s="6">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="D35" s="7">
-        <v>1265.401736</v>
+        <v>1266.759766</v>
       </c>
       <c r="E35" s="8">
-        <v>4440000</v>
+        <v>4400000</v>
       </c>
       <c r="F35" s="9">
         <v>0</v>
       </c>
       <c r="G35" s="8">
-        <v>5618383708.4</v>
+        <v>5573742971.36</v>
       </c>
       <c r="H35" s="8">
-        <v>1267</v>
+        <v>1271</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>12.06.2026 12:03:47</t>
+    <t>15.06.2026 12:05:22</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -233,12 +233,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="5">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="###0.000000;-###0.000000;0"/>
     <numFmt numFmtId="166" formatCode="###0.00;-###0.00;0"/>
     <numFmt numFmtId="167" formatCode="###0;-###0;0"/>
     <numFmt numFmtId="168" formatCode="###0.00000;-###0.00000;0"/>
+    <numFmt numFmtId="169" formatCode="###0.000;-###0.000;0"/>
+    <numFmt numFmtId="170" formatCode="###0.0000;-###0.0000;0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -308,7 +310,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -334,6 +336,12 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -743,10 +751,10 @@
         <v>13</v>
       </c>
       <c r="C6" s="6">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="D6" s="7">
-        <v>45.027594</v>
+        <v>47.868965</v>
       </c>
       <c r="E6" s="8">
         <v>58200000</v>
@@ -755,10 +763,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="8">
-        <v>2620605951.61</v>
+        <v>2785973777.37</v>
       </c>
       <c r="H6" s="8">
-        <v>45.12</v>
+        <v>47.61</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -769,10 +777,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="6">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="D7" s="7">
-        <v>36.042632</v>
+        <v>36.228727</v>
       </c>
       <c r="E7" s="8">
         <v>14400000</v>
@@ -781,10 +789,10 @@
         <v>0</v>
       </c>
       <c r="G7" s="8">
-        <v>519013897.97</v>
+        <v>521693664.65</v>
       </c>
       <c r="H7" s="8">
-        <v>36.05</v>
+        <v>36.07</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -795,10 +803,10 @@
         <v>17</v>
       </c>
       <c r="C8" s="6">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="D8" s="7">
-        <v>37.731087</v>
+        <v>38.369607</v>
       </c>
       <c r="E8" s="8">
         <v>33900000</v>
@@ -807,10 +815,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="8">
-        <v>1279083864.2</v>
+        <v>1300729674.1</v>
       </c>
       <c r="H8" s="8">
-        <v>37.7</v>
+        <v>38.3</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -821,10 +829,10 @@
         <v>19</v>
       </c>
       <c r="C9" s="6">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="D9" s="7">
-        <v>58.728889</v>
+        <v>58.915018</v>
       </c>
       <c r="E9" s="8">
         <v>2250000</v>
@@ -833,10 +841,10 @@
         <v>0</v>
       </c>
       <c r="G9" s="8">
-        <v>132139999.95</v>
+        <v>132558790.61</v>
       </c>
       <c r="H9" s="8">
-        <v>58.92</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -847,10 +855,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="6">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="D10" s="7">
-        <v>344.960037</v>
+        <v>348.911795</v>
       </c>
       <c r="E10" s="8">
         <v>135000</v>
@@ -859,10 +867,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="8">
-        <v>46569605.05</v>
+        <v>47103092.39</v>
       </c>
       <c r="H10" s="8">
-        <v>345.3</v>
+        <v>349.5</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -873,10 +881,10 @@
         <v>23</v>
       </c>
       <c r="C11" s="6">
-        <v>46185</v>
-      </c>
-      <c r="D11" s="7">
-        <v>507.504756</v>
+        <v>46188</v>
+      </c>
+      <c r="D11" s="10">
+        <v>524.59689</v>
       </c>
       <c r="E11" s="8">
         <v>44350000</v>
@@ -885,10 +893,10 @@
         <v>0</v>
       </c>
       <c r="G11" s="8">
-        <v>22507835914.12</v>
+        <v>23265872052.07</v>
       </c>
       <c r="H11" s="8">
-        <v>510.75</v>
+        <v>526.5</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -899,10 +907,10 @@
         <v>25</v>
       </c>
       <c r="C12" s="6">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="D12" s="7">
-        <v>587.455858</v>
+        <v>616.033861</v>
       </c>
       <c r="E12" s="8">
         <v>74800000</v>
@@ -911,10 +919,10 @@
         <v>0</v>
       </c>
       <c r="G12" s="8">
-        <v>43941698153.88</v>
+        <v>46079332806.04</v>
       </c>
       <c r="H12" s="8">
-        <v>590</v>
+        <v>619.75</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -925,10 +933,10 @@
         <v>27</v>
       </c>
       <c r="C13" s="6">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="D13" s="7">
-        <v>4299.715422</v>
+        <v>4310.343194</v>
       </c>
       <c r="E13" s="8">
         <v>280000</v>
@@ -937,10 +945,10 @@
         <v>0</v>
       </c>
       <c r="G13" s="8">
-        <v>1203920318.14</v>
+        <v>1206896094.2</v>
       </c>
       <c r="H13" s="8">
-        <v>4318</v>
+        <v>4331</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -951,10 +959,10 @@
         <v>29</v>
       </c>
       <c r="C14" s="6">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="D14" s="7">
-        <v>614.207023</v>
+        <v>628.855993</v>
       </c>
       <c r="E14" s="8">
         <v>113800000</v>
@@ -963,10 +971,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="8">
-        <v>69896759219.93</v>
+        <v>71563811987</v>
       </c>
       <c r="H14" s="8">
-        <v>640</v>
+        <v>658</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -977,10 +985,10 @@
         <v>31</v>
       </c>
       <c r="C15" s="6">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="D15" s="7">
-        <v>504.616511</v>
+        <v>516.120817</v>
       </c>
       <c r="E15" s="8">
         <v>33450000</v>
@@ -989,10 +997,10 @@
         <v>0</v>
       </c>
       <c r="G15" s="8">
-        <v>16879422303.66</v>
+        <v>17264241315.68</v>
       </c>
       <c r="H15" s="8">
-        <v>504</v>
+        <v>523.5</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1003,10 +1011,10 @@
         <v>33</v>
       </c>
       <c r="C16" s="6">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="D16" s="7">
-        <v>24.848576</v>
+        <v>25.513229</v>
       </c>
       <c r="E16" s="8">
         <v>10800000</v>
@@ -1015,10 +1023,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="8">
-        <v>268364617.72</v>
+        <v>275542868.07</v>
       </c>
       <c r="H16" s="8">
-        <v>24.85</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1029,10 +1037,10 @@
         <v>35</v>
       </c>
       <c r="C17" s="6">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="D17" s="7">
-        <v>47.482181</v>
+        <v>47.633712</v>
       </c>
       <c r="E17" s="8">
         <v>1575000</v>
@@ -1041,10 +1049,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="8">
-        <v>74784434.99</v>
+        <v>75023096.56</v>
       </c>
       <c r="H17" s="8">
-        <v>47.62</v>
+        <v>47.69</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1055,10 +1063,10 @@
         <v>37</v>
       </c>
       <c r="C18" s="6">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="D18" s="7">
-        <v>72.897474</v>
+        <v>73.366537</v>
       </c>
       <c r="E18" s="8">
         <v>1140000</v>
@@ -1067,10 +1075,10 @@
         <v>0</v>
       </c>
       <c r="G18" s="8">
-        <v>83103120.73</v>
+        <v>83637852.54</v>
       </c>
       <c r="H18" s="8">
-        <v>72.9</v>
+        <v>73.58</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1081,10 +1089,10 @@
         <v>39</v>
       </c>
       <c r="C19" s="6">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="D19" s="7">
-        <v>81.529607</v>
+        <v>82.866069</v>
       </c>
       <c r="E19" s="8">
         <v>1155000</v>
@@ -1093,10 +1101,10 @@
         <v>0</v>
       </c>
       <c r="G19" s="8">
-        <v>94166696.64</v>
+        <v>95710309.99</v>
       </c>
       <c r="H19" s="8">
-        <v>81.32</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1107,10 +1115,10 @@
         <v>41</v>
       </c>
       <c r="C20" s="6">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="D20" s="7">
-        <v>50.440511</v>
+        <v>51.602272</v>
       </c>
       <c r="E20" s="8">
         <v>3135000</v>
@@ -1119,10 +1127,10 @@
         <v>0</v>
       </c>
       <c r="G20" s="8">
-        <v>158131001.16</v>
+        <v>161773122.31</v>
       </c>
       <c r="H20" s="8">
-        <v>50.44</v>
+        <v>51.56</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1133,10 +1141,10 @@
         <v>43</v>
       </c>
       <c r="C21" s="6">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="D21" s="7">
-        <v>163.548985</v>
+        <v>164.834861</v>
       </c>
       <c r="E21" s="8">
         <v>600000</v>
@@ -1145,10 +1153,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="8">
-        <v>98129391.2</v>
+        <v>98900916.43</v>
       </c>
       <c r="H21" s="8">
-        <v>164</v>
+        <v>165.5</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1159,22 +1167,22 @@
         <v>45</v>
       </c>
       <c r="C22" s="6">
-        <v>46185</v>
-      </c>
-      <c r="D22" s="10">
-        <v>203.66368</v>
+        <v>46188</v>
+      </c>
+      <c r="D22" s="7">
+        <v>207.005206</v>
       </c>
       <c r="E22" s="8">
-        <v>116160000</v>
+        <v>114560000</v>
       </c>
       <c r="F22" s="9">
         <v>0</v>
       </c>
       <c r="G22" s="8">
-        <v>23657573091.21</v>
+        <v>23714516359.07</v>
       </c>
       <c r="H22" s="8">
-        <v>202.45</v>
+        <v>207.35</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1185,22 +1193,22 @@
         <v>47</v>
       </c>
       <c r="C23" s="6">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="D23" s="7">
-        <v>191.218539</v>
+        <v>203.300234</v>
       </c>
       <c r="E23" s="8">
-        <v>216120000</v>
+        <v>219120000</v>
       </c>
       <c r="F23" s="9">
         <v>0</v>
       </c>
       <c r="G23" s="8">
-        <v>41326150645.63</v>
+        <v>44547147168.27</v>
       </c>
       <c r="H23" s="8">
-        <v>192.5</v>
+        <v>203.15</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1211,10 +1219,10 @@
         <v>49</v>
       </c>
       <c r="C24" s="6">
-        <v>46185</v>
-      </c>
-      <c r="D24" s="7">
-        <v>190.020607</v>
+        <v>46188</v>
+      </c>
+      <c r="D24" s="11">
+        <v>193.637</v>
       </c>
       <c r="E24" s="8">
         <v>400000</v>
@@ -1223,10 +1231,10 @@
         <v>0</v>
       </c>
       <c r="G24" s="8">
-        <v>76008242.85</v>
+        <v>77454799.82</v>
       </c>
       <c r="H24" s="8">
-        <v>190.1</v>
+        <v>193.85</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1237,10 +1245,10 @@
         <v>51</v>
       </c>
       <c r="C25" s="6">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="D25" s="7">
-        <v>119.381809</v>
+        <v>120.363293</v>
       </c>
       <c r="E25" s="8">
         <v>600000</v>
@@ -1249,10 +1257,10 @@
         <v>0</v>
       </c>
       <c r="G25" s="8">
-        <v>71629085.35</v>
+        <v>72217975.84</v>
       </c>
       <c r="H25" s="8">
-        <v>119.15</v>
+        <v>120.55</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1263,10 +1271,10 @@
         <v>53</v>
       </c>
       <c r="C26" s="6">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="D26" s="7">
-        <v>618.834845</v>
+        <v>638.121068</v>
       </c>
       <c r="E26" s="8">
         <v>152040000</v>
@@ -1275,10 +1283,10 @@
         <v>0</v>
       </c>
       <c r="G26" s="8">
-        <v>94087649878.92</v>
+        <v>97019927137.17</v>
       </c>
       <c r="H26" s="8">
-        <v>644.25</v>
+        <v>658</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1289,22 +1297,22 @@
         <v>55</v>
       </c>
       <c r="C27" s="6">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="D27" s="7">
-        <v>176.168699</v>
+        <v>177.447354</v>
       </c>
       <c r="E27" s="8">
-        <v>10960000</v>
+        <v>11880000</v>
       </c>
       <c r="F27" s="9">
         <v>0</v>
       </c>
       <c r="G27" s="8">
-        <v>1930808938.51</v>
+        <v>2108074570</v>
       </c>
       <c r="H27" s="8">
-        <v>177.75</v>
+        <v>180</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1315,22 +1323,22 @@
         <v>57</v>
       </c>
       <c r="C28" s="6">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="D28" s="7">
-        <v>251.152008</v>
+        <v>252.602303</v>
       </c>
       <c r="E28" s="8">
-        <v>32200000</v>
+        <v>33280000</v>
       </c>
       <c r="F28" s="9">
         <v>0</v>
       </c>
       <c r="G28" s="8">
-        <v>8087094645.7</v>
+        <v>8406604637.97</v>
       </c>
       <c r="H28" s="8">
-        <v>248.15</v>
+        <v>254</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1341,22 +1349,22 @@
         <v>59</v>
       </c>
       <c r="C29" s="6">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="D29" s="7">
-        <v>242.114057</v>
+        <v>243.343282</v>
       </c>
       <c r="E29" s="8">
-        <v>3200000</v>
+        <v>3160000</v>
       </c>
       <c r="F29" s="9">
         <v>0</v>
       </c>
       <c r="G29" s="8">
-        <v>774764982.12</v>
+        <v>768964771.08</v>
       </c>
       <c r="H29" s="8">
-        <v>241.65</v>
+        <v>242.9</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1367,10 +1375,10 @@
         <v>61</v>
       </c>
       <c r="C30" s="6">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="D30" s="7">
-        <v>124.499899</v>
+        <v>125.906471</v>
       </c>
       <c r="E30" s="8">
         <v>440000</v>
@@ -1379,10 +1387,10 @@
         <v>0</v>
       </c>
       <c r="G30" s="8">
-        <v>54779955.43</v>
+        <v>55398847.09</v>
       </c>
       <c r="H30" s="8">
-        <v>122.95</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1393,10 +1401,10 @@
         <v>63</v>
       </c>
       <c r="C31" s="6">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="D31" s="7">
-        <v>174.017504</v>
+        <v>175.569388</v>
       </c>
       <c r="E31" s="8">
         <v>400000</v>
@@ -1405,10 +1413,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="8">
-        <v>69607001.64</v>
+        <v>70227755.23</v>
       </c>
       <c r="H31" s="8">
-        <v>174.05</v>
+        <v>178.15</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1419,10 +1427,10 @@
         <v>65</v>
       </c>
       <c r="C32" s="6">
-        <v>46185</v>
-      </c>
-      <c r="D32" s="7">
-        <v>46.244261</v>
+        <v>46188</v>
+      </c>
+      <c r="D32" s="12">
+        <v>47.4568</v>
       </c>
       <c r="E32" s="8">
         <v>1200000</v>
@@ -1431,10 +1439,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="8">
-        <v>55493113.79</v>
+        <v>56948159.4</v>
       </c>
       <c r="H32" s="8">
-        <v>46.1</v>
+        <v>46.92</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1445,10 +1453,10 @@
         <v>67</v>
       </c>
       <c r="C33" s="6">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="D33" s="7">
-        <v>1265.780564</v>
+        <v>1269.874485</v>
       </c>
       <c r="E33" s="8">
         <v>560000</v>
@@ -1457,10 +1465,10 @@
         <v>0</v>
       </c>
       <c r="G33" s="8">
-        <v>708837115.8</v>
+        <v>711129711.47</v>
       </c>
       <c r="H33" s="8">
-        <v>1270</v>
+        <v>1271.5</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -1471,10 +1479,10 @@
         <v>69</v>
       </c>
       <c r="C34" s="6">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="D34" s="7">
-        <v>180.354754</v>
+        <v>184.584166</v>
       </c>
       <c r="E34" s="8">
         <v>680000</v>
@@ -1483,10 +1491,10 @@
         <v>0</v>
       </c>
       <c r="G34" s="8">
-        <v>122641232.59</v>
+        <v>125517232.64</v>
       </c>
       <c r="H34" s="8">
-        <v>179.35</v>
+        <v>182.9</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -1497,10 +1505,10 @@
         <v>71</v>
       </c>
       <c r="C35" s="6">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="D35" s="7">
-        <v>1266.759766</v>
+        <v>1270.839387</v>
       </c>
       <c r="E35" s="8">
         <v>4400000</v>
@@ -1509,10 +1517,10 @@
         <v>0</v>
       </c>
       <c r="G35" s="8">
-        <v>5573742971.36</v>
+        <v>5591693302.06</v>
       </c>
       <c r="H35" s="8">
-        <v>1271</v>
+        <v>1272.5</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>15.06.2026 12:05:22</t>
+    <t>16.06.2026 10:59:09</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -233,14 +233,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="7">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="###0.000000;-###0.000000;0"/>
     <numFmt numFmtId="166" formatCode="###0.00;-###0.00;0"/>
     <numFmt numFmtId="167" formatCode="###0;-###0;0"/>
     <numFmt numFmtId="168" formatCode="###0.00000;-###0.00000;0"/>
-    <numFmt numFmtId="169" formatCode="###0.000;-###0.000;0"/>
-    <numFmt numFmtId="170" formatCode="###0.0000;-###0.0000;0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -310,7 +308,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -336,12 +334,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -692,7 +684,7 @@
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="24" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="19" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
     <col min="8" max="8" width="21" customWidth="1"/>
   </cols>
   <sheetData>
@@ -751,10 +743,10 @@
         <v>13</v>
       </c>
       <c r="C6" s="6">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="D6" s="7">
-        <v>47.868965</v>
+        <v>50.328556</v>
       </c>
       <c r="E6" s="8">
         <v>58200000</v>
@@ -763,10 +755,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="8">
-        <v>2785973777.37</v>
+        <v>2929121980.55</v>
       </c>
       <c r="H6" s="8">
-        <v>47.61</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -777,10 +769,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="6">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="D7" s="7">
-        <v>36.228727</v>
+        <v>37.234549</v>
       </c>
       <c r="E7" s="8">
         <v>14400000</v>
@@ -789,10 +781,10 @@
         <v>0</v>
       </c>
       <c r="G7" s="8">
-        <v>521693664.65</v>
+        <v>536177505.83</v>
       </c>
       <c r="H7" s="8">
-        <v>36.07</v>
+        <v>37.44</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -803,10 +795,10 @@
         <v>17</v>
       </c>
       <c r="C8" s="6">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="D8" s="7">
-        <v>38.369607</v>
+        <v>39.822453</v>
       </c>
       <c r="E8" s="8">
         <v>33900000</v>
@@ -815,10 +807,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="8">
-        <v>1300729674.1</v>
+        <v>1349981164.43</v>
       </c>
       <c r="H8" s="8">
-        <v>38.3</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -829,10 +821,10 @@
         <v>19</v>
       </c>
       <c r="C9" s="6">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="D9" s="7">
-        <v>58.915018</v>
+        <v>58.977523</v>
       </c>
       <c r="E9" s="8">
         <v>2250000</v>
@@ -841,10 +833,10 @@
         <v>0</v>
       </c>
       <c r="G9" s="8">
-        <v>132558790.61</v>
+        <v>132699427.38</v>
       </c>
       <c r="H9" s="8">
-        <v>59</v>
+        <v>59.06</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -855,10 +847,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="6">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="D10" s="7">
-        <v>348.911795</v>
+        <v>358.360611</v>
       </c>
       <c r="E10" s="8">
         <v>135000</v>
@@ -867,10 +859,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="8">
-        <v>47103092.39</v>
+        <v>48378682.49</v>
       </c>
       <c r="H10" s="8">
-        <v>349.5</v>
+        <v>358.5</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -881,10 +873,10 @@
         <v>23</v>
       </c>
       <c r="C11" s="6">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="D11" s="10">
-        <v>524.59689</v>
+        <v>542.70619</v>
       </c>
       <c r="E11" s="8">
         <v>44350000</v>
@@ -893,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="G11" s="8">
-        <v>23265872052.07</v>
+        <v>24069019514.58</v>
       </c>
       <c r="H11" s="8">
-        <v>526.5</v>
+        <v>544</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -907,10 +899,10 @@
         <v>25</v>
       </c>
       <c r="C12" s="6">
-        <v>46188</v>
-      </c>
-      <c r="D12" s="7">
-        <v>616.033861</v>
+        <v>46189</v>
+      </c>
+      <c r="D12" s="10">
+        <v>648.42375</v>
       </c>
       <c r="E12" s="8">
         <v>74800000</v>
@@ -919,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="G12" s="8">
-        <v>46079332806.04</v>
+        <v>48502096467.35</v>
       </c>
       <c r="H12" s="8">
-        <v>619.75</v>
+        <v>654.75</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -933,10 +925,10 @@
         <v>27</v>
       </c>
       <c r="C13" s="6">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="D13" s="7">
-        <v>4310.343194</v>
+        <v>4310.425538</v>
       </c>
       <c r="E13" s="8">
         <v>280000</v>
@@ -945,10 +937,10 @@
         <v>0</v>
       </c>
       <c r="G13" s="8">
-        <v>1206896094.2</v>
+        <v>1206919150.58</v>
       </c>
       <c r="H13" s="8">
-        <v>4331</v>
+        <v>4321</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -959,10 +951,10 @@
         <v>29</v>
       </c>
       <c r="C14" s="6">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="D14" s="7">
-        <v>628.855993</v>
+        <v>650.948269</v>
       </c>
       <c r="E14" s="8">
         <v>113800000</v>
@@ -971,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="8">
-        <v>71563811987</v>
+        <v>74077913042.38</v>
       </c>
       <c r="H14" s="8">
-        <v>658</v>
+        <v>687</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -985,10 +977,10 @@
         <v>31</v>
       </c>
       <c r="C15" s="6">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="D15" s="7">
-        <v>516.120817</v>
+        <v>532.179861</v>
       </c>
       <c r="E15" s="8">
         <v>33450000</v>
@@ -997,10 +989,10 @@
         <v>0</v>
       </c>
       <c r="G15" s="8">
-        <v>17264241315.68</v>
+        <v>17801416357.5</v>
       </c>
       <c r="H15" s="8">
-        <v>523.5</v>
+        <v>542.25</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1011,10 +1003,10 @@
         <v>33</v>
       </c>
       <c r="C16" s="6">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="D16" s="7">
-        <v>25.513229</v>
+        <v>26.497519</v>
       </c>
       <c r="E16" s="8">
         <v>10800000</v>
@@ -1023,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="8">
-        <v>275542868.07</v>
+        <v>286173206.04</v>
       </c>
       <c r="H16" s="8">
-        <v>25.5</v>
+        <v>26.48</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1037,10 +1029,10 @@
         <v>35</v>
       </c>
       <c r="C17" s="6">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="D17" s="7">
-        <v>47.633712</v>
+        <v>47.683881</v>
       </c>
       <c r="E17" s="8">
         <v>1575000</v>
@@ -1049,10 +1041,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="8">
-        <v>75023096.56</v>
+        <v>75102113.05</v>
       </c>
       <c r="H17" s="8">
-        <v>47.69</v>
+        <v>47.73</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1063,10 +1055,10 @@
         <v>37</v>
       </c>
       <c r="C18" s="6">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="D18" s="7">
-        <v>73.366537</v>
+        <v>74.981245</v>
       </c>
       <c r="E18" s="8">
         <v>1140000</v>
@@ -1075,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="G18" s="8">
-        <v>83637852.54</v>
+        <v>85478618.79</v>
       </c>
       <c r="H18" s="8">
-        <v>73.58</v>
+        <v>75.36</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1089,10 +1081,10 @@
         <v>39</v>
       </c>
       <c r="C19" s="6">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="D19" s="7">
-        <v>82.866069</v>
+        <v>85.913868</v>
       </c>
       <c r="E19" s="8">
         <v>1155000</v>
@@ -1101,10 +1093,10 @@
         <v>0</v>
       </c>
       <c r="G19" s="8">
-        <v>95710309.99</v>
+        <v>99230517.48</v>
       </c>
       <c r="H19" s="8">
-        <v>82.5</v>
+        <v>86.24</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1115,10 +1107,10 @@
         <v>41</v>
       </c>
       <c r="C20" s="6">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="D20" s="7">
-        <v>51.602272</v>
+        <v>53.278735</v>
       </c>
       <c r="E20" s="8">
         <v>3135000</v>
@@ -1127,10 +1119,10 @@
         <v>0</v>
       </c>
       <c r="G20" s="8">
-        <v>161773122.31</v>
+        <v>167028834.29</v>
       </c>
       <c r="H20" s="8">
-        <v>51.56</v>
+        <v>53.52</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1141,10 +1133,10 @@
         <v>43</v>
       </c>
       <c r="C21" s="6">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="D21" s="7">
-        <v>164.834861</v>
+        <v>171.154472</v>
       </c>
       <c r="E21" s="8">
         <v>600000</v>
@@ -1153,10 +1145,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="8">
-        <v>98900916.43</v>
+        <v>102692683.18</v>
       </c>
       <c r="H21" s="8">
-        <v>165.5</v>
+        <v>169.75</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1167,22 +1159,22 @@
         <v>45</v>
       </c>
       <c r="C22" s="6">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="D22" s="7">
-        <v>207.005206</v>
+        <v>214.847772</v>
       </c>
       <c r="E22" s="8">
-        <v>114560000</v>
+        <v>113920000</v>
       </c>
       <c r="F22" s="9">
         <v>0</v>
       </c>
       <c r="G22" s="8">
-        <v>23714516359.07</v>
+        <v>24475458232.2</v>
       </c>
       <c r="H22" s="8">
-        <v>207.35</v>
+        <v>215.4</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1193,22 +1185,22 @@
         <v>47</v>
       </c>
       <c r="C23" s="6">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="D23" s="7">
-        <v>203.300234</v>
+        <v>213.760701</v>
       </c>
       <c r="E23" s="8">
-        <v>219120000</v>
+        <v>219400000</v>
       </c>
       <c r="F23" s="9">
         <v>0</v>
       </c>
       <c r="G23" s="8">
-        <v>44547147168.27</v>
+        <v>46899097765.78</v>
       </c>
       <c r="H23" s="8">
-        <v>203.15</v>
+        <v>215</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1219,10 +1211,10 @@
         <v>49</v>
       </c>
       <c r="C24" s="6">
-        <v>46188</v>
-      </c>
-      <c r="D24" s="11">
-        <v>193.637</v>
+        <v>46189</v>
+      </c>
+      <c r="D24" s="10">
+        <v>202.37232</v>
       </c>
       <c r="E24" s="8">
         <v>400000</v>
@@ -1231,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="G24" s="8">
-        <v>77454799.82</v>
+        <v>80948928.01</v>
       </c>
       <c r="H24" s="8">
-        <v>193.85</v>
+        <v>202.8</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1245,10 +1237,10 @@
         <v>51</v>
       </c>
       <c r="C25" s="6">
-        <v>46188</v>
-      </c>
-      <c r="D25" s="7">
-        <v>120.363293</v>
+        <v>46189</v>
+      </c>
+      <c r="D25" s="10">
+        <v>122.80245</v>
       </c>
       <c r="E25" s="8">
         <v>600000</v>
@@ -1257,10 +1249,10 @@
         <v>0</v>
       </c>
       <c r="G25" s="8">
-        <v>72217975.84</v>
+        <v>73681470.1</v>
       </c>
       <c r="H25" s="8">
-        <v>120.55</v>
+        <v>123.25</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1271,10 +1263,10 @@
         <v>53</v>
       </c>
       <c r="C26" s="6">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="D26" s="7">
-        <v>638.121068</v>
+        <v>660.225109</v>
       </c>
       <c r="E26" s="8">
         <v>152040000</v>
@@ -1283,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="G26" s="8">
-        <v>97019927137.17</v>
+        <v>100380625643.71</v>
       </c>
       <c r="H26" s="8">
-        <v>658</v>
+        <v>690</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1297,22 +1289,22 @@
         <v>55</v>
       </c>
       <c r="C27" s="6">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="D27" s="7">
-        <v>177.447354</v>
+        <v>182.197329</v>
       </c>
       <c r="E27" s="8">
-        <v>11880000</v>
+        <v>11840000</v>
       </c>
       <c r="F27" s="9">
         <v>0</v>
       </c>
       <c r="G27" s="8">
-        <v>2108074570</v>
+        <v>2157216372.53</v>
       </c>
       <c r="H27" s="8">
-        <v>180</v>
+        <v>183.4</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1323,22 +1315,22 @@
         <v>57</v>
       </c>
       <c r="C28" s="6">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="D28" s="7">
-        <v>252.602303</v>
+        <v>258.395986</v>
       </c>
       <c r="E28" s="8">
-        <v>33280000</v>
+        <v>33200000</v>
       </c>
       <c r="F28" s="9">
         <v>0</v>
       </c>
       <c r="G28" s="8">
-        <v>8406604637.97</v>
+        <v>8578746719.49</v>
       </c>
       <c r="H28" s="8">
-        <v>254</v>
+        <v>260</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1349,10 +1341,10 @@
         <v>59</v>
       </c>
       <c r="C29" s="6">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="D29" s="7">
-        <v>243.343282</v>
+        <v>250.110146</v>
       </c>
       <c r="E29" s="8">
         <v>3160000</v>
@@ -1361,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="G29" s="8">
-        <v>768964771.08</v>
+        <v>790348061.77</v>
       </c>
       <c r="H29" s="8">
-        <v>242.9</v>
+        <v>251.2</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1375,10 +1367,10 @@
         <v>61</v>
       </c>
       <c r="C30" s="6">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="D30" s="7">
-        <v>125.906471</v>
+        <v>127.858263</v>
       </c>
       <c r="E30" s="8">
         <v>440000</v>
@@ -1387,10 +1379,10 @@
         <v>0</v>
       </c>
       <c r="G30" s="8">
-        <v>55398847.09</v>
+        <v>56257635.66</v>
       </c>
       <c r="H30" s="8">
-        <v>125.8</v>
+        <v>127.9</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1401,10 +1393,10 @@
         <v>63</v>
       </c>
       <c r="C31" s="6">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="D31" s="7">
-        <v>175.569388</v>
+        <v>183.032902</v>
       </c>
       <c r="E31" s="8">
         <v>400000</v>
@@ -1413,10 +1405,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="8">
-        <v>70227755.23</v>
+        <v>73213160.93</v>
       </c>
       <c r="H31" s="8">
-        <v>178.15</v>
+        <v>182.95</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1427,10 +1419,10 @@
         <v>65</v>
       </c>
       <c r="C32" s="6">
-        <v>46188</v>
-      </c>
-      <c r="D32" s="12">
-        <v>47.4568</v>
+        <v>46189</v>
+      </c>
+      <c r="D32" s="7">
+        <v>49.219313</v>
       </c>
       <c r="E32" s="8">
         <v>1200000</v>
@@ -1439,10 +1431,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="8">
-        <v>56948159.4</v>
+        <v>59063175.13</v>
       </c>
       <c r="H32" s="8">
-        <v>46.92</v>
+        <v>49.38</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1453,10 +1445,10 @@
         <v>67</v>
       </c>
       <c r="C33" s="6">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="D33" s="7">
-        <v>1269.874485</v>
+        <v>1271.242234</v>
       </c>
       <c r="E33" s="8">
         <v>560000</v>
@@ -1465,10 +1457,10 @@
         <v>0</v>
       </c>
       <c r="G33" s="8">
-        <v>711129711.47</v>
+        <v>711895650.95</v>
       </c>
       <c r="H33" s="8">
-        <v>1271.5</v>
+        <v>1272.5</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -1479,10 +1471,10 @@
         <v>69</v>
       </c>
       <c r="C34" s="6">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="D34" s="7">
-        <v>184.584166</v>
+        <v>190.765364</v>
       </c>
       <c r="E34" s="8">
         <v>680000</v>
@@ -1491,10 +1483,10 @@
         <v>0</v>
       </c>
       <c r="G34" s="8">
-        <v>125517232.64</v>
+        <v>129720447.34</v>
       </c>
       <c r="H34" s="8">
-        <v>182.9</v>
+        <v>191.5</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -1505,22 +1497,22 @@
         <v>71</v>
       </c>
       <c r="C35" s="6">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="D35" s="7">
-        <v>1270.839387</v>
+        <v>1272.203701</v>
       </c>
       <c r="E35" s="8">
-        <v>4400000</v>
+        <v>4320000</v>
       </c>
       <c r="F35" s="9">
         <v>0</v>
       </c>
       <c r="G35" s="8">
-        <v>5591693302.06</v>
+        <v>5495919989.42</v>
       </c>
       <c r="H35" s="8">
-        <v>1272.5</v>
+        <v>1274</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>16.06.2026 10:59:09</t>
+    <t>17.06.2026 10:04:51</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -233,12 +233,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="5">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="###0.000000;-###0.000000;0"/>
     <numFmt numFmtId="166" formatCode="###0.00;-###0.00;0"/>
     <numFmt numFmtId="167" formatCode="###0;-###0;0"/>
-    <numFmt numFmtId="168" formatCode="###0.00000;-###0.00000;0"/>
+    <numFmt numFmtId="168" formatCode="###0.000;-###0.000;0"/>
+    <numFmt numFmtId="169" formatCode="###0.00000;-###0.00000;0"/>
+    <numFmt numFmtId="170" formatCode="###0.0000;-###0.0000;0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -308,7 +310,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -334,6 +336,12 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -684,7 +692,7 @@
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="24" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="7" max="7" width="19" customWidth="1"/>
     <col min="8" max="8" width="21" customWidth="1"/>
   </cols>
   <sheetData>
@@ -743,10 +751,10 @@
         <v>13</v>
       </c>
       <c r="C6" s="6">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="D6" s="7">
-        <v>50.328556</v>
+        <v>50.421528</v>
       </c>
       <c r="E6" s="8">
         <v>58200000</v>
@@ -755,10 +763,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="8">
-        <v>2929121980.55</v>
+        <v>2934532949.57</v>
       </c>
       <c r="H6" s="8">
-        <v>50.5</v>
+        <v>50.26</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -769,10 +777,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="6">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="D7" s="7">
-        <v>37.234549</v>
+        <v>37.565293</v>
       </c>
       <c r="E7" s="8">
         <v>14400000</v>
@@ -781,10 +789,10 @@
         <v>0</v>
       </c>
       <c r="G7" s="8">
-        <v>536177505.83</v>
+        <v>540940223.97</v>
       </c>
       <c r="H7" s="8">
-        <v>37.44</v>
+        <v>37.58</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -795,10 +803,10 @@
         <v>17</v>
       </c>
       <c r="C8" s="6">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="D8" s="7">
-        <v>39.822453</v>
+        <v>40.101117</v>
       </c>
       <c r="E8" s="8">
         <v>33900000</v>
@@ -807,10 +815,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="8">
-        <v>1349981164.43</v>
+        <v>1359427853.56</v>
       </c>
       <c r="H8" s="8">
-        <v>40</v>
+        <v>40.01</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -821,10 +829,10 @@
         <v>19</v>
       </c>
       <c r="C9" s="6">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="D9" s="7">
-        <v>58.977523</v>
+        <v>59.039495</v>
       </c>
       <c r="E9" s="8">
         <v>2250000</v>
@@ -833,10 +841,10 @@
         <v>0</v>
       </c>
       <c r="G9" s="8">
-        <v>132699427.38</v>
+        <v>132838864.38</v>
       </c>
       <c r="H9" s="8">
-        <v>59.06</v>
+        <v>59.12</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -847,10 +855,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="6">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="D10" s="7">
-        <v>358.360611</v>
+        <v>360.359434</v>
       </c>
       <c r="E10" s="8">
         <v>135000</v>
@@ -859,10 +867,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="8">
-        <v>48378682.49</v>
+        <v>48648523.53</v>
       </c>
       <c r="H10" s="8">
-        <v>358.5</v>
+        <v>359.6</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -873,10 +881,10 @@
         <v>23</v>
       </c>
       <c r="C11" s="6">
-        <v>46189</v>
-      </c>
-      <c r="D11" s="10">
-        <v>542.70619</v>
+        <v>46190</v>
+      </c>
+      <c r="D11" s="7">
+        <v>539.211442</v>
       </c>
       <c r="E11" s="8">
         <v>44350000</v>
@@ -885,10 +893,10 @@
         <v>0</v>
       </c>
       <c r="G11" s="8">
-        <v>24069019514.58</v>
+        <v>23914027461.55</v>
       </c>
       <c r="H11" s="8">
-        <v>544</v>
+        <v>540.5</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -899,10 +907,10 @@
         <v>25</v>
       </c>
       <c r="C12" s="6">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="D12" s="10">
-        <v>648.42375</v>
+        <v>640.979</v>
       </c>
       <c r="E12" s="8">
         <v>74800000</v>
@@ -911,10 +919,10 @@
         <v>0</v>
       </c>
       <c r="G12" s="8">
-        <v>48502096467.35</v>
+        <v>47945229199.14</v>
       </c>
       <c r="H12" s="8">
-        <v>654.75</v>
+        <v>644.25</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -925,10 +933,10 @@
         <v>27</v>
       </c>
       <c r="C13" s="6">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="D13" s="7">
-        <v>4310.425538</v>
+        <v>4312.109185</v>
       </c>
       <c r="E13" s="8">
         <v>280000</v>
@@ -937,10 +945,10 @@
         <v>0</v>
       </c>
       <c r="G13" s="8">
-        <v>1206919150.58</v>
+        <v>1207390571.78</v>
       </c>
       <c r="H13" s="8">
-        <v>4321</v>
+        <v>4319</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -951,10 +959,10 @@
         <v>29</v>
       </c>
       <c r="C14" s="6">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="D14" s="7">
-        <v>650.948269</v>
+        <v>653.278721</v>
       </c>
       <c r="E14" s="8">
         <v>113800000</v>
@@ -963,10 +971,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="8">
-        <v>74077913042.38</v>
+        <v>74343118438.93</v>
       </c>
       <c r="H14" s="8">
-        <v>687</v>
+        <v>680.25</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -977,10 +985,10 @@
         <v>31</v>
       </c>
       <c r="C15" s="6">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="D15" s="7">
-        <v>532.179861</v>
+        <v>539.319951</v>
       </c>
       <c r="E15" s="8">
         <v>33450000</v>
@@ -989,10 +997,10 @@
         <v>0</v>
       </c>
       <c r="G15" s="8">
-        <v>17801416357.5</v>
+        <v>18040252363.75</v>
       </c>
       <c r="H15" s="8">
-        <v>542.25</v>
+        <v>539</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1003,10 +1011,10 @@
         <v>33</v>
       </c>
       <c r="C16" s="6">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="D16" s="7">
-        <v>26.497519</v>
+        <v>26.404491</v>
       </c>
       <c r="E16" s="8">
         <v>10800000</v>
@@ -1015,10 +1023,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="8">
-        <v>286173206.04</v>
+        <v>285168502.96</v>
       </c>
       <c r="H16" s="8">
-        <v>26.48</v>
+        <v>26.34</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1029,22 +1037,22 @@
         <v>35</v>
       </c>
       <c r="C17" s="6">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="D17" s="7">
-        <v>47.683881</v>
+        <v>47.734587</v>
       </c>
       <c r="E17" s="8">
-        <v>1575000</v>
+        <v>1625000</v>
       </c>
       <c r="F17" s="9">
         <v>0</v>
       </c>
       <c r="G17" s="8">
-        <v>75102113.05</v>
+        <v>77568703.45</v>
       </c>
       <c r="H17" s="8">
-        <v>47.73</v>
+        <v>47.79</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1055,10 +1063,10 @@
         <v>37</v>
       </c>
       <c r="C18" s="6">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="D18" s="7">
-        <v>74.981245</v>
+        <v>75.081302</v>
       </c>
       <c r="E18" s="8">
         <v>1140000</v>
@@ -1067,10 +1075,10 @@
         <v>0</v>
       </c>
       <c r="G18" s="8">
-        <v>85478618.79</v>
+        <v>85592683.92</v>
       </c>
       <c r="H18" s="8">
-        <v>75.36</v>
+        <v>75.18</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1081,10 +1089,10 @@
         <v>39</v>
       </c>
       <c r="C19" s="6">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="D19" s="7">
-        <v>85.913868</v>
+        <v>86.508374</v>
       </c>
       <c r="E19" s="8">
         <v>1155000</v>
@@ -1093,10 +1101,10 @@
         <v>0</v>
       </c>
       <c r="G19" s="8">
-        <v>99230517.48</v>
+        <v>99917172.34</v>
       </c>
       <c r="H19" s="8">
-        <v>86.24</v>
+        <v>86.46</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1107,10 +1115,10 @@
         <v>41</v>
       </c>
       <c r="C20" s="6">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="D20" s="7">
-        <v>53.278735</v>
+        <v>53.073008</v>
       </c>
       <c r="E20" s="8">
         <v>3135000</v>
@@ -1119,10 +1127,10 @@
         <v>0</v>
       </c>
       <c r="G20" s="8">
-        <v>167028834.29</v>
+        <v>166383881.34</v>
       </c>
       <c r="H20" s="8">
-        <v>53.52</v>
+        <v>53.08</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1133,10 +1141,10 @@
         <v>43</v>
       </c>
       <c r="C21" s="6">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="D21" s="7">
-        <v>171.154472</v>
+        <v>170.438473</v>
       </c>
       <c r="E21" s="8">
         <v>600000</v>
@@ -1145,10 +1153,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="8">
-        <v>102692683.18</v>
+        <v>102263083.64</v>
       </c>
       <c r="H21" s="8">
-        <v>169.75</v>
+        <v>170.9</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1159,22 +1167,22 @@
         <v>45</v>
       </c>
       <c r="C22" s="6">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="D22" s="7">
-        <v>214.847772</v>
+        <v>216.375533</v>
       </c>
       <c r="E22" s="8">
-        <v>113920000</v>
+        <v>116040000</v>
       </c>
       <c r="F22" s="9">
         <v>0</v>
       </c>
       <c r="G22" s="8">
-        <v>24475458232.2</v>
+        <v>25108216856.94</v>
       </c>
       <c r="H22" s="8">
-        <v>215.4</v>
+        <v>216.5</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1185,22 +1193,22 @@
         <v>47</v>
       </c>
       <c r="C23" s="6">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="D23" s="7">
-        <v>213.760701</v>
+        <v>214.154693</v>
       </c>
       <c r="E23" s="8">
-        <v>219400000</v>
+        <v>218400000</v>
       </c>
       <c r="F23" s="9">
         <v>0</v>
       </c>
       <c r="G23" s="8">
-        <v>46899097765.78</v>
+        <v>46771384854.08</v>
       </c>
       <c r="H23" s="8">
-        <v>215</v>
+        <v>213.75</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1211,10 +1219,10 @@
         <v>49</v>
       </c>
       <c r="C24" s="6">
-        <v>46189</v>
-      </c>
-      <c r="D24" s="10">
-        <v>202.37232</v>
+        <v>46190</v>
+      </c>
+      <c r="D24" s="7">
+        <v>203.709667</v>
       </c>
       <c r="E24" s="8">
         <v>400000</v>
@@ -1223,10 +1231,10 @@
         <v>0</v>
       </c>
       <c r="G24" s="8">
-        <v>80948928.01</v>
+        <v>81483866.63</v>
       </c>
       <c r="H24" s="8">
-        <v>202.8</v>
+        <v>204.2</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1237,10 +1245,10 @@
         <v>51</v>
       </c>
       <c r="C25" s="6">
-        <v>46189</v>
-      </c>
-      <c r="D25" s="10">
-        <v>122.80245</v>
+        <v>46190</v>
+      </c>
+      <c r="D25" s="11">
+        <v>122.01819</v>
       </c>
       <c r="E25" s="8">
         <v>600000</v>
@@ -1249,10 +1257,10 @@
         <v>0</v>
       </c>
       <c r="G25" s="8">
-        <v>73681470.1</v>
+        <v>73210913.9</v>
       </c>
       <c r="H25" s="8">
-        <v>123.25</v>
+        <v>122.5</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1263,10 +1271,10 @@
         <v>53</v>
       </c>
       <c r="C26" s="6">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="D26" s="7">
-        <v>660.225109</v>
+        <v>657.340254</v>
       </c>
       <c r="E26" s="8">
         <v>152040000</v>
@@ -1275,10 +1283,10 @@
         <v>0</v>
       </c>
       <c r="G26" s="8">
-        <v>100380625643.71</v>
+        <v>99942012278.58</v>
       </c>
       <c r="H26" s="8">
-        <v>690</v>
+        <v>687</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1289,22 +1297,22 @@
         <v>55</v>
       </c>
       <c r="C27" s="6">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="D27" s="7">
-        <v>182.197329</v>
+        <v>183.625359</v>
       </c>
       <c r="E27" s="8">
-        <v>11840000</v>
+        <v>11680000</v>
       </c>
       <c r="F27" s="9">
         <v>0</v>
       </c>
       <c r="G27" s="8">
-        <v>2157216372.53</v>
+        <v>2144744194.63</v>
       </c>
       <c r="H27" s="8">
-        <v>183.4</v>
+        <v>184</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1315,22 +1323,22 @@
         <v>57</v>
       </c>
       <c r="C28" s="6">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="D28" s="7">
-        <v>258.395986</v>
+        <v>258.607009</v>
       </c>
       <c r="E28" s="8">
-        <v>33200000</v>
+        <v>32960000</v>
       </c>
       <c r="F28" s="9">
         <v>0</v>
       </c>
       <c r="G28" s="8">
-        <v>8578746719.49</v>
+        <v>8523687032.13</v>
       </c>
       <c r="H28" s="8">
-        <v>260</v>
+        <v>259.5</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1341,10 +1349,10 @@
         <v>59</v>
       </c>
       <c r="C29" s="6">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="D29" s="7">
-        <v>250.110146</v>
+        <v>252.329031</v>
       </c>
       <c r="E29" s="8">
         <v>3160000</v>
@@ -1353,10 +1361,10 @@
         <v>0</v>
       </c>
       <c r="G29" s="8">
-        <v>790348061.77</v>
+        <v>797359739.03</v>
       </c>
       <c r="H29" s="8">
-        <v>251.2</v>
+        <v>252</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1367,10 +1375,10 @@
         <v>61</v>
       </c>
       <c r="C30" s="6">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="D30" s="7">
-        <v>127.858263</v>
+        <v>129.729387</v>
       </c>
       <c r="E30" s="8">
         <v>440000</v>
@@ -1379,10 +1387,10 @@
         <v>0</v>
       </c>
       <c r="G30" s="8">
-        <v>56257635.66</v>
+        <v>57080930.35</v>
       </c>
       <c r="H30" s="8">
-        <v>127.9</v>
+        <v>129.2</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1393,10 +1401,10 @@
         <v>63</v>
       </c>
       <c r="C31" s="6">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="D31" s="7">
-        <v>183.032902</v>
+        <v>184.521562</v>
       </c>
       <c r="E31" s="8">
         <v>400000</v>
@@ -1405,10 +1413,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="8">
-        <v>73213160.93</v>
+        <v>73808624.97</v>
       </c>
       <c r="H31" s="8">
-        <v>182.95</v>
+        <v>184.6</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1419,10 +1427,10 @@
         <v>65</v>
       </c>
       <c r="C32" s="6">
-        <v>46189</v>
-      </c>
-      <c r="D32" s="7">
-        <v>49.219313</v>
+        <v>46190</v>
+      </c>
+      <c r="D32" s="11">
+        <v>49.32922</v>
       </c>
       <c r="E32" s="8">
         <v>1200000</v>
@@ -1431,10 +1439,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="8">
-        <v>59063175.13</v>
+        <v>59195063.78</v>
       </c>
       <c r="H32" s="8">
-        <v>49.38</v>
+        <v>49.45</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1445,10 +1453,10 @@
         <v>67</v>
       </c>
       <c r="C33" s="6">
-        <v>46189</v>
-      </c>
-      <c r="D33" s="7">
-        <v>1271.242234</v>
+        <v>46190</v>
+      </c>
+      <c r="D33" s="12">
+        <v>1272.6112</v>
       </c>
       <c r="E33" s="8">
         <v>560000</v>
@@ -1457,10 +1465,10 @@
         <v>0</v>
       </c>
       <c r="G33" s="8">
-        <v>711895650.95</v>
+        <v>712662271.96</v>
       </c>
       <c r="H33" s="8">
-        <v>1272.5</v>
+        <v>1274.5</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -1471,10 +1479,10 @@
         <v>69</v>
       </c>
       <c r="C34" s="6">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="D34" s="7">
-        <v>190.765364</v>
+        <v>189.992384</v>
       </c>
       <c r="E34" s="8">
         <v>680000</v>
@@ -1483,10 +1491,10 @@
         <v>0</v>
       </c>
       <c r="G34" s="8">
-        <v>129720447.34</v>
+        <v>129194821.14</v>
       </c>
       <c r="H34" s="8">
-        <v>191.5</v>
+        <v>190</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -1497,22 +1505,22 @@
         <v>71</v>
       </c>
       <c r="C35" s="6">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="D35" s="7">
-        <v>1272.203701</v>
+        <v>1273.570299</v>
       </c>
       <c r="E35" s="8">
-        <v>4320000</v>
+        <v>2440000</v>
       </c>
       <c r="F35" s="9">
         <v>0</v>
       </c>
       <c r="G35" s="8">
-        <v>5495919989.42</v>
+        <v>3107511528.66</v>
       </c>
       <c r="H35" s="8">
-        <v>1274</v>
+        <v>1274.5</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>17.06.2026 10:04:51</t>
+    <t>18.06.2026 10:31:40</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -233,14 +233,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="7">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="###0.000000;-###0.000000;0"/>
     <numFmt numFmtId="166" formatCode="###0.00;-###0.00;0"/>
     <numFmt numFmtId="167" formatCode="###0;-###0;0"/>
-    <numFmt numFmtId="168" formatCode="###0.000;-###0.000;0"/>
-    <numFmt numFmtId="169" formatCode="###0.00000;-###0.00000;0"/>
-    <numFmt numFmtId="170" formatCode="###0.0000;-###0.0000;0"/>
+    <numFmt numFmtId="168" formatCode="###0.00000;-###0.00000;0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -310,7 +308,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -336,12 +334,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -692,7 +684,7 @@
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="24" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="19" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
     <col min="8" max="8" width="21" customWidth="1"/>
   </cols>
   <sheetData>
@@ -751,10 +743,10 @@
         <v>13</v>
       </c>
       <c r="C6" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D6" s="7">
-        <v>50.421528</v>
+        <v>50.704317</v>
       </c>
       <c r="E6" s="8">
         <v>58200000</v>
@@ -763,10 +755,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="8">
-        <v>2934532949.57</v>
+        <v>2950991248.39</v>
       </c>
       <c r="H6" s="8">
-        <v>50.26</v>
+        <v>50.56</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -777,10 +769,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D7" s="7">
-        <v>37.565293</v>
+        <v>37.385511</v>
       </c>
       <c r="E7" s="8">
         <v>14400000</v>
@@ -789,10 +781,10 @@
         <v>0</v>
       </c>
       <c r="G7" s="8">
-        <v>540940223.97</v>
+        <v>538351353.76</v>
       </c>
       <c r="H7" s="8">
-        <v>37.58</v>
+        <v>37.36</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -803,10 +795,10 @@
         <v>17</v>
       </c>
       <c r="C8" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D8" s="7">
-        <v>40.101117</v>
+        <v>39.829226</v>
       </c>
       <c r="E8" s="8">
         <v>33900000</v>
@@ -815,10 +807,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="8">
-        <v>1359427853.56</v>
+        <v>1350210754.03</v>
       </c>
       <c r="H8" s="8">
-        <v>40.01</v>
+        <v>39.85</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -829,10 +821,10 @@
         <v>19</v>
       </c>
       <c r="C9" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D9" s="7">
-        <v>59.039495</v>
+        <v>59.101904</v>
       </c>
       <c r="E9" s="8">
         <v>2250000</v>
@@ -841,10 +833,10 @@
         <v>0</v>
       </c>
       <c r="G9" s="8">
-        <v>132838864.38</v>
+        <v>132979283.35</v>
       </c>
       <c r="H9" s="8">
-        <v>59.12</v>
+        <v>59.18</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -855,10 +847,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D10" s="7">
-        <v>360.359434</v>
+        <v>353.054162</v>
       </c>
       <c r="E10" s="8">
         <v>135000</v>
@@ -867,10 +859,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="8">
-        <v>48648523.53</v>
+        <v>47662311.87</v>
       </c>
       <c r="H10" s="8">
-        <v>359.6</v>
+        <v>353.1</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -881,10 +873,10 @@
         <v>23</v>
       </c>
       <c r="C11" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D11" s="7">
-        <v>539.211442</v>
+        <v>541.976235</v>
       </c>
       <c r="E11" s="8">
         <v>44350000</v>
@@ -893,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="G11" s="8">
-        <v>23914027461.55</v>
+        <v>24036646013.72</v>
       </c>
       <c r="H11" s="8">
-        <v>540.5</v>
+        <v>546.25</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -907,10 +899,10 @@
         <v>25</v>
       </c>
       <c r="C12" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D12" s="10">
-        <v>640.979</v>
+        <v>46191</v>
+      </c>
+      <c r="D12" s="7">
+        <v>645.979853</v>
       </c>
       <c r="E12" s="8">
         <v>74800000</v>
@@ -919,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="G12" s="8">
-        <v>47945229199.14</v>
+        <v>48319292974.53</v>
       </c>
       <c r="H12" s="8">
-        <v>644.25</v>
+        <v>643.75</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -933,10 +925,10 @@
         <v>27</v>
       </c>
       <c r="C13" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D13" s="7">
-        <v>4312.109185</v>
+        <v>4313.988319</v>
       </c>
       <c r="E13" s="8">
         <v>280000</v>
@@ -945,10 +937,10 @@
         <v>0</v>
       </c>
       <c r="G13" s="8">
-        <v>1207390571.78</v>
+        <v>1207916729.23</v>
       </c>
       <c r="H13" s="8">
-        <v>4319</v>
+        <v>4308</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -959,10 +951,10 @@
         <v>29</v>
       </c>
       <c r="C14" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D14" s="7">
-        <v>653.278721</v>
+        <v>652.342772</v>
       </c>
       <c r="E14" s="8">
         <v>113800000</v>
@@ -971,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="8">
-        <v>74343118438.93</v>
+        <v>74236607482.2</v>
       </c>
       <c r="H14" s="8">
-        <v>680.25</v>
+        <v>680</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -985,10 +977,10 @@
         <v>31</v>
       </c>
       <c r="C15" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D15" s="7">
-        <v>539.319951</v>
+        <v>537.638968</v>
       </c>
       <c r="E15" s="8">
         <v>33450000</v>
@@ -997,10 +989,10 @@
         <v>0</v>
       </c>
       <c r="G15" s="8">
-        <v>18040252363.75</v>
+        <v>17984023492.57</v>
       </c>
       <c r="H15" s="8">
-        <v>539</v>
+        <v>537.5</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1011,10 +1003,10 @@
         <v>33</v>
       </c>
       <c r="C16" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D16" s="7">
-        <v>26.404491</v>
+        <v>26.240334</v>
       </c>
       <c r="E16" s="8">
         <v>10800000</v>
@@ -1023,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="8">
-        <v>285168502.96</v>
+        <v>283395611.56</v>
       </c>
       <c r="H16" s="8">
-        <v>26.34</v>
+        <v>26.28</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1037,10 +1029,10 @@
         <v>35</v>
       </c>
       <c r="C17" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D17" s="7">
-        <v>47.734587</v>
+        <v>47.785433</v>
       </c>
       <c r="E17" s="8">
         <v>1625000</v>
@@ -1049,10 +1041,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="8">
-        <v>77568703.45</v>
+        <v>77651328.72</v>
       </c>
       <c r="H17" s="8">
-        <v>47.79</v>
+        <v>47.84</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1063,10 +1055,10 @@
         <v>37</v>
       </c>
       <c r="C18" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D18" s="7">
-        <v>75.081302</v>
+        <v>75.026545</v>
       </c>
       <c r="E18" s="8">
         <v>1140000</v>
@@ -1075,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="G18" s="8">
-        <v>85592683.92</v>
+        <v>85530261.28</v>
       </c>
       <c r="H18" s="8">
-        <v>75.18</v>
+        <v>75.04</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1089,10 +1081,10 @@
         <v>39</v>
       </c>
       <c r="C19" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D19" s="7">
-        <v>86.508374</v>
+        <v>46191</v>
+      </c>
+      <c r="D19" s="10">
+        <v>85.93664</v>
       </c>
       <c r="E19" s="8">
         <v>1155000</v>
@@ -1101,10 +1093,10 @@
         <v>0</v>
       </c>
       <c r="G19" s="8">
-        <v>99917172.34</v>
+        <v>99256819.35</v>
       </c>
       <c r="H19" s="8">
-        <v>86.46</v>
+        <v>85.8</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1115,10 +1107,10 @@
         <v>41</v>
       </c>
       <c r="C20" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D20" s="7">
-        <v>53.073008</v>
+        <v>46191</v>
+      </c>
+      <c r="D20" s="10">
+        <v>52.61265</v>
       </c>
       <c r="E20" s="8">
         <v>3135000</v>
@@ -1127,10 +1119,10 @@
         <v>0</v>
       </c>
       <c r="G20" s="8">
-        <v>166383881.34</v>
+        <v>164940656.44</v>
       </c>
       <c r="H20" s="8">
-        <v>53.08</v>
+        <v>52.68</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1141,10 +1133,10 @@
         <v>43</v>
       </c>
       <c r="C21" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D21" s="7">
-        <v>170.438473</v>
+        <v>169.855027</v>
       </c>
       <c r="E21" s="8">
         <v>600000</v>
@@ -1153,10 +1145,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="8">
-        <v>102263083.64</v>
+        <v>101913016.47</v>
       </c>
       <c r="H21" s="8">
-        <v>170.9</v>
+        <v>169.9</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1167,22 +1159,22 @@
         <v>45</v>
       </c>
       <c r="C22" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D22" s="7">
-        <v>216.375533</v>
+        <v>214.886981</v>
       </c>
       <c r="E22" s="8">
-        <v>116040000</v>
+        <v>116360000</v>
       </c>
       <c r="F22" s="9">
         <v>0</v>
       </c>
       <c r="G22" s="8">
-        <v>25108216856.94</v>
+        <v>25004249142.97</v>
       </c>
       <c r="H22" s="8">
-        <v>216.5</v>
+        <v>214.85</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1193,22 +1185,22 @@
         <v>47</v>
       </c>
       <c r="C23" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D23" s="7">
-        <v>214.154693</v>
+        <v>215.356019</v>
       </c>
       <c r="E23" s="8">
-        <v>218400000</v>
+        <v>219800000</v>
       </c>
       <c r="F23" s="9">
         <v>0</v>
       </c>
       <c r="G23" s="8">
-        <v>46771384854.08</v>
+        <v>47335252942.67</v>
       </c>
       <c r="H23" s="8">
-        <v>213.75</v>
+        <v>214.95</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1219,10 +1211,10 @@
         <v>49</v>
       </c>
       <c r="C24" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D24" s="7">
-        <v>203.709667</v>
+        <v>201.868382</v>
       </c>
       <c r="E24" s="8">
         <v>400000</v>
@@ -1231,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="G24" s="8">
-        <v>81483866.63</v>
+        <v>80747352.83</v>
       </c>
       <c r="H24" s="8">
-        <v>204.2</v>
+        <v>201.85</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1245,10 +1237,10 @@
         <v>51</v>
       </c>
       <c r="C25" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D25" s="11">
-        <v>122.01819</v>
+        <v>46191</v>
+      </c>
+      <c r="D25" s="7">
+        <v>121.331855</v>
       </c>
       <c r="E25" s="8">
         <v>600000</v>
@@ -1257,10 +1249,10 @@
         <v>0</v>
       </c>
       <c r="G25" s="8">
-        <v>73210913.9</v>
+        <v>72799112.85</v>
       </c>
       <c r="H25" s="8">
-        <v>122.5</v>
+        <v>121.4</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1271,10 +1263,10 @@
         <v>53</v>
       </c>
       <c r="C26" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D26" s="7">
-        <v>657.340254</v>
+        <v>661.326748</v>
       </c>
       <c r="E26" s="8">
         <v>152040000</v>
@@ -1283,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="G26" s="8">
-        <v>99942012278.58</v>
+        <v>100548118736.46</v>
       </c>
       <c r="H26" s="8">
-        <v>687</v>
+        <v>684.75</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1297,19 +1289,19 @@
         <v>55</v>
       </c>
       <c r="C27" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D27" s="7">
-        <v>183.625359</v>
+        <v>181.644176</v>
       </c>
       <c r="E27" s="8">
-        <v>11680000</v>
+        <v>11760000</v>
       </c>
       <c r="F27" s="9">
         <v>0</v>
       </c>
       <c r="G27" s="8">
-        <v>2144744194.63</v>
+        <v>2136135512.73</v>
       </c>
       <c r="H27" s="8">
         <v>184</v>
@@ -1323,22 +1315,22 @@
         <v>57</v>
       </c>
       <c r="C28" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D28" s="7">
-        <v>258.607009</v>
+        <v>258.003767</v>
       </c>
       <c r="E28" s="8">
-        <v>32960000</v>
+        <v>32720000</v>
       </c>
       <c r="F28" s="9">
         <v>0</v>
       </c>
       <c r="G28" s="8">
-        <v>8523687032.13</v>
+        <v>8441883268.84</v>
       </c>
       <c r="H28" s="8">
-        <v>259.5</v>
+        <v>258</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1349,10 +1341,10 @@
         <v>59</v>
       </c>
       <c r="C29" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D29" s="7">
-        <v>252.329031</v>
+        <v>251.141343</v>
       </c>
       <c r="E29" s="8">
         <v>3160000</v>
@@ -1361,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="G29" s="8">
-        <v>797359739.03</v>
+        <v>793606642.81</v>
       </c>
       <c r="H29" s="8">
-        <v>252</v>
+        <v>251.1</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1375,10 +1367,10 @@
         <v>61</v>
       </c>
       <c r="C30" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D30" s="7">
-        <v>129.729387</v>
+        <v>129.594073</v>
       </c>
       <c r="E30" s="8">
         <v>440000</v>
@@ -1387,10 +1379,10 @@
         <v>0</v>
       </c>
       <c r="G30" s="8">
-        <v>57080930.35</v>
+        <v>57021392.26</v>
       </c>
       <c r="H30" s="8">
-        <v>129.2</v>
+        <v>129.6</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1401,10 +1393,10 @@
         <v>63</v>
       </c>
       <c r="C31" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D31" s="7">
-        <v>184.521562</v>
+        <v>182.555306</v>
       </c>
       <c r="E31" s="8">
         <v>400000</v>
@@ -1413,10 +1405,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="8">
-        <v>73808624.97</v>
+        <v>73022122.46</v>
       </c>
       <c r="H31" s="8">
-        <v>184.6</v>
+        <v>182.55</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1427,10 +1419,10 @@
         <v>65</v>
       </c>
       <c r="C32" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D32" s="11">
-        <v>49.32922</v>
+        <v>46191</v>
+      </c>
+      <c r="D32" s="7">
+        <v>49.053189</v>
       </c>
       <c r="E32" s="8">
         <v>1200000</v>
@@ -1439,10 +1431,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="8">
-        <v>59195063.78</v>
+        <v>58863827.21</v>
       </c>
       <c r="H32" s="8">
-        <v>49.45</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1453,10 +1445,10 @@
         <v>67</v>
       </c>
       <c r="C33" s="6">
-        <v>46190</v>
-      </c>
-      <c r="D33" s="12">
-        <v>1272.6112</v>
+        <v>46191</v>
+      </c>
+      <c r="D33" s="7">
+        <v>1273.982291</v>
       </c>
       <c r="E33" s="8">
         <v>560000</v>
@@ -1465,10 +1457,10 @@
         <v>0</v>
       </c>
       <c r="G33" s="8">
-        <v>712662271.96</v>
+        <v>713430082.98</v>
       </c>
       <c r="H33" s="8">
-        <v>1274.5</v>
+        <v>1275.5</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -1479,10 +1471,10 @@
         <v>69</v>
       </c>
       <c r="C34" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D34" s="7">
-        <v>189.992384</v>
+        <v>188.268886</v>
       </c>
       <c r="E34" s="8">
         <v>680000</v>
@@ -1491,10 +1483,10 @@
         <v>0</v>
       </c>
       <c r="G34" s="8">
-        <v>129194821.14</v>
+        <v>128022842.41</v>
       </c>
       <c r="H34" s="8">
-        <v>190</v>
+        <v>188.25</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -1505,22 +1497,22 @@
         <v>71</v>
       </c>
       <c r="C35" s="6">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="D35" s="7">
-        <v>1273.570299</v>
+        <v>1274.937485</v>
       </c>
       <c r="E35" s="8">
-        <v>2440000</v>
+        <v>4440000</v>
       </c>
       <c r="F35" s="9">
         <v>0</v>
       </c>
       <c r="G35" s="8">
-        <v>3107511528.66</v>
+        <v>5660722433.75</v>
       </c>
       <c r="H35" s="8">
-        <v>1274.5</v>
+        <v>1276.5</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>18.06.2026 10:31:40</t>
+    <t>19.06.2026 10:09:27</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -233,12 +233,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="###0.000000;-###0.000000;0"/>
     <numFmt numFmtId="166" formatCode="###0.00;-###0.00;0"/>
     <numFmt numFmtId="167" formatCode="###0;-###0;0"/>
-    <numFmt numFmtId="168" formatCode="###0.00000;-###0.00000;0"/>
+    <numFmt numFmtId="168" formatCode="###0.000;-###0.000;0"/>
+    <numFmt numFmtId="169" formatCode="###0.0000;-###0.0000;0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -308,7 +309,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -334,6 +335,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -684,7 +688,7 @@
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="24" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="7" max="7" width="19" customWidth="1"/>
     <col min="8" max="8" width="21" customWidth="1"/>
   </cols>
   <sheetData>
@@ -743,10 +747,10 @@
         <v>13</v>
       </c>
       <c r="C6" s="6">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="D6" s="7">
-        <v>50.704317</v>
+        <v>52.468703</v>
       </c>
       <c r="E6" s="8">
         <v>58200000</v>
@@ -755,10 +759,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="8">
-        <v>2950991248.39</v>
+        <v>3053678534.27</v>
       </c>
       <c r="H6" s="8">
-        <v>50.56</v>
+        <v>52.58</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -769,10 +773,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="6">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="D7" s="7">
-        <v>37.385511</v>
+        <v>38.276099</v>
       </c>
       <c r="E7" s="8">
         <v>14400000</v>
@@ -781,10 +785,10 @@
         <v>0</v>
       </c>
       <c r="G7" s="8">
-        <v>538351353.76</v>
+        <v>551175830.28</v>
       </c>
       <c r="H7" s="8">
-        <v>37.36</v>
+        <v>38.16</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -795,10 +799,10 @@
         <v>17</v>
       </c>
       <c r="C8" s="6">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="D8" s="7">
-        <v>39.829226</v>
+        <v>40.960319</v>
       </c>
       <c r="E8" s="8">
         <v>33900000</v>
@@ -807,10 +811,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="8">
-        <v>1350210754.03</v>
+        <v>1388554807.12</v>
       </c>
       <c r="H8" s="8">
-        <v>39.85</v>
+        <v>40.52</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -821,10 +825,10 @@
         <v>19</v>
       </c>
       <c r="C9" s="6">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="D9" s="7">
-        <v>59.101904</v>
+        <v>59.164292</v>
       </c>
       <c r="E9" s="8">
         <v>2250000</v>
@@ -833,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="G9" s="8">
-        <v>132979283.35</v>
+        <v>133119656.6</v>
       </c>
       <c r="H9" s="8">
-        <v>59.18</v>
+        <v>59.38</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -847,10 +851,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="6">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="D10" s="7">
-        <v>353.054162</v>
+        <v>358.511677</v>
       </c>
       <c r="E10" s="8">
         <v>135000</v>
@@ -859,10 +863,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="8">
-        <v>47662311.87</v>
+        <v>48399076.37</v>
       </c>
       <c r="H10" s="8">
-        <v>353.1</v>
+        <v>358.2</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -873,10 +877,10 @@
         <v>23</v>
       </c>
       <c r="C11" s="6">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="D11" s="7">
-        <v>541.976235</v>
+        <v>532.045957</v>
       </c>
       <c r="E11" s="8">
         <v>44350000</v>
@@ -885,10 +889,10 @@
         <v>0</v>
       </c>
       <c r="G11" s="8">
-        <v>24036646013.72</v>
+        <v>23596238186.21</v>
       </c>
       <c r="H11" s="8">
-        <v>546.25</v>
+        <v>534.75</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -899,10 +903,10 @@
         <v>25</v>
       </c>
       <c r="C12" s="6">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="D12" s="7">
-        <v>645.979853</v>
+        <v>612.132062</v>
       </c>
       <c r="E12" s="8">
         <v>74800000</v>
@@ -911,10 +915,10 @@
         <v>0</v>
       </c>
       <c r="G12" s="8">
-        <v>48319292974.53</v>
+        <v>45787478212.64</v>
       </c>
       <c r="H12" s="8">
-        <v>643.75</v>
+        <v>610</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -925,10 +929,10 @@
         <v>27</v>
       </c>
       <c r="C13" s="6">
-        <v>46191</v>
-      </c>
-      <c r="D13" s="7">
-        <v>4313.988319</v>
+        <v>46192</v>
+      </c>
+      <c r="D13" s="10">
+        <v>4325.708</v>
       </c>
       <c r="E13" s="8">
         <v>280000</v>
@@ -937,10 +941,10 @@
         <v>0</v>
       </c>
       <c r="G13" s="8">
-        <v>1207916729.23</v>
+        <v>1211198240.05</v>
       </c>
       <c r="H13" s="8">
-        <v>4308</v>
+        <v>4322</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -951,10 +955,10 @@
         <v>29</v>
       </c>
       <c r="C14" s="6">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="D14" s="7">
-        <v>652.342772</v>
+        <v>642.142039</v>
       </c>
       <c r="E14" s="8">
         <v>113800000</v>
@@ -963,10 +967,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="8">
-        <v>74236607482.2</v>
+        <v>73075764006.89</v>
       </c>
       <c r="H14" s="8">
-        <v>680</v>
+        <v>668</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -977,10 +981,10 @@
         <v>31</v>
       </c>
       <c r="C15" s="6">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="D15" s="7">
-        <v>537.638968</v>
+        <v>529.739855</v>
       </c>
       <c r="E15" s="8">
         <v>33450000</v>
@@ -989,10 +993,10 @@
         <v>0</v>
       </c>
       <c r="G15" s="8">
-        <v>17984023492.57</v>
+        <v>17719798155.85</v>
       </c>
       <c r="H15" s="8">
-        <v>537.5</v>
+        <v>525.75</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1003,10 +1007,10 @@
         <v>33</v>
       </c>
       <c r="C16" s="6">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="D16" s="7">
-        <v>26.240334</v>
+        <v>26.725821</v>
       </c>
       <c r="E16" s="8">
         <v>10800000</v>
@@ -1015,10 +1019,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="8">
-        <v>283395611.56</v>
+        <v>288638863.18</v>
       </c>
       <c r="H16" s="8">
-        <v>26.28</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1029,10 +1033,10 @@
         <v>35</v>
       </c>
       <c r="C17" s="6">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="D17" s="7">
-        <v>47.785433</v>
+        <v>47.836257</v>
       </c>
       <c r="E17" s="8">
         <v>1625000</v>
@@ -1041,10 +1045,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="8">
-        <v>77651328.72</v>
+        <v>77733917.85</v>
       </c>
       <c r="H17" s="8">
-        <v>47.84</v>
+        <v>47.99</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1055,10 +1059,10 @@
         <v>37</v>
       </c>
       <c r="C18" s="6">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="D18" s="7">
-        <v>75.026545</v>
+        <v>76.545903</v>
       </c>
       <c r="E18" s="8">
         <v>1140000</v>
@@ -1067,10 +1071,10 @@
         <v>0</v>
       </c>
       <c r="G18" s="8">
-        <v>85530261.28</v>
+        <v>87262329.7</v>
       </c>
       <c r="H18" s="8">
-        <v>75.04</v>
+        <v>76.3</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1081,10 +1085,10 @@
         <v>39</v>
       </c>
       <c r="C19" s="6">
-        <v>46191</v>
-      </c>
-      <c r="D19" s="10">
-        <v>85.93664</v>
+        <v>46192</v>
+      </c>
+      <c r="D19" s="7">
+        <v>88.315479</v>
       </c>
       <c r="E19" s="8">
         <v>1155000</v>
@@ -1093,10 +1097,10 @@
         <v>0</v>
       </c>
       <c r="G19" s="8">
-        <v>99256819.35</v>
+        <v>102004377.77</v>
       </c>
       <c r="H19" s="8">
-        <v>85.8</v>
+        <v>87.74</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1107,10 +1111,10 @@
         <v>41</v>
       </c>
       <c r="C20" s="6">
-        <v>46191</v>
-      </c>
-      <c r="D20" s="10">
-        <v>52.61265</v>
+        <v>46192</v>
+      </c>
+      <c r="D20" s="7">
+        <v>53.621577</v>
       </c>
       <c r="E20" s="8">
         <v>3135000</v>
@@ -1119,10 +1123,10 @@
         <v>0</v>
       </c>
       <c r="G20" s="8">
-        <v>164940656.44</v>
+        <v>168103645.45</v>
       </c>
       <c r="H20" s="8">
-        <v>52.68</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1133,10 +1137,10 @@
         <v>43</v>
       </c>
       <c r="C21" s="6">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="D21" s="7">
-        <v>169.855027</v>
+        <v>173.040693</v>
       </c>
       <c r="E21" s="8">
         <v>600000</v>
@@ -1145,10 +1149,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="8">
-        <v>101913016.47</v>
+        <v>103824415.77</v>
       </c>
       <c r="H21" s="8">
-        <v>169.9</v>
+        <v>172.15</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1159,22 +1163,22 @@
         <v>45</v>
       </c>
       <c r="C22" s="6">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="D22" s="7">
-        <v>214.886981</v>
+        <v>220.958459</v>
       </c>
       <c r="E22" s="8">
-        <v>116360000</v>
+        <v>114000000</v>
       </c>
       <c r="F22" s="9">
         <v>0</v>
       </c>
       <c r="G22" s="8">
-        <v>25004249142.97</v>
+        <v>25189264340.26</v>
       </c>
       <c r="H22" s="8">
-        <v>214.85</v>
+        <v>221</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1185,22 +1189,22 @@
         <v>47</v>
       </c>
       <c r="C23" s="6">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="D23" s="7">
-        <v>215.356019</v>
+        <v>222.859248</v>
       </c>
       <c r="E23" s="8">
-        <v>219800000</v>
+        <v>224000000</v>
       </c>
       <c r="F23" s="9">
         <v>0</v>
       </c>
       <c r="G23" s="8">
-        <v>47335252942.67</v>
+        <v>49920471616.26</v>
       </c>
       <c r="H23" s="8">
-        <v>214.95</v>
+        <v>224.2</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1211,10 +1215,10 @@
         <v>49</v>
       </c>
       <c r="C24" s="6">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="D24" s="7">
-        <v>201.868382</v>
+        <v>207.978504</v>
       </c>
       <c r="E24" s="8">
         <v>400000</v>
@@ -1223,10 +1227,10 @@
         <v>0</v>
       </c>
       <c r="G24" s="8">
-        <v>80747352.83</v>
+        <v>83191401.56</v>
       </c>
       <c r="H24" s="8">
-        <v>201.85</v>
+        <v>207.45</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1237,10 +1241,10 @@
         <v>51</v>
       </c>
       <c r="C25" s="6">
-        <v>46191</v>
-      </c>
-      <c r="D25" s="7">
-        <v>121.331855</v>
+        <v>46192</v>
+      </c>
+      <c r="D25" s="11">
+        <v>123.1259</v>
       </c>
       <c r="E25" s="8">
         <v>600000</v>
@@ -1249,10 +1253,10 @@
         <v>0</v>
       </c>
       <c r="G25" s="8">
-        <v>72799112.85</v>
+        <v>73875539.78</v>
       </c>
       <c r="H25" s="8">
-        <v>121.4</v>
+        <v>124.45</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1263,10 +1267,10 @@
         <v>53</v>
       </c>
       <c r="C26" s="6">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="D26" s="7">
-        <v>661.326748</v>
+        <v>649.794371</v>
       </c>
       <c r="E26" s="8">
         <v>152040000</v>
@@ -1275,10 +1279,10 @@
         <v>0</v>
       </c>
       <c r="G26" s="8">
-        <v>100548118736.46</v>
+        <v>98794736227.12</v>
       </c>
       <c r="H26" s="8">
-        <v>684.75</v>
+        <v>674</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1289,22 +1293,22 @@
         <v>55</v>
       </c>
       <c r="C27" s="6">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="D27" s="7">
-        <v>181.644176</v>
+        <v>183.393721</v>
       </c>
       <c r="E27" s="8">
-        <v>11760000</v>
+        <v>11600000</v>
       </c>
       <c r="F27" s="9">
         <v>0</v>
       </c>
       <c r="G27" s="8">
-        <v>2136135512.73</v>
+        <v>2127367164.16</v>
       </c>
       <c r="H27" s="8">
-        <v>184</v>
+        <v>184.25</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1315,22 +1319,22 @@
         <v>57</v>
       </c>
       <c r="C28" s="6">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="D28" s="7">
-        <v>258.003767</v>
+        <v>262.881589</v>
       </c>
       <c r="E28" s="8">
-        <v>32720000</v>
+        <v>31800000</v>
       </c>
       <c r="F28" s="9">
         <v>0</v>
       </c>
       <c r="G28" s="8">
-        <v>8441883268.84</v>
+        <v>8359634545.19</v>
       </c>
       <c r="H28" s="8">
-        <v>258</v>
+        <v>262.3</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1341,10 +1345,10 @@
         <v>59</v>
       </c>
       <c r="C29" s="6">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="D29" s="7">
-        <v>251.141343</v>
+        <v>257.112285</v>
       </c>
       <c r="E29" s="8">
         <v>3160000</v>
@@ -1353,10 +1357,10 @@
         <v>0</v>
       </c>
       <c r="G29" s="8">
-        <v>793606642.81</v>
+        <v>812474821.45</v>
       </c>
       <c r="H29" s="8">
-        <v>251.1</v>
+        <v>257.6</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1367,10 +1371,10 @@
         <v>61</v>
       </c>
       <c r="C30" s="6">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="D30" s="7">
-        <v>129.594073</v>
+        <v>129.229482</v>
       </c>
       <c r="E30" s="8">
         <v>440000</v>
@@ -1379,10 +1383,10 @@
         <v>0</v>
       </c>
       <c r="G30" s="8">
-        <v>57021392.26</v>
+        <v>56860971.96</v>
       </c>
       <c r="H30" s="8">
-        <v>129.6</v>
+        <v>130</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1393,10 +1397,10 @@
         <v>63</v>
       </c>
       <c r="C31" s="6">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="D31" s="7">
-        <v>182.555306</v>
+        <v>188.209921</v>
       </c>
       <c r="E31" s="8">
         <v>400000</v>
@@ -1405,10 +1409,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="8">
-        <v>73022122.46</v>
+        <v>75283968.4</v>
       </c>
       <c r="H31" s="8">
-        <v>182.55</v>
+        <v>187.85</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1419,10 +1423,10 @@
         <v>65</v>
       </c>
       <c r="C32" s="6">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="D32" s="7">
-        <v>49.053189</v>
+        <v>50.327701</v>
       </c>
       <c r="E32" s="8">
         <v>1200000</v>
@@ -1431,10 +1435,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="8">
-        <v>58863827.21</v>
+        <v>60393241.34</v>
       </c>
       <c r="H32" s="8">
-        <v>49.06</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1445,10 +1449,10 @@
         <v>67</v>
       </c>
       <c r="C33" s="6">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="D33" s="7">
-        <v>1273.982291</v>
+        <v>1275.354878</v>
       </c>
       <c r="E33" s="8">
         <v>560000</v>
@@ -1457,10 +1461,10 @@
         <v>0</v>
       </c>
       <c r="G33" s="8">
-        <v>713430082.98</v>
+        <v>714198731.84</v>
       </c>
       <c r="H33" s="8">
-        <v>1275.5</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -1471,10 +1475,10 @@
         <v>69</v>
       </c>
       <c r="C34" s="6">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="D34" s="7">
-        <v>188.268886</v>
+        <v>191.988771</v>
       </c>
       <c r="E34" s="8">
         <v>680000</v>
@@ -1483,10 +1487,10 @@
         <v>0</v>
       </c>
       <c r="G34" s="8">
-        <v>128022842.41</v>
+        <v>130552364.07</v>
       </c>
       <c r="H34" s="8">
-        <v>188.25</v>
+        <v>192.1</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -1497,10 +1501,10 @@
         <v>71</v>
       </c>
       <c r="C35" s="6">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="D35" s="7">
-        <v>1274.937485</v>
+        <v>1276.306352</v>
       </c>
       <c r="E35" s="8">
         <v>4440000</v>
@@ -1509,10 +1513,10 @@
         <v>0</v>
       </c>
       <c r="G35" s="8">
-        <v>5660722433.75</v>
+        <v>5666800202.41</v>
       </c>
       <c r="H35" s="8">
-        <v>1276.5</v>
+        <v>1280.5</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/borsa-yatirim-fonlari-tarihsel/data/borsa-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>19.06.2026 10:09:27</t>
+    <t>22.06.2026 10:03:06</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -238,7 +238,7 @@
     <numFmt numFmtId="165" formatCode="###0.000000;-###0.000000;0"/>
     <numFmt numFmtId="166" formatCode="###0.00;-###0.00;0"/>
     <numFmt numFmtId="167" formatCode="###0;-###0;0"/>
-    <numFmt numFmtId="168" formatCode="###0.000;-###0.000;0"/>
+    <numFmt numFmtId="168" formatCode="###0.00000;-###0.00000;0"/>
     <numFmt numFmtId="169" formatCode="###0.0000;-###0.0000;0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
@@ -747,10 +747,10 @@
         <v>13</v>
       </c>
       <c r="C6" s="6">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="D6" s="7">
-        <v>52.468703</v>
+        <v>52.595403</v>
       </c>
       <c r="E6" s="8">
         <v>58200000</v>
@@ -759,10 +759,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="8">
-        <v>3053678534.27</v>
+        <v>3061052431.35</v>
       </c>
       <c r="H6" s="8">
-        <v>52.58</v>
+        <v>52.62</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -773,10 +773,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="6">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="D7" s="7">
-        <v>38.276099</v>
+        <v>37.821352</v>
       </c>
       <c r="E7" s="8">
         <v>14400000</v>
@@ -785,10 +785,10 @@
         <v>0</v>
       </c>
       <c r="G7" s="8">
-        <v>551175830.28</v>
+        <v>544627463.18</v>
       </c>
       <c r="H7" s="8">
-        <v>38.16</v>
+        <v>37.92</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -799,10 +799,10 @@
         <v>17</v>
       </c>
       <c r="C8" s="6">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="D8" s="7">
-        <v>40.960319</v>
+        <v>40.562995</v>
       </c>
       <c r="E8" s="8">
         <v>33900000</v>
@@ -811,10 +811,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="8">
-        <v>1388554807.12</v>
+        <v>1375085547.19</v>
       </c>
       <c r="H8" s="8">
-        <v>40.52</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -825,10 +825,10 @@
         <v>19</v>
       </c>
       <c r="C9" s="6">
-        <v>46192</v>
-      </c>
-      <c r="D9" s="7">
-        <v>59.164292</v>
+        <v>46195</v>
+      </c>
+      <c r="D9" s="10">
+        <v>59.35165</v>
       </c>
       <c r="E9" s="8">
         <v>2250000</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="G9" s="8">
-        <v>133119656.6</v>
+        <v>133541212.29</v>
       </c>
       <c r="H9" s="8">
-        <v>59.38</v>
+        <v>59.42</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -851,10 +851,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="6">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="D10" s="7">
-        <v>358.511677</v>
+        <v>358.711843</v>
       </c>
       <c r="E10" s="8">
         <v>135000</v>
@@ -863,10 +863,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="8">
-        <v>48399076.37</v>
+        <v>48426098.82</v>
       </c>
       <c r="H10" s="8">
-        <v>358.2</v>
+        <v>360</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -877,10 +877,10 @@
         <v>23</v>
       </c>
       <c r="C11" s="6">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="D11" s="7">
-        <v>532.045957</v>
+        <v>519.516821</v>
       </c>
       <c r="E11" s="8">
         <v>44350000</v>
@@ -889,10 +889,10 @@
         <v>0</v>
       </c>
       <c r="G11" s="8">
-        <v>23596238186.21</v>
+        <v>23040571026.91</v>
       </c>
       <c r="H11" s="8">
-        <v>534.75</v>
+        <v>523.5</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -903,10 +903,10 @@
         <v>25</v>
       </c>
       <c r="C12" s="6">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="D12" s="7">
-        <v>612.132062</v>
+        <v>595.431832</v>
       </c>
       <c r="E12" s="8">
         <v>74800000</v>
@@ -915,10 +915,10 @@
         <v>0</v>
       </c>
       <c r="G12" s="8">
-        <v>45787478212.64</v>
+        <v>44538301008.88</v>
       </c>
       <c r="H12" s="8">
-        <v>610</v>
+        <v>592</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -929,10 +929,10 @@
         <v>27</v>
       </c>
       <c r="C13" s="6">
-        <v>46192</v>
-      </c>
-      <c r="D13" s="10">
-        <v>4325.708</v>
+        <v>46195</v>
+      </c>
+      <c r="D13" s="7">
+        <v>4326.792317</v>
       </c>
       <c r="E13" s="8">
         <v>280000</v>
@@ -941,10 +941,10 @@
         <v>0</v>
       </c>
       <c r="G13" s="8">
-        <v>1211198240.05</v>
+        <v>1211501848.68</v>
       </c>
       <c r="H13" s="8">
-        <v>4322</v>
+        <v>4316</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -955,10 +955,10 @@
         <v>29</v>
       </c>
       <c r="C14" s="6">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="D14" s="7">
-        <v>642.142039</v>
+        <v>634.838455</v>
       </c>
       <c r="E14" s="8">
         <v>113800000</v>
@@ -967,10 +967,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="8">
-        <v>73075764006.89</v>
+        <v>72244616168.06</v>
       </c>
       <c r="H14" s="8">
-        <v>668</v>
+        <v>657</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -981,10 +981,10 @@
         <v>31</v>
       </c>
       <c r="C15" s="6">
-        <v>46192</v>
-      </c>
-      <c r="D15" s="7">
-        <v>529.739855</v>
+        <v>46195</v>
+      </c>
+      <c r="D15" s="10">
+        <v>517.62217</v>
       </c>
       <c r="E15" s="8">
         <v>33450000</v>
@@ -993,10 +993,10 @@
         <v>0</v>
       </c>
       <c r="G15" s="8">
-        <v>17719798155.85</v>
+        <v>17314461574.37</v>
       </c>
       <c r="H15" s="8">
-        <v>525.75</v>
+        <v>517</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1007,10 +1007,10 @@
         <v>33</v>
       </c>
       <c r="C16" s="6">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="D16" s="7">
-        <v>26.725821</v>
+        <v>26.771656</v>
       </c>
       <c r="E16" s="8">
         <v>10800000</v>
@@ -1019,10 +1019,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="8">
-        <v>288638863.18</v>
+        <v>289133879.62</v>
       </c>
       <c r="H16" s="8">
-        <v>26.7</v>
+        <v>26.68</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1033,10 +1033,10 @@
         <v>35</v>
       </c>
       <c r="C17" s="6">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="D17" s="7">
-        <v>47.836257</v>
+        <v>47.989241</v>
       </c>
       <c r="E17" s="8">
         <v>1625000</v>
@@ -1045,10 +1045,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="8">
-        <v>77733917.85</v>
+        <v>77982516.78</v>
       </c>
       <c r="H17" s="8">
-        <v>47.99</v>
+        <v>48.04</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1059,10 +1059,10 @@
         <v>37</v>
       </c>
       <c r="C18" s="6">
-        <v>46192</v>
-      </c>
-      <c r="D18" s="7">
-        <v>76.545903</v>
+        <v>46195</v>
+      </c>
+      <c r="D18" s="11">
+        <v>75.7338</v>
       </c>
       <c r="E18" s="8">
         <v>1140000</v>
@@ -1071,10 +1071,10 @@
         <v>0</v>
       </c>
       <c r="G18" s="8">
-        <v>87262329.7</v>
+        <v>86336532.21</v>
       </c>
       <c r="H18" s="8">
-        <v>76.3</v>
+        <v>76.4</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1085,10 +1085,10 @@
         <v>39</v>
       </c>
       <c r="C19" s="6">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="D19" s="7">
-        <v>88.315479</v>
+        <v>87.451863</v>
       </c>
       <c r="E19" s="8">
         <v>1155000</v>
@@ -1097,10 +1097,10 @@
         <v>0</v>
       </c>
       <c r="G19" s="8">
-        <v>102004377.77</v>
+        <v>101006902.32</v>
       </c>
       <c r="H19" s="8">
-        <v>87.74</v>
+        <v>89.88</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1111,10 +1111,10 @@
         <v>41</v>
       </c>
       <c r="C20" s="6">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="D20" s="7">
-        <v>53.621577</v>
+        <v>53.264731</v>
       </c>
       <c r="E20" s="8">
         <v>3135000</v>
@@ -1123,10 +1123,10 @@
         <v>0</v>
       </c>
       <c r="G20" s="8">
-        <v>168103645.45</v>
+        <v>166984930.16</v>
       </c>
       <c r="H20" s="8">
-        <v>53.6</v>
+        <v>53.28</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1137,10 +1137,10 @@
         <v>43</v>
       </c>
       <c r="C21" s="6">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="D21" s="7">
-        <v>173.040693</v>
+        <v>173.622306</v>
       </c>
       <c r="E21" s="8">
         <v>600000</v>
@@ -1149,10 +1149,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="8">
-        <v>103824415.77</v>
+        <v>104173383.72</v>
       </c>
       <c r="H21" s="8">
-        <v>172.15</v>
+        <v>173</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1163,22 +1163,22 @@
         <v>45</v>
       </c>
       <c r="C22" s="6">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="D22" s="7">
-        <v>220.958459</v>
+        <v>218.732718</v>
       </c>
       <c r="E22" s="8">
-        <v>114000000</v>
+        <v>116360000</v>
       </c>
       <c r="F22" s="9">
         <v>0</v>
       </c>
       <c r="G22" s="8">
-        <v>25189264340.26</v>
+        <v>25451739070.01</v>
       </c>
       <c r="H22" s="8">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1189,22 +1189,22 @@
         <v>47</v>
       </c>
       <c r="C23" s="6">
-        <v>46192</v>
-      </c>
-      <c r="D23" s="7">
-        <v>222.859248</v>
+        <v>46195</v>
+      </c>
+      <c r="D23" s="10">
+        <v>223.39342</v>
       </c>
       <c r="E23" s="8">
-        <v>224000000</v>
+        <v>221000000</v>
       </c>
       <c r="F23" s="9">
         <v>0</v>
       </c>
       <c r="G23" s="8">
-        <v>49920471616.26</v>
+        <v>49369945727.85</v>
       </c>
       <c r="H23" s="8">
-        <v>224.2</v>
+        <v>224.3</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1215,10 +1215,10 @@
         <v>49</v>
       </c>
       <c r="C24" s="6">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="D24" s="7">
-        <v>207.978504</v>
+        <v>206.166385</v>
       </c>
       <c r="E24" s="8">
         <v>400000</v>
@@ -1227,10 +1227,10 @@
         <v>0</v>
       </c>
       <c r="G24" s="8">
-        <v>83191401.56</v>
+        <v>82466554.13</v>
       </c>
       <c r="H24" s="8">
-        <v>207.45</v>
+        <v>207.35</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1241,10 +1241,10 @@
         <v>51</v>
       </c>
       <c r="C25" s="6">
-        <v>46192</v>
-      </c>
-      <c r="D25" s="11">
-        <v>123.1259</v>
+        <v>46195</v>
+      </c>
+      <c r="D25" s="10">
+        <v>122.02228</v>
       </c>
       <c r="E25" s="8">
         <v>600000</v>
@@ -1253,10 +1253,10 @@
         <v>0</v>
       </c>
       <c r="G25" s="8">
-        <v>73875539.78</v>
+        <v>73213368.2</v>
       </c>
       <c r="H25" s="8">
-        <v>124.45</v>
+        <v>122.1</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1267,10 +1267,10 @@
         <v>53</v>
       </c>
       <c r="C26" s="6">
-        <v>46192</v>
-      </c>
-      <c r="D26" s="7">
-        <v>649.794371</v>
+        <v>46195</v>
+      </c>
+      <c r="D26" s="10">
+        <v>627.43995</v>
       </c>
       <c r="E26" s="8">
         <v>152040000</v>
@@ -1279,10 +1279,10 @@
         <v>0</v>
       </c>
       <c r="G26" s="8">
-        <v>98794736227.12</v>
+        <v>95395969993.15</v>
       </c>
       <c r="H26" s="8">
-        <v>674</v>
+        <v>662.25</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1293,10 +1293,10 @@
         <v>55</v>
       </c>
       <c r="C27" s="6">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="D27" s="7">
-        <v>183.393721</v>
+        <v>183.207027</v>
       </c>
       <c r="E27" s="8">
         <v>11600000</v>
@@ -1305,10 +1305,10 @@
         <v>0</v>
       </c>
       <c r="G27" s="8">
-        <v>2127367164.16</v>
+        <v>2125201513.7</v>
       </c>
       <c r="H27" s="8">
-        <v>184.25</v>
+        <v>184.1</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1319,22 +1319,22 @@
         <v>57</v>
       </c>
       <c r="C28" s="6">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="D28" s="7">
-        <v>262.881589</v>
+        <v>260.320082</v>
       </c>
       <c r="E28" s="8">
-        <v>31800000</v>
+        <v>31600000</v>
       </c>
       <c r="F28" s="9">
         <v>0</v>
       </c>
       <c r="G28" s="8">
-        <v>8359634545.19</v>
+        <v>8226114587.77</v>
       </c>
       <c r="H28" s="8">
-        <v>262.3</v>
+        <v>265</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1345,10 +1345,10 @@
         <v>59</v>
       </c>
       <c r="C29" s="6">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="D29" s="7">
-        <v>257.112285</v>
+        <v>254.048115</v>
       </c>
       <c r="E29" s="8">
         <v>3160000</v>
@@ -1357,10 +1357,10 @@
         <v>0</v>
       </c>
       <c r="G29" s="8">
-        <v>812474821.45</v>
+        <v>802792043.02</v>
       </c>
       <c r="H29" s="8">
-        <v>257.6</v>
+        <v>254</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1371,10 +1371,10 @@
         <v>61</v>
       </c>
       <c r="C30" s="6">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="D30" s="7">
-        <v>129.229482</v>
+        <v>129.217719</v>
       </c>
       <c r="E30" s="8">
         <v>440000</v>
@@ -1383,10 +1383,10 @@
         <v>0</v>
       </c>
       <c r="G30" s="8">
-        <v>56860971.96</v>
+        <v>56855796.28</v>
       </c>
       <c r="H30" s="8">
-        <v>130</v>
+        <v>128.4</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1397,10 +1397,10 @@
         <v>63</v>
       </c>
       <c r="C31" s="6">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="D31" s="7">
-        <v>188.209921</v>
+        <v>186.302453</v>
       </c>
       <c r="E31" s="8">
         <v>400000</v>
@@ -1409,10 +1409,10 @@
         <v>0</v>
       </c>
       <c r="G31" s="8">
-        <v>75283968.4</v>
+        <v>74520981.24</v>
       </c>
       <c r="H31" s="8">
-        <v>187.85</v>
+        <v>185.8</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1423,10 +1423,10 @@
         <v>65</v>
       </c>
       <c r="C32" s="6">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="D32" s="7">
-        <v>50.327701</v>
+        <v>49.902273</v>
       </c>
       <c r="E32" s="8">
         <v>1200000</v>
@@ -1435,10 +1435,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="8">
-        <v>60393241.34</v>
+        <v>59882727.11</v>
       </c>
       <c r="H32" s="8">
-        <v>50</v>
+        <v>49.93</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1449,10 +1449,10 @@
         <v>67</v>
       </c>
       <c r="C33" s="6">
-        <v>46192</v>
-      </c>
-      <c r="D33" s="7">
-        <v>1275.354878</v>
+        <v>46195</v>
+      </c>
+      <c r="D33" s="10">
+        <v>1279.47692</v>
       </c>
       <c r="E33" s="8">
         <v>560000</v>
@@ -1461,10 +1461,10 @@
         <v>0</v>
       </c>
       <c r="G33" s="8">
-        <v>714198731.84</v>
+        <v>716507075.26</v>
       </c>
       <c r="H33" s="8">
-        <v>1280</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -1475,10 +1475,10 @@
         <v>69</v>
       </c>
       <c r="C34" s="6">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="D34" s="7">
-        <v>191.988771</v>
+        <v>190.657473</v>
       </c>
       <c r="E34" s="8">
         <v>680000</v>
@@ -1487,10 +1487,10 @@
         <v>0</v>
       </c>
       <c r="G34" s="8">
-        <v>130552364.07</v>
+        <v>129647081.31</v>
       </c>
       <c r="H34" s="8">
-        <v>192.1</v>
+        <v>190.6</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -1501,10 +1501,10 @@
         <v>71</v>
       </c>
       <c r="C35" s="6">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="D35" s="7">
-        <v>1276.306352</v>
+        <v>1280.417357</v>
       </c>
       <c r="E35" s="8">
         <v>4440000</v>
@@ -1513,10 +1513,10 @@
         <v>0</v>
       </c>
       <c r="G35" s="8">
-        <v>5666800202.41</v>
+        <v>5685053065.97</v>
       </c>
       <c r="H35" s="8">
-        <v>1280.5</v>
+        <v>1282</v>
       </c>
     </row>
   </sheetData>
